--- a/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
+++ b/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FA624A2-FFA4-4047-9C68-EACBAF9F75F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FDF6AAF-378B-4A11-9EB1-540F600E829B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -366,6 +366,8 @@
       <sheetName val="INVENTARIO NACIONAL 08-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 09-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 10-09-26"/>
+      <sheetName val="INVENTARIO NACIONAL 11-09-26"/>
+      <sheetName val="INVENTARIO NACIONAL 14-09-26"/>
       <sheetName val="CCC"/>
       <sheetName val="VINCULO VTS BY SKU AGOSTO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
@@ -382,13 +384,15 @@
       <sheetData sheetId="7"/>
       <sheetData sheetId="8"/>
       <sheetData sheetId="9"/>
-      <sheetData sheetId="10">
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12">
         <row r="4">
           <cell r="F4">
-            <v>975.625</v>
+            <v>1117.7777777777778</v>
           </cell>
           <cell r="G4">
-            <v>-0.17883266533066133</v>
+            <v>-5.9185036740146857E-2</v>
           </cell>
           <cell r="H4" t="str">
             <v>BAJO</v>
@@ -396,21 +400,21 @@
         </row>
         <row r="5">
           <cell r="F5">
-            <v>76.375</v>
+            <v>77.666666666666671</v>
           </cell>
           <cell r="G5">
-            <v>-7.7930174563589638E-5</v>
+            <v>1.6832917705735806E-2</v>
           </cell>
           <cell r="H5" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="6">
           <cell r="F6">
-            <v>391.25</v>
+            <v>422.22222222222223</v>
           </cell>
           <cell r="G6">
-            <v>-0.23205439760725299</v>
+            <v>-0.1712621117238371</v>
           </cell>
           <cell r="H6" t="str">
             <v>BAJO</v>
@@ -418,10 +422,10 @@
         </row>
         <row r="7">
           <cell r="F7">
-            <v>91.625</v>
+            <v>97.222222222222229</v>
           </cell>
           <cell r="G7">
-            <v>-6.505102040816324E-2</v>
+            <v>-7.9365079365079083E-3</v>
           </cell>
           <cell r="H7" t="str">
             <v>BAJO</v>
@@ -429,10 +433,10 @@
         </row>
         <row r="8">
           <cell r="F8">
-            <v>13.125</v>
+            <v>13.222222222222221</v>
           </cell>
           <cell r="G8">
-            <v>9.8107569721115562E-2</v>
+            <v>0.10624169986719778</v>
           </cell>
           <cell r="H8" t="str">
             <v>SUBIÓ</v>
@@ -440,10 +444,10 @@
         </row>
         <row r="9">
           <cell r="F9">
-            <v>1136.125</v>
+            <v>1315</v>
           </cell>
           <cell r="G9">
-            <v>-0.22200981511070528</v>
+            <v>-9.9520657384158828E-2</v>
           </cell>
           <cell r="H9" t="str">
             <v>BAJO</v>
@@ -451,10 +455,10 @@
         </row>
         <row r="10">
           <cell r="F10">
-            <v>117.125</v>
+            <v>132</v>
           </cell>
           <cell r="G10">
-            <v>-0.2211447118429386</v>
+            <v>-0.12222925902469917</v>
           </cell>
           <cell r="H10" t="str">
             <v>BAJO</v>
@@ -462,10 +466,10 @@
         </row>
         <row r="11">
           <cell r="F11">
-            <v>244.375</v>
+            <v>272.22222222222223</v>
           </cell>
           <cell r="G11">
-            <v>-0.28872141372141369</v>
+            <v>-0.2076692076692076</v>
           </cell>
           <cell r="H11" t="str">
             <v>BAJO</v>
@@ -473,10 +477,10 @@
         </row>
         <row r="12">
           <cell r="F12">
-            <v>636.625</v>
+            <v>687.55555555555554</v>
           </cell>
           <cell r="G12">
-            <v>-0.16910348042262269</v>
+            <v>-0.10263103376838612</v>
           </cell>
           <cell r="H12" t="str">
             <v>BAJO</v>
@@ -484,10 +488,10 @@
         </row>
         <row r="13">
           <cell r="F13">
-            <v>283.875</v>
+            <v>320.55555555555554</v>
           </cell>
           <cell r="G13">
-            <v>-0.21756464102900641</v>
+            <v>-0.11646322789517438</v>
           </cell>
           <cell r="H13" t="str">
             <v>BAJO</v>
@@ -495,10 +499,10 @@
         </row>
         <row r="14">
           <cell r="F14">
-            <v>2852.125</v>
+            <v>3274.6666666666665</v>
           </cell>
           <cell r="G14">
-            <v>-0.19008782723929041</v>
+            <v>-7.009952401557773E-2</v>
           </cell>
           <cell r="H14" t="str">
             <v>BAJO</v>
@@ -506,10 +510,10 @@
         </row>
         <row r="15">
           <cell r="F15">
-            <v>1730.375</v>
+            <v>2013.2222222222222</v>
           </cell>
           <cell r="G15">
-            <v>-0.24929501084598693</v>
+            <v>-0.12658471920944803</v>
           </cell>
           <cell r="H15" t="str">
             <v>BAJO</v>
@@ -517,10 +521,10 @@
         </row>
         <row r="16">
           <cell r="F16">
-            <v>1865.25</v>
+            <v>2115.7777777777778</v>
           </cell>
           <cell r="G16">
-            <v>-0.17702643079250358</v>
+            <v>-6.6490181247723878E-2</v>
           </cell>
           <cell r="H16" t="str">
             <v>BAJO</v>
@@ -528,10 +532,10 @@
         </row>
         <row r="17">
           <cell r="F17">
-            <v>2207.5</v>
+            <v>2528</v>
           </cell>
           <cell r="G17">
-            <v>-0.1744577412116679</v>
+            <v>-5.4599850411368722E-2</v>
           </cell>
           <cell r="H17" t="str">
             <v>BAJO</v>
@@ -539,10 +543,10 @@
         </row>
         <row r="18">
           <cell r="F18">
-            <v>601.75</v>
+            <v>678.55555555555554</v>
           </cell>
           <cell r="G18">
-            <v>0.54615808148782574</v>
+            <v>0.74350503691015124</v>
           </cell>
           <cell r="H18" t="str">
             <v>SUBIÓ</v>
@@ -550,10 +554,10 @@
         </row>
         <row r="19">
           <cell r="F19">
-            <v>713.75</v>
+            <v>810</v>
           </cell>
           <cell r="G19">
-            <v>0.66615718096931964</v>
+            <v>0.89084037349933287</v>
           </cell>
           <cell r="H19" t="str">
             <v>SUBIÓ</v>
@@ -561,10 +565,10 @@
         </row>
         <row r="20">
           <cell r="F20">
-            <v>703.5</v>
+            <v>800.11111111111109</v>
           </cell>
           <cell r="G20">
-            <v>0.80032902754082369</v>
+            <v>1.0475668210252662</v>
           </cell>
           <cell r="H20" t="str">
             <v>SUBIÓ</v>
@@ -572,21 +576,21 @@
         </row>
         <row r="21">
           <cell r="F21">
-            <v>216.25</v>
+            <v>252.77777777777777</v>
           </cell>
           <cell r="G21">
-            <v>-0.10640495867768596</v>
+            <v>4.4536271808998995E-2</v>
           </cell>
           <cell r="H21" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="22">
           <cell r="F22">
-            <v>98.125</v>
+            <v>119.11111111111111</v>
           </cell>
           <cell r="G22">
-            <v>-0.30990455458807775</v>
+            <v>-0.16231301629828088</v>
           </cell>
           <cell r="H22" t="str">
             <v>BAJO</v>
@@ -594,10 +598,10 @@
         </row>
         <row r="23">
           <cell r="F23">
-            <v>453.125</v>
+            <v>500.88888888888891</v>
           </cell>
           <cell r="G23">
-            <v>-0.11687935034802777</v>
+            <v>-2.3789636504253586E-2</v>
           </cell>
           <cell r="H23" t="str">
             <v>BAJO</v>
@@ -605,21 +609,21 @@
         </row>
         <row r="24">
           <cell r="F24">
-            <v>733.125</v>
+            <v>821.55555555555554</v>
           </cell>
           <cell r="G24">
-            <v>-9.6447854921063447E-2</v>
+            <v>1.2539859537922693E-2</v>
           </cell>
           <cell r="H24" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="25">
           <cell r="F25">
-            <v>74.875</v>
+            <v>68.888888888888886</v>
           </cell>
           <cell r="G25">
-            <v>-1.0324015247775709E-3</v>
+            <v>-8.0897924608216876E-2</v>
           </cell>
           <cell r="H25" t="str">
             <v>BAJO</v>
@@ -627,10 +631,10 @@
         </row>
         <row r="26">
           <cell r="F26">
-            <v>554</v>
+            <v>659.55555555555554</v>
           </cell>
           <cell r="G26">
-            <v>-0.29691182691726603</v>
+            <v>-0.16294998086259349</v>
           </cell>
           <cell r="H26" t="str">
             <v>BAJO</v>
@@ -638,10 +642,10 @@
         </row>
         <row r="27">
           <cell r="F27">
-            <v>801.625</v>
+            <v>957.66666666666663</v>
           </cell>
           <cell r="G27">
-            <v>-0.37063986092418133</v>
+            <v>-0.24813070136084947</v>
           </cell>
           <cell r="H27" t="str">
             <v>BAJO</v>
@@ -649,10 +653,10 @@
         </row>
         <row r="28">
           <cell r="F28">
-            <v>420.75</v>
+            <v>509.66666666666669</v>
           </cell>
           <cell r="G28">
-            <v>-0.20491766399712041</v>
+            <v>-3.6893728066228593E-2</v>
           </cell>
           <cell r="H28" t="str">
             <v>BAJO</v>
@@ -660,10 +664,10 @@
         </row>
         <row r="29">
           <cell r="F29">
-            <v>287.875</v>
+            <v>377.66666666666669</v>
           </cell>
           <cell r="G29">
-            <v>-0.28363846427301809</v>
+            <v>-6.0196705770825809E-2</v>
           </cell>
           <cell r="H29" t="str">
             <v>BAJO</v>
@@ -671,10 +675,10 @@
         </row>
         <row r="30">
           <cell r="F30">
-            <v>190.875</v>
+            <v>213.22222222222223</v>
           </cell>
           <cell r="G30">
-            <v>1.5083698372966206</v>
+            <v>1.8020442219440964</v>
           </cell>
           <cell r="H30" t="str">
             <v>SUBIÓ</v>
@@ -682,10 +686,10 @@
         </row>
         <row r="31">
           <cell r="F31">
-            <v>222.125</v>
+            <v>248</v>
           </cell>
           <cell r="G31">
-            <v>2.080994055482166</v>
+            <v>2.4398943196829586</v>
           </cell>
           <cell r="H31" t="str">
             <v>SUBIÓ</v>
@@ -693,10 +697,10 @@
         </row>
         <row r="32">
           <cell r="F32">
-            <v>103.75</v>
+            <v>123.55555555555556</v>
           </cell>
           <cell r="G32">
-            <v>-0.18854748603351956</v>
+            <v>-3.3643699565487295E-2</v>
           </cell>
           <cell r="H32" t="str">
             <v>BAJO</v>
@@ -704,10 +708,10 @@
         </row>
         <row r="33">
           <cell r="F33">
-            <v>104.125</v>
+            <v>127.55555555555556</v>
           </cell>
           <cell r="G33">
-            <v>-0.273546511627907</v>
+            <v>-0.110077519379845</v>
           </cell>
           <cell r="H33" t="str">
             <v>BAJO</v>
@@ -715,21 +719,21 @@
         </row>
         <row r="34">
           <cell r="F34">
-            <v>636.5</v>
+            <v>747.88888888888891</v>
           </cell>
           <cell r="G34">
-            <v>-2.4058119158878455E-2</v>
+            <v>0.1467338395638631</v>
           </cell>
           <cell r="H34" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="35">
           <cell r="F35">
-            <v>507.125</v>
+            <v>574.77777777777783</v>
           </cell>
           <cell r="G35">
-            <v>-0.1938209689629069</v>
+            <v>-8.6273025485743005E-2</v>
           </cell>
           <cell r="H35" t="str">
             <v>BAJO</v>
@@ -737,10 +741,10 @@
         </row>
         <row r="36">
           <cell r="F36">
-            <v>670.375</v>
+            <v>758.22222222222217</v>
           </cell>
           <cell r="G36">
-            <v>-0.21335074877067495</v>
+            <v>-0.11026672627030254</v>
           </cell>
           <cell r="H36" t="str">
             <v>BAJO</v>
@@ -748,10 +752,10 @@
         </row>
         <row r="37">
           <cell r="F37">
-            <v>394.125</v>
+            <v>472.88888888888891</v>
           </cell>
           <cell r="G37">
-            <v>-0.31930051813471505</v>
+            <v>-0.18326616772212623</v>
           </cell>
           <cell r="H37" t="str">
             <v>BAJO</v>
@@ -759,10 +763,10 @@
         </row>
         <row r="38">
           <cell r="F38">
-            <v>3.5</v>
+            <v>5.1111111111111107</v>
           </cell>
           <cell r="G38">
-            <v>0.41346153846153832</v>
+            <v>1.0641025641025639</v>
           </cell>
           <cell r="H38" t="str">
             <v>SUBIÓ</v>
@@ -770,10 +774,10 @@
         </row>
         <row r="39">
           <cell r="F39">
-            <v>0.75</v>
+            <v>0.66666666666666663</v>
           </cell>
           <cell r="G39">
-            <v>0.75</v>
+            <v>0.55555555555555558</v>
           </cell>
           <cell r="H39" t="str">
             <v>SUBIÓ</v>
@@ -781,21 +785,21 @@
         </row>
         <row r="40">
           <cell r="F40">
-            <v>116</v>
+            <v>143.88888888888889</v>
           </cell>
           <cell r="G40">
-            <v>-0.15416666666666667</v>
+            <v>4.9189814814814881E-2</v>
           </cell>
           <cell r="H40" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="41">
           <cell r="F41">
-            <v>432.375</v>
+            <v>509.22222222222223</v>
           </cell>
           <cell r="G41">
-            <v>-0.22014300438031442</v>
+            <v>-8.1536831858913805E-2</v>
           </cell>
           <cell r="H41" t="str">
             <v>BAJO</v>
@@ -803,10 +807,10 @@
         </row>
         <row r="42">
           <cell r="F42">
-            <v>372.25</v>
+            <v>415.66666666666669</v>
           </cell>
           <cell r="G42">
-            <v>1.8028863391896741</v>
+            <v>2.1297956256722843</v>
           </cell>
           <cell r="H42" t="str">
             <v>SUBIÓ</v>
@@ -814,10 +818,10 @@
         </row>
         <row r="43">
           <cell r="F43">
-            <v>124.625</v>
+            <v>177.66666666666666</v>
           </cell>
           <cell r="G43">
-            <v>-0.57917269657501214</v>
+            <v>-0.40006431902235096</v>
           </cell>
           <cell r="H43" t="str">
             <v>BAJO</v>
@@ -825,10 +829,10 @@
         </row>
         <row r="44">
           <cell r="F44">
-            <v>250.375</v>
+            <v>461.33333333333331</v>
           </cell>
           <cell r="G44">
-            <v>-0.52644555525533643</v>
+            <v>-0.12744303341439245</v>
           </cell>
           <cell r="H44" t="str">
             <v>BAJO</v>
@@ -836,10 +840,10 @@
         </row>
         <row r="45">
           <cell r="F45">
-            <v>166.875</v>
+            <v>295.77777777777777</v>
           </cell>
           <cell r="G45">
-            <v>-0.45389200561009813</v>
+            <v>-3.2050283102176502E-2</v>
           </cell>
           <cell r="H45" t="str">
             <v>BAJO</v>
@@ -847,10 +851,10 @@
         </row>
         <row r="46">
           <cell r="F46">
-            <v>191</v>
+            <v>210.44444444444446</v>
           </cell>
           <cell r="G46">
-            <v>-0.34116294349540088</v>
+            <v>-0.27409110819097682</v>
           </cell>
           <cell r="H46" t="str">
             <v>BAJO</v>
@@ -858,10 +862,10 @@
         </row>
         <row r="47">
           <cell r="F47">
-            <v>27</v>
+            <v>31.555555555555557</v>
           </cell>
           <cell r="G47">
-            <v>-0.53217821782178221</v>
+            <v>-0.45324532453245325</v>
           </cell>
           <cell r="H47" t="str">
             <v>BAJO</v>
@@ -869,21 +873,21 @@
         </row>
         <row r="48">
           <cell r="F48">
-            <v>65.125</v>
+            <v>108.11111111111111</v>
           </cell>
           <cell r="G48">
-            <v>-0.37806957708049105</v>
+            <v>3.2438987418523579E-2</v>
           </cell>
           <cell r="H48" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="49">
           <cell r="F49">
-            <v>22.75</v>
+            <v>45.555555555555557</v>
           </cell>
           <cell r="G49">
-            <v>-0.53885135135135132</v>
+            <v>-7.6576576576576572E-2</v>
           </cell>
           <cell r="H49" t="str">
             <v>BAJO</v>
@@ -891,13 +895,13 @@
         </row>
         <row r="50">
           <cell r="F50">
-            <v>29.625</v>
+            <v>65</v>
           </cell>
           <cell r="G50">
-            <v>-0.46460843373493976</v>
+            <v>0.17469879518072284</v>
           </cell>
           <cell r="H50" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
       </sheetData>
@@ -1157,11 +1161,11 @@
       </c>
       <c r="E2" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F4</f>
-        <v>975.625</v>
+        <v>1117.7777777777778</v>
       </c>
       <c r="F2" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G4</f>
-        <v>-0.17883266533066133</v>
+        <v>-5.9185036740146857E-2</v>
       </c>
       <c r="G2" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H4</f>
@@ -1186,15 +1190,15 @@
       </c>
       <c r="E3" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F5</f>
-        <v>76.375</v>
+        <v>77.666666666666671</v>
       </c>
       <c r="F3" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G5</f>
-        <v>-7.7930174563589638E-5</v>
+        <v>1.6832917705735806E-2</v>
       </c>
       <c r="G3" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H5</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H3">
         <v>1.59</v>
@@ -1215,11 +1219,11 @@
       </c>
       <c r="E4" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F6</f>
-        <v>391.25</v>
+        <v>422.22222222222223</v>
       </c>
       <c r="F4" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G6</f>
-        <v>-0.23205439760725299</v>
+        <v>-0.1712621117238371</v>
       </c>
       <c r="G4" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H6</f>
@@ -1244,11 +1248,11 @@
       </c>
       <c r="E5" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F7</f>
-        <v>91.625</v>
+        <v>97.222222222222229</v>
       </c>
       <c r="F5" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G7</f>
-        <v>-6.505102040816324E-2</v>
+        <v>-7.9365079365079083E-3</v>
       </c>
       <c r="G5" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H7</f>
@@ -1273,11 +1277,11 @@
       </c>
       <c r="E6" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F8</f>
-        <v>13.125</v>
+        <v>13.222222222222221</v>
       </c>
       <c r="F6" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G8</f>
-        <v>9.8107569721115562E-2</v>
+        <v>0.10624169986719778</v>
       </c>
       <c r="G6" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H8</f>
@@ -1302,11 +1306,11 @@
       </c>
       <c r="E7" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F9</f>
-        <v>1136.125</v>
+        <v>1315</v>
       </c>
       <c r="F7" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G9</f>
-        <v>-0.22200981511070528</v>
+        <v>-9.9520657384158828E-2</v>
       </c>
       <c r="G7" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H9</f>
@@ -1331,11 +1335,11 @@
       </c>
       <c r="E8" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F10</f>
-        <v>117.125</v>
+        <v>132</v>
       </c>
       <c r="F8" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G10</f>
-        <v>-0.2211447118429386</v>
+        <v>-0.12222925902469917</v>
       </c>
       <c r="G8" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H10</f>
@@ -1360,11 +1364,11 @@
       </c>
       <c r="E9" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F11</f>
-        <v>244.375</v>
+        <v>272.22222222222223</v>
       </c>
       <c r="F9" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G11</f>
-        <v>-0.28872141372141369</v>
+        <v>-0.2076692076692076</v>
       </c>
       <c r="G9" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H11</f>
@@ -1389,11 +1393,11 @@
       </c>
       <c r="E10" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F12</f>
-        <v>636.625</v>
+        <v>687.55555555555554</v>
       </c>
       <c r="F10" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G12</f>
-        <v>-0.16910348042262269</v>
+        <v>-0.10263103376838612</v>
       </c>
       <c r="G10" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H12</f>
@@ -1418,11 +1422,11 @@
       </c>
       <c r="E11" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F13</f>
-        <v>283.875</v>
+        <v>320.55555555555554</v>
       </c>
       <c r="F11" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G13</f>
-        <v>-0.21756464102900641</v>
+        <v>-0.11646322789517438</v>
       </c>
       <c r="G11" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H13</f>
@@ -1447,11 +1451,11 @@
       </c>
       <c r="E12" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F14</f>
-        <v>2852.125</v>
+        <v>3274.6666666666665</v>
       </c>
       <c r="F12" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G14</f>
-        <v>-0.19008782723929041</v>
+        <v>-7.009952401557773E-2</v>
       </c>
       <c r="G12" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H14</f>
@@ -1476,11 +1480,11 @@
       </c>
       <c r="E13" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F15</f>
-        <v>1730.375</v>
+        <v>2013.2222222222222</v>
       </c>
       <c r="F13" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G15</f>
-        <v>-0.24929501084598693</v>
+        <v>-0.12658471920944803</v>
       </c>
       <c r="G13" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H15</f>
@@ -1505,11 +1509,11 @@
       </c>
       <c r="E14" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F16</f>
-        <v>1865.25</v>
+        <v>2115.7777777777778</v>
       </c>
       <c r="F14" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G16</f>
-        <v>-0.17702643079250358</v>
+        <v>-6.6490181247723878E-2</v>
       </c>
       <c r="G14" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H16</f>
@@ -1534,11 +1538,11 @@
       </c>
       <c r="E15" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F17</f>
-        <v>2207.5</v>
+        <v>2528</v>
       </c>
       <c r="F15" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G17</f>
-        <v>-0.1744577412116679</v>
+        <v>-5.4599850411368722E-2</v>
       </c>
       <c r="G15" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H17</f>
@@ -1563,11 +1567,11 @@
       </c>
       <c r="E16" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F18</f>
-        <v>601.75</v>
+        <v>678.55555555555554</v>
       </c>
       <c r="F16" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G18</f>
-        <v>0.54615808148782574</v>
+        <v>0.74350503691015124</v>
       </c>
       <c r="G16" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H18</f>
@@ -1592,11 +1596,11 @@
       </c>
       <c r="E17" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F19</f>
-        <v>713.75</v>
+        <v>810</v>
       </c>
       <c r="F17" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G19</f>
-        <v>0.66615718096931964</v>
+        <v>0.89084037349933287</v>
       </c>
       <c r="G17" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H19</f>
@@ -1621,11 +1625,11 @@
       </c>
       <c r="E18" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F20</f>
-        <v>703.5</v>
+        <v>800.11111111111109</v>
       </c>
       <c r="F18" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G20</f>
-        <v>0.80032902754082369</v>
+        <v>1.0475668210252662</v>
       </c>
       <c r="G18" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H20</f>
@@ -1650,15 +1654,15 @@
       </c>
       <c r="E19" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F21</f>
-        <v>216.25</v>
+        <v>252.77777777777777</v>
       </c>
       <c r="F19" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G21</f>
-        <v>-0.10640495867768596</v>
+        <v>4.4536271808998995E-2</v>
       </c>
       <c r="G19" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H21</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H19">
         <v>3.68</v>
@@ -1679,11 +1683,11 @@
       </c>
       <c r="E20" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F22</f>
-        <v>98.125</v>
+        <v>119.11111111111111</v>
       </c>
       <c r="F20" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G22</f>
-        <v>-0.30990455458807775</v>
+        <v>-0.16231301629828088</v>
       </c>
       <c r="G20" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H22</f>
@@ -1708,11 +1712,11 @@
       </c>
       <c r="E21" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F23</f>
-        <v>453.125</v>
+        <v>500.88888888888891</v>
       </c>
       <c r="F21" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G23</f>
-        <v>-0.11687935034802777</v>
+        <v>-2.3789636504253586E-2</v>
       </c>
       <c r="G21" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H23</f>
@@ -1737,15 +1741,15 @@
       </c>
       <c r="E22" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F24</f>
-        <v>733.125</v>
+        <v>821.55555555555554</v>
       </c>
       <c r="F22" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G24</f>
-        <v>-9.6447854921063447E-2</v>
+        <v>1.2539859537922693E-2</v>
       </c>
       <c r="G22" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H24</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H22">
         <v>4.1500000000000004</v>
@@ -1766,11 +1770,11 @@
       </c>
       <c r="E23" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F25</f>
-        <v>74.875</v>
+        <v>68.888888888888886</v>
       </c>
       <c r="F23" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G25</f>
-        <v>-1.0324015247775709E-3</v>
+        <v>-8.0897924608216876E-2</v>
       </c>
       <c r="G23" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H25</f>
@@ -1795,11 +1799,11 @@
       </c>
       <c r="E24" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F26</f>
-        <v>554</v>
+        <v>659.55555555555554</v>
       </c>
       <c r="F24" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G26</f>
-        <v>-0.29691182691726603</v>
+        <v>-0.16294998086259349</v>
       </c>
       <c r="G24" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H26</f>
@@ -1824,11 +1828,11 @@
       </c>
       <c r="E25" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F27</f>
-        <v>801.625</v>
+        <v>957.66666666666663</v>
       </c>
       <c r="F25" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G27</f>
-        <v>-0.37063986092418133</v>
+        <v>-0.24813070136084947</v>
       </c>
       <c r="G25" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H27</f>
@@ -1853,11 +1857,11 @@
       </c>
       <c r="E26" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F28</f>
-        <v>420.75</v>
+        <v>509.66666666666669</v>
       </c>
       <c r="F26" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G28</f>
-        <v>-0.20491766399712041</v>
+        <v>-3.6893728066228593E-2</v>
       </c>
       <c r="G26" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H28</f>
@@ -1882,11 +1886,11 @@
       </c>
       <c r="E27" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F29</f>
-        <v>287.875</v>
+        <v>377.66666666666669</v>
       </c>
       <c r="F27" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G29</f>
-        <v>-0.28363846427301809</v>
+        <v>-6.0196705770825809E-2</v>
       </c>
       <c r="G27" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H29</f>
@@ -1911,11 +1915,11 @@
       </c>
       <c r="E28" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F30</f>
-        <v>190.875</v>
+        <v>213.22222222222223</v>
       </c>
       <c r="F28" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G30</f>
-        <v>1.5083698372966206</v>
+        <v>1.8020442219440964</v>
       </c>
       <c r="G28" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H30</f>
@@ -1940,11 +1944,11 @@
       </c>
       <c r="E29" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F31</f>
-        <v>222.125</v>
+        <v>248</v>
       </c>
       <c r="F29" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G31</f>
-        <v>2.080994055482166</v>
+        <v>2.4398943196829586</v>
       </c>
       <c r="G29" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H31</f>
@@ -1969,11 +1973,11 @@
       </c>
       <c r="E30" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F32</f>
-        <v>103.75</v>
+        <v>123.55555555555556</v>
       </c>
       <c r="F30" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G32</f>
-        <v>-0.18854748603351956</v>
+        <v>-3.3643699565487295E-2</v>
       </c>
       <c r="G30" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H32</f>
@@ -1998,11 +2002,11 @@
       </c>
       <c r="E31" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F33</f>
-        <v>104.125</v>
+        <v>127.55555555555556</v>
       </c>
       <c r="F31" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G33</f>
-        <v>-0.273546511627907</v>
+        <v>-0.110077519379845</v>
       </c>
       <c r="G31" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H33</f>
@@ -2027,15 +2031,15 @@
       </c>
       <c r="E32" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F34</f>
-        <v>636.5</v>
+        <v>747.88888888888891</v>
       </c>
       <c r="F32" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G34</f>
-        <v>-2.4058119158878455E-2</v>
+        <v>0.1467338395638631</v>
       </c>
       <c r="G32" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H34</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H32">
         <v>1.1599999999999999</v>
@@ -2056,11 +2060,11 @@
       </c>
       <c r="E33" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F35</f>
-        <v>507.125</v>
+        <v>574.77777777777783</v>
       </c>
       <c r="F33" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G35</f>
-        <v>-0.1938209689629069</v>
+        <v>-8.6273025485743005E-2</v>
       </c>
       <c r="G33" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H35</f>
@@ -2085,11 +2089,11 @@
       </c>
       <c r="E34" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F36</f>
-        <v>670.375</v>
+        <v>758.22222222222217</v>
       </c>
       <c r="F34" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G36</f>
-        <v>-0.21335074877067495</v>
+        <v>-0.11026672627030254</v>
       </c>
       <c r="G34" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H36</f>
@@ -2114,11 +2118,11 @@
       </c>
       <c r="E35" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F37</f>
-        <v>394.125</v>
+        <v>472.88888888888891</v>
       </c>
       <c r="F35" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G37</f>
-        <v>-0.31930051813471505</v>
+        <v>-0.18326616772212623</v>
       </c>
       <c r="G35" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H37</f>
@@ -2143,11 +2147,11 @@
       </c>
       <c r="E36" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F38</f>
-        <v>3.5</v>
+        <v>5.1111111111111107</v>
       </c>
       <c r="F36" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G38</f>
-        <v>0.41346153846153832</v>
+        <v>1.0641025641025639</v>
       </c>
       <c r="G36" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H38</f>
@@ -2172,11 +2176,11 @@
       </c>
       <c r="E37" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F39</f>
-        <v>0.75</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F37" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G39</f>
-        <v>0.75</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="G37" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H39</f>
@@ -2201,15 +2205,15 @@
       </c>
       <c r="E38" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F40</f>
-        <v>116</v>
+        <v>143.88888888888889</v>
       </c>
       <c r="F38" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G40</f>
-        <v>-0.15416666666666667</v>
+        <v>4.9189814814814881E-2</v>
       </c>
       <c r="G38" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H40</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H38">
         <v>1.1599999999999999</v>
@@ -2230,11 +2234,11 @@
       </c>
       <c r="E39" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F41</f>
-        <v>432.375</v>
+        <v>509.22222222222223</v>
       </c>
       <c r="F39" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G41</f>
-        <v>-0.22014300438031442</v>
+        <v>-8.1536831858913805E-2</v>
       </c>
       <c r="G39" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H41</f>
@@ -2259,11 +2263,11 @@
       </c>
       <c r="E40" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F42</f>
-        <v>372.25</v>
+        <v>415.66666666666669</v>
       </c>
       <c r="F40" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G42</f>
-        <v>1.8028863391896741</v>
+        <v>2.1297956256722843</v>
       </c>
       <c r="G40" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H42</f>
@@ -2288,11 +2292,11 @@
       </c>
       <c r="E41" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F43</f>
-        <v>124.625</v>
+        <v>177.66666666666666</v>
       </c>
       <c r="F41" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G43</f>
-        <v>-0.57917269657501214</v>
+        <v>-0.40006431902235096</v>
       </c>
       <c r="G41" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H43</f>
@@ -2317,11 +2321,11 @@
       </c>
       <c r="E42" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F44</f>
-        <v>250.375</v>
+        <v>461.33333333333331</v>
       </c>
       <c r="F42" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G44</f>
-        <v>-0.52644555525533643</v>
+        <v>-0.12744303341439245</v>
       </c>
       <c r="G42" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H44</f>
@@ -2346,11 +2350,11 @@
       </c>
       <c r="E43" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F45</f>
-        <v>166.875</v>
+        <v>295.77777777777777</v>
       </c>
       <c r="F43" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G45</f>
-        <v>-0.45389200561009813</v>
+        <v>-3.2050283102176502E-2</v>
       </c>
       <c r="G43" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H45</f>
@@ -2375,11 +2379,11 @@
       </c>
       <c r="E44" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F46</f>
-        <v>191</v>
+        <v>210.44444444444446</v>
       </c>
       <c r="F44" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G46</f>
-        <v>-0.34116294349540088</v>
+        <v>-0.27409110819097682</v>
       </c>
       <c r="G44" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H46</f>
@@ -2404,11 +2408,11 @@
       </c>
       <c r="E45" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F47</f>
-        <v>27</v>
+        <v>31.555555555555557</v>
       </c>
       <c r="F45" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G47</f>
-        <v>-0.53217821782178221</v>
+        <v>-0.45324532453245325</v>
       </c>
       <c r="G45" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H47</f>
@@ -2433,15 +2437,15 @@
       </c>
       <c r="E46" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F48</f>
-        <v>65.125</v>
+        <v>108.11111111111111</v>
       </c>
       <c r="F46" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G48</f>
-        <v>-0.37806957708049105</v>
+        <v>3.2438987418523579E-2</v>
       </c>
       <c r="G46" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H48</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H46">
         <v>2.62</v>
@@ -2462,11 +2466,11 @@
       </c>
       <c r="E47" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F49</f>
-        <v>22.75</v>
+        <v>45.555555555555557</v>
       </c>
       <c r="F47" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G49</f>
-        <v>-0.53885135135135132</v>
+        <v>-7.6576576576576572E-2</v>
       </c>
       <c r="G47" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H49</f>
@@ -2491,15 +2495,15 @@
       </c>
       <c r="E48" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F50</f>
-        <v>29.625</v>
+        <v>65</v>
       </c>
       <c r="F48" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G50</f>
-        <v>-0.46460843373493976</v>
+        <v>0.17469879518072284</v>
       </c>
       <c r="G48" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H50</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H48">
         <v>2.62</v>

--- a/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
+++ b/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FDF6AAF-378B-4A11-9EB1-540F600E829B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D547433-D1C6-474C-B2DB-CE7A42C9D6EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -389,32 +389,32 @@
       <sheetData sheetId="12">
         <row r="4">
           <cell r="F4">
-            <v>1117.7777777777778</v>
+            <v>1215.3</v>
           </cell>
           <cell r="G4">
-            <v>-5.9185036740146857E-2</v>
+            <v>2.2897795591182435E-2</v>
           </cell>
           <cell r="H4" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="5">
           <cell r="F5">
-            <v>77.666666666666671</v>
+            <v>74.2</v>
           </cell>
           <cell r="G5">
-            <v>1.6832917705735806E-2</v>
+            <v>-2.8553615960099643E-2</v>
           </cell>
           <cell r="H5" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="6">
           <cell r="F6">
-            <v>422.22222222222223</v>
+            <v>484.6</v>
           </cell>
           <cell r="G6">
-            <v>-0.1712621117238371</v>
+            <v>-4.8826993176932398E-2</v>
           </cell>
           <cell r="H6" t="str">
             <v>BAJO</v>
@@ -422,21 +422,21 @@
         </row>
         <row r="7">
           <cell r="F7">
-            <v>97.222222222222229</v>
+            <v>108</v>
           </cell>
           <cell r="G7">
-            <v>-7.9365079365079083E-3</v>
+            <v>0.1020408163265305</v>
           </cell>
           <cell r="H7" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="8">
           <cell r="F8">
-            <v>13.222222222222221</v>
+            <v>15.1</v>
           </cell>
           <cell r="G8">
-            <v>0.10624169986719778</v>
+            <v>0.26334661354581668</v>
           </cell>
           <cell r="H8" t="str">
             <v>SUBIÓ</v>
@@ -444,21 +444,21 @@
         </row>
         <row r="9">
           <cell r="F9">
-            <v>1315</v>
+            <v>1477.3</v>
           </cell>
           <cell r="G9">
-            <v>-9.9520657384158828E-2</v>
+            <v>1.1618351974435059E-2</v>
           </cell>
           <cell r="H9" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="10">
           <cell r="F10">
-            <v>132</v>
+            <v>136.9</v>
           </cell>
           <cell r="G10">
-            <v>-0.12222925902469917</v>
+            <v>-8.9645345155161427E-2</v>
           </cell>
           <cell r="H10" t="str">
             <v>BAJO</v>
@@ -466,10 +466,10 @@
         </row>
         <row r="11">
           <cell r="F11">
-            <v>272.22222222222223</v>
+            <v>268.7</v>
           </cell>
           <cell r="G11">
-            <v>-0.2076692076692076</v>
+            <v>-0.21792099792099795</v>
           </cell>
           <cell r="H11" t="str">
             <v>BAJO</v>
@@ -477,10 +477,10 @@
         </row>
         <row r="12">
           <cell r="F12">
-            <v>687.55555555555554</v>
+            <v>687.6</v>
           </cell>
           <cell r="G12">
-            <v>-0.10263103376838612</v>
+            <v>-0.10257302672467361</v>
           </cell>
           <cell r="H12" t="str">
             <v>BAJO</v>
@@ -488,10 +488,10 @@
         </row>
         <row r="13">
           <cell r="F13">
-            <v>320.55555555555554</v>
+            <v>320</v>
           </cell>
           <cell r="G13">
-            <v>-0.11646322789517438</v>
+            <v>-0.11799448746554664</v>
           </cell>
           <cell r="H13" t="str">
             <v>BAJO</v>
@@ -499,10 +499,10 @@
         </row>
         <row r="14">
           <cell r="F14">
-            <v>3274.6666666666665</v>
+            <v>3476.1</v>
           </cell>
           <cell r="G14">
-            <v>-7.009952401557773E-2</v>
+            <v>-1.2898907399394255E-2</v>
           </cell>
           <cell r="H14" t="str">
             <v>BAJO</v>
@@ -510,10 +510,10 @@
         </row>
         <row r="15">
           <cell r="F15">
-            <v>2013.2222222222222</v>
+            <v>2130.4</v>
           </cell>
           <cell r="G15">
-            <v>-0.12658471920944803</v>
+            <v>-7.574837310195226E-2</v>
           </cell>
           <cell r="H15" t="str">
             <v>BAJO</v>
@@ -521,10 +521,10 @@
         </row>
         <row r="16">
           <cell r="F16">
-            <v>2115.7777777777778</v>
+            <v>2189.3000000000002</v>
           </cell>
           <cell r="G16">
-            <v>-6.6490181247723878E-2</v>
+            <v>-3.4051180771493272E-2</v>
           </cell>
           <cell r="H16" t="str">
             <v>BAJO</v>
@@ -532,10 +532,10 @@
         </row>
         <row r="17">
           <cell r="F17">
-            <v>2528</v>
+            <v>2655.4</v>
           </cell>
           <cell r="G17">
-            <v>-5.4599850411368722E-2</v>
+            <v>-6.9558713537770656E-3</v>
           </cell>
           <cell r="H17" t="str">
             <v>BAJO</v>
@@ -543,10 +543,10 @@
         </row>
         <row r="18">
           <cell r="F18">
-            <v>678.55555555555554</v>
+            <v>669.2</v>
           </cell>
           <cell r="G18">
-            <v>0.74350503691015124</v>
+            <v>0.7194665361556345</v>
           </cell>
           <cell r="H18" t="str">
             <v>SUBIÓ</v>
@@ -554,10 +554,10 @@
         </row>
         <row r="19">
           <cell r="F19">
-            <v>810</v>
+            <v>806.4</v>
           </cell>
           <cell r="G19">
-            <v>0.89084037349933287</v>
+            <v>0.88243663850600251</v>
           </cell>
           <cell r="H19" t="str">
             <v>SUBIÓ</v>
@@ -565,10 +565,10 @@
         </row>
         <row r="20">
           <cell r="F20">
-            <v>800.11111111111109</v>
+            <v>795</v>
           </cell>
           <cell r="G20">
-            <v>1.0475668210252662</v>
+            <v>1.034486960760419</v>
           </cell>
           <cell r="H20" t="str">
             <v>SUBIÓ</v>
@@ -576,10 +576,10 @@
         </row>
         <row r="21">
           <cell r="F21">
-            <v>252.77777777777777</v>
+            <v>249.8</v>
           </cell>
           <cell r="G21">
-            <v>4.4536271808998995E-2</v>
+            <v>3.2231404958677823E-2</v>
           </cell>
           <cell r="H21" t="str">
             <v>SUBIÓ</v>
@@ -587,10 +587,10 @@
         </row>
         <row r="22">
           <cell r="F22">
-            <v>119.11111111111111</v>
+            <v>121</v>
           </cell>
           <cell r="G22">
-            <v>-0.16231301629828088</v>
+            <v>-0.14902880107166783</v>
           </cell>
           <cell r="H22" t="str">
             <v>BAJO</v>
@@ -598,10 +598,10 @@
         </row>
         <row r="23">
           <cell r="F23">
-            <v>500.88888888888891</v>
+            <v>491.8</v>
           </cell>
           <cell r="G23">
-            <v>-2.3789636504253586E-2</v>
+            <v>-4.1503480278422211E-2</v>
           </cell>
           <cell r="H23" t="str">
             <v>BAJO</v>
@@ -609,21 +609,21 @@
         </row>
         <row r="24">
           <cell r="F24">
-            <v>821.55555555555554</v>
+            <v>807.7</v>
           </cell>
           <cell r="G24">
-            <v>1.2539859537922693E-2</v>
+            <v>-4.5366512119255908E-3</v>
           </cell>
           <cell r="H24" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="25">
           <cell r="F25">
-            <v>68.888888888888886</v>
+            <v>62</v>
           </cell>
           <cell r="G25">
-            <v>-8.0897924608216876E-2</v>
+            <v>-0.1728081321473951</v>
           </cell>
           <cell r="H25" t="str">
             <v>BAJO</v>
@@ -631,10 +631,10 @@
         </row>
         <row r="26">
           <cell r="F26">
-            <v>659.55555555555554</v>
+            <v>705.3</v>
           </cell>
           <cell r="G26">
-            <v>-0.16294998086259349</v>
+            <v>-0.10489514715658432</v>
           </cell>
           <cell r="H26" t="str">
             <v>BAJO</v>
@@ -642,10 +642,10 @@
         </row>
         <row r="27">
           <cell r="F27">
-            <v>957.66666666666663</v>
+            <v>1106.8</v>
           </cell>
           <cell r="G27">
-            <v>-0.24813070136084947</v>
+            <v>-0.13104531179901313</v>
           </cell>
           <cell r="H27" t="str">
             <v>BAJO</v>
@@ -653,10 +653,10 @@
         </row>
         <row r="28">
           <cell r="F28">
-            <v>509.66666666666669</v>
+            <v>517.1</v>
           </cell>
           <cell r="G28">
-            <v>-3.6893728066228593E-2</v>
+            <v>-2.2847115990281552E-2</v>
           </cell>
           <cell r="H28" t="str">
             <v>BAJO</v>
@@ -664,10 +664,10 @@
         </row>
         <row r="29">
           <cell r="F29">
-            <v>377.66666666666669</v>
+            <v>386.6</v>
           </cell>
           <cell r="G29">
-            <v>-6.0196705770825809E-2</v>
+            <v>-3.7966583718449964E-2</v>
           </cell>
           <cell r="H29" t="str">
             <v>BAJO</v>
@@ -675,10 +675,10 @@
         </row>
         <row r="30">
           <cell r="F30">
-            <v>213.22222222222223</v>
+            <v>236.1</v>
           </cell>
           <cell r="G30">
-            <v>1.8020442219440964</v>
+            <v>2.1026908635794741</v>
           </cell>
           <cell r="H30" t="str">
             <v>SUBIÓ</v>
@@ -686,10 +686,10 @@
         </row>
         <row r="31">
           <cell r="F31">
-            <v>248</v>
+            <v>283.89999999999998</v>
           </cell>
           <cell r="G31">
-            <v>2.4398943196829586</v>
+            <v>2.9378467635402901</v>
           </cell>
           <cell r="H31" t="str">
             <v>SUBIÓ</v>
@@ -697,10 +697,10 @@
         </row>
         <row r="32">
           <cell r="F32">
-            <v>123.55555555555556</v>
+            <v>127.4</v>
           </cell>
           <cell r="G32">
-            <v>-3.3643699565487295E-2</v>
+            <v>-3.5754189944133818E-3</v>
           </cell>
           <cell r="H32" t="str">
             <v>BAJO</v>
@@ -708,10 +708,10 @@
         </row>
         <row r="33">
           <cell r="F33">
-            <v>127.55555555555556</v>
+            <v>129.9</v>
           </cell>
           <cell r="G33">
-            <v>-0.110077519379845</v>
+            <v>-9.3720930232558119E-2</v>
           </cell>
           <cell r="H33" t="str">
             <v>BAJO</v>
@@ -719,10 +719,10 @@
         </row>
         <row r="34">
           <cell r="F34">
-            <v>747.88888888888891</v>
+            <v>749.3</v>
           </cell>
           <cell r="G34">
-            <v>0.1467338395638631</v>
+            <v>0.14889748831775695</v>
           </cell>
           <cell r="H34" t="str">
             <v>SUBIÓ</v>
@@ -730,10 +730,10 @@
         </row>
         <row r="35">
           <cell r="F35">
-            <v>574.77777777777783</v>
+            <v>578.9</v>
           </cell>
           <cell r="G35">
-            <v>-8.6273025485743005E-2</v>
+            <v>-7.9719909159727487E-2</v>
           </cell>
           <cell r="H35" t="str">
             <v>BAJO</v>
@@ -741,10 +741,10 @@
         </row>
         <row r="36">
           <cell r="F36">
-            <v>758.22222222222217</v>
+            <v>771.8</v>
           </cell>
           <cell r="G36">
-            <v>-0.11026672627030254</v>
+            <v>-9.4333929369691538E-2</v>
           </cell>
           <cell r="H36" t="str">
             <v>BAJO</v>
@@ -752,10 +752,10 @@
         </row>
         <row r="37">
           <cell r="F37">
-            <v>472.88888888888891</v>
+            <v>493.6</v>
           </cell>
           <cell r="G37">
-            <v>-0.18326616772212623</v>
+            <v>-0.14749568221070808</v>
           </cell>
           <cell r="H37" t="str">
             <v>BAJO</v>
@@ -763,10 +763,10 @@
         </row>
         <row r="38">
           <cell r="F38">
-            <v>5.1111111111111107</v>
+            <v>4.8</v>
           </cell>
           <cell r="G38">
-            <v>1.0641025641025639</v>
+            <v>0.93846153846153824</v>
           </cell>
           <cell r="H38" t="str">
             <v>SUBIÓ</v>
@@ -774,10 +774,10 @@
         </row>
         <row r="39">
           <cell r="F39">
-            <v>0.66666666666666663</v>
+            <v>0.7</v>
           </cell>
           <cell r="G39">
-            <v>0.55555555555555558</v>
+            <v>0.6333333333333333</v>
           </cell>
           <cell r="H39" t="str">
             <v>SUBIÓ</v>
@@ -785,10 +785,10 @@
         </row>
         <row r="40">
           <cell r="F40">
-            <v>143.88888888888889</v>
+            <v>147.6</v>
           </cell>
           <cell r="G40">
-            <v>4.9189814814814881E-2</v>
+            <v>7.6249999999999929E-2</v>
           </cell>
           <cell r="H40" t="str">
             <v>SUBIÓ</v>
@@ -796,10 +796,10 @@
         </row>
         <row r="41">
           <cell r="F41">
-            <v>509.22222222222223</v>
+            <v>512.70000000000005</v>
           </cell>
           <cell r="G41">
-            <v>-8.1536831858913805E-2</v>
+            <v>-7.5264107188868778E-2</v>
           </cell>
           <cell r="H41" t="str">
             <v>BAJO</v>
@@ -807,10 +807,10 @@
         </row>
         <row r="42">
           <cell r="F42">
-            <v>415.66666666666669</v>
+            <v>409.7</v>
           </cell>
           <cell r="G42">
-            <v>2.1297956256722843</v>
+            <v>2.0848691287199714</v>
           </cell>
           <cell r="H42" t="str">
             <v>SUBIÓ</v>
@@ -818,10 +818,10 @@
         </row>
         <row r="43">
           <cell r="F43">
-            <v>177.66666666666666</v>
+            <v>181.9</v>
           </cell>
           <cell r="G43">
-            <v>-0.40006431902235096</v>
+            <v>-0.38576941630487216</v>
           </cell>
           <cell r="H43" t="str">
             <v>BAJO</v>
@@ -829,10 +829,10 @@
         </row>
         <row r="44">
           <cell r="F44">
-            <v>461.33333333333331</v>
+            <v>455.4</v>
           </cell>
           <cell r="G44">
-            <v>-0.12744303341439245</v>
+            <v>-0.13866522561469874</v>
           </cell>
           <cell r="H44" t="str">
             <v>BAJO</v>
@@ -840,10 +840,10 @@
         </row>
         <row r="45">
           <cell r="F45">
-            <v>295.77777777777777</v>
+            <v>287.89999999999998</v>
           </cell>
           <cell r="G45">
-            <v>-3.2050283102176502E-2</v>
+            <v>-5.7830762038335704E-2</v>
           </cell>
           <cell r="H45" t="str">
             <v>BAJO</v>
@@ -851,10 +851,10 @@
         </row>
         <row r="46">
           <cell r="F46">
-            <v>210.44444444444446</v>
+            <v>211.7</v>
           </cell>
           <cell r="G46">
-            <v>-0.27409110819097682</v>
+            <v>-0.26976018396846269</v>
           </cell>
           <cell r="H46" t="str">
             <v>BAJO</v>
@@ -862,10 +862,10 @@
         </row>
         <row r="47">
           <cell r="F47">
-            <v>31.555555555555557</v>
+            <v>31.2</v>
           </cell>
           <cell r="G47">
-            <v>-0.45324532453245325</v>
+            <v>-0.45940594059405948</v>
           </cell>
           <cell r="H47" t="str">
             <v>BAJO</v>
@@ -873,10 +873,10 @@
         </row>
         <row r="48">
           <cell r="F48">
-            <v>108.11111111111111</v>
+            <v>107</v>
           </cell>
           <cell r="G48">
-            <v>3.2438987418523579E-2</v>
+            <v>2.1828103683492639E-2</v>
           </cell>
           <cell r="H48" t="str">
             <v>SUBIÓ</v>
@@ -884,10 +884,10 @@
         </row>
         <row r="49">
           <cell r="F49">
-            <v>45.555555555555557</v>
+            <v>44.3</v>
           </cell>
           <cell r="G49">
-            <v>-7.6576576576576572E-2</v>
+            <v>-0.10202702702702715</v>
           </cell>
           <cell r="H49" t="str">
             <v>BAJO</v>
@@ -895,10 +895,10 @@
         </row>
         <row r="50">
           <cell r="F50">
-            <v>65</v>
+            <v>61.8</v>
           </cell>
           <cell r="G50">
-            <v>0.17469879518072284</v>
+            <v>0.11686746987951802</v>
           </cell>
           <cell r="H50" t="str">
             <v>SUBIÓ</v>
@@ -1161,15 +1161,15 @@
       </c>
       <c r="E2" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F4</f>
-        <v>1117.7777777777778</v>
+        <v>1215.3</v>
       </c>
       <c r="F2" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G4</f>
-        <v>-5.9185036740146857E-2</v>
+        <v>2.2897795591182435E-2</v>
       </c>
       <c r="G2" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H4</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H2">
         <v>1.36</v>
@@ -1190,15 +1190,15 @@
       </c>
       <c r="E3" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F5</f>
-        <v>77.666666666666671</v>
+        <v>74.2</v>
       </c>
       <c r="F3" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G5</f>
-        <v>1.6832917705735806E-2</v>
+        <v>-2.8553615960099643E-2</v>
       </c>
       <c r="G3" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H5</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H3">
         <v>1.59</v>
@@ -1219,11 +1219,11 @@
       </c>
       <c r="E4" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F6</f>
-        <v>422.22222222222223</v>
+        <v>484.6</v>
       </c>
       <c r="F4" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G6</f>
-        <v>-0.1712621117238371</v>
+        <v>-4.8826993176932398E-2</v>
       </c>
       <c r="G4" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H6</f>
@@ -1248,15 +1248,15 @@
       </c>
       <c r="E5" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F7</f>
-        <v>97.222222222222229</v>
+        <v>108</v>
       </c>
       <c r="F5" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G7</f>
-        <v>-7.9365079365079083E-3</v>
+        <v>0.1020408163265305</v>
       </c>
       <c r="G5" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H7</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H5">
         <v>3.61</v>
@@ -1277,11 +1277,11 @@
       </c>
       <c r="E6" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F8</f>
-        <v>13.222222222222221</v>
+        <v>15.1</v>
       </c>
       <c r="F6" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G8</f>
-        <v>0.10624169986719778</v>
+        <v>0.26334661354581668</v>
       </c>
       <c r="G6" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H8</f>
@@ -1306,15 +1306,15 @@
       </c>
       <c r="E7" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F9</f>
-        <v>1315</v>
+        <v>1477.3</v>
       </c>
       <c r="F7" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G9</f>
-        <v>-9.9520657384158828E-2</v>
+        <v>1.1618351974435059E-2</v>
       </c>
       <c r="G7" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H9</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H7">
         <v>0.63</v>
@@ -1335,11 +1335,11 @@
       </c>
       <c r="E8" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F10</f>
-        <v>132</v>
+        <v>136.9</v>
       </c>
       <c r="F8" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G10</f>
-        <v>-0.12222925902469917</v>
+        <v>-8.9645345155161427E-2</v>
       </c>
       <c r="G8" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H10</f>
@@ -1364,11 +1364,11 @@
       </c>
       <c r="E9" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F11</f>
-        <v>272.22222222222223</v>
+        <v>268.7</v>
       </c>
       <c r="F9" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G11</f>
-        <v>-0.2076692076692076</v>
+        <v>-0.21792099792099795</v>
       </c>
       <c r="G9" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H11</f>
@@ -1393,11 +1393,11 @@
       </c>
       <c r="E10" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F12</f>
-        <v>687.55555555555554</v>
+        <v>687.6</v>
       </c>
       <c r="F10" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G12</f>
-        <v>-0.10263103376838612</v>
+        <v>-0.10257302672467361</v>
       </c>
       <c r="G10" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H12</f>
@@ -1422,11 +1422,11 @@
       </c>
       <c r="E11" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F13</f>
-        <v>320.55555555555554</v>
+        <v>320</v>
       </c>
       <c r="F11" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G13</f>
-        <v>-0.11646322789517438</v>
+        <v>-0.11799448746554664</v>
       </c>
       <c r="G11" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H13</f>
@@ -1451,11 +1451,11 @@
       </c>
       <c r="E12" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F14</f>
-        <v>3274.6666666666665</v>
+        <v>3476.1</v>
       </c>
       <c r="F12" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G14</f>
-        <v>-7.009952401557773E-2</v>
+        <v>-1.2898907399394255E-2</v>
       </c>
       <c r="G12" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H14</f>
@@ -1480,11 +1480,11 @@
       </c>
       <c r="E13" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F15</f>
-        <v>2013.2222222222222</v>
+        <v>2130.4</v>
       </c>
       <c r="F13" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G15</f>
-        <v>-0.12658471920944803</v>
+        <v>-7.574837310195226E-2</v>
       </c>
       <c r="G13" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H15</f>
@@ -1509,11 +1509,11 @@
       </c>
       <c r="E14" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F16</f>
-        <v>2115.7777777777778</v>
+        <v>2189.3000000000002</v>
       </c>
       <c r="F14" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G16</f>
-        <v>-6.6490181247723878E-2</v>
+        <v>-3.4051180771493272E-2</v>
       </c>
       <c r="G14" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H16</f>
@@ -1538,11 +1538,11 @@
       </c>
       <c r="E15" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F17</f>
-        <v>2528</v>
+        <v>2655.4</v>
       </c>
       <c r="F15" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G17</f>
-        <v>-5.4599850411368722E-2</v>
+        <v>-6.9558713537770656E-3</v>
       </c>
       <c r="G15" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H17</f>
@@ -1567,11 +1567,11 @@
       </c>
       <c r="E16" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F18</f>
-        <v>678.55555555555554</v>
+        <v>669.2</v>
       </c>
       <c r="F16" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G18</f>
-        <v>0.74350503691015124</v>
+        <v>0.7194665361556345</v>
       </c>
       <c r="G16" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H18</f>
@@ -1596,11 +1596,11 @@
       </c>
       <c r="E17" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F19</f>
-        <v>810</v>
+        <v>806.4</v>
       </c>
       <c r="F17" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G19</f>
-        <v>0.89084037349933287</v>
+        <v>0.88243663850600251</v>
       </c>
       <c r="G17" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H19</f>
@@ -1625,11 +1625,11 @@
       </c>
       <c r="E18" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F20</f>
-        <v>800.11111111111109</v>
+        <v>795</v>
       </c>
       <c r="F18" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G20</f>
-        <v>1.0475668210252662</v>
+        <v>1.034486960760419</v>
       </c>
       <c r="G18" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H20</f>
@@ -1654,11 +1654,11 @@
       </c>
       <c r="E19" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F21</f>
-        <v>252.77777777777777</v>
+        <v>249.8</v>
       </c>
       <c r="F19" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G21</f>
-        <v>4.4536271808998995E-2</v>
+        <v>3.2231404958677823E-2</v>
       </c>
       <c r="G19" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H21</f>
@@ -1683,11 +1683,11 @@
       </c>
       <c r="E20" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F22</f>
-        <v>119.11111111111111</v>
+        <v>121</v>
       </c>
       <c r="F20" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G22</f>
-        <v>-0.16231301629828088</v>
+        <v>-0.14902880107166783</v>
       </c>
       <c r="G20" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H22</f>
@@ -1712,11 +1712,11 @@
       </c>
       <c r="E21" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F23</f>
-        <v>500.88888888888891</v>
+        <v>491.8</v>
       </c>
       <c r="F21" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G23</f>
-        <v>-2.3789636504253586E-2</v>
+        <v>-4.1503480278422211E-2</v>
       </c>
       <c r="G21" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H23</f>
@@ -1741,15 +1741,15 @@
       </c>
       <c r="E22" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F24</f>
-        <v>821.55555555555554</v>
+        <v>807.7</v>
       </c>
       <c r="F22" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G24</f>
-        <v>1.2539859537922693E-2</v>
+        <v>-4.5366512119255908E-3</v>
       </c>
       <c r="G22" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H24</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H22">
         <v>4.1500000000000004</v>
@@ -1770,11 +1770,11 @@
       </c>
       <c r="E23" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F25</f>
-        <v>68.888888888888886</v>
+        <v>62</v>
       </c>
       <c r="F23" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G25</f>
-        <v>-8.0897924608216876E-2</v>
+        <v>-0.1728081321473951</v>
       </c>
       <c r="G23" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H25</f>
@@ -1799,11 +1799,11 @@
       </c>
       <c r="E24" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F26</f>
-        <v>659.55555555555554</v>
+        <v>705.3</v>
       </c>
       <c r="F24" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G26</f>
-        <v>-0.16294998086259349</v>
+        <v>-0.10489514715658432</v>
       </c>
       <c r="G24" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H26</f>
@@ -1828,11 +1828,11 @@
       </c>
       <c r="E25" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F27</f>
-        <v>957.66666666666663</v>
+        <v>1106.8</v>
       </c>
       <c r="F25" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G27</f>
-        <v>-0.24813070136084947</v>
+        <v>-0.13104531179901313</v>
       </c>
       <c r="G25" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H27</f>
@@ -1857,11 +1857,11 @@
       </c>
       <c r="E26" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F28</f>
-        <v>509.66666666666669</v>
+        <v>517.1</v>
       </c>
       <c r="F26" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G28</f>
-        <v>-3.6893728066228593E-2</v>
+        <v>-2.2847115990281552E-2</v>
       </c>
       <c r="G26" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H28</f>
@@ -1886,11 +1886,11 @@
       </c>
       <c r="E27" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F29</f>
-        <v>377.66666666666669</v>
+        <v>386.6</v>
       </c>
       <c r="F27" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G29</f>
-        <v>-6.0196705770825809E-2</v>
+        <v>-3.7966583718449964E-2</v>
       </c>
       <c r="G27" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H29</f>
@@ -1915,11 +1915,11 @@
       </c>
       <c r="E28" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F30</f>
-        <v>213.22222222222223</v>
+        <v>236.1</v>
       </c>
       <c r="F28" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G30</f>
-        <v>1.8020442219440964</v>
+        <v>2.1026908635794741</v>
       </c>
       <c r="G28" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H30</f>
@@ -1944,11 +1944,11 @@
       </c>
       <c r="E29" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F31</f>
-        <v>248</v>
+        <v>283.89999999999998</v>
       </c>
       <c r="F29" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G31</f>
-        <v>2.4398943196829586</v>
+        <v>2.9378467635402901</v>
       </c>
       <c r="G29" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H31</f>
@@ -1973,11 +1973,11 @@
       </c>
       <c r="E30" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F32</f>
-        <v>123.55555555555556</v>
+        <v>127.4</v>
       </c>
       <c r="F30" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G32</f>
-        <v>-3.3643699565487295E-2</v>
+        <v>-3.5754189944133818E-3</v>
       </c>
       <c r="G30" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H32</f>
@@ -2002,11 +2002,11 @@
       </c>
       <c r="E31" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F33</f>
-        <v>127.55555555555556</v>
+        <v>129.9</v>
       </c>
       <c r="F31" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G33</f>
-        <v>-0.110077519379845</v>
+        <v>-9.3720930232558119E-2</v>
       </c>
       <c r="G31" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H33</f>
@@ -2031,11 +2031,11 @@
       </c>
       <c r="E32" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F34</f>
-        <v>747.88888888888891</v>
+        <v>749.3</v>
       </c>
       <c r="F32" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G34</f>
-        <v>0.1467338395638631</v>
+        <v>0.14889748831775695</v>
       </c>
       <c r="G32" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H34</f>
@@ -2060,11 +2060,11 @@
       </c>
       <c r="E33" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F35</f>
-        <v>574.77777777777783</v>
+        <v>578.9</v>
       </c>
       <c r="F33" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G35</f>
-        <v>-8.6273025485743005E-2</v>
+        <v>-7.9719909159727487E-2</v>
       </c>
       <c r="G33" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H35</f>
@@ -2089,11 +2089,11 @@
       </c>
       <c r="E34" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F36</f>
-        <v>758.22222222222217</v>
+        <v>771.8</v>
       </c>
       <c r="F34" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G36</f>
-        <v>-0.11026672627030254</v>
+        <v>-9.4333929369691538E-2</v>
       </c>
       <c r="G34" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H36</f>
@@ -2118,11 +2118,11 @@
       </c>
       <c r="E35" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F37</f>
-        <v>472.88888888888891</v>
+        <v>493.6</v>
       </c>
       <c r="F35" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G37</f>
-        <v>-0.18326616772212623</v>
+        <v>-0.14749568221070808</v>
       </c>
       <c r="G35" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H37</f>
@@ -2147,11 +2147,11 @@
       </c>
       <c r="E36" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F38</f>
-        <v>5.1111111111111107</v>
+        <v>4.8</v>
       </c>
       <c r="F36" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G38</f>
-        <v>1.0641025641025639</v>
+        <v>0.93846153846153824</v>
       </c>
       <c r="G36" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H38</f>
@@ -2176,11 +2176,11 @@
       </c>
       <c r="E37" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F39</f>
-        <v>0.66666666666666663</v>
+        <v>0.7</v>
       </c>
       <c r="F37" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G39</f>
-        <v>0.55555555555555558</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="G37" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H39</f>
@@ -2205,11 +2205,11 @@
       </c>
       <c r="E38" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F40</f>
-        <v>143.88888888888889</v>
+        <v>147.6</v>
       </c>
       <c r="F38" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G40</f>
-        <v>4.9189814814814881E-2</v>
+        <v>7.6249999999999929E-2</v>
       </c>
       <c r="G38" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H40</f>
@@ -2234,11 +2234,11 @@
       </c>
       <c r="E39" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F41</f>
-        <v>509.22222222222223</v>
+        <v>512.70000000000005</v>
       </c>
       <c r="F39" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G41</f>
-        <v>-8.1536831858913805E-2</v>
+        <v>-7.5264107188868778E-2</v>
       </c>
       <c r="G39" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H41</f>
@@ -2263,11 +2263,11 @@
       </c>
       <c r="E40" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F42</f>
-        <v>415.66666666666669</v>
+        <v>409.7</v>
       </c>
       <c r="F40" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G42</f>
-        <v>2.1297956256722843</v>
+        <v>2.0848691287199714</v>
       </c>
       <c r="G40" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H42</f>
@@ -2292,11 +2292,11 @@
       </c>
       <c r="E41" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F43</f>
-        <v>177.66666666666666</v>
+        <v>181.9</v>
       </c>
       <c r="F41" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G43</f>
-        <v>-0.40006431902235096</v>
+        <v>-0.38576941630487216</v>
       </c>
       <c r="G41" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H43</f>
@@ -2321,11 +2321,11 @@
       </c>
       <c r="E42" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F44</f>
-        <v>461.33333333333331</v>
+        <v>455.4</v>
       </c>
       <c r="F42" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G44</f>
-        <v>-0.12744303341439245</v>
+        <v>-0.13866522561469874</v>
       </c>
       <c r="G42" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H44</f>
@@ -2350,11 +2350,11 @@
       </c>
       <c r="E43" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F45</f>
-        <v>295.77777777777777</v>
+        <v>287.89999999999998</v>
       </c>
       <c r="F43" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G45</f>
-        <v>-3.2050283102176502E-2</v>
+        <v>-5.7830762038335704E-2</v>
       </c>
       <c r="G43" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H45</f>
@@ -2379,11 +2379,11 @@
       </c>
       <c r="E44" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F46</f>
-        <v>210.44444444444446</v>
+        <v>211.7</v>
       </c>
       <c r="F44" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G46</f>
-        <v>-0.27409110819097682</v>
+        <v>-0.26976018396846269</v>
       </c>
       <c r="G44" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H46</f>
@@ -2408,11 +2408,11 @@
       </c>
       <c r="E45" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F47</f>
-        <v>31.555555555555557</v>
+        <v>31.2</v>
       </c>
       <c r="F45" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G47</f>
-        <v>-0.45324532453245325</v>
+        <v>-0.45940594059405948</v>
       </c>
       <c r="G45" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H47</f>
@@ -2437,11 +2437,11 @@
       </c>
       <c r="E46" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F48</f>
-        <v>108.11111111111111</v>
+        <v>107</v>
       </c>
       <c r="F46" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G48</f>
-        <v>3.2438987418523579E-2</v>
+        <v>2.1828103683492639E-2</v>
       </c>
       <c r="G46" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H48</f>
@@ -2466,11 +2466,11 @@
       </c>
       <c r="E47" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F49</f>
-        <v>45.555555555555557</v>
+        <v>44.3</v>
       </c>
       <c r="F47" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G49</f>
-        <v>-7.6576576576576572E-2</v>
+        <v>-0.10202702702702715</v>
       </c>
       <c r="G47" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H49</f>
@@ -2495,11 +2495,11 @@
       </c>
       <c r="E48" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F50</f>
-        <v>65</v>
+        <v>61.8</v>
       </c>
       <c r="F48" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G50</f>
-        <v>0.17469879518072284</v>
+        <v>0.11686746987951802</v>
       </c>
       <c r="G48" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H50</f>

--- a/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
+++ b/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D547433-D1C6-474C-B2DB-CE7A42C9D6EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67A4F1FA-6E6B-402A-94F3-B3A5928C0D4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -368,6 +368,8 @@
       <sheetName val="INVENTARIO NACIONAL 10-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 11-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 14-09-26"/>
+      <sheetName val="INVENTARIO NACIONAL 15-09-26"/>
+      <sheetName val="INVENTARIO NACIONAL 16-09-26"/>
       <sheetName val="CCC"/>
       <sheetName val="VINCULO VTS BY SKU AGOSTO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
@@ -386,13 +388,15 @@
       <sheetData sheetId="9"/>
       <sheetData sheetId="10"/>
       <sheetData sheetId="11"/>
-      <sheetData sheetId="12">
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14">
         <row r="4">
           <cell r="F4">
-            <v>1215.3</v>
+            <v>1257.5454545454545</v>
           </cell>
           <cell r="G4">
-            <v>2.2897795591182435E-2</v>
+            <v>5.8455092002186237E-2</v>
           </cell>
           <cell r="H4" t="str">
             <v>SUBIÓ</v>
@@ -400,10 +404,10 @@
         </row>
         <row r="5">
           <cell r="F5">
-            <v>74.2</v>
+            <v>70.63636363636364</v>
           </cell>
           <cell r="G5">
-            <v>-2.8553615960099643E-2</v>
+            <v>-7.5209703015189255E-2</v>
           </cell>
           <cell r="H5" t="str">
             <v>BAJO</v>
@@ -411,21 +415,21 @@
         </row>
         <row r="6">
           <cell r="F6">
-            <v>484.6</v>
+            <v>511.63636363636363</v>
           </cell>
           <cell r="G6">
-            <v>-4.8826993176932398E-2</v>
+            <v>4.2399884441195468E-3</v>
           </cell>
           <cell r="H6" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="7">
           <cell r="F7">
-            <v>108</v>
+            <v>122.90909090909091</v>
           </cell>
           <cell r="G7">
-            <v>0.1020408163265305</v>
+            <v>0.25417439703153977</v>
           </cell>
           <cell r="H7" t="str">
             <v>SUBIÓ</v>
@@ -433,10 +437,10 @@
         </row>
         <row r="8">
           <cell r="F8">
-            <v>15.1</v>
+            <v>15.363636363636363</v>
           </cell>
           <cell r="G8">
-            <v>0.26334661354581668</v>
+            <v>0.28540383918869972</v>
           </cell>
           <cell r="H8" t="str">
             <v>SUBIÓ</v>
@@ -444,10 +448,10 @@
         </row>
         <row r="9">
           <cell r="F9">
-            <v>1477.3</v>
+            <v>1460.5454545454545</v>
           </cell>
           <cell r="G9">
-            <v>1.1618351974435059E-2</v>
+            <v>1.4525533813380953E-4</v>
           </cell>
           <cell r="H9" t="str">
             <v>SUBIÓ</v>
@@ -455,10 +459,10 @@
         </row>
         <row r="10">
           <cell r="F10">
-            <v>136.9</v>
+            <v>146.18181818181819</v>
           </cell>
           <cell r="G10">
-            <v>-8.9645345155161427E-2</v>
+            <v>-2.7923311647187421E-2</v>
           </cell>
           <cell r="H10" t="str">
             <v>BAJO</v>
@@ -466,10 +470,10 @@
         </row>
         <row r="11">
           <cell r="F11">
-            <v>268.7</v>
+            <v>278.72727272727275</v>
           </cell>
           <cell r="G11">
-            <v>-0.21792099792099795</v>
+            <v>-0.1887355887355886</v>
           </cell>
           <cell r="H11" t="str">
             <v>BAJO</v>
@@ -477,10 +481,10 @@
         </row>
         <row r="12">
           <cell r="F12">
-            <v>687.6</v>
+            <v>731.81818181818187</v>
           </cell>
           <cell r="G12">
-            <v>-0.10257302672467361</v>
+            <v>-4.4861291598395248E-2</v>
           </cell>
           <cell r="H12" t="str">
             <v>BAJO</v>
@@ -488,10 +492,10 @@
         </row>
         <row r="13">
           <cell r="F13">
-            <v>320</v>
+            <v>355.27272727272725</v>
           </cell>
           <cell r="G13">
-            <v>-0.11799448746554664</v>
+            <v>-2.0773425288453495E-2</v>
           </cell>
           <cell r="H13" t="str">
             <v>BAJO</v>
@@ -499,21 +503,21 @@
         </row>
         <row r="14">
           <cell r="F14">
-            <v>3476.1</v>
+            <v>3541.4545454545455</v>
           </cell>
           <cell r="G14">
-            <v>-1.2898907399394255E-2</v>
+            <v>5.6596908068131668E-3</v>
           </cell>
           <cell r="H14" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="15">
           <cell r="F15">
-            <v>2130.4</v>
+            <v>2175.181818181818</v>
           </cell>
           <cell r="G15">
-            <v>-7.574837310195226E-2</v>
+            <v>-5.6320252415697158E-2</v>
           </cell>
           <cell r="H15" t="str">
             <v>BAJO</v>
@@ -521,10 +525,10 @@
         </row>
         <row r="16">
           <cell r="F16">
-            <v>2189.3000000000002</v>
+            <v>2220.4545454545455</v>
           </cell>
           <cell r="G16">
-            <v>-3.4051180771493272E-2</v>
+            <v>-2.0305373255200876E-2</v>
           </cell>
           <cell r="H16" t="str">
             <v>BAJO</v>
@@ -532,21 +536,21 @@
         </row>
         <row r="17">
           <cell r="F17">
-            <v>2655.4</v>
+            <v>2708.7272727272725</v>
           </cell>
           <cell r="G17">
-            <v>-6.9558713537770656E-3</v>
+            <v>1.298701298701288E-2</v>
           </cell>
           <cell r="H17" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="18">
           <cell r="F18">
-            <v>669.2</v>
+            <v>704.90909090909088</v>
           </cell>
           <cell r="G18">
-            <v>0.7194665361556345</v>
+            <v>0.81121875799472742</v>
           </cell>
           <cell r="H18" t="str">
             <v>SUBIÓ</v>
@@ -554,10 +558,10 @@
         </row>
         <row r="19">
           <cell r="F19">
-            <v>806.4</v>
+            <v>853</v>
           </cell>
           <cell r="G19">
-            <v>0.88243663850600251</v>
+            <v>0.9912183192530013</v>
           </cell>
           <cell r="H19" t="str">
             <v>SUBIÓ</v>
@@ -565,10 +569,10 @@
         </row>
         <row r="20">
           <cell r="F20">
-            <v>795</v>
+            <v>865.90909090909088</v>
           </cell>
           <cell r="G20">
-            <v>1.034486960760419</v>
+            <v>1.215950634790508</v>
           </cell>
           <cell r="H20" t="str">
             <v>SUBIÓ</v>
@@ -576,10 +580,10 @@
         </row>
         <row r="21">
           <cell r="F21">
-            <v>249.8</v>
+            <v>257</v>
           </cell>
           <cell r="G21">
-            <v>3.2231404958677823E-2</v>
+            <v>6.198347107438007E-2</v>
           </cell>
           <cell r="H21" t="str">
             <v>SUBIÓ</v>
@@ -587,10 +591,10 @@
         </row>
         <row r="22">
           <cell r="F22">
-            <v>121</v>
+            <v>124.09090909090909</v>
           </cell>
           <cell r="G22">
-            <v>-0.14902880107166783</v>
+            <v>-0.12729099433721003</v>
           </cell>
           <cell r="H22" t="str">
             <v>BAJO</v>
@@ -598,32 +602,32 @@
         </row>
         <row r="23">
           <cell r="F23">
-            <v>491.8</v>
+            <v>513.5454545454545</v>
           </cell>
           <cell r="G23">
-            <v>-4.1503480278422211E-2</v>
+            <v>8.7745201434286102E-4</v>
           </cell>
           <cell r="H23" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="24">
           <cell r="F24">
-            <v>807.7</v>
+            <v>852.81818181818187</v>
           </cell>
           <cell r="G24">
-            <v>-4.5366512119255908E-3</v>
+            <v>5.1070005175293032E-2</v>
           </cell>
           <cell r="H24" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="25">
           <cell r="F25">
-            <v>62</v>
+            <v>57.272727272727273</v>
           </cell>
           <cell r="G25">
-            <v>-0.1728081321473951</v>
+            <v>-0.23587847984290167</v>
           </cell>
           <cell r="H25" t="str">
             <v>BAJO</v>
@@ -631,10 +635,10 @@
         </row>
         <row r="26">
           <cell r="F26">
-            <v>705.3</v>
+            <v>719.09090909090912</v>
           </cell>
           <cell r="G26">
-            <v>-0.10489514715658432</v>
+            <v>-8.7392935824675666E-2</v>
           </cell>
           <cell r="H26" t="str">
             <v>BAJO</v>
@@ -642,10 +646,10 @@
         </row>
         <row r="27">
           <cell r="F27">
-            <v>1106.8</v>
+            <v>1127.6363636363637</v>
           </cell>
           <cell r="G27">
-            <v>-0.13104531179901313</v>
+            <v>-0.11468656959908641</v>
           </cell>
           <cell r="H27" t="str">
             <v>BAJO</v>
@@ -653,32 +657,32 @@
         </row>
         <row r="28">
           <cell r="F28">
-            <v>517.1</v>
+            <v>567.81818181818187</v>
           </cell>
           <cell r="G28">
-            <v>-2.2847115990281552E-2</v>
+            <v>7.2993954664070992E-2</v>
           </cell>
           <cell r="H28" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="29">
           <cell r="F29">
-            <v>386.6</v>
+            <v>433.36363636363637</v>
           </cell>
           <cell r="G29">
-            <v>-3.7966583718449964E-2</v>
+            <v>7.8402223443105212E-2</v>
           </cell>
           <cell r="H29" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="30">
           <cell r="F30">
-            <v>236.1</v>
+            <v>228.09090909090909</v>
           </cell>
           <cell r="G30">
-            <v>2.1026908635794741</v>
+            <v>1.9974399817954258</v>
           </cell>
           <cell r="H30" t="str">
             <v>SUBIÓ</v>
@@ -686,10 +690,10 @@
         </row>
         <row r="31">
           <cell r="F31">
-            <v>283.89999999999998</v>
+            <v>275</v>
           </cell>
           <cell r="G31">
-            <v>2.9378467635402901</v>
+            <v>2.8143989431968293</v>
           </cell>
           <cell r="H31" t="str">
             <v>SUBIÓ</v>
@@ -697,21 +701,21 @@
         </row>
         <row r="32">
           <cell r="F32">
-            <v>127.4</v>
+            <v>139.54545454545453</v>
           </cell>
           <cell r="G32">
-            <v>-3.5754189944133818E-3</v>
+            <v>9.1416962925342737E-2</v>
           </cell>
           <cell r="H32" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="33">
           <cell r="F33">
-            <v>129.9</v>
+            <v>139.27272727272728</v>
           </cell>
           <cell r="G33">
-            <v>-9.3720930232558119E-2</v>
+            <v>-2.8329809725158528E-2</v>
           </cell>
           <cell r="H33" t="str">
             <v>BAJO</v>
@@ -719,10 +723,10 @@
         </row>
         <row r="34">
           <cell r="F34">
-            <v>749.3</v>
+            <v>761.5454545454545</v>
           </cell>
           <cell r="G34">
-            <v>0.14889748831775695</v>
+            <v>0.16767337510620228</v>
           </cell>
           <cell r="H34" t="str">
             <v>SUBIÓ</v>
@@ -730,10 +734,10 @@
         </row>
         <row r="35">
           <cell r="F35">
-            <v>578.9</v>
+            <v>606.81818181818187</v>
           </cell>
           <cell r="G35">
-            <v>-7.9719909159727487E-2</v>
+            <v>-3.533824237836336E-2</v>
           </cell>
           <cell r="H35" t="str">
             <v>BAJO</v>
@@ -741,10 +745,10 @@
         </row>
         <row r="36">
           <cell r="F36">
-            <v>771.8</v>
+            <v>799.63636363636363</v>
           </cell>
           <cell r="G36">
-            <v>-9.4333929369691538E-2</v>
+            <v>-6.1669443654244649E-2</v>
           </cell>
           <cell r="H36" t="str">
             <v>BAJO</v>
@@ -752,10 +756,10 @@
         </row>
         <row r="37">
           <cell r="F37">
-            <v>493.6</v>
+            <v>529.90909090909088</v>
           </cell>
           <cell r="G37">
-            <v>-0.14749568221070808</v>
+            <v>-8.4785680640602989E-2</v>
           </cell>
           <cell r="H37" t="str">
             <v>BAJO</v>
@@ -763,10 +767,10 @@
         </row>
         <row r="38">
           <cell r="F38">
-            <v>4.8</v>
+            <v>4.6363636363636367</v>
           </cell>
           <cell r="G38">
-            <v>0.93846153846153824</v>
+            <v>0.87237762237762251</v>
           </cell>
           <cell r="H38" t="str">
             <v>SUBIÓ</v>
@@ -774,10 +778,10 @@
         </row>
         <row r="39">
           <cell r="F39">
-            <v>0.7</v>
+            <v>0.63636363636363635</v>
           </cell>
           <cell r="G39">
-            <v>0.6333333333333333</v>
+            <v>0.48484848484848486</v>
           </cell>
           <cell r="H39" t="str">
             <v>SUBIÓ</v>
@@ -785,10 +789,10 @@
         </row>
         <row r="40">
           <cell r="F40">
-            <v>147.6</v>
+            <v>151.54545454545453</v>
           </cell>
           <cell r="G40">
-            <v>7.6249999999999929E-2</v>
+            <v>0.10501893939393936</v>
           </cell>
           <cell r="H40" t="str">
             <v>SUBIÓ</v>
@@ -796,10 +800,10 @@
         </row>
         <row r="41">
           <cell r="F41">
-            <v>512.70000000000005</v>
+            <v>533.4545454545455</v>
           </cell>
           <cell r="G41">
-            <v>-7.5264107188868778E-2</v>
+            <v>-3.7829987585205282E-2</v>
           </cell>
           <cell r="H41" t="str">
             <v>BAJO</v>
@@ -807,10 +811,10 @@
         </row>
         <row r="42">
           <cell r="F42">
-            <v>409.7</v>
+            <v>417.09090909090907</v>
           </cell>
           <cell r="G42">
-            <v>2.0848691287199714</v>
+            <v>2.140519573649728</v>
           </cell>
           <cell r="H42" t="str">
             <v>SUBIÓ</v>
@@ -818,10 +822,10 @@
         </row>
         <row r="43">
           <cell r="F43">
-            <v>181.9</v>
+            <v>189.81818181818181</v>
           </cell>
           <cell r="G43">
-            <v>-0.38576941630487216</v>
+            <v>-0.35903170635442716</v>
           </cell>
           <cell r="H43" t="str">
             <v>BAJO</v>
@@ -829,10 +833,10 @@
         </row>
         <row r="44">
           <cell r="F44">
-            <v>455.4</v>
+            <v>464.09090909090907</v>
           </cell>
           <cell r="G44">
-            <v>-0.13866522561469874</v>
+            <v>-0.1222274078258947</v>
           </cell>
           <cell r="H44" t="str">
             <v>BAJO</v>
@@ -840,10 +844,10 @@
         </row>
         <row r="45">
           <cell r="F45">
-            <v>287.89999999999998</v>
+            <v>292.54545454545456</v>
           </cell>
           <cell r="G45">
-            <v>-5.7830762038335704E-2</v>
+            <v>-4.2628245994304814E-2</v>
           </cell>
           <cell r="H45" t="str">
             <v>BAJO</v>
@@ -851,10 +855,10 @@
         </row>
         <row r="46">
           <cell r="F46">
-            <v>211.7</v>
+            <v>219.72727272727272</v>
           </cell>
           <cell r="G46">
-            <v>-0.26976018396846269</v>
+            <v>-0.24207083980408561</v>
           </cell>
           <cell r="H46" t="str">
             <v>BAJO</v>
@@ -862,10 +866,10 @@
         </row>
         <row r="47">
           <cell r="F47">
-            <v>31.2</v>
+            <v>36.363636363636367</v>
           </cell>
           <cell r="G47">
-            <v>-0.45940594059405948</v>
+            <v>-0.36993699369936994</v>
           </cell>
           <cell r="H47" t="str">
             <v>BAJO</v>
@@ -873,10 +877,10 @@
         </row>
         <row r="48">
           <cell r="F48">
-            <v>107</v>
+            <v>110.72727272727273</v>
           </cell>
           <cell r="G48">
-            <v>2.1828103683492639E-2</v>
+            <v>5.7422795485551514E-2</v>
           </cell>
           <cell r="H48" t="str">
             <v>SUBIÓ</v>
@@ -884,10 +888,10 @@
         </row>
         <row r="49">
           <cell r="F49">
-            <v>44.3</v>
+            <v>45.81818181818182</v>
           </cell>
           <cell r="G49">
-            <v>-0.10202702702702715</v>
+            <v>-7.1253071253071232E-2</v>
           </cell>
           <cell r="H49" t="str">
             <v>BAJO</v>
@@ -895,10 +899,10 @@
         </row>
         <row r="50">
           <cell r="F50">
-            <v>61.8</v>
+            <v>61.18181818181818</v>
           </cell>
           <cell r="G50">
-            <v>0.11686746987951802</v>
+            <v>0.10569550930996696</v>
           </cell>
           <cell r="H50" t="str">
             <v>SUBIÓ</v>
@@ -1161,11 +1165,11 @@
       </c>
       <c r="E2" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F4</f>
-        <v>1215.3</v>
+        <v>1257.5454545454545</v>
       </c>
       <c r="F2" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G4</f>
-        <v>2.2897795591182435E-2</v>
+        <v>5.8455092002186237E-2</v>
       </c>
       <c r="G2" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H4</f>
@@ -1190,11 +1194,11 @@
       </c>
       <c r="E3" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F5</f>
-        <v>74.2</v>
+        <v>70.63636363636364</v>
       </c>
       <c r="F3" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G5</f>
-        <v>-2.8553615960099643E-2</v>
+        <v>-7.5209703015189255E-2</v>
       </c>
       <c r="G3" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H5</f>
@@ -1219,15 +1223,15 @@
       </c>
       <c r="E4" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F6</f>
-        <v>484.6</v>
+        <v>511.63636363636363</v>
       </c>
       <c r="F4" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G6</f>
-        <v>-4.8826993176932398E-2</v>
+        <v>4.2399884441195468E-3</v>
       </c>
       <c r="G4" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H6</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H4">
         <v>2.0299999999999998</v>
@@ -1248,11 +1252,11 @@
       </c>
       <c r="E5" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F7</f>
-        <v>108</v>
+        <v>122.90909090909091</v>
       </c>
       <c r="F5" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G7</f>
-        <v>0.1020408163265305</v>
+        <v>0.25417439703153977</v>
       </c>
       <c r="G5" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H7</f>
@@ -1277,11 +1281,11 @@
       </c>
       <c r="E6" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F8</f>
-        <v>15.1</v>
+        <v>15.363636363636363</v>
       </c>
       <c r="F6" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G8</f>
-        <v>0.26334661354581668</v>
+        <v>0.28540383918869972</v>
       </c>
       <c r="G6" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H8</f>
@@ -1306,11 +1310,11 @@
       </c>
       <c r="E7" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F9</f>
-        <v>1477.3</v>
+        <v>1460.5454545454545</v>
       </c>
       <c r="F7" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G9</f>
-        <v>1.1618351974435059E-2</v>
+        <v>1.4525533813380953E-4</v>
       </c>
       <c r="G7" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H9</f>
@@ -1335,11 +1339,11 @@
       </c>
       <c r="E8" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F10</f>
-        <v>136.9</v>
+        <v>146.18181818181819</v>
       </c>
       <c r="F8" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G10</f>
-        <v>-8.9645345155161427E-2</v>
+        <v>-2.7923311647187421E-2</v>
       </c>
       <c r="G8" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H10</f>
@@ -1364,11 +1368,11 @@
       </c>
       <c r="E9" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F11</f>
-        <v>268.7</v>
+        <v>278.72727272727275</v>
       </c>
       <c r="F9" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G11</f>
-        <v>-0.21792099792099795</v>
+        <v>-0.1887355887355886</v>
       </c>
       <c r="G9" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H11</f>
@@ -1393,11 +1397,11 @@
       </c>
       <c r="E10" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F12</f>
-        <v>687.6</v>
+        <v>731.81818181818187</v>
       </c>
       <c r="F10" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G12</f>
-        <v>-0.10257302672467361</v>
+        <v>-4.4861291598395248E-2</v>
       </c>
       <c r="G10" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H12</f>
@@ -1422,11 +1426,11 @@
       </c>
       <c r="E11" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F13</f>
-        <v>320</v>
+        <v>355.27272727272725</v>
       </c>
       <c r="F11" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G13</f>
-        <v>-0.11799448746554664</v>
+        <v>-2.0773425288453495E-2</v>
       </c>
       <c r="G11" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H13</f>
@@ -1451,15 +1455,15 @@
       </c>
       <c r="E12" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F14</f>
-        <v>3476.1</v>
+        <v>3541.4545454545455</v>
       </c>
       <c r="F12" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G14</f>
-        <v>-1.2898907399394255E-2</v>
+        <v>5.6596908068131668E-3</v>
       </c>
       <c r="G12" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H14</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H12">
         <v>1.1599999999999999</v>
@@ -1480,11 +1484,11 @@
       </c>
       <c r="E13" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F15</f>
-        <v>2130.4</v>
+        <v>2175.181818181818</v>
       </c>
       <c r="F13" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G15</f>
-        <v>-7.574837310195226E-2</v>
+        <v>-5.6320252415697158E-2</v>
       </c>
       <c r="G13" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H15</f>
@@ -1509,11 +1513,11 @@
       </c>
       <c r="E14" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F16</f>
-        <v>2189.3000000000002</v>
+        <v>2220.4545454545455</v>
       </c>
       <c r="F14" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G16</f>
-        <v>-3.4051180771493272E-2</v>
+        <v>-2.0305373255200876E-2</v>
       </c>
       <c r="G14" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H16</f>
@@ -1538,15 +1542,15 @@
       </c>
       <c r="E15" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F17</f>
-        <v>2655.4</v>
+        <v>2708.7272727272725</v>
       </c>
       <c r="F15" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G17</f>
-        <v>-6.9558713537770656E-3</v>
+        <v>1.298701298701288E-2</v>
       </c>
       <c r="G15" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H17</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H15">
         <v>1.1599999999999999</v>
@@ -1567,11 +1571,11 @@
       </c>
       <c r="E16" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F18</f>
-        <v>669.2</v>
+        <v>704.90909090909088</v>
       </c>
       <c r="F16" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G18</f>
-        <v>0.7194665361556345</v>
+        <v>0.81121875799472742</v>
       </c>
       <c r="G16" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H18</f>
@@ -1596,11 +1600,11 @@
       </c>
       <c r="E17" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F19</f>
-        <v>806.4</v>
+        <v>853</v>
       </c>
       <c r="F17" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G19</f>
-        <v>0.88243663850600251</v>
+        <v>0.9912183192530013</v>
       </c>
       <c r="G17" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H19</f>
@@ -1625,11 +1629,11 @@
       </c>
       <c r="E18" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F20</f>
-        <v>795</v>
+        <v>865.90909090909088</v>
       </c>
       <c r="F18" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G20</f>
-        <v>1.034486960760419</v>
+        <v>1.215950634790508</v>
       </c>
       <c r="G18" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H20</f>
@@ -1654,11 +1658,11 @@
       </c>
       <c r="E19" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F21</f>
-        <v>249.8</v>
+        <v>257</v>
       </c>
       <c r="F19" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G21</f>
-        <v>3.2231404958677823E-2</v>
+        <v>6.198347107438007E-2</v>
       </c>
       <c r="G19" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H21</f>
@@ -1683,11 +1687,11 @@
       </c>
       <c r="E20" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F22</f>
-        <v>121</v>
+        <v>124.09090909090909</v>
       </c>
       <c r="F20" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G22</f>
-        <v>-0.14902880107166783</v>
+        <v>-0.12729099433721003</v>
       </c>
       <c r="G20" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H22</f>
@@ -1712,15 +1716,15 @@
       </c>
       <c r="E21" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F23</f>
-        <v>491.8</v>
+        <v>513.5454545454545</v>
       </c>
       <c r="F21" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G23</f>
-        <v>-4.1503480278422211E-2</v>
+        <v>8.7745201434286102E-4</v>
       </c>
       <c r="G21" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H23</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H21">
         <v>4.1500000000000004</v>
@@ -1741,15 +1745,15 @@
       </c>
       <c r="E22" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F24</f>
-        <v>807.7</v>
+        <v>852.81818181818187</v>
       </c>
       <c r="F22" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G24</f>
-        <v>-4.5366512119255908E-3</v>
+        <v>5.1070005175293032E-2</v>
       </c>
       <c r="G22" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H24</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H22">
         <v>4.1500000000000004</v>
@@ -1770,11 +1774,11 @@
       </c>
       <c r="E23" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F25</f>
-        <v>62</v>
+        <v>57.272727272727273</v>
       </c>
       <c r="F23" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G25</f>
-        <v>-0.1728081321473951</v>
+        <v>-0.23587847984290167</v>
       </c>
       <c r="G23" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H25</f>
@@ -1799,11 +1803,11 @@
       </c>
       <c r="E24" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F26</f>
-        <v>705.3</v>
+        <v>719.09090909090912</v>
       </c>
       <c r="F24" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G26</f>
-        <v>-0.10489514715658432</v>
+        <v>-8.7392935824675666E-2</v>
       </c>
       <c r="G24" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H26</f>
@@ -1828,11 +1832,11 @@
       </c>
       <c r="E25" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F27</f>
-        <v>1106.8</v>
+        <v>1127.6363636363637</v>
       </c>
       <c r="F25" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G27</f>
-        <v>-0.13104531179901313</v>
+        <v>-0.11468656959908641</v>
       </c>
       <c r="G25" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H27</f>
@@ -1857,15 +1861,15 @@
       </c>
       <c r="E26" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F28</f>
-        <v>517.1</v>
+        <v>567.81818181818187</v>
       </c>
       <c r="F26" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G28</f>
-        <v>-2.2847115990281552E-2</v>
+        <v>7.2993954664070992E-2</v>
       </c>
       <c r="G26" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H28</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H26">
         <v>1.63</v>
@@ -1886,15 +1890,15 @@
       </c>
       <c r="E27" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F29</f>
-        <v>386.6</v>
+        <v>433.36363636363637</v>
       </c>
       <c r="F27" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G29</f>
-        <v>-3.7966583718449964E-2</v>
+        <v>7.8402223443105212E-2</v>
       </c>
       <c r="G27" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H29</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H27">
         <v>1.63</v>
@@ -1915,11 +1919,11 @@
       </c>
       <c r="E28" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F30</f>
-        <v>236.1</v>
+        <v>228.09090909090909</v>
       </c>
       <c r="F28" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G30</f>
-        <v>2.1026908635794741</v>
+        <v>1.9974399817954258</v>
       </c>
       <c r="G28" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H30</f>
@@ -1944,11 +1948,11 @@
       </c>
       <c r="E29" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F31</f>
-        <v>283.89999999999998</v>
+        <v>275</v>
       </c>
       <c r="F29" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G31</f>
-        <v>2.9378467635402901</v>
+        <v>2.8143989431968293</v>
       </c>
       <c r="G29" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H31</f>
@@ -1973,15 +1977,15 @@
       </c>
       <c r="E30" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F32</f>
-        <v>127.4</v>
+        <v>139.54545454545453</v>
       </c>
       <c r="F30" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G32</f>
-        <v>-3.5754189944133818E-3</v>
+        <v>9.1416962925342737E-2</v>
       </c>
       <c r="G30" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H32</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H30">
         <v>6.15</v>
@@ -2002,11 +2006,11 @@
       </c>
       <c r="E31" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F33</f>
-        <v>129.9</v>
+        <v>139.27272727272728</v>
       </c>
       <c r="F31" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G33</f>
-        <v>-9.3720930232558119E-2</v>
+        <v>-2.8329809725158528E-2</v>
       </c>
       <c r="G31" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H33</f>
@@ -2031,11 +2035,11 @@
       </c>
       <c r="E32" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F34</f>
-        <v>749.3</v>
+        <v>761.5454545454545</v>
       </c>
       <c r="F32" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G34</f>
-        <v>0.14889748831775695</v>
+        <v>0.16767337510620228</v>
       </c>
       <c r="G32" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H34</f>
@@ -2060,11 +2064,11 @@
       </c>
       <c r="E33" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F35</f>
-        <v>578.9</v>
+        <v>606.81818181818187</v>
       </c>
       <c r="F33" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G35</f>
-        <v>-7.9719909159727487E-2</v>
+        <v>-3.533824237836336E-2</v>
       </c>
       <c r="G33" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H35</f>
@@ -2089,11 +2093,11 @@
       </c>
       <c r="E34" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F36</f>
-        <v>771.8</v>
+        <v>799.63636363636363</v>
       </c>
       <c r="F34" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G36</f>
-        <v>-9.4333929369691538E-2</v>
+        <v>-6.1669443654244649E-2</v>
       </c>
       <c r="G34" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H36</f>
@@ -2118,11 +2122,11 @@
       </c>
       <c r="E35" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F37</f>
-        <v>493.6</v>
+        <v>529.90909090909088</v>
       </c>
       <c r="F35" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G37</f>
-        <v>-0.14749568221070808</v>
+        <v>-8.4785680640602989E-2</v>
       </c>
       <c r="G35" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H37</f>
@@ -2147,11 +2151,11 @@
       </c>
       <c r="E36" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F38</f>
-        <v>4.8</v>
+        <v>4.6363636363636367</v>
       </c>
       <c r="F36" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G38</f>
-        <v>0.93846153846153824</v>
+        <v>0.87237762237762251</v>
       </c>
       <c r="G36" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H38</f>
@@ -2176,11 +2180,11 @@
       </c>
       <c r="E37" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F39</f>
-        <v>0.7</v>
+        <v>0.63636363636363635</v>
       </c>
       <c r="F37" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G39</f>
-        <v>0.6333333333333333</v>
+        <v>0.48484848484848486</v>
       </c>
       <c r="G37" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H39</f>
@@ -2205,11 +2209,11 @@
       </c>
       <c r="E38" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F40</f>
-        <v>147.6</v>
+        <v>151.54545454545453</v>
       </c>
       <c r="F38" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G40</f>
-        <v>7.6249999999999929E-2</v>
+        <v>0.10501893939393936</v>
       </c>
       <c r="G38" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H40</f>
@@ -2234,11 +2238,11 @@
       </c>
       <c r="E39" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F41</f>
-        <v>512.70000000000005</v>
+        <v>533.4545454545455</v>
       </c>
       <c r="F39" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G41</f>
-        <v>-7.5264107188868778E-2</v>
+        <v>-3.7829987585205282E-2</v>
       </c>
       <c r="G39" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H41</f>
@@ -2263,11 +2267,11 @@
       </c>
       <c r="E40" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F42</f>
-        <v>409.7</v>
+        <v>417.09090909090907</v>
       </c>
       <c r="F40" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G42</f>
-        <v>2.0848691287199714</v>
+        <v>2.140519573649728</v>
       </c>
       <c r="G40" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H42</f>
@@ -2292,11 +2296,11 @@
       </c>
       <c r="E41" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F43</f>
-        <v>181.9</v>
+        <v>189.81818181818181</v>
       </c>
       <c r="F41" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G43</f>
-        <v>-0.38576941630487216</v>
+        <v>-0.35903170635442716</v>
       </c>
       <c r="G41" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H43</f>
@@ -2321,11 +2325,11 @@
       </c>
       <c r="E42" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F44</f>
-        <v>455.4</v>
+        <v>464.09090909090907</v>
       </c>
       <c r="F42" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G44</f>
-        <v>-0.13866522561469874</v>
+        <v>-0.1222274078258947</v>
       </c>
       <c r="G42" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H44</f>
@@ -2350,11 +2354,11 @@
       </c>
       <c r="E43" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F45</f>
-        <v>287.89999999999998</v>
+        <v>292.54545454545456</v>
       </c>
       <c r="F43" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G45</f>
-        <v>-5.7830762038335704E-2</v>
+        <v>-4.2628245994304814E-2</v>
       </c>
       <c r="G43" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H45</f>
@@ -2379,11 +2383,11 @@
       </c>
       <c r="E44" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F46</f>
-        <v>211.7</v>
+        <v>219.72727272727272</v>
       </c>
       <c r="F44" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G46</f>
-        <v>-0.26976018396846269</v>
+        <v>-0.24207083980408561</v>
       </c>
       <c r="G44" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H46</f>
@@ -2408,11 +2412,11 @@
       </c>
       <c r="E45" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F47</f>
-        <v>31.2</v>
+        <v>36.363636363636367</v>
       </c>
       <c r="F45" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G47</f>
-        <v>-0.45940594059405948</v>
+        <v>-0.36993699369936994</v>
       </c>
       <c r="G45" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H47</f>
@@ -2437,11 +2441,11 @@
       </c>
       <c r="E46" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F48</f>
-        <v>107</v>
+        <v>110.72727272727273</v>
       </c>
       <c r="F46" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G48</f>
-        <v>2.1828103683492639E-2</v>
+        <v>5.7422795485551514E-2</v>
       </c>
       <c r="G46" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H48</f>
@@ -2466,11 +2470,11 @@
       </c>
       <c r="E47" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F49</f>
-        <v>44.3</v>
+        <v>45.81818181818182</v>
       </c>
       <c r="F47" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G49</f>
-        <v>-0.10202702702702715</v>
+        <v>-7.1253071253071232E-2</v>
       </c>
       <c r="G47" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H49</f>
@@ -2495,11 +2499,11 @@
       </c>
       <c r="E48" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F50</f>
-        <v>61.8</v>
+        <v>61.18181818181818</v>
       </c>
       <c r="F48" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G50</f>
-        <v>0.11686746987951802</v>
+        <v>0.10569550930996696</v>
       </c>
       <c r="G48" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H50</f>

--- a/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
+++ b/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67A4F1FA-6E6B-402A-94F3-B3A5928C0D4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{803DD141-6C99-4077-A6CA-5D34B0F78172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -370,6 +370,7 @@
       <sheetName val="INVENTARIO NACIONAL 14-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 15-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 16-09-26"/>
+      <sheetName val="INVENTARIO NACIONAL 17-09-26"/>
       <sheetName val="CCC"/>
       <sheetName val="VINCULO VTS BY SKU AGOSTO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
@@ -390,13 +391,14 @@
       <sheetData sheetId="11"/>
       <sheetData sheetId="12"/>
       <sheetData sheetId="13"/>
-      <sheetData sheetId="14">
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15">
         <row r="4">
           <cell r="F4">
-            <v>1257.5454545454545</v>
+            <v>1236.8333333333333</v>
           </cell>
           <cell r="G4">
-            <v>5.8455092002186237E-2</v>
+            <v>4.1022044088176335E-2</v>
           </cell>
           <cell r="H4" t="str">
             <v>SUBIÓ</v>
@@ -404,10 +406,10 @@
         </row>
         <row r="5">
           <cell r="F5">
-            <v>70.63636363636364</v>
+            <v>66.75</v>
           </cell>
           <cell r="G5">
-            <v>-7.5209703015189255E-2</v>
+            <v>-0.12609102244389025</v>
           </cell>
           <cell r="H5" t="str">
             <v>BAJO</v>
@@ -415,21 +417,21 @@
         </row>
         <row r="6">
           <cell r="F6">
-            <v>511.63636363636363</v>
+            <v>495.08333333333331</v>
           </cell>
           <cell r="G6">
-            <v>4.2399884441195468E-3</v>
+            <v>-2.825030376670723E-2</v>
           </cell>
           <cell r="H6" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="7">
           <cell r="F7">
-            <v>122.90909090909091</v>
+            <v>119.91666666666667</v>
           </cell>
           <cell r="G7">
-            <v>0.25417439703153977</v>
+            <v>0.22363945578231292</v>
           </cell>
           <cell r="H7" t="str">
             <v>SUBIÓ</v>
@@ -437,10 +439,10 @@
         </row>
         <row r="8">
           <cell r="F8">
-            <v>15.363636363636363</v>
+            <v>15.416666666666666</v>
           </cell>
           <cell r="G8">
-            <v>0.28540383918869972</v>
+            <v>0.28984063745019917</v>
           </cell>
           <cell r="H8" t="str">
             <v>SUBIÓ</v>
@@ -448,21 +450,21 @@
         </row>
         <row r="9">
           <cell r="F9">
-            <v>1460.5454545454545</v>
+            <v>1430.3333333333333</v>
           </cell>
           <cell r="G9">
-            <v>1.4525533813380953E-4</v>
+            <v>-2.054325496461995E-2</v>
           </cell>
           <cell r="H9" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="10">
           <cell r="F10">
-            <v>146.18181818181819</v>
+            <v>147.33333333333334</v>
           </cell>
           <cell r="G10">
-            <v>-2.7923311647187421E-2</v>
+            <v>-2.0265991133628813E-2</v>
           </cell>
           <cell r="H10" t="str">
             <v>BAJO</v>
@@ -470,10 +472,10 @@
         </row>
         <row r="11">
           <cell r="F11">
-            <v>278.72727272727275</v>
+            <v>285.33333333333331</v>
           </cell>
           <cell r="G11">
-            <v>-0.1887355887355886</v>
+            <v>-0.16950796950796954</v>
           </cell>
           <cell r="H11" t="str">
             <v>BAJO</v>
@@ -481,10 +483,10 @@
         </row>
         <row r="12">
           <cell r="F12">
-            <v>731.81818181818187</v>
+            <v>738.41666666666663</v>
           </cell>
           <cell r="G12">
-            <v>-4.4861291598395248E-2</v>
+            <v>-3.6249223119950269E-2</v>
           </cell>
           <cell r="H12" t="str">
             <v>BAJO</v>
@@ -492,10 +494,10 @@
         </row>
         <row r="13">
           <cell r="F13">
-            <v>355.27272727272725</v>
+            <v>349.91666666666669</v>
           </cell>
           <cell r="G13">
-            <v>-2.0773425288453495E-2</v>
+            <v>-3.553615960099743E-2</v>
           </cell>
           <cell r="H13" t="str">
             <v>BAJO</v>
@@ -503,21 +505,21 @@
         </row>
         <row r="14">
           <cell r="F14">
-            <v>3541.4545454545455</v>
+            <v>3468.3333333333335</v>
           </cell>
           <cell r="G14">
-            <v>5.6596908068131668E-3</v>
+            <v>-1.5104392038078784E-2</v>
           </cell>
           <cell r="H14" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="15">
           <cell r="F15">
-            <v>2175.181818181818</v>
+            <v>2143</v>
           </cell>
           <cell r="G15">
-            <v>-5.6320252415697158E-2</v>
+            <v>-7.0281995661605201E-2</v>
           </cell>
           <cell r="H15" t="str">
             <v>BAJO</v>
@@ -525,10 +527,10 @@
         </row>
         <row r="16">
           <cell r="F16">
-            <v>2220.4545454545455</v>
+            <v>2182.6666666666665</v>
           </cell>
           <cell r="G16">
-            <v>-2.0305373255200876E-2</v>
+            <v>-3.6977897302294283E-2</v>
           </cell>
           <cell r="H16" t="str">
             <v>BAJO</v>
@@ -536,21 +538,21 @@
         </row>
         <row r="17">
           <cell r="F17">
-            <v>2708.7272727272725</v>
+            <v>2656.75</v>
           </cell>
           <cell r="G17">
-            <v>1.298701298701288E-2</v>
+            <v>-6.4510097232610697E-3</v>
           </cell>
           <cell r="H17" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="18">
           <cell r="F18">
-            <v>704.90909090909088</v>
+            <v>704</v>
           </cell>
           <cell r="G18">
-            <v>0.81121875799472742</v>
+            <v>0.80888290713324351</v>
           </cell>
           <cell r="H18" t="str">
             <v>SUBIÓ</v>
@@ -558,10 +560,10 @@
         </row>
         <row r="19">
           <cell r="F19">
-            <v>853</v>
+            <v>819.25</v>
           </cell>
           <cell r="G19">
-            <v>0.9912183192530013</v>
+            <v>0.912433303690529</v>
           </cell>
           <cell r="H19" t="str">
             <v>SUBIÓ</v>
@@ -569,10 +571,10 @@
         </row>
         <row r="20">
           <cell r="F20">
-            <v>865.90909090909088</v>
+            <v>861.66666666666663</v>
           </cell>
           <cell r="G20">
-            <v>1.215950634790508</v>
+            <v>1.2050938337801607</v>
           </cell>
           <cell r="H20" t="str">
             <v>SUBIÓ</v>
@@ -580,10 +582,10 @@
         </row>
         <row r="21">
           <cell r="F21">
-            <v>257</v>
+            <v>256</v>
           </cell>
           <cell r="G21">
-            <v>6.198347107438007E-2</v>
+            <v>5.7851239669421517E-2</v>
           </cell>
           <cell r="H21" t="str">
             <v>SUBIÓ</v>
@@ -591,10 +593,10 @@
         </row>
         <row r="22">
           <cell r="F22">
-            <v>124.09090909090909</v>
+            <v>121.58333333333333</v>
           </cell>
           <cell r="G22">
-            <v>-0.12729099433721003</v>
+            <v>-0.14492632283991969</v>
           </cell>
           <cell r="H22" t="str">
             <v>BAJO</v>
@@ -602,10 +604,10 @@
         </row>
         <row r="23">
           <cell r="F23">
-            <v>513.5454545454545</v>
+            <v>514.58333333333337</v>
           </cell>
           <cell r="G23">
-            <v>8.7745201434286102E-4</v>
+            <v>2.9002320185615993E-3</v>
           </cell>
           <cell r="H23" t="str">
             <v>SUBIÓ</v>
@@ -613,10 +615,10 @@
         </row>
         <row r="24">
           <cell r="F24">
-            <v>852.81818181818187</v>
+            <v>841.58333333333337</v>
           </cell>
           <cell r="G24">
-            <v>5.1070005175293032E-2</v>
+            <v>3.7223428604965081E-2</v>
           </cell>
           <cell r="H24" t="str">
             <v>SUBIÓ</v>
@@ -624,21 +626,21 @@
         </row>
         <row r="25">
           <cell r="F25">
-            <v>57.272727272727273</v>
+            <v>77.5</v>
           </cell>
           <cell r="G25">
-            <v>-0.23587847984290167</v>
+            <v>3.3989834815756126E-2</v>
           </cell>
           <cell r="H25" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="26">
           <cell r="F26">
-            <v>719.09090909090912</v>
+            <v>695.41666666666663</v>
           </cell>
           <cell r="G26">
-            <v>-8.7392935824675666E-2</v>
+            <v>-0.11743820632138757</v>
           </cell>
           <cell r="H26" t="str">
             <v>BAJO</v>
@@ -646,10 +648,10 @@
         </row>
         <row r="27">
           <cell r="F27">
-            <v>1127.6363636363637</v>
+            <v>1112.25</v>
           </cell>
           <cell r="G27">
-            <v>-0.11468656959908641</v>
+            <v>-0.1267664872139973</v>
           </cell>
           <cell r="H27" t="str">
             <v>BAJO</v>
@@ -657,10 +659,10 @@
         </row>
         <row r="28">
           <cell r="F28">
-            <v>567.81818181818187</v>
+            <v>567.16666666666663</v>
           </cell>
           <cell r="G28">
-            <v>7.2993954664070992E-2</v>
+            <v>7.1762800323944997E-2</v>
           </cell>
           <cell r="H28" t="str">
             <v>SUBIÓ</v>
@@ -668,10 +670,10 @@
         </row>
         <row r="29">
           <cell r="F29">
-            <v>433.36363636363637</v>
+            <v>434.91666666666669</v>
           </cell>
           <cell r="G29">
-            <v>7.8402223443105212E-2</v>
+            <v>8.226685626259056E-2</v>
           </cell>
           <cell r="H29" t="str">
             <v>SUBIÓ</v>
@@ -679,10 +681,10 @@
         </row>
         <row r="30">
           <cell r="F30">
-            <v>228.09090909090909</v>
+            <v>223.83333333333334</v>
           </cell>
           <cell r="G30">
-            <v>1.9974399817954258</v>
+            <v>1.9414893617021276</v>
           </cell>
           <cell r="H30" t="str">
             <v>SUBIÓ</v>
@@ -690,10 +692,10 @@
         </row>
         <row r="31">
           <cell r="F31">
-            <v>275</v>
+            <v>267.75</v>
           </cell>
           <cell r="G31">
-            <v>2.8143989431968293</v>
+            <v>2.713837516512549</v>
           </cell>
           <cell r="H31" t="str">
             <v>SUBIÓ</v>
@@ -701,10 +703,10 @@
         </row>
         <row r="32">
           <cell r="F32">
-            <v>139.54545454545453</v>
+            <v>134.75</v>
           </cell>
           <cell r="G32">
-            <v>9.1416962925342737E-2</v>
+            <v>5.3910614525139566E-2</v>
           </cell>
           <cell r="H32" t="str">
             <v>SUBIÓ</v>
@@ -712,10 +714,10 @@
         </row>
         <row r="33">
           <cell r="F33">
-            <v>139.27272727272728</v>
+            <v>136.5</v>
           </cell>
           <cell r="G33">
-            <v>-2.8329809725158528E-2</v>
+            <v>-4.767441860465127E-2</v>
           </cell>
           <cell r="H33" t="str">
             <v>BAJO</v>
@@ -723,10 +725,10 @@
         </row>
         <row r="34">
           <cell r="F34">
-            <v>761.5454545454545</v>
+            <v>757.91666666666663</v>
           </cell>
           <cell r="G34">
-            <v>0.16767337510620228</v>
+            <v>0.162109375</v>
           </cell>
           <cell r="H34" t="str">
             <v>SUBIÓ</v>
@@ -734,10 +736,10 @@
         </row>
         <row r="35">
           <cell r="F35">
-            <v>606.81818181818187</v>
+            <v>591.41666666666663</v>
           </cell>
           <cell r="G35">
-            <v>-3.533824237836336E-2</v>
+            <v>-5.9822104466313419E-2</v>
           </cell>
           <cell r="H35" t="str">
             <v>BAJO</v>
@@ -745,10 +747,10 @@
         </row>
         <row r="36">
           <cell r="F36">
-            <v>799.63636363636363</v>
+            <v>794.66666666666663</v>
           </cell>
           <cell r="G36">
-            <v>-6.1669443654244649E-2</v>
+            <v>-6.7501117568171676E-2</v>
           </cell>
           <cell r="H36" t="str">
             <v>BAJO</v>
@@ -756,10 +758,10 @@
         </row>
         <row r="37">
           <cell r="F37">
-            <v>529.90909090909088</v>
+            <v>517.41666666666663</v>
           </cell>
           <cell r="G37">
-            <v>-8.4785680640602989E-2</v>
+            <v>-0.10636154289004041</v>
           </cell>
           <cell r="H37" t="str">
             <v>BAJO</v>
@@ -767,10 +769,10 @@
         </row>
         <row r="38">
           <cell r="F38">
-            <v>4.6363636363636367</v>
+            <v>4.25</v>
           </cell>
           <cell r="G38">
-            <v>0.87237762237762251</v>
+            <v>0.71634615384615374</v>
           </cell>
           <cell r="H38" t="str">
             <v>SUBIÓ</v>
@@ -778,10 +780,10 @@
         </row>
         <row r="39">
           <cell r="F39">
-            <v>0.63636363636363635</v>
+            <v>0.58333333333333337</v>
           </cell>
           <cell r="G39">
-            <v>0.48484848484848486</v>
+            <v>0.36111111111111138</v>
           </cell>
           <cell r="H39" t="str">
             <v>SUBIÓ</v>
@@ -789,10 +791,10 @@
         </row>
         <row r="40">
           <cell r="F40">
-            <v>151.54545454545453</v>
+            <v>146.41666666666666</v>
           </cell>
           <cell r="G40">
-            <v>0.10501893939393936</v>
+            <v>6.7621527777777635E-2</v>
           </cell>
           <cell r="H40" t="str">
             <v>SUBIÓ</v>
@@ -800,10 +802,10 @@
         </row>
         <row r="41">
           <cell r="F41">
-            <v>533.4545454545455</v>
+            <v>542.91666666666663</v>
           </cell>
           <cell r="G41">
-            <v>-3.7829987585205282E-2</v>
+            <v>-2.0763548913510399E-2</v>
           </cell>
           <cell r="H41" t="str">
             <v>BAJO</v>
@@ -811,10 +813,10 @@
         </row>
         <row r="42">
           <cell r="F42">
-            <v>417.09090909090907</v>
+            <v>420.25</v>
           </cell>
           <cell r="G42">
-            <v>2.140519573649728</v>
+            <v>2.1643062029401223</v>
           </cell>
           <cell r="H42" t="str">
             <v>SUBIÓ</v>
@@ -822,10 +824,10 @@
         </row>
         <row r="43">
           <cell r="F43">
-            <v>189.81818181818181</v>
+            <v>199.41666666666666</v>
           </cell>
           <cell r="G43">
-            <v>-0.35903170635442716</v>
+            <v>-0.32662003537546236</v>
           </cell>
           <cell r="H43" t="str">
             <v>BAJO</v>
@@ -833,10 +835,10 @@
         </row>
         <row r="44">
           <cell r="F44">
-            <v>464.09090909090907</v>
+            <v>474.41666666666669</v>
           </cell>
           <cell r="G44">
-            <v>-0.1222274078258947</v>
+            <v>-0.10269746915248124</v>
           </cell>
           <cell r="H44" t="str">
             <v>BAJO</v>
@@ -844,10 +846,10 @@
         </row>
         <row r="45">
           <cell r="F45">
-            <v>292.54545454545456</v>
+            <v>295.58333333333331</v>
           </cell>
           <cell r="G45">
-            <v>-4.2628245994304814E-2</v>
+            <v>-3.2686613682406107E-2</v>
           </cell>
           <cell r="H45" t="str">
             <v>BAJO</v>
@@ -855,10 +857,10 @@
         </row>
         <row r="46">
           <cell r="F46">
-            <v>219.72727272727272</v>
+            <v>229.5</v>
           </cell>
           <cell r="G46">
-            <v>-0.24207083980408561</v>
+            <v>-0.2083607095926413</v>
           </cell>
           <cell r="H46" t="str">
             <v>BAJO</v>
@@ -866,10 +868,10 @@
         </row>
         <row r="47">
           <cell r="F47">
-            <v>36.363636363636367</v>
+            <v>36.833333333333336</v>
           </cell>
           <cell r="G47">
-            <v>-0.36993699369936994</v>
+            <v>-0.36179867986798675</v>
           </cell>
           <cell r="H47" t="str">
             <v>BAJO</v>
@@ -877,10 +879,10 @@
         </row>
         <row r="48">
           <cell r="F48">
-            <v>110.72727272727273</v>
+            <v>110.58333333333333</v>
           </cell>
           <cell r="G48">
-            <v>5.7422795485551514E-2</v>
+            <v>5.6048203728967794E-2</v>
           </cell>
           <cell r="H48" t="str">
             <v>SUBIÓ</v>
@@ -888,10 +890,10 @@
         </row>
         <row r="49">
           <cell r="F49">
-            <v>45.81818181818182</v>
+            <v>45.75</v>
           </cell>
           <cell r="G49">
-            <v>-7.1253071253071232E-2</v>
+            <v>-7.2635135135135198E-2</v>
           </cell>
           <cell r="H49" t="str">
             <v>BAJO</v>
@@ -899,10 +901,10 @@
         </row>
         <row r="50">
           <cell r="F50">
-            <v>61.18181818181818</v>
+            <v>60.5</v>
           </cell>
           <cell r="G50">
-            <v>0.10569550930996696</v>
+            <v>9.3373493975903665E-2</v>
           </cell>
           <cell r="H50" t="str">
             <v>SUBIÓ</v>
@@ -1165,11 +1167,11 @@
       </c>
       <c r="E2" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F4</f>
-        <v>1257.5454545454545</v>
+        <v>1236.8333333333333</v>
       </c>
       <c r="F2" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G4</f>
-        <v>5.8455092002186237E-2</v>
+        <v>4.1022044088176335E-2</v>
       </c>
       <c r="G2" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H4</f>
@@ -1194,11 +1196,11 @@
       </c>
       <c r="E3" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F5</f>
-        <v>70.63636363636364</v>
+        <v>66.75</v>
       </c>
       <c r="F3" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G5</f>
-        <v>-7.5209703015189255E-2</v>
+        <v>-0.12609102244389025</v>
       </c>
       <c r="G3" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H5</f>
@@ -1223,15 +1225,15 @@
       </c>
       <c r="E4" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F6</f>
-        <v>511.63636363636363</v>
+        <v>495.08333333333331</v>
       </c>
       <c r="F4" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G6</f>
-        <v>4.2399884441195468E-3</v>
+        <v>-2.825030376670723E-2</v>
       </c>
       <c r="G4" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H6</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H4">
         <v>2.0299999999999998</v>
@@ -1252,11 +1254,11 @@
       </c>
       <c r="E5" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F7</f>
-        <v>122.90909090909091</v>
+        <v>119.91666666666667</v>
       </c>
       <c r="F5" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G7</f>
-        <v>0.25417439703153977</v>
+        <v>0.22363945578231292</v>
       </c>
       <c r="G5" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H7</f>
@@ -1281,11 +1283,11 @@
       </c>
       <c r="E6" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F8</f>
-        <v>15.363636363636363</v>
+        <v>15.416666666666666</v>
       </c>
       <c r="F6" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G8</f>
-        <v>0.28540383918869972</v>
+        <v>0.28984063745019917</v>
       </c>
       <c r="G6" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H8</f>
@@ -1310,15 +1312,15 @@
       </c>
       <c r="E7" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F9</f>
-        <v>1460.5454545454545</v>
+        <v>1430.3333333333333</v>
       </c>
       <c r="F7" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G9</f>
-        <v>1.4525533813380953E-4</v>
+        <v>-2.054325496461995E-2</v>
       </c>
       <c r="G7" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H9</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H7">
         <v>0.63</v>
@@ -1339,11 +1341,11 @@
       </c>
       <c r="E8" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F10</f>
-        <v>146.18181818181819</v>
+        <v>147.33333333333334</v>
       </c>
       <c r="F8" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G10</f>
-        <v>-2.7923311647187421E-2</v>
+        <v>-2.0265991133628813E-2</v>
       </c>
       <c r="G8" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H10</f>
@@ -1368,11 +1370,11 @@
       </c>
       <c r="E9" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F11</f>
-        <v>278.72727272727275</v>
+        <v>285.33333333333331</v>
       </c>
       <c r="F9" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G11</f>
-        <v>-0.1887355887355886</v>
+        <v>-0.16950796950796954</v>
       </c>
       <c r="G9" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H11</f>
@@ -1397,11 +1399,11 @@
       </c>
       <c r="E10" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F12</f>
-        <v>731.81818181818187</v>
+        <v>738.41666666666663</v>
       </c>
       <c r="F10" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G12</f>
-        <v>-4.4861291598395248E-2</v>
+        <v>-3.6249223119950269E-2</v>
       </c>
       <c r="G10" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H12</f>
@@ -1426,11 +1428,11 @@
       </c>
       <c r="E11" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F13</f>
-        <v>355.27272727272725</v>
+        <v>349.91666666666669</v>
       </c>
       <c r="F11" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G13</f>
-        <v>-2.0773425288453495E-2</v>
+        <v>-3.553615960099743E-2</v>
       </c>
       <c r="G11" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H13</f>
@@ -1455,15 +1457,15 @@
       </c>
       <c r="E12" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F14</f>
-        <v>3541.4545454545455</v>
+        <v>3468.3333333333335</v>
       </c>
       <c r="F12" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G14</f>
-        <v>5.6596908068131668E-3</v>
+        <v>-1.5104392038078784E-2</v>
       </c>
       <c r="G12" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H14</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H12">
         <v>1.1599999999999999</v>
@@ -1484,11 +1486,11 @@
       </c>
       <c r="E13" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F15</f>
-        <v>2175.181818181818</v>
+        <v>2143</v>
       </c>
       <c r="F13" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G15</f>
-        <v>-5.6320252415697158E-2</v>
+        <v>-7.0281995661605201E-2</v>
       </c>
       <c r="G13" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H15</f>
@@ -1513,11 +1515,11 @@
       </c>
       <c r="E14" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F16</f>
-        <v>2220.4545454545455</v>
+        <v>2182.6666666666665</v>
       </c>
       <c r="F14" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G16</f>
-        <v>-2.0305373255200876E-2</v>
+        <v>-3.6977897302294283E-2</v>
       </c>
       <c r="G14" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H16</f>
@@ -1542,15 +1544,15 @@
       </c>
       <c r="E15" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F17</f>
-        <v>2708.7272727272725</v>
+        <v>2656.75</v>
       </c>
       <c r="F15" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G17</f>
-        <v>1.298701298701288E-2</v>
+        <v>-6.4510097232610697E-3</v>
       </c>
       <c r="G15" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H17</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H15">
         <v>1.1599999999999999</v>
@@ -1571,11 +1573,11 @@
       </c>
       <c r="E16" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F18</f>
-        <v>704.90909090909088</v>
+        <v>704</v>
       </c>
       <c r="F16" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G18</f>
-        <v>0.81121875799472742</v>
+        <v>0.80888290713324351</v>
       </c>
       <c r="G16" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H18</f>
@@ -1600,11 +1602,11 @@
       </c>
       <c r="E17" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F19</f>
-        <v>853</v>
+        <v>819.25</v>
       </c>
       <c r="F17" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G19</f>
-        <v>0.9912183192530013</v>
+        <v>0.912433303690529</v>
       </c>
       <c r="G17" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H19</f>
@@ -1629,11 +1631,11 @@
       </c>
       <c r="E18" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F20</f>
-        <v>865.90909090909088</v>
+        <v>861.66666666666663</v>
       </c>
       <c r="F18" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G20</f>
-        <v>1.215950634790508</v>
+        <v>1.2050938337801607</v>
       </c>
       <c r="G18" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H20</f>
@@ -1658,11 +1660,11 @@
       </c>
       <c r="E19" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F21</f>
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F19" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G21</f>
-        <v>6.198347107438007E-2</v>
+        <v>5.7851239669421517E-2</v>
       </c>
       <c r="G19" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H21</f>
@@ -1687,11 +1689,11 @@
       </c>
       <c r="E20" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F22</f>
-        <v>124.09090909090909</v>
+        <v>121.58333333333333</v>
       </c>
       <c r="F20" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G22</f>
-        <v>-0.12729099433721003</v>
+        <v>-0.14492632283991969</v>
       </c>
       <c r="G20" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H22</f>
@@ -1716,11 +1718,11 @@
       </c>
       <c r="E21" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F23</f>
-        <v>513.5454545454545</v>
+        <v>514.58333333333337</v>
       </c>
       <c r="F21" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G23</f>
-        <v>8.7745201434286102E-4</v>
+        <v>2.9002320185615993E-3</v>
       </c>
       <c r="G21" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H23</f>
@@ -1745,11 +1747,11 @@
       </c>
       <c r="E22" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F24</f>
-        <v>852.81818181818187</v>
+        <v>841.58333333333337</v>
       </c>
       <c r="F22" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G24</f>
-        <v>5.1070005175293032E-2</v>
+        <v>3.7223428604965081E-2</v>
       </c>
       <c r="G22" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H24</f>
@@ -1774,15 +1776,15 @@
       </c>
       <c r="E23" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F25</f>
-        <v>57.272727272727273</v>
+        <v>77.5</v>
       </c>
       <c r="F23" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G25</f>
-        <v>-0.23587847984290167</v>
+        <v>3.3989834815756126E-2</v>
       </c>
       <c r="G23" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H25</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H23">
         <v>4.1500000000000004</v>
@@ -1803,11 +1805,11 @@
       </c>
       <c r="E24" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F26</f>
-        <v>719.09090909090912</v>
+        <v>695.41666666666663</v>
       </c>
       <c r="F24" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G26</f>
-        <v>-8.7392935824675666E-2</v>
+        <v>-0.11743820632138757</v>
       </c>
       <c r="G24" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H26</f>
@@ -1832,11 +1834,11 @@
       </c>
       <c r="E25" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F27</f>
-        <v>1127.6363636363637</v>
+        <v>1112.25</v>
       </c>
       <c r="F25" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G27</f>
-        <v>-0.11468656959908641</v>
+        <v>-0.1267664872139973</v>
       </c>
       <c r="G25" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H27</f>
@@ -1861,11 +1863,11 @@
       </c>
       <c r="E26" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F28</f>
-        <v>567.81818181818187</v>
+        <v>567.16666666666663</v>
       </c>
       <c r="F26" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G28</f>
-        <v>7.2993954664070992E-2</v>
+        <v>7.1762800323944997E-2</v>
       </c>
       <c r="G26" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H28</f>
@@ -1890,11 +1892,11 @@
       </c>
       <c r="E27" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F29</f>
-        <v>433.36363636363637</v>
+        <v>434.91666666666669</v>
       </c>
       <c r="F27" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G29</f>
-        <v>7.8402223443105212E-2</v>
+        <v>8.226685626259056E-2</v>
       </c>
       <c r="G27" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H29</f>
@@ -1919,11 +1921,11 @@
       </c>
       <c r="E28" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F30</f>
-        <v>228.09090909090909</v>
+        <v>223.83333333333334</v>
       </c>
       <c r="F28" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G30</f>
-        <v>1.9974399817954258</v>
+        <v>1.9414893617021276</v>
       </c>
       <c r="G28" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H30</f>
@@ -1948,11 +1950,11 @@
       </c>
       <c r="E29" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F31</f>
-        <v>275</v>
+        <v>267.75</v>
       </c>
       <c r="F29" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G31</f>
-        <v>2.8143989431968293</v>
+        <v>2.713837516512549</v>
       </c>
       <c r="G29" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H31</f>
@@ -1977,11 +1979,11 @@
       </c>
       <c r="E30" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F32</f>
-        <v>139.54545454545453</v>
+        <v>134.75</v>
       </c>
       <c r="F30" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G32</f>
-        <v>9.1416962925342737E-2</v>
+        <v>5.3910614525139566E-2</v>
       </c>
       <c r="G30" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H32</f>
@@ -2006,11 +2008,11 @@
       </c>
       <c r="E31" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F33</f>
-        <v>139.27272727272728</v>
+        <v>136.5</v>
       </c>
       <c r="F31" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G33</f>
-        <v>-2.8329809725158528E-2</v>
+        <v>-4.767441860465127E-2</v>
       </c>
       <c r="G31" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H33</f>
@@ -2035,11 +2037,11 @@
       </c>
       <c r="E32" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F34</f>
-        <v>761.5454545454545</v>
+        <v>757.91666666666663</v>
       </c>
       <c r="F32" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G34</f>
-        <v>0.16767337510620228</v>
+        <v>0.162109375</v>
       </c>
       <c r="G32" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H34</f>
@@ -2064,11 +2066,11 @@
       </c>
       <c r="E33" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F35</f>
-        <v>606.81818181818187</v>
+        <v>591.41666666666663</v>
       </c>
       <c r="F33" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G35</f>
-        <v>-3.533824237836336E-2</v>
+        <v>-5.9822104466313419E-2</v>
       </c>
       <c r="G33" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H35</f>
@@ -2093,11 +2095,11 @@
       </c>
       <c r="E34" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F36</f>
-        <v>799.63636363636363</v>
+        <v>794.66666666666663</v>
       </c>
       <c r="F34" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G36</f>
-        <v>-6.1669443654244649E-2</v>
+        <v>-6.7501117568171676E-2</v>
       </c>
       <c r="G34" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H36</f>
@@ -2122,11 +2124,11 @@
       </c>
       <c r="E35" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F37</f>
-        <v>529.90909090909088</v>
+        <v>517.41666666666663</v>
       </c>
       <c r="F35" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G37</f>
-        <v>-8.4785680640602989E-2</v>
+        <v>-0.10636154289004041</v>
       </c>
       <c r="G35" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H37</f>
@@ -2151,11 +2153,11 @@
       </c>
       <c r="E36" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F38</f>
-        <v>4.6363636363636367</v>
+        <v>4.25</v>
       </c>
       <c r="F36" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G38</f>
-        <v>0.87237762237762251</v>
+        <v>0.71634615384615374</v>
       </c>
       <c r="G36" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H38</f>
@@ -2180,11 +2182,11 @@
       </c>
       <c r="E37" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F39</f>
-        <v>0.63636363636363635</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="F37" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G39</f>
-        <v>0.48484848484848486</v>
+        <v>0.36111111111111138</v>
       </c>
       <c r="G37" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H39</f>
@@ -2209,11 +2211,11 @@
       </c>
       <c r="E38" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F40</f>
-        <v>151.54545454545453</v>
+        <v>146.41666666666666</v>
       </c>
       <c r="F38" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G40</f>
-        <v>0.10501893939393936</v>
+        <v>6.7621527777777635E-2</v>
       </c>
       <c r="G38" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H40</f>
@@ -2238,11 +2240,11 @@
       </c>
       <c r="E39" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F41</f>
-        <v>533.4545454545455</v>
+        <v>542.91666666666663</v>
       </c>
       <c r="F39" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G41</f>
-        <v>-3.7829987585205282E-2</v>
+        <v>-2.0763548913510399E-2</v>
       </c>
       <c r="G39" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H41</f>
@@ -2267,11 +2269,11 @@
       </c>
       <c r="E40" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F42</f>
-        <v>417.09090909090907</v>
+        <v>420.25</v>
       </c>
       <c r="F40" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G42</f>
-        <v>2.140519573649728</v>
+        <v>2.1643062029401223</v>
       </c>
       <c r="G40" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H42</f>
@@ -2296,11 +2298,11 @@
       </c>
       <c r="E41" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F43</f>
-        <v>189.81818181818181</v>
+        <v>199.41666666666666</v>
       </c>
       <c r="F41" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G43</f>
-        <v>-0.35903170635442716</v>
+        <v>-0.32662003537546236</v>
       </c>
       <c r="G41" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H43</f>
@@ -2325,11 +2327,11 @@
       </c>
       <c r="E42" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F44</f>
-        <v>464.09090909090907</v>
+        <v>474.41666666666669</v>
       </c>
       <c r="F42" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G44</f>
-        <v>-0.1222274078258947</v>
+        <v>-0.10269746915248124</v>
       </c>
       <c r="G42" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H44</f>
@@ -2354,11 +2356,11 @@
       </c>
       <c r="E43" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F45</f>
-        <v>292.54545454545456</v>
+        <v>295.58333333333331</v>
       </c>
       <c r="F43" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G45</f>
-        <v>-4.2628245994304814E-2</v>
+        <v>-3.2686613682406107E-2</v>
       </c>
       <c r="G43" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H45</f>
@@ -2383,11 +2385,11 @@
       </c>
       <c r="E44" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F46</f>
-        <v>219.72727272727272</v>
+        <v>229.5</v>
       </c>
       <c r="F44" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G46</f>
-        <v>-0.24207083980408561</v>
+        <v>-0.2083607095926413</v>
       </c>
       <c r="G44" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H46</f>
@@ -2412,11 +2414,11 @@
       </c>
       <c r="E45" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F47</f>
-        <v>36.363636363636367</v>
+        <v>36.833333333333336</v>
       </c>
       <c r="F45" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G47</f>
-        <v>-0.36993699369936994</v>
+        <v>-0.36179867986798675</v>
       </c>
       <c r="G45" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H47</f>
@@ -2441,11 +2443,11 @@
       </c>
       <c r="E46" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F48</f>
-        <v>110.72727272727273</v>
+        <v>110.58333333333333</v>
       </c>
       <c r="F46" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G48</f>
-        <v>5.7422795485551514E-2</v>
+        <v>5.6048203728967794E-2</v>
       </c>
       <c r="G46" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H48</f>
@@ -2470,11 +2472,11 @@
       </c>
       <c r="E47" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F49</f>
-        <v>45.81818181818182</v>
+        <v>45.75</v>
       </c>
       <c r="F47" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G49</f>
-        <v>-7.1253071253071232E-2</v>
+        <v>-7.2635135135135198E-2</v>
       </c>
       <c r="G47" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H49</f>
@@ -2499,11 +2501,11 @@
       </c>
       <c r="E48" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F50</f>
-        <v>61.18181818181818</v>
+        <v>60.5</v>
       </c>
       <c r="F48" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G50</f>
-        <v>0.10569550930996696</v>
+        <v>9.3373493975903665E-2</v>
       </c>
       <c r="G48" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H50</f>

--- a/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
+++ b/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{803DD141-6C99-4077-A6CA-5D34B0F78172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46288EA8-BE6E-4AD7-BFF0-FD4F98F8EB18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -371,6 +371,8 @@
       <sheetName val="INVENTARIO NACIONAL 15-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 16-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 17-09-26"/>
+      <sheetName val="INVENTARIO NACIONAL 17-09-16;15"/>
+      <sheetName val="INVENTARIO NACIONAL 18-09-26"/>
       <sheetName val="CCC"/>
       <sheetName val="VINCULO VTS BY SKU AGOSTO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
@@ -392,13 +394,15 @@
       <sheetData sheetId="12"/>
       <sheetData sheetId="13"/>
       <sheetData sheetId="14"/>
-      <sheetData sheetId="15">
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17">
         <row r="4">
           <cell r="F4">
-            <v>1236.8333333333333</v>
+            <v>1221.5384615384614</v>
           </cell>
           <cell r="G4">
-            <v>4.1022044088176335E-2</v>
+            <v>2.8148604902111796E-2</v>
           </cell>
           <cell r="H4" t="str">
             <v>SUBIÓ</v>
@@ -406,10 +410,10 @@
         </row>
         <row r="5">
           <cell r="F5">
-            <v>66.75</v>
+            <v>66.92307692307692</v>
           </cell>
           <cell r="G5">
-            <v>-0.12609102244389025</v>
+            <v>-0.12382505275273359</v>
           </cell>
           <cell r="H5" t="str">
             <v>BAJO</v>
@@ -417,10 +421,10 @@
         </row>
         <row r="6">
           <cell r="F6">
-            <v>495.08333333333331</v>
+            <v>498.46153846153845</v>
           </cell>
           <cell r="G6">
-            <v>-2.825030376670723E-2</v>
+            <v>-2.1619561856967229E-2</v>
           </cell>
           <cell r="H6" t="str">
             <v>BAJO</v>
@@ -428,10 +432,10 @@
         </row>
         <row r="7">
           <cell r="F7">
-            <v>119.91666666666667</v>
+            <v>116</v>
           </cell>
           <cell r="G7">
-            <v>0.22363945578231292</v>
+            <v>0.18367346938775508</v>
           </cell>
           <cell r="H7" t="str">
             <v>SUBIÓ</v>
@@ -439,10 +443,10 @@
         </row>
         <row r="8">
           <cell r="F8">
-            <v>15.416666666666666</v>
+            <v>14.846153846153847</v>
           </cell>
           <cell r="G8">
-            <v>0.28984063745019917</v>
+            <v>0.24210848912044125</v>
           </cell>
           <cell r="H8" t="str">
             <v>SUBIÓ</v>
@@ -450,10 +454,10 @@
         </row>
         <row r="9">
           <cell r="F9">
-            <v>1430.3333333333333</v>
+            <v>1438.7692307692307</v>
           </cell>
           <cell r="G9">
-            <v>-2.054325496461995E-2</v>
+            <v>-1.4766561901919162E-2</v>
           </cell>
           <cell r="H9" t="str">
             <v>BAJO</v>
@@ -461,10 +465,10 @@
         </row>
         <row r="10">
           <cell r="F10">
-            <v>147.33333333333334</v>
+            <v>144.38461538461539</v>
           </cell>
           <cell r="G10">
-            <v>-2.0265991133628813E-2</v>
+            <v>-3.9874311881911595E-2</v>
           </cell>
           <cell r="H10" t="str">
             <v>BAJO</v>
@@ -472,10 +476,10 @@
         </row>
         <row r="11">
           <cell r="F11">
-            <v>285.33333333333331</v>
+            <v>281.07692307692309</v>
           </cell>
           <cell r="G11">
-            <v>-0.16950796950796954</v>
+            <v>-0.18189668958899718</v>
           </cell>
           <cell r="H11" t="str">
             <v>BAJO</v>
@@ -483,10 +487,10 @@
         </row>
         <row r="12">
           <cell r="F12">
-            <v>738.41666666666663</v>
+            <v>728.23076923076928</v>
           </cell>
           <cell r="G12">
-            <v>-3.6249223119950269E-2</v>
+            <v>-4.9543433570779616E-2</v>
           </cell>
           <cell r="H12" t="str">
             <v>BAJO</v>
@@ -494,10 +498,10 @@
         </row>
         <row r="13">
           <cell r="F13">
-            <v>349.91666666666669</v>
+            <v>341.23076923076923</v>
           </cell>
           <cell r="G13">
-            <v>-3.553615960099743E-2</v>
+            <v>-5.9476814037780046E-2</v>
           </cell>
           <cell r="H13" t="str">
             <v>BAJO</v>
@@ -505,10 +509,10 @@
         </row>
         <row r="14">
           <cell r="F14">
-            <v>3468.3333333333335</v>
+            <v>3441.8461538461538</v>
           </cell>
           <cell r="G14">
-            <v>-1.5104392038078784E-2</v>
+            <v>-2.2625902872549397E-2</v>
           </cell>
           <cell r="H14" t="str">
             <v>BAJO</v>
@@ -516,10 +520,10 @@
         </row>
         <row r="15">
           <cell r="F15">
-            <v>2143</v>
+            <v>2126.0769230769229</v>
           </cell>
           <cell r="G15">
-            <v>-7.0281995661605201E-2</v>
+            <v>-7.7623894543634386E-2</v>
           </cell>
           <cell r="H15" t="str">
             <v>BAJO</v>
@@ -527,10 +531,10 @@
         </row>
         <row r="16">
           <cell r="F16">
-            <v>2182.6666666666665</v>
+            <v>2166.6923076923076</v>
           </cell>
           <cell r="G16">
-            <v>-3.6977897302294283E-2</v>
+            <v>-4.4026000892124051E-2</v>
           </cell>
           <cell r="H16" t="str">
             <v>BAJO</v>
@@ -538,10 +542,10 @@
         </row>
         <row r="17">
           <cell r="F17">
-            <v>2656.75</v>
+            <v>2638.9230769230771</v>
           </cell>
           <cell r="G17">
-            <v>-6.4510097232610697E-3</v>
+            <v>-1.3117772280075823E-2</v>
           </cell>
           <cell r="H17" t="str">
             <v>BAJO</v>
@@ -549,10 +553,10 @@
         </row>
         <row r="18">
           <cell r="F18">
-            <v>704</v>
+            <v>694.46153846153845</v>
           </cell>
           <cell r="G18">
-            <v>0.80888290713324351</v>
+            <v>0.78437444117121102</v>
           </cell>
           <cell r="H18" t="str">
             <v>SUBIÓ</v>
@@ -560,10 +564,10 @@
         </row>
         <row r="19">
           <cell r="F19">
-            <v>819.25</v>
+            <v>788.15384615384619</v>
           </cell>
           <cell r="G19">
-            <v>0.912433303690529</v>
+            <v>0.83984334918083237</v>
           </cell>
           <cell r="H19" t="str">
             <v>SUBIÓ</v>
@@ -571,10 +575,10 @@
         </row>
         <row r="20">
           <cell r="F20">
-            <v>861.66666666666663</v>
+            <v>837.76923076923072</v>
           </cell>
           <cell r="G20">
-            <v>1.2050938337801607</v>
+            <v>1.1439378316053919</v>
           </cell>
           <cell r="H20" t="str">
             <v>SUBIÓ</v>
@@ -582,10 +586,10 @@
         </row>
         <row r="21">
           <cell r="F21">
-            <v>256</v>
+            <v>250.15384615384616</v>
           </cell>
           <cell r="G21">
-            <v>5.7851239669421517E-2</v>
+            <v>3.3693579148124542E-2</v>
           </cell>
           <cell r="H21" t="str">
             <v>SUBIÓ</v>
@@ -593,10 +597,10 @@
         </row>
         <row r="22">
           <cell r="F22">
-            <v>121.58333333333333</v>
+            <v>118.38461538461539</v>
           </cell>
           <cell r="G22">
-            <v>-0.14492632283991969</v>
+            <v>-0.16742232984697825</v>
           </cell>
           <cell r="H22" t="str">
             <v>BAJO</v>
@@ -604,21 +608,21 @@
         </row>
         <row r="23">
           <cell r="F23">
-            <v>514.58333333333337</v>
+            <v>497.46153846153845</v>
           </cell>
           <cell r="G23">
-            <v>2.9002320185615993E-3</v>
+            <v>-3.0469391397465628E-2</v>
           </cell>
           <cell r="H23" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="24">
           <cell r="F24">
-            <v>841.58333333333337</v>
+            <v>821.46153846153845</v>
           </cell>
           <cell r="G24">
-            <v>3.7223428604965081E-2</v>
+            <v>1.2423986600874848E-2</v>
           </cell>
           <cell r="H24" t="str">
             <v>SUBIÓ</v>
@@ -626,21 +630,21 @@
         </row>
         <row r="25">
           <cell r="F25">
-            <v>77.5</v>
+            <v>73.84615384615384</v>
           </cell>
           <cell r="G25">
-            <v>3.3989834815756126E-2</v>
+            <v>-1.4759065584986852E-2</v>
           </cell>
           <cell r="H25" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="26">
           <cell r="F26">
-            <v>695.41666666666663</v>
+            <v>700.76923076923072</v>
           </cell>
           <cell r="G26">
-            <v>-0.11743820632138757</v>
+            <v>-0.1106452017795464</v>
           </cell>
           <cell r="H26" t="str">
             <v>BAJO</v>
@@ -648,10 +652,10 @@
         </row>
         <row r="27">
           <cell r="F27">
-            <v>1112.25</v>
+            <v>1126.6153846153845</v>
           </cell>
           <cell r="G27">
-            <v>-0.1267664872139973</v>
+            <v>-0.11548814577078381</v>
           </cell>
           <cell r="H27" t="str">
             <v>BAJO</v>
@@ -659,10 +663,10 @@
         </row>
         <row r="28">
           <cell r="F28">
-            <v>567.16666666666663</v>
+            <v>549</v>
           </cell>
           <cell r="G28">
-            <v>7.1762800323944997E-2</v>
+            <v>3.7433636281832161E-2</v>
           </cell>
           <cell r="H28" t="str">
             <v>SUBIÓ</v>
@@ -670,10 +674,10 @@
         </row>
         <row r="29">
           <cell r="F29">
-            <v>434.91666666666669</v>
+            <v>428.84615384615387</v>
           </cell>
           <cell r="G29">
-            <v>8.226685626259056E-2</v>
+            <v>6.716070989089129E-2</v>
           </cell>
           <cell r="H29" t="str">
             <v>SUBIÓ</v>
@@ -681,10 +685,10 @@
         </row>
         <row r="30">
           <cell r="F30">
-            <v>223.83333333333334</v>
+            <v>239.46153846153845</v>
           </cell>
           <cell r="G30">
-            <v>1.9414893617021276</v>
+            <v>2.1468662751516314</v>
           </cell>
           <cell r="H30" t="str">
             <v>SUBIÓ</v>
@@ -692,10 +696,10 @@
         </row>
         <row r="31">
           <cell r="F31">
-            <v>267.75</v>
+            <v>289.69230769230768</v>
           </cell>
           <cell r="G31">
-            <v>2.713837516512549</v>
+            <v>3.0181892084137782</v>
           </cell>
           <cell r="H31" t="str">
             <v>SUBIÓ</v>
@@ -703,21 +707,21 @@
         </row>
         <row r="32">
           <cell r="F32">
-            <v>134.75</v>
+            <v>127</v>
           </cell>
           <cell r="G32">
-            <v>5.3910614525139566E-2</v>
+            <v>-6.7039106145251326E-3</v>
           </cell>
           <cell r="H32" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="33">
           <cell r="F33">
-            <v>136.5</v>
+            <v>130</v>
           </cell>
           <cell r="G33">
-            <v>-4.767441860465127E-2</v>
+            <v>-9.3023255813953543E-2</v>
           </cell>
           <cell r="H33" t="str">
             <v>BAJO</v>
@@ -725,10 +729,10 @@
         </row>
         <row r="34">
           <cell r="F34">
-            <v>757.91666666666663</v>
+            <v>746.07692307692309</v>
           </cell>
           <cell r="G34">
-            <v>0.162109375</v>
+            <v>0.1439555625449318</v>
           </cell>
           <cell r="H34" t="str">
             <v>SUBIÓ</v>
@@ -736,10 +740,10 @@
         </row>
         <row r="35">
           <cell r="F35">
-            <v>591.41666666666663</v>
+            <v>574.30769230769226</v>
           </cell>
           <cell r="G35">
-            <v>-5.9822104466313419E-2</v>
+            <v>-8.7020322599429378E-2</v>
           </cell>
           <cell r="H35" t="str">
             <v>BAJO</v>
@@ -747,10 +751,10 @@
         </row>
         <row r="36">
           <cell r="F36">
-            <v>794.66666666666663</v>
+            <v>771.15384615384619</v>
           </cell>
           <cell r="G36">
-            <v>-6.7501117568171676E-2</v>
+            <v>-9.509215639077051E-2</v>
           </cell>
           <cell r="H36" t="str">
             <v>BAJO</v>
@@ -758,10 +762,10 @@
         </row>
         <row r="37">
           <cell r="F37">
-            <v>517.41666666666663</v>
+            <v>500.69230769230768</v>
           </cell>
           <cell r="G37">
-            <v>-0.10636154289004041</v>
+            <v>-0.13524644612727521</v>
           </cell>
           <cell r="H37" t="str">
             <v>BAJO</v>
@@ -769,10 +773,10 @@
         </row>
         <row r="38">
           <cell r="F38">
-            <v>4.25</v>
+            <v>4</v>
           </cell>
           <cell r="G38">
-            <v>0.71634615384615374</v>
+            <v>0.61538461538461542</v>
           </cell>
           <cell r="H38" t="str">
             <v>SUBIÓ</v>
@@ -780,10 +784,10 @@
         </row>
         <row r="39">
           <cell r="F39">
-            <v>0.58333333333333337</v>
+            <v>0.53846153846153844</v>
           </cell>
           <cell r="G39">
-            <v>0.36111111111111138</v>
+            <v>0.25641025641025639</v>
           </cell>
           <cell r="H39" t="str">
             <v>SUBIÓ</v>
@@ -791,10 +795,10 @@
         </row>
         <row r="40">
           <cell r="F40">
-            <v>146.41666666666666</v>
+            <v>142.38461538461539</v>
           </cell>
           <cell r="G40">
-            <v>6.7621527777777635E-2</v>
+            <v>3.8221153846153877E-2</v>
           </cell>
           <cell r="H40" t="str">
             <v>SUBIÓ</v>
@@ -802,10 +806,10 @@
         </row>
         <row r="41">
           <cell r="F41">
-            <v>542.91666666666663</v>
+            <v>528</v>
           </cell>
           <cell r="G41">
-            <v>-2.0763548913510399E-2</v>
+            <v>-4.7668126771450714E-2</v>
           </cell>
           <cell r="H41" t="str">
             <v>BAJO</v>
@@ -813,10 +817,10 @@
         </row>
         <row r="42">
           <cell r="F42">
-            <v>420.25</v>
+            <v>418</v>
           </cell>
           <cell r="G42">
-            <v>2.1643062029401223</v>
+            <v>2.1473646468268202</v>
           </cell>
           <cell r="H42" t="str">
             <v>SUBIÓ</v>
@@ -824,10 +828,10 @@
         </row>
         <row r="43">
           <cell r="F43">
-            <v>199.41666666666666</v>
+            <v>194.07692307692307</v>
           </cell>
           <cell r="G43">
-            <v>-0.32662003537546236</v>
+            <v>-0.34465100745853283</v>
           </cell>
           <cell r="H43" t="str">
             <v>BAJO</v>
@@ -835,10 +839,10 @@
         </row>
         <row r="44">
           <cell r="F44">
-            <v>474.41666666666669</v>
+            <v>458.30769230769232</v>
           </cell>
           <cell r="G44">
-            <v>-0.10269746915248124</v>
+            <v>-0.13316567247937139</v>
           </cell>
           <cell r="H44" t="str">
             <v>BAJO</v>
@@ -846,10 +850,10 @@
         </row>
         <row r="45">
           <cell r="F45">
-            <v>295.58333333333331</v>
+            <v>286.07692307692309</v>
           </cell>
           <cell r="G45">
-            <v>-3.2686613682406107E-2</v>
+            <v>-6.3796885676268511E-2</v>
           </cell>
           <cell r="H45" t="str">
             <v>BAJO</v>
@@ -857,10 +861,10 @@
         </row>
         <row r="46">
           <cell r="F46">
-            <v>229.5</v>
+            <v>222.61538461538461</v>
           </cell>
           <cell r="G46">
-            <v>-0.2083607095926413</v>
+            <v>-0.23210856160921867</v>
           </cell>
           <cell r="H46" t="str">
             <v>BAJO</v>
@@ -868,10 +872,10 @@
         </row>
         <row r="47">
           <cell r="F47">
-            <v>36.833333333333336</v>
+            <v>36</v>
           </cell>
           <cell r="G47">
-            <v>-0.36179867986798675</v>
+            <v>-0.37623762376237624</v>
           </cell>
           <cell r="H47" t="str">
             <v>BAJO</v>
@@ -879,21 +883,21 @@
         </row>
         <row r="48">
           <cell r="F48">
-            <v>110.58333333333333</v>
+            <v>104.53846153846153</v>
           </cell>
           <cell r="G48">
-            <v>5.6048203728967794E-2</v>
+            <v>-1.6790848987301432E-3</v>
           </cell>
           <cell r="H48" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="49">
           <cell r="F49">
-            <v>45.75</v>
+            <v>43.153846153846153</v>
           </cell>
           <cell r="G49">
-            <v>-7.2635135135135198E-2</v>
+            <v>-0.12525987525987536</v>
           </cell>
           <cell r="H49" t="str">
             <v>BAJO</v>
@@ -901,10 +905,10 @@
         </row>
         <row r="50">
           <cell r="F50">
-            <v>60.5</v>
+            <v>56.92307692307692</v>
           </cell>
           <cell r="G50">
-            <v>9.3373493975903665E-2</v>
+            <v>2.8730305838739367E-2</v>
           </cell>
           <cell r="H50" t="str">
             <v>SUBIÓ</v>
@@ -1167,11 +1171,11 @@
       </c>
       <c r="E2" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F4</f>
-        <v>1236.8333333333333</v>
+        <v>1221.5384615384614</v>
       </c>
       <c r="F2" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G4</f>
-        <v>4.1022044088176335E-2</v>
+        <v>2.8148604902111796E-2</v>
       </c>
       <c r="G2" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H4</f>
@@ -1196,11 +1200,11 @@
       </c>
       <c r="E3" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F5</f>
-        <v>66.75</v>
+        <v>66.92307692307692</v>
       </c>
       <c r="F3" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G5</f>
-        <v>-0.12609102244389025</v>
+        <v>-0.12382505275273359</v>
       </c>
       <c r="G3" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H5</f>
@@ -1225,11 +1229,11 @@
       </c>
       <c r="E4" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F6</f>
-        <v>495.08333333333331</v>
+        <v>498.46153846153845</v>
       </c>
       <c r="F4" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G6</f>
-        <v>-2.825030376670723E-2</v>
+        <v>-2.1619561856967229E-2</v>
       </c>
       <c r="G4" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H6</f>
@@ -1254,11 +1258,11 @@
       </c>
       <c r="E5" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F7</f>
-        <v>119.91666666666667</v>
+        <v>116</v>
       </c>
       <c r="F5" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G7</f>
-        <v>0.22363945578231292</v>
+        <v>0.18367346938775508</v>
       </c>
       <c r="G5" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H7</f>
@@ -1283,11 +1287,11 @@
       </c>
       <c r="E6" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F8</f>
-        <v>15.416666666666666</v>
+        <v>14.846153846153847</v>
       </c>
       <c r="F6" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G8</f>
-        <v>0.28984063745019917</v>
+        <v>0.24210848912044125</v>
       </c>
       <c r="G6" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H8</f>
@@ -1312,11 +1316,11 @@
       </c>
       <c r="E7" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F9</f>
-        <v>1430.3333333333333</v>
+        <v>1438.7692307692307</v>
       </c>
       <c r="F7" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G9</f>
-        <v>-2.054325496461995E-2</v>
+        <v>-1.4766561901919162E-2</v>
       </c>
       <c r="G7" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H9</f>
@@ -1341,11 +1345,11 @@
       </c>
       <c r="E8" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F10</f>
-        <v>147.33333333333334</v>
+        <v>144.38461538461539</v>
       </c>
       <c r="F8" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G10</f>
-        <v>-2.0265991133628813E-2</v>
+        <v>-3.9874311881911595E-2</v>
       </c>
       <c r="G8" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H10</f>
@@ -1370,11 +1374,11 @@
       </c>
       <c r="E9" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F11</f>
-        <v>285.33333333333331</v>
+        <v>281.07692307692309</v>
       </c>
       <c r="F9" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G11</f>
-        <v>-0.16950796950796954</v>
+        <v>-0.18189668958899718</v>
       </c>
       <c r="G9" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H11</f>
@@ -1399,11 +1403,11 @@
       </c>
       <c r="E10" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F12</f>
-        <v>738.41666666666663</v>
+        <v>728.23076923076928</v>
       </c>
       <c r="F10" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G12</f>
-        <v>-3.6249223119950269E-2</v>
+        <v>-4.9543433570779616E-2</v>
       </c>
       <c r="G10" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H12</f>
@@ -1428,11 +1432,11 @@
       </c>
       <c r="E11" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F13</f>
-        <v>349.91666666666669</v>
+        <v>341.23076923076923</v>
       </c>
       <c r="F11" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G13</f>
-        <v>-3.553615960099743E-2</v>
+        <v>-5.9476814037780046E-2</v>
       </c>
       <c r="G11" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H13</f>
@@ -1457,11 +1461,11 @@
       </c>
       <c r="E12" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F14</f>
-        <v>3468.3333333333335</v>
+        <v>3441.8461538461538</v>
       </c>
       <c r="F12" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G14</f>
-        <v>-1.5104392038078784E-2</v>
+        <v>-2.2625902872549397E-2</v>
       </c>
       <c r="G12" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H14</f>
@@ -1486,11 +1490,11 @@
       </c>
       <c r="E13" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F15</f>
-        <v>2143</v>
+        <v>2126.0769230769229</v>
       </c>
       <c r="F13" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G15</f>
-        <v>-7.0281995661605201E-2</v>
+        <v>-7.7623894543634386E-2</v>
       </c>
       <c r="G13" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H15</f>
@@ -1515,11 +1519,11 @@
       </c>
       <c r="E14" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F16</f>
-        <v>2182.6666666666665</v>
+        <v>2166.6923076923076</v>
       </c>
       <c r="F14" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G16</f>
-        <v>-3.6977897302294283E-2</v>
+        <v>-4.4026000892124051E-2</v>
       </c>
       <c r="G14" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H16</f>
@@ -1544,11 +1548,11 @@
       </c>
       <c r="E15" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F17</f>
-        <v>2656.75</v>
+        <v>2638.9230769230771</v>
       </c>
       <c r="F15" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G17</f>
-        <v>-6.4510097232610697E-3</v>
+        <v>-1.3117772280075823E-2</v>
       </c>
       <c r="G15" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H17</f>
@@ -1573,11 +1577,11 @@
       </c>
       <c r="E16" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F18</f>
-        <v>704</v>
+        <v>694.46153846153845</v>
       </c>
       <c r="F16" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G18</f>
-        <v>0.80888290713324351</v>
+        <v>0.78437444117121102</v>
       </c>
       <c r="G16" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H18</f>
@@ -1602,11 +1606,11 @@
       </c>
       <c r="E17" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F19</f>
-        <v>819.25</v>
+        <v>788.15384615384619</v>
       </c>
       <c r="F17" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G19</f>
-        <v>0.912433303690529</v>
+        <v>0.83984334918083237</v>
       </c>
       <c r="G17" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H19</f>
@@ -1631,11 +1635,11 @@
       </c>
       <c r="E18" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F20</f>
-        <v>861.66666666666663</v>
+        <v>837.76923076923072</v>
       </c>
       <c r="F18" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G20</f>
-        <v>1.2050938337801607</v>
+        <v>1.1439378316053919</v>
       </c>
       <c r="G18" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H20</f>
@@ -1660,11 +1664,11 @@
       </c>
       <c r="E19" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F21</f>
-        <v>256</v>
+        <v>250.15384615384616</v>
       </c>
       <c r="F19" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G21</f>
-        <v>5.7851239669421517E-2</v>
+        <v>3.3693579148124542E-2</v>
       </c>
       <c r="G19" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H21</f>
@@ -1689,11 +1693,11 @@
       </c>
       <c r="E20" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F22</f>
-        <v>121.58333333333333</v>
+        <v>118.38461538461539</v>
       </c>
       <c r="F20" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G22</f>
-        <v>-0.14492632283991969</v>
+        <v>-0.16742232984697825</v>
       </c>
       <c r="G20" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H22</f>
@@ -1718,15 +1722,15 @@
       </c>
       <c r="E21" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F23</f>
-        <v>514.58333333333337</v>
+        <v>497.46153846153845</v>
       </c>
       <c r="F21" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G23</f>
-        <v>2.9002320185615993E-3</v>
+        <v>-3.0469391397465628E-2</v>
       </c>
       <c r="G21" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H23</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H21">
         <v>4.1500000000000004</v>
@@ -1747,11 +1751,11 @@
       </c>
       <c r="E22" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F24</f>
-        <v>841.58333333333337</v>
+        <v>821.46153846153845</v>
       </c>
       <c r="F22" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G24</f>
-        <v>3.7223428604965081E-2</v>
+        <v>1.2423986600874848E-2</v>
       </c>
       <c r="G22" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H24</f>
@@ -1776,15 +1780,15 @@
       </c>
       <c r="E23" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F25</f>
-        <v>77.5</v>
+        <v>73.84615384615384</v>
       </c>
       <c r="F23" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G25</f>
-        <v>3.3989834815756126E-2</v>
+        <v>-1.4759065584986852E-2</v>
       </c>
       <c r="G23" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H25</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H23">
         <v>4.1500000000000004</v>
@@ -1805,11 +1809,11 @@
       </c>
       <c r="E24" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F26</f>
-        <v>695.41666666666663</v>
+        <v>700.76923076923072</v>
       </c>
       <c r="F24" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G26</f>
-        <v>-0.11743820632138757</v>
+        <v>-0.1106452017795464</v>
       </c>
       <c r="G24" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H26</f>
@@ -1834,11 +1838,11 @@
       </c>
       <c r="E25" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F27</f>
-        <v>1112.25</v>
+        <v>1126.6153846153845</v>
       </c>
       <c r="F25" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G27</f>
-        <v>-0.1267664872139973</v>
+        <v>-0.11548814577078381</v>
       </c>
       <c r="G25" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H27</f>
@@ -1863,11 +1867,11 @@
       </c>
       <c r="E26" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F28</f>
-        <v>567.16666666666663</v>
+        <v>549</v>
       </c>
       <c r="F26" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G28</f>
-        <v>7.1762800323944997E-2</v>
+        <v>3.7433636281832161E-2</v>
       </c>
       <c r="G26" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H28</f>
@@ -1892,11 +1896,11 @@
       </c>
       <c r="E27" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F29</f>
-        <v>434.91666666666669</v>
+        <v>428.84615384615387</v>
       </c>
       <c r="F27" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G29</f>
-        <v>8.226685626259056E-2</v>
+        <v>6.716070989089129E-2</v>
       </c>
       <c r="G27" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H29</f>
@@ -1921,11 +1925,11 @@
       </c>
       <c r="E28" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F30</f>
-        <v>223.83333333333334</v>
+        <v>239.46153846153845</v>
       </c>
       <c r="F28" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G30</f>
-        <v>1.9414893617021276</v>
+        <v>2.1468662751516314</v>
       </c>
       <c r="G28" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H30</f>
@@ -1950,11 +1954,11 @@
       </c>
       <c r="E29" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F31</f>
-        <v>267.75</v>
+        <v>289.69230769230768</v>
       </c>
       <c r="F29" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G31</f>
-        <v>2.713837516512549</v>
+        <v>3.0181892084137782</v>
       </c>
       <c r="G29" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H31</f>
@@ -1979,15 +1983,15 @@
       </c>
       <c r="E30" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F32</f>
-        <v>134.75</v>
+        <v>127</v>
       </c>
       <c r="F30" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G32</f>
-        <v>5.3910614525139566E-2</v>
+        <v>-6.7039106145251326E-3</v>
       </c>
       <c r="G30" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H32</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H30">
         <v>6.15</v>
@@ -2008,11 +2012,11 @@
       </c>
       <c r="E31" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F33</f>
-        <v>136.5</v>
+        <v>130</v>
       </c>
       <c r="F31" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G33</f>
-        <v>-4.767441860465127E-2</v>
+        <v>-9.3023255813953543E-2</v>
       </c>
       <c r="G31" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H33</f>
@@ -2037,11 +2041,11 @@
       </c>
       <c r="E32" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F34</f>
-        <v>757.91666666666663</v>
+        <v>746.07692307692309</v>
       </c>
       <c r="F32" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G34</f>
-        <v>0.162109375</v>
+        <v>0.1439555625449318</v>
       </c>
       <c r="G32" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H34</f>
@@ -2066,11 +2070,11 @@
       </c>
       <c r="E33" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F35</f>
-        <v>591.41666666666663</v>
+        <v>574.30769230769226</v>
       </c>
       <c r="F33" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G35</f>
-        <v>-5.9822104466313419E-2</v>
+        <v>-8.7020322599429378E-2</v>
       </c>
       <c r="G33" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H35</f>
@@ -2095,11 +2099,11 @@
       </c>
       <c r="E34" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F36</f>
-        <v>794.66666666666663</v>
+        <v>771.15384615384619</v>
       </c>
       <c r="F34" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G36</f>
-        <v>-6.7501117568171676E-2</v>
+        <v>-9.509215639077051E-2</v>
       </c>
       <c r="G34" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H36</f>
@@ -2124,11 +2128,11 @@
       </c>
       <c r="E35" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F37</f>
-        <v>517.41666666666663</v>
+        <v>500.69230769230768</v>
       </c>
       <c r="F35" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G37</f>
-        <v>-0.10636154289004041</v>
+        <v>-0.13524644612727521</v>
       </c>
       <c r="G35" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H37</f>
@@ -2153,11 +2157,11 @@
       </c>
       <c r="E36" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F38</f>
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="F36" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G38</f>
-        <v>0.71634615384615374</v>
+        <v>0.61538461538461542</v>
       </c>
       <c r="G36" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H38</f>
@@ -2182,11 +2186,11 @@
       </c>
       <c r="E37" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F39</f>
-        <v>0.58333333333333337</v>
+        <v>0.53846153846153844</v>
       </c>
       <c r="F37" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G39</f>
-        <v>0.36111111111111138</v>
+        <v>0.25641025641025639</v>
       </c>
       <c r="G37" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H39</f>
@@ -2211,11 +2215,11 @@
       </c>
       <c r="E38" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F40</f>
-        <v>146.41666666666666</v>
+        <v>142.38461538461539</v>
       </c>
       <c r="F38" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G40</f>
-        <v>6.7621527777777635E-2</v>
+        <v>3.8221153846153877E-2</v>
       </c>
       <c r="G38" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H40</f>
@@ -2240,11 +2244,11 @@
       </c>
       <c r="E39" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F41</f>
-        <v>542.91666666666663</v>
+        <v>528</v>
       </c>
       <c r="F39" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G41</f>
-        <v>-2.0763548913510399E-2</v>
+        <v>-4.7668126771450714E-2</v>
       </c>
       <c r="G39" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H41</f>
@@ -2269,11 +2273,11 @@
       </c>
       <c r="E40" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F42</f>
-        <v>420.25</v>
+        <v>418</v>
       </c>
       <c r="F40" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G42</f>
-        <v>2.1643062029401223</v>
+        <v>2.1473646468268202</v>
       </c>
       <c r="G40" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H42</f>
@@ -2298,11 +2302,11 @@
       </c>
       <c r="E41" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F43</f>
-        <v>199.41666666666666</v>
+        <v>194.07692307692307</v>
       </c>
       <c r="F41" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G43</f>
-        <v>-0.32662003537546236</v>
+        <v>-0.34465100745853283</v>
       </c>
       <c r="G41" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H43</f>
@@ -2327,11 +2331,11 @@
       </c>
       <c r="E42" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F44</f>
-        <v>474.41666666666669</v>
+        <v>458.30769230769232</v>
       </c>
       <c r="F42" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G44</f>
-        <v>-0.10269746915248124</v>
+        <v>-0.13316567247937139</v>
       </c>
       <c r="G42" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H44</f>
@@ -2356,11 +2360,11 @@
       </c>
       <c r="E43" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F45</f>
-        <v>295.58333333333331</v>
+        <v>286.07692307692309</v>
       </c>
       <c r="F43" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G45</f>
-        <v>-3.2686613682406107E-2</v>
+        <v>-6.3796885676268511E-2</v>
       </c>
       <c r="G43" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H45</f>
@@ -2385,11 +2389,11 @@
       </c>
       <c r="E44" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F46</f>
-        <v>229.5</v>
+        <v>222.61538461538461</v>
       </c>
       <c r="F44" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G46</f>
-        <v>-0.2083607095926413</v>
+        <v>-0.23210856160921867</v>
       </c>
       <c r="G44" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H46</f>
@@ -2414,11 +2418,11 @@
       </c>
       <c r="E45" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F47</f>
-        <v>36.833333333333336</v>
+        <v>36</v>
       </c>
       <c r="F45" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G47</f>
-        <v>-0.36179867986798675</v>
+        <v>-0.37623762376237624</v>
       </c>
       <c r="G45" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H47</f>
@@ -2443,15 +2447,15 @@
       </c>
       <c r="E46" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F48</f>
-        <v>110.58333333333333</v>
+        <v>104.53846153846153</v>
       </c>
       <c r="F46" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G48</f>
-        <v>5.6048203728967794E-2</v>
+        <v>-1.6790848987301432E-3</v>
       </c>
       <c r="G46" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H48</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H46">
         <v>2.62</v>
@@ -2472,11 +2476,11 @@
       </c>
       <c r="E47" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F49</f>
-        <v>45.75</v>
+        <v>43.153846153846153</v>
       </c>
       <c r="F47" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G49</f>
-        <v>-7.2635135135135198E-2</v>
+        <v>-0.12525987525987536</v>
       </c>
       <c r="G47" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H49</f>
@@ -2501,11 +2505,11 @@
       </c>
       <c r="E48" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F50</f>
-        <v>60.5</v>
+        <v>56.92307692307692</v>
       </c>
       <c r="F48" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G50</f>
-        <v>9.3373493975903665E-2</v>
+        <v>2.8730305838739367E-2</v>
       </c>
       <c r="G48" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H50</f>

--- a/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
+++ b/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46288EA8-BE6E-4AD7-BFF0-FD4F98F8EB18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7A7DA80-DE7B-4557-9457-EFF0F7003C16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -373,6 +373,7 @@
       <sheetName val="INVENTARIO NACIONAL 17-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 17-09-16;15"/>
       <sheetName val="INVENTARIO NACIONAL 18-09-26"/>
+      <sheetName val="INVENTARIO NACIONAL 20-09-26"/>
       <sheetName val="CCC"/>
       <sheetName val="VINCULO VTS BY SKU AGOSTO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
@@ -396,13 +397,14 @@
       <sheetData sheetId="14"/>
       <sheetData sheetId="15"/>
       <sheetData sheetId="16"/>
-      <sheetData sheetId="17">
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18">
         <row r="4">
           <cell r="F4">
-            <v>1221.5384615384614</v>
+            <v>1195.7857142857142</v>
           </cell>
           <cell r="G4">
-            <v>2.8148604902111796E-2</v>
+            <v>6.4729458917835991E-3</v>
           </cell>
           <cell r="H4" t="str">
             <v>SUBIÓ</v>
@@ -410,10 +412,10 @@
         </row>
         <row r="5">
           <cell r="F5">
-            <v>66.92307692307692</v>
+            <v>62.785714285714285</v>
           </cell>
           <cell r="G5">
-            <v>-0.12382505275273359</v>
+            <v>-0.17799251870324184</v>
           </cell>
           <cell r="H5" t="str">
             <v>BAJO</v>
@@ -421,10 +423,10 @@
         </row>
         <row r="6">
           <cell r="F6">
-            <v>498.46153846153845</v>
+            <v>483.64285714285717</v>
           </cell>
           <cell r="G6">
-            <v>-2.1619561856967229E-2</v>
+            <v>-5.0705673427423048E-2</v>
           </cell>
           <cell r="H6" t="str">
             <v>BAJO</v>
@@ -432,10 +434,10 @@
         </row>
         <row r="7">
           <cell r="F7">
-            <v>116</v>
+            <v>110.5</v>
           </cell>
           <cell r="G7">
-            <v>0.18367346938775508</v>
+            <v>0.12755102040816335</v>
           </cell>
           <cell r="H7" t="str">
             <v>SUBIÓ</v>
@@ -443,10 +445,10 @@
         </row>
         <row r="8">
           <cell r="F8">
-            <v>14.846153846153847</v>
+            <v>13.785714285714286</v>
           </cell>
           <cell r="G8">
-            <v>0.24210848912044125</v>
+            <v>0.15338645418326702</v>
           </cell>
           <cell r="H8" t="str">
             <v>SUBIÓ</v>
@@ -454,10 +456,10 @@
         </row>
         <row r="9">
           <cell r="F9">
-            <v>1438.7692307692307</v>
+            <v>1408.6428571428571</v>
           </cell>
           <cell r="G9">
-            <v>-1.4766561901919162E-2</v>
+            <v>-3.5396354387452256E-2</v>
           </cell>
           <cell r="H9" t="str">
             <v>BAJO</v>
@@ -465,10 +467,10 @@
         </row>
         <row r="10">
           <cell r="F10">
-            <v>144.38461538461539</v>
+            <v>143.28571428571428</v>
           </cell>
           <cell r="G10">
-            <v>-3.9874311881911595E-2</v>
+            <v>-4.7181760607979739E-2</v>
           </cell>
           <cell r="H10" t="str">
             <v>BAJO</v>
@@ -476,10 +478,10 @@
         </row>
         <row r="11">
           <cell r="F11">
-            <v>281.07692307692309</v>
+            <v>289.78571428571428</v>
           </cell>
           <cell r="G11">
-            <v>-0.18189668958899718</v>
+            <v>-0.15654885654885653</v>
           </cell>
           <cell r="H11" t="str">
             <v>BAJO</v>
@@ -487,10 +489,10 @@
         </row>
         <row r="12">
           <cell r="F12">
-            <v>728.23076923076928</v>
+            <v>724.78571428571433</v>
           </cell>
           <cell r="G12">
-            <v>-4.9543433570779616E-2</v>
+            <v>-5.4039776258545613E-2</v>
           </cell>
           <cell r="H12" t="str">
             <v>BAJO</v>
@@ -498,10 +500,10 @@
         </row>
         <row r="13">
           <cell r="F13">
-            <v>341.23076923076923</v>
+            <v>341.92857142857144</v>
           </cell>
           <cell r="G13">
-            <v>-5.9476814037780046E-2</v>
+            <v>-5.7553484709279346E-2</v>
           </cell>
           <cell r="H13" t="str">
             <v>BAJO</v>
@@ -509,10 +511,10 @@
         </row>
         <row r="14">
           <cell r="F14">
-            <v>3441.8461538461538</v>
+            <v>3334.6428571428573</v>
           </cell>
           <cell r="G14">
-            <v>-2.2625902872549397E-2</v>
+            <v>-5.3068206404153995E-2</v>
           </cell>
           <cell r="H14" t="str">
             <v>BAJO</v>
@@ -520,10 +522,10 @@
         </row>
         <row r="15">
           <cell r="F15">
-            <v>2126.0769230769229</v>
+            <v>2062.9285714285716</v>
           </cell>
           <cell r="G15">
-            <v>-7.7623894543634386E-2</v>
+            <v>-0.10502014254725744</v>
           </cell>
           <cell r="H15" t="str">
             <v>BAJO</v>
@@ -531,10 +533,10 @@
         </row>
         <row r="16">
           <cell r="F16">
-            <v>2166.6923076923076</v>
+            <v>2112.3571428571427</v>
           </cell>
           <cell r="G16">
-            <v>-4.4026000892124051E-2</v>
+            <v>-6.7999411715270242E-2</v>
           </cell>
           <cell r="H16" t="str">
             <v>BAJO</v>
@@ -542,10 +544,10 @@
         </row>
         <row r="17">
           <cell r="F17">
-            <v>2638.9230769230771</v>
+            <v>2573.3571428571427</v>
           </cell>
           <cell r="G17">
-            <v>-1.3117772280075823E-2</v>
+            <v>-3.7637568116251852E-2</v>
           </cell>
           <cell r="H17" t="str">
             <v>BAJO</v>
@@ -553,10 +555,10 @@
         </row>
         <row r="18">
           <cell r="F18">
-            <v>694.46153846153845</v>
+            <v>678.5</v>
           </cell>
           <cell r="G18">
-            <v>0.78437444117121102</v>
+            <v>0.74336229046861613</v>
           </cell>
           <cell r="H18" t="str">
             <v>SUBIÓ</v>
@@ -564,10 +566,10 @@
         </row>
         <row r="19">
           <cell r="F19">
-            <v>788.15384615384619</v>
+            <v>769.35714285714289</v>
           </cell>
           <cell r="G19">
-            <v>0.83984334918083237</v>
+            <v>0.79596487327701193</v>
           </cell>
           <cell r="H19" t="str">
             <v>SUBIÓ</v>
@@ -575,10 +577,10 @@
         </row>
         <row r="20">
           <cell r="F20">
-            <v>837.76923076923072</v>
+            <v>818.71428571428567</v>
           </cell>
           <cell r="G20">
-            <v>1.1439378316053919</v>
+            <v>1.0951742627345844</v>
           </cell>
           <cell r="H20" t="str">
             <v>SUBIÓ</v>
@@ -586,10 +588,10 @@
         </row>
         <row r="21">
           <cell r="F21">
-            <v>250.15384615384616</v>
+            <v>243.42857142857142</v>
           </cell>
           <cell r="G21">
-            <v>3.3693579148124542E-2</v>
+            <v>5.9031877213695516E-3</v>
           </cell>
           <cell r="H21" t="str">
             <v>SUBIÓ</v>
@@ -597,10 +599,10 @@
         </row>
         <row r="22">
           <cell r="F22">
-            <v>118.38461538461539</v>
+            <v>116.14285714285714</v>
           </cell>
           <cell r="G22">
-            <v>-0.16742232984697825</v>
+            <v>-0.18318821165438726</v>
           </cell>
           <cell r="H22" t="str">
             <v>BAJO</v>
@@ -608,10 +610,10 @@
         </row>
         <row r="23">
           <cell r="F23">
-            <v>497.46153846153845</v>
+            <v>483.64285714285717</v>
           </cell>
           <cell r="G23">
-            <v>-3.0469391397465628E-2</v>
+            <v>-5.7401392111368854E-2</v>
           </cell>
           <cell r="H23" t="str">
             <v>BAJO</v>
@@ -619,10 +621,10 @@
         </row>
         <row r="24">
           <cell r="F24">
-            <v>821.46153846153845</v>
+            <v>813.71428571428567</v>
           </cell>
           <cell r="G24">
-            <v>1.2423986600874848E-2</v>
+            <v>2.8757556194611844E-3</v>
           </cell>
           <cell r="H24" t="str">
             <v>SUBIÓ</v>
@@ -630,10 +632,10 @@
         </row>
         <row r="25">
           <cell r="F25">
-            <v>73.84615384615384</v>
+            <v>70.857142857142861</v>
           </cell>
           <cell r="G25">
-            <v>-1.4759065584986852E-2</v>
+            <v>-5.4637865311308653E-2</v>
           </cell>
           <cell r="H25" t="str">
             <v>BAJO</v>
@@ -641,10 +643,10 @@
         </row>
         <row r="26">
           <cell r="F26">
-            <v>700.76923076923072</v>
+            <v>686</v>
           </cell>
           <cell r="G26">
-            <v>-0.1106452017795464</v>
+            <v>-0.12938901311415962</v>
           </cell>
           <cell r="H26" t="str">
             <v>BAJO</v>
@@ -652,10 +654,10 @@
         </row>
         <row r="27">
           <cell r="F27">
-            <v>1126.6153846153845</v>
+            <v>1077.5</v>
           </cell>
           <cell r="G27">
-            <v>-0.11548814577078381</v>
+            <v>-0.15404890085240019</v>
           </cell>
           <cell r="H27" t="str">
             <v>BAJO</v>
@@ -663,10 +665,10 @@
         </row>
         <row r="28">
           <cell r="F28">
-            <v>549</v>
+            <v>539.28571428571433</v>
           </cell>
           <cell r="G28">
-            <v>3.7433636281832161E-2</v>
+            <v>1.9076756951318385E-2</v>
           </cell>
           <cell r="H28" t="str">
             <v>SUBIÓ</v>
@@ -674,10 +676,10 @@
         </row>
         <row r="29">
           <cell r="F29">
-            <v>428.84615384615387</v>
+            <v>420.28571428571428</v>
           </cell>
           <cell r="G29">
-            <v>6.716070989089129E-2</v>
+            <v>4.5858514041948073E-2</v>
           </cell>
           <cell r="H29" t="str">
             <v>SUBIÓ</v>
@@ -685,10 +687,10 @@
         </row>
         <row r="30">
           <cell r="F30">
-            <v>239.46153846153845</v>
+            <v>228.71428571428572</v>
           </cell>
           <cell r="G30">
-            <v>2.1468662751516314</v>
+            <v>2.0056320400500622</v>
           </cell>
           <cell r="H30" t="str">
             <v>SUBIÓ</v>
@@ -696,10 +698,10 @@
         </row>
         <row r="31">
           <cell r="F31">
-            <v>289.69230769230768</v>
+            <v>274.78571428571428</v>
           </cell>
           <cell r="G31">
-            <v>3.0181892084137782</v>
+            <v>2.8114266842800522</v>
           </cell>
           <cell r="H31" t="str">
             <v>SUBIÓ</v>
@@ -707,10 +709,10 @@
         </row>
         <row r="32">
           <cell r="F32">
-            <v>127</v>
+            <v>121.14285714285714</v>
           </cell>
           <cell r="G32">
-            <v>-6.7039106145251326E-3</v>
+            <v>-5.2513966480447039E-2</v>
           </cell>
           <cell r="H32" t="str">
             <v>BAJO</v>
@@ -718,10 +720,10 @@
         </row>
         <row r="33">
           <cell r="F33">
-            <v>130</v>
+            <v>133.14285714285714</v>
           </cell>
           <cell r="G33">
-            <v>-9.3023255813953543E-2</v>
+            <v>-7.1096345514950254E-2</v>
           </cell>
           <cell r="H33" t="str">
             <v>BAJO</v>
@@ -729,10 +731,10 @@
         </row>
         <row r="34">
           <cell r="F34">
-            <v>746.07692307692309</v>
+            <v>735.21428571428567</v>
           </cell>
           <cell r="G34">
-            <v>0.1439555625449318</v>
+            <v>0.12729994158878499</v>
           </cell>
           <cell r="H34" t="str">
             <v>SUBIÓ</v>
@@ -740,10 +742,10 @@
         </row>
         <row r="35">
           <cell r="F35">
-            <v>574.30769230769226</v>
+            <v>573.71428571428567</v>
           </cell>
           <cell r="G35">
-            <v>-8.7020322599429378E-2</v>
+            <v>-8.796366389099175E-2</v>
           </cell>
           <cell r="H35" t="str">
             <v>BAJO</v>
@@ -751,10 +753,10 @@
         </row>
         <row r="36">
           <cell r="F36">
-            <v>771.15384615384619</v>
+            <v>768.78571428571433</v>
           </cell>
           <cell r="G36">
-            <v>-9.509215639077051E-2</v>
+            <v>-9.7871032632990462E-2</v>
           </cell>
           <cell r="H36" t="str">
             <v>BAJO</v>
@@ -762,10 +764,10 @@
         </row>
         <row r="37">
           <cell r="F37">
-            <v>500.69230769230768</v>
+            <v>496</v>
           </cell>
           <cell r="G37">
-            <v>-0.13524644612727521</v>
+            <v>-0.14335060449050085</v>
           </cell>
           <cell r="H37" t="str">
             <v>BAJO</v>
@@ -773,10 +775,10 @@
         </row>
         <row r="38">
           <cell r="F38">
-            <v>4</v>
+            <v>3.8571428571428572</v>
           </cell>
           <cell r="G38">
-            <v>0.61538461538461542</v>
+            <v>0.55769230769230771</v>
           </cell>
           <cell r="H38" t="str">
             <v>SUBIÓ</v>
@@ -784,10 +786,10 @@
         </row>
         <row r="39">
           <cell r="F39">
-            <v>0.53846153846153844</v>
+            <v>0.5</v>
           </cell>
           <cell r="G39">
-            <v>0.25641025641025639</v>
+            <v>0.16666666666666674</v>
           </cell>
           <cell r="H39" t="str">
             <v>SUBIÓ</v>
@@ -795,10 +797,10 @@
         </row>
         <row r="40">
           <cell r="F40">
-            <v>142.38461538461539</v>
+            <v>138.85714285714286</v>
           </cell>
           <cell r="G40">
-            <v>3.8221153846153877E-2</v>
+            <v>1.2499999999999956E-2</v>
           </cell>
           <cell r="H40" t="str">
             <v>SUBIÓ</v>
@@ -806,10 +808,10 @@
         </row>
         <row r="41">
           <cell r="F41">
-            <v>528</v>
+            <v>527.14285714285711</v>
           </cell>
           <cell r="G41">
-            <v>-4.7668126771450714E-2</v>
+            <v>-4.9214120072146428E-2</v>
           </cell>
           <cell r="H41" t="str">
             <v>BAJO</v>
@@ -817,10 +819,10 @@
         </row>
         <row r="42">
           <cell r="F42">
-            <v>418</v>
+            <v>411.57142857142856</v>
           </cell>
           <cell r="G42">
-            <v>2.1473646468268202</v>
+            <v>2.0989602007888135</v>
           </cell>
           <cell r="H42" t="str">
             <v>SUBIÓ</v>
@@ -828,10 +830,10 @@
         </row>
         <row r="43">
           <cell r="F43">
-            <v>194.07692307692307</v>
+            <v>203.85714285714286</v>
           </cell>
           <cell r="G43">
-            <v>-0.34465100745853283</v>
+            <v>-0.31162566328991803</v>
           </cell>
           <cell r="H43" t="str">
             <v>BAJO</v>
@@ -839,10 +841,10 @@
         </row>
         <row r="44">
           <cell r="F44">
-            <v>458.30769230769232</v>
+            <v>455.64285714285717</v>
           </cell>
           <cell r="G44">
-            <v>-0.13316567247937139</v>
+            <v>-0.13820589029991881</v>
           </cell>
           <cell r="H44" t="str">
             <v>BAJO</v>
@@ -850,10 +852,10 @@
         </row>
         <row r="45">
           <cell r="F45">
-            <v>286.07692307692309</v>
+            <v>281.57142857142856</v>
           </cell>
           <cell r="G45">
-            <v>-6.3796885676268511E-2</v>
+            <v>-7.8541374474053294E-2</v>
           </cell>
           <cell r="H45" t="str">
             <v>BAJO</v>
@@ -861,10 +863,10 @@
         </row>
         <row r="46">
           <cell r="F46">
-            <v>222.61538461538461</v>
+            <v>277</v>
           </cell>
           <cell r="G46">
-            <v>-0.23210856160921867</v>
+            <v>-4.4513797634691321E-2</v>
           </cell>
           <cell r="H46" t="str">
             <v>BAJO</v>
@@ -872,10 +874,10 @@
         </row>
         <row r="47">
           <cell r="F47">
-            <v>36</v>
+            <v>55.357142857142854</v>
           </cell>
           <cell r="G47">
-            <v>-0.37623762376237624</v>
+            <v>-4.0841584158415878E-2</v>
           </cell>
           <cell r="H47" t="str">
             <v>BAJO</v>
@@ -883,21 +885,21 @@
         </row>
         <row r="48">
           <cell r="F48">
-            <v>104.53846153846153</v>
+            <v>129.21428571428572</v>
           </cell>
           <cell r="G48">
-            <v>-1.6790848987301432E-3</v>
+            <v>0.23396998635743538</v>
           </cell>
           <cell r="H48" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="49">
           <cell r="F49">
-            <v>43.153846153846153</v>
+            <v>40.071428571428569</v>
           </cell>
           <cell r="G49">
-            <v>-0.12525987525987536</v>
+            <v>-0.18774131274131278</v>
           </cell>
           <cell r="H49" t="str">
             <v>BAJO</v>
@@ -905,13 +907,13 @@
         </row>
         <row r="50">
           <cell r="F50">
-            <v>56.92307692307692</v>
+            <v>53</v>
           </cell>
           <cell r="G50">
-            <v>2.8730305838739367E-2</v>
+            <v>-4.2168674698795261E-2</v>
           </cell>
           <cell r="H50" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
       </sheetData>
@@ -1171,11 +1173,11 @@
       </c>
       <c r="E2" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F4</f>
-        <v>1221.5384615384614</v>
+        <v>1195.7857142857142</v>
       </c>
       <c r="F2" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G4</f>
-        <v>2.8148604902111796E-2</v>
+        <v>6.4729458917835991E-3</v>
       </c>
       <c r="G2" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H4</f>
@@ -1200,11 +1202,11 @@
       </c>
       <c r="E3" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F5</f>
-        <v>66.92307692307692</v>
+        <v>62.785714285714285</v>
       </c>
       <c r="F3" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G5</f>
-        <v>-0.12382505275273359</v>
+        <v>-0.17799251870324184</v>
       </c>
       <c r="G3" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H5</f>
@@ -1229,11 +1231,11 @@
       </c>
       <c r="E4" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F6</f>
-        <v>498.46153846153845</v>
+        <v>483.64285714285717</v>
       </c>
       <c r="F4" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G6</f>
-        <v>-2.1619561856967229E-2</v>
+        <v>-5.0705673427423048E-2</v>
       </c>
       <c r="G4" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H6</f>
@@ -1258,11 +1260,11 @@
       </c>
       <c r="E5" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F7</f>
-        <v>116</v>
+        <v>110.5</v>
       </c>
       <c r="F5" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G7</f>
-        <v>0.18367346938775508</v>
+        <v>0.12755102040816335</v>
       </c>
       <c r="G5" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H7</f>
@@ -1287,11 +1289,11 @@
       </c>
       <c r="E6" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F8</f>
-        <v>14.846153846153847</v>
+        <v>13.785714285714286</v>
       </c>
       <c r="F6" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G8</f>
-        <v>0.24210848912044125</v>
+        <v>0.15338645418326702</v>
       </c>
       <c r="G6" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H8</f>
@@ -1316,11 +1318,11 @@
       </c>
       <c r="E7" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F9</f>
-        <v>1438.7692307692307</v>
+        <v>1408.6428571428571</v>
       </c>
       <c r="F7" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G9</f>
-        <v>-1.4766561901919162E-2</v>
+        <v>-3.5396354387452256E-2</v>
       </c>
       <c r="G7" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H9</f>
@@ -1345,11 +1347,11 @@
       </c>
       <c r="E8" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F10</f>
-        <v>144.38461538461539</v>
+        <v>143.28571428571428</v>
       </c>
       <c r="F8" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G10</f>
-        <v>-3.9874311881911595E-2</v>
+        <v>-4.7181760607979739E-2</v>
       </c>
       <c r="G8" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H10</f>
@@ -1374,11 +1376,11 @@
       </c>
       <c r="E9" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F11</f>
-        <v>281.07692307692309</v>
+        <v>289.78571428571428</v>
       </c>
       <c r="F9" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G11</f>
-        <v>-0.18189668958899718</v>
+        <v>-0.15654885654885653</v>
       </c>
       <c r="G9" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H11</f>
@@ -1403,11 +1405,11 @@
       </c>
       <c r="E10" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F12</f>
-        <v>728.23076923076928</v>
+        <v>724.78571428571433</v>
       </c>
       <c r="F10" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G12</f>
-        <v>-4.9543433570779616E-2</v>
+        <v>-5.4039776258545613E-2</v>
       </c>
       <c r="G10" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H12</f>
@@ -1432,11 +1434,11 @@
       </c>
       <c r="E11" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F13</f>
-        <v>341.23076923076923</v>
+        <v>341.92857142857144</v>
       </c>
       <c r="F11" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G13</f>
-        <v>-5.9476814037780046E-2</v>
+        <v>-5.7553484709279346E-2</v>
       </c>
       <c r="G11" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H13</f>
@@ -1461,11 +1463,11 @@
       </c>
       <c r="E12" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F14</f>
-        <v>3441.8461538461538</v>
+        <v>3334.6428571428573</v>
       </c>
       <c r="F12" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G14</f>
-        <v>-2.2625902872549397E-2</v>
+        <v>-5.3068206404153995E-2</v>
       </c>
       <c r="G12" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H14</f>
@@ -1490,11 +1492,11 @@
       </c>
       <c r="E13" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F15</f>
-        <v>2126.0769230769229</v>
+        <v>2062.9285714285716</v>
       </c>
       <c r="F13" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G15</f>
-        <v>-7.7623894543634386E-2</v>
+        <v>-0.10502014254725744</v>
       </c>
       <c r="G13" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H15</f>
@@ -1519,11 +1521,11 @@
       </c>
       <c r="E14" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F16</f>
-        <v>2166.6923076923076</v>
+        <v>2112.3571428571427</v>
       </c>
       <c r="F14" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G16</f>
-        <v>-4.4026000892124051E-2</v>
+        <v>-6.7999411715270242E-2</v>
       </c>
       <c r="G14" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H16</f>
@@ -1548,11 +1550,11 @@
       </c>
       <c r="E15" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F17</f>
-        <v>2638.9230769230771</v>
+        <v>2573.3571428571427</v>
       </c>
       <c r="F15" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G17</f>
-        <v>-1.3117772280075823E-2</v>
+        <v>-3.7637568116251852E-2</v>
       </c>
       <c r="G15" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H17</f>
@@ -1577,11 +1579,11 @@
       </c>
       <c r="E16" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F18</f>
-        <v>694.46153846153845</v>
+        <v>678.5</v>
       </c>
       <c r="F16" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G18</f>
-        <v>0.78437444117121102</v>
+        <v>0.74336229046861613</v>
       </c>
       <c r="G16" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H18</f>
@@ -1606,11 +1608,11 @@
       </c>
       <c r="E17" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F19</f>
-        <v>788.15384615384619</v>
+        <v>769.35714285714289</v>
       </c>
       <c r="F17" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G19</f>
-        <v>0.83984334918083237</v>
+        <v>0.79596487327701193</v>
       </c>
       <c r="G17" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H19</f>
@@ -1635,11 +1637,11 @@
       </c>
       <c r="E18" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F20</f>
-        <v>837.76923076923072</v>
+        <v>818.71428571428567</v>
       </c>
       <c r="F18" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G20</f>
-        <v>1.1439378316053919</v>
+        <v>1.0951742627345844</v>
       </c>
       <c r="G18" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H20</f>
@@ -1664,11 +1666,11 @@
       </c>
       <c r="E19" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F21</f>
-        <v>250.15384615384616</v>
+        <v>243.42857142857142</v>
       </c>
       <c r="F19" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G21</f>
-        <v>3.3693579148124542E-2</v>
+        <v>5.9031877213695516E-3</v>
       </c>
       <c r="G19" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H21</f>
@@ -1693,11 +1695,11 @@
       </c>
       <c r="E20" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F22</f>
-        <v>118.38461538461539</v>
+        <v>116.14285714285714</v>
       </c>
       <c r="F20" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G22</f>
-        <v>-0.16742232984697825</v>
+        <v>-0.18318821165438726</v>
       </c>
       <c r="G20" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H22</f>
@@ -1722,11 +1724,11 @@
       </c>
       <c r="E21" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F23</f>
-        <v>497.46153846153845</v>
+        <v>483.64285714285717</v>
       </c>
       <c r="F21" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G23</f>
-        <v>-3.0469391397465628E-2</v>
+        <v>-5.7401392111368854E-2</v>
       </c>
       <c r="G21" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H23</f>
@@ -1751,11 +1753,11 @@
       </c>
       <c r="E22" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F24</f>
-        <v>821.46153846153845</v>
+        <v>813.71428571428567</v>
       </c>
       <c r="F22" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G24</f>
-        <v>1.2423986600874848E-2</v>
+        <v>2.8757556194611844E-3</v>
       </c>
       <c r="G22" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H24</f>
@@ -1780,11 +1782,11 @@
       </c>
       <c r="E23" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F25</f>
-        <v>73.84615384615384</v>
+        <v>70.857142857142861</v>
       </c>
       <c r="F23" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G25</f>
-        <v>-1.4759065584986852E-2</v>
+        <v>-5.4637865311308653E-2</v>
       </c>
       <c r="G23" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H25</f>
@@ -1809,11 +1811,11 @@
       </c>
       <c r="E24" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F26</f>
-        <v>700.76923076923072</v>
+        <v>686</v>
       </c>
       <c r="F24" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G26</f>
-        <v>-0.1106452017795464</v>
+        <v>-0.12938901311415962</v>
       </c>
       <c r="G24" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H26</f>
@@ -1838,11 +1840,11 @@
       </c>
       <c r="E25" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F27</f>
-        <v>1126.6153846153845</v>
+        <v>1077.5</v>
       </c>
       <c r="F25" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G27</f>
-        <v>-0.11548814577078381</v>
+        <v>-0.15404890085240019</v>
       </c>
       <c r="G25" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H27</f>
@@ -1867,11 +1869,11 @@
       </c>
       <c r="E26" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F28</f>
-        <v>549</v>
+        <v>539.28571428571433</v>
       </c>
       <c r="F26" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G28</f>
-        <v>3.7433636281832161E-2</v>
+        <v>1.9076756951318385E-2</v>
       </c>
       <c r="G26" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H28</f>
@@ -1896,11 +1898,11 @@
       </c>
       <c r="E27" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F29</f>
-        <v>428.84615384615387</v>
+        <v>420.28571428571428</v>
       </c>
       <c r="F27" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G29</f>
-        <v>6.716070989089129E-2</v>
+        <v>4.5858514041948073E-2</v>
       </c>
       <c r="G27" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H29</f>
@@ -1925,11 +1927,11 @@
       </c>
       <c r="E28" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F30</f>
-        <v>239.46153846153845</v>
+        <v>228.71428571428572</v>
       </c>
       <c r="F28" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G30</f>
-        <v>2.1468662751516314</v>
+        <v>2.0056320400500622</v>
       </c>
       <c r="G28" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H30</f>
@@ -1954,11 +1956,11 @@
       </c>
       <c r="E29" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F31</f>
-        <v>289.69230769230768</v>
+        <v>274.78571428571428</v>
       </c>
       <c r="F29" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G31</f>
-        <v>3.0181892084137782</v>
+        <v>2.8114266842800522</v>
       </c>
       <c r="G29" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H31</f>
@@ -1983,11 +1985,11 @@
       </c>
       <c r="E30" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F32</f>
-        <v>127</v>
+        <v>121.14285714285714</v>
       </c>
       <c r="F30" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G32</f>
-        <v>-6.7039106145251326E-3</v>
+        <v>-5.2513966480447039E-2</v>
       </c>
       <c r="G30" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H32</f>
@@ -2012,11 +2014,11 @@
       </c>
       <c r="E31" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F33</f>
-        <v>130</v>
+        <v>133.14285714285714</v>
       </c>
       <c r="F31" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G33</f>
-        <v>-9.3023255813953543E-2</v>
+        <v>-7.1096345514950254E-2</v>
       </c>
       <c r="G31" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H33</f>
@@ -2041,11 +2043,11 @@
       </c>
       <c r="E32" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F34</f>
-        <v>746.07692307692309</v>
+        <v>735.21428571428567</v>
       </c>
       <c r="F32" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G34</f>
-        <v>0.1439555625449318</v>
+        <v>0.12729994158878499</v>
       </c>
       <c r="G32" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H34</f>
@@ -2070,11 +2072,11 @@
       </c>
       <c r="E33" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F35</f>
-        <v>574.30769230769226</v>
+        <v>573.71428571428567</v>
       </c>
       <c r="F33" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G35</f>
-        <v>-8.7020322599429378E-2</v>
+        <v>-8.796366389099175E-2</v>
       </c>
       <c r="G33" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H35</f>
@@ -2099,11 +2101,11 @@
       </c>
       <c r="E34" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F36</f>
-        <v>771.15384615384619</v>
+        <v>768.78571428571433</v>
       </c>
       <c r="F34" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G36</f>
-        <v>-9.509215639077051E-2</v>
+        <v>-9.7871032632990462E-2</v>
       </c>
       <c r="G34" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H36</f>
@@ -2128,11 +2130,11 @@
       </c>
       <c r="E35" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F37</f>
-        <v>500.69230769230768</v>
+        <v>496</v>
       </c>
       <c r="F35" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G37</f>
-        <v>-0.13524644612727521</v>
+        <v>-0.14335060449050085</v>
       </c>
       <c r="G35" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H37</f>
@@ -2157,11 +2159,11 @@
       </c>
       <c r="E36" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F38</f>
-        <v>4</v>
+        <v>3.8571428571428572</v>
       </c>
       <c r="F36" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G38</f>
-        <v>0.61538461538461542</v>
+        <v>0.55769230769230771</v>
       </c>
       <c r="G36" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H38</f>
@@ -2186,11 +2188,11 @@
       </c>
       <c r="E37" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F39</f>
-        <v>0.53846153846153844</v>
+        <v>0.5</v>
       </c>
       <c r="F37" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G39</f>
-        <v>0.25641025641025639</v>
+        <v>0.16666666666666674</v>
       </c>
       <c r="G37" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H39</f>
@@ -2215,11 +2217,11 @@
       </c>
       <c r="E38" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F40</f>
-        <v>142.38461538461539</v>
+        <v>138.85714285714286</v>
       </c>
       <c r="F38" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G40</f>
-        <v>3.8221153846153877E-2</v>
+        <v>1.2499999999999956E-2</v>
       </c>
       <c r="G38" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H40</f>
@@ -2244,11 +2246,11 @@
       </c>
       <c r="E39" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F41</f>
-        <v>528</v>
+        <v>527.14285714285711</v>
       </c>
       <c r="F39" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G41</f>
-        <v>-4.7668126771450714E-2</v>
+        <v>-4.9214120072146428E-2</v>
       </c>
       <c r="G39" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H41</f>
@@ -2273,11 +2275,11 @@
       </c>
       <c r="E40" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F42</f>
-        <v>418</v>
+        <v>411.57142857142856</v>
       </c>
       <c r="F40" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G42</f>
-        <v>2.1473646468268202</v>
+        <v>2.0989602007888135</v>
       </c>
       <c r="G40" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H42</f>
@@ -2302,11 +2304,11 @@
       </c>
       <c r="E41" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F43</f>
-        <v>194.07692307692307</v>
+        <v>203.85714285714286</v>
       </c>
       <c r="F41" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G43</f>
-        <v>-0.34465100745853283</v>
+        <v>-0.31162566328991803</v>
       </c>
       <c r="G41" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H43</f>
@@ -2331,11 +2333,11 @@
       </c>
       <c r="E42" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F44</f>
-        <v>458.30769230769232</v>
+        <v>455.64285714285717</v>
       </c>
       <c r="F42" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G44</f>
-        <v>-0.13316567247937139</v>
+        <v>-0.13820589029991881</v>
       </c>
       <c r="G42" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H44</f>
@@ -2360,11 +2362,11 @@
       </c>
       <c r="E43" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F45</f>
-        <v>286.07692307692309</v>
+        <v>281.57142857142856</v>
       </c>
       <c r="F43" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G45</f>
-        <v>-6.3796885676268511E-2</v>
+        <v>-7.8541374474053294E-2</v>
       </c>
       <c r="G43" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H45</f>
@@ -2389,11 +2391,11 @@
       </c>
       <c r="E44" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F46</f>
-        <v>222.61538461538461</v>
+        <v>277</v>
       </c>
       <c r="F44" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G46</f>
-        <v>-0.23210856160921867</v>
+        <v>-4.4513797634691321E-2</v>
       </c>
       <c r="G44" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H46</f>
@@ -2418,11 +2420,11 @@
       </c>
       <c r="E45" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F47</f>
-        <v>36</v>
+        <v>55.357142857142854</v>
       </c>
       <c r="F45" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G47</f>
-        <v>-0.37623762376237624</v>
+        <v>-4.0841584158415878E-2</v>
       </c>
       <c r="G45" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H47</f>
@@ -2447,15 +2449,15 @@
       </c>
       <c r="E46" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F48</f>
-        <v>104.53846153846153</v>
+        <v>129.21428571428572</v>
       </c>
       <c r="F46" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G48</f>
-        <v>-1.6790848987301432E-3</v>
+        <v>0.23396998635743538</v>
       </c>
       <c r="G46" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H48</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H46">
         <v>2.62</v>
@@ -2476,11 +2478,11 @@
       </c>
       <c r="E47" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F49</f>
-        <v>43.153846153846153</v>
+        <v>40.071428571428569</v>
       </c>
       <c r="F47" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G49</f>
-        <v>-0.12525987525987536</v>
+        <v>-0.18774131274131278</v>
       </c>
       <c r="G47" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H49</f>
@@ -2505,15 +2507,15 @@
       </c>
       <c r="E48" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F50</f>
-        <v>56.92307692307692</v>
+        <v>53</v>
       </c>
       <c r="F48" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G50</f>
-        <v>2.8730305838739367E-2</v>
+        <v>-4.2168674698795261E-2</v>
       </c>
       <c r="G48" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H50</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H48">
         <v>2.62</v>

--- a/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
+++ b/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7A7DA80-DE7B-4557-9457-EFF0F7003C16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B234038D-3495-4A68-9664-1B33A7C05584}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -373,7 +373,8 @@
       <sheetName val="INVENTARIO NACIONAL 17-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 17-09-16;15"/>
       <sheetName val="INVENTARIO NACIONAL 18-09-26"/>
-      <sheetName val="INVENTARIO NACIONAL 20-09-26"/>
+      <sheetName val="INVENTARIO NACIONAL 21-09-26"/>
+      <sheetName val="INVENTARIO NACIONAL 22-09-26"/>
       <sheetName val="CCC"/>
       <sheetName val="VINCULO VTS BY SKU AGOSTO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
@@ -398,13 +399,14 @@
       <sheetData sheetId="15"/>
       <sheetData sheetId="16"/>
       <sheetData sheetId="17"/>
-      <sheetData sheetId="18">
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19">
         <row r="4">
           <cell r="F4">
-            <v>1195.7857142857142</v>
+            <v>1204.6666666666667</v>
           </cell>
           <cell r="G4">
-            <v>6.4729458917835991E-3</v>
+            <v>1.3947895791583287E-2</v>
           </cell>
           <cell r="H4" t="str">
             <v>SUBIÓ</v>
@@ -412,10 +414,10 @@
         </row>
         <row r="5">
           <cell r="F5">
-            <v>62.785714285714285</v>
+            <v>59.06666666666667</v>
           </cell>
           <cell r="G5">
-            <v>-0.17799251870324184</v>
+            <v>-0.22668329177057356</v>
           </cell>
           <cell r="H5" t="str">
             <v>BAJO</v>
@@ -423,10 +425,10 @@
         </row>
         <row r="6">
           <cell r="F6">
-            <v>483.64285714285717</v>
+            <v>495.13333333333333</v>
           </cell>
           <cell r="G6">
-            <v>-5.0705673427423048E-2</v>
+            <v>-2.8152163753621839E-2</v>
           </cell>
           <cell r="H6" t="str">
             <v>BAJO</v>
@@ -434,10 +436,10 @@
         </row>
         <row r="7">
           <cell r="F7">
-            <v>110.5</v>
+            <v>105.4</v>
           </cell>
           <cell r="G7">
-            <v>0.12755102040816335</v>
+            <v>7.551020408163267E-2</v>
           </cell>
           <cell r="H7" t="str">
             <v>SUBIÓ</v>
@@ -445,10 +447,10 @@
         </row>
         <row r="8">
           <cell r="F8">
-            <v>13.785714285714286</v>
+            <v>13.2</v>
           </cell>
           <cell r="G8">
-            <v>0.15338645418326702</v>
+            <v>0.10438247011952173</v>
           </cell>
           <cell r="H8" t="str">
             <v>SUBIÓ</v>
@@ -456,10 +458,10 @@
         </row>
         <row r="9">
           <cell r="F9">
-            <v>1408.6428571428571</v>
+            <v>1422.2666666666667</v>
           </cell>
           <cell r="G9">
-            <v>-3.5396354387452256E-2</v>
+            <v>-2.6067107966217695E-2</v>
           </cell>
           <cell r="H9" t="str">
             <v>BAJO</v>
@@ -467,10 +469,10 @@
         </row>
         <row r="10">
           <cell r="F10">
-            <v>143.28571428571428</v>
+            <v>143.33333333333334</v>
           </cell>
           <cell r="G10">
-            <v>-4.7181760607979739E-2</v>
+            <v>-4.6865104496516707E-2</v>
           </cell>
           <cell r="H10" t="str">
             <v>BAJO</v>
@@ -478,10 +480,10 @@
         </row>
         <row r="11">
           <cell r="F11">
-            <v>289.78571428571428</v>
+            <v>295.66666666666669</v>
           </cell>
           <cell r="G11">
-            <v>-0.15654885654885653</v>
+            <v>-0.13943173943173937</v>
           </cell>
           <cell r="H11" t="str">
             <v>BAJO</v>
@@ -489,10 +491,10 @@
         </row>
         <row r="12">
           <cell r="F12">
-            <v>724.78571428571433</v>
+            <v>739.6</v>
           </cell>
           <cell r="G12">
-            <v>-5.4039776258545613E-2</v>
+            <v>-3.4704785581106234E-2</v>
           </cell>
           <cell r="H12" t="str">
             <v>BAJO</v>
@@ -500,10 +502,10 @@
         </row>
         <row r="13">
           <cell r="F13">
-            <v>341.92857142857144</v>
+            <v>351.26666666666665</v>
           </cell>
           <cell r="G13">
-            <v>-5.7553484709279346E-2</v>
+            <v>-3.1815198844992731E-2</v>
           </cell>
           <cell r="H13" t="str">
             <v>BAJO</v>
@@ -511,10 +513,10 @@
         </row>
         <row r="14">
           <cell r="F14">
-            <v>3334.6428571428573</v>
+            <v>3358.6</v>
           </cell>
           <cell r="G14">
-            <v>-5.3068206404153995E-2</v>
+            <v>-4.6265144958892335E-2</v>
           </cell>
           <cell r="H14" t="str">
             <v>BAJO</v>
@@ -522,10 +524,10 @@
         </row>
         <row r="15">
           <cell r="F15">
-            <v>2062.9285714285716</v>
+            <v>2080.5333333333333</v>
           </cell>
           <cell r="G15">
-            <v>-0.10502014254725744</v>
+            <v>-9.7382501807664501E-2</v>
           </cell>
           <cell r="H15" t="str">
             <v>BAJO</v>
@@ -533,10 +535,10 @@
         </row>
         <row r="16">
           <cell r="F16">
-            <v>2112.3571428571427</v>
+            <v>2120.8000000000002</v>
           </cell>
           <cell r="G16">
-            <v>-6.7999411715270242E-2</v>
+            <v>-6.4274308765442378E-2</v>
           </cell>
           <cell r="H16" t="str">
             <v>BAJO</v>
@@ -544,10 +546,10 @@
         </row>
         <row r="17">
           <cell r="F17">
-            <v>2573.3571428571427</v>
+            <v>2601.8666666666668</v>
           </cell>
           <cell r="G17">
-            <v>-3.7637568116251852E-2</v>
+            <v>-2.6975816504612227E-2</v>
           </cell>
           <cell r="H17" t="str">
             <v>BAJO</v>
@@ -555,10 +557,10 @@
         </row>
         <row r="18">
           <cell r="F18">
-            <v>678.5</v>
+            <v>682.13333333333333</v>
           </cell>
           <cell r="G18">
-            <v>0.74336229046861613</v>
+            <v>0.75269790774501399</v>
           </cell>
           <cell r="H18" t="str">
             <v>SUBIÓ</v>
@@ -566,10 +568,10 @@
         </row>
         <row r="19">
           <cell r="F19">
-            <v>769.35714285714289</v>
+            <v>781.8</v>
           </cell>
           <cell r="G19">
-            <v>0.79596487327701193</v>
+            <v>0.82501111605157829</v>
           </cell>
           <cell r="H19" t="str">
             <v>SUBIÓ</v>
@@ -577,10 +579,10 @@
         </row>
         <row r="20">
           <cell r="F20">
-            <v>818.71428571428567</v>
+            <v>831.73333333333335</v>
           </cell>
           <cell r="G20">
-            <v>1.0951742627345844</v>
+            <v>1.1284913477942968</v>
           </cell>
           <cell r="H20" t="str">
             <v>SUBIÓ</v>
@@ -588,10 +590,10 @@
         </row>
         <row r="21">
           <cell r="F21">
-            <v>243.42857142857142</v>
+            <v>257.8</v>
           </cell>
           <cell r="G21">
-            <v>5.9031877213695516E-3</v>
+            <v>6.5289256198347134E-2</v>
           </cell>
           <cell r="H21" t="str">
             <v>SUBIÓ</v>
@@ -599,10 +601,10 @@
         </row>
         <row r="22">
           <cell r="F22">
-            <v>116.14285714285714</v>
+            <v>120.86666666666666</v>
           </cell>
           <cell r="G22">
-            <v>-0.18318821165438726</v>
+            <v>-0.14996651038178177</v>
           </cell>
           <cell r="H22" t="str">
             <v>BAJO</v>
@@ -610,10 +612,10 @@
         </row>
         <row r="23">
           <cell r="F23">
-            <v>483.64285714285717</v>
+            <v>497.13333333333333</v>
           </cell>
           <cell r="G23">
-            <v>-5.7401392111368854E-2</v>
+            <v>-3.1109048723897859E-2</v>
           </cell>
           <cell r="H23" t="str">
             <v>BAJO</v>
@@ -621,10 +623,10 @@
         </row>
         <row r="24">
           <cell r="F24">
-            <v>813.71428571428567</v>
+            <v>828.4666666666667</v>
           </cell>
           <cell r="G24">
-            <v>2.8757556194611844E-3</v>
+            <v>2.1057573801279483E-2</v>
           </cell>
           <cell r="H24" t="str">
             <v>SUBIÓ</v>
@@ -632,10 +634,10 @@
         </row>
         <row r="25">
           <cell r="F25">
-            <v>70.857142857142861</v>
+            <v>68.8</v>
           </cell>
           <cell r="G25">
-            <v>-5.4637865311308653E-2</v>
+            <v>-8.2083862770012672E-2</v>
           </cell>
           <cell r="H25" t="str">
             <v>BAJO</v>
@@ -643,10 +645,10 @@
         </row>
         <row r="26">
           <cell r="F26">
-            <v>686</v>
+            <v>696.66666666666663</v>
           </cell>
           <cell r="G26">
-            <v>-0.12938901311415962</v>
+            <v>-0.11585181603916128</v>
           </cell>
           <cell r="H26" t="str">
             <v>BAJO</v>
@@ -654,10 +656,10 @@
         </row>
         <row r="27">
           <cell r="F27">
-            <v>1077.5</v>
+            <v>1084.8</v>
           </cell>
           <cell r="G27">
-            <v>-0.15404890085240019</v>
+            <v>-0.1483176312247646</v>
           </cell>
           <cell r="H27" t="str">
             <v>BAJO</v>
@@ -665,10 +667,10 @@
         </row>
         <row r="28">
           <cell r="F28">
-            <v>539.28571428571433</v>
+            <v>540.79999999999995</v>
           </cell>
           <cell r="G28">
-            <v>1.9076756951318385E-2</v>
+            <v>2.1938270494016088E-2</v>
           </cell>
           <cell r="H28" t="str">
             <v>SUBIÓ</v>
@@ -676,10 +678,10 @@
         </row>
         <row r="29">
           <cell r="F29">
-            <v>420.28571428571428</v>
+            <v>409.93333333333334</v>
           </cell>
           <cell r="G29">
-            <v>4.5858514041948073E-2</v>
+            <v>2.009716791088989E-2</v>
           </cell>
           <cell r="H29" t="str">
             <v>SUBIÓ</v>
@@ -687,10 +689,10 @@
         </row>
         <row r="30">
           <cell r="F30">
-            <v>228.71428571428572</v>
+            <v>243.33333333333334</v>
           </cell>
           <cell r="G30">
-            <v>2.0056320400500622</v>
+            <v>2.1977471839799749</v>
           </cell>
           <cell r="H30" t="str">
             <v>SUBIÓ</v>
@@ -698,10 +700,10 @@
         </row>
         <row r="31">
           <cell r="F31">
-            <v>274.78571428571428</v>
+            <v>299.73333333333335</v>
           </cell>
           <cell r="G31">
-            <v>2.8114266842800522</v>
+            <v>3.1574636723910166</v>
           </cell>
           <cell r="H31" t="str">
             <v>SUBIÓ</v>
@@ -709,10 +711,10 @@
         </row>
         <row r="32">
           <cell r="F32">
-            <v>121.14285714285714</v>
+            <v>124.06666666666666</v>
           </cell>
           <cell r="G32">
-            <v>-5.2513966480447039E-2</v>
+            <v>-2.9646182495344564E-2</v>
           </cell>
           <cell r="H32" t="str">
             <v>BAJO</v>
@@ -720,10 +722,10 @@
         </row>
         <row r="33">
           <cell r="F33">
-            <v>133.14285714285714</v>
+            <v>134.33333333333334</v>
           </cell>
           <cell r="G33">
-            <v>-7.1096345514950254E-2</v>
+            <v>-6.2790697674418583E-2</v>
           </cell>
           <cell r="H33" t="str">
             <v>BAJO</v>
@@ -731,10 +733,10 @@
         </row>
         <row r="34">
           <cell r="F34">
-            <v>735.21428571428567</v>
+            <v>738.33333333333337</v>
           </cell>
           <cell r="G34">
-            <v>0.12729994158878499</v>
+            <v>0.13208235981308425</v>
           </cell>
           <cell r="H34" t="str">
             <v>SUBIÓ</v>
@@ -742,10 +744,10 @@
         </row>
         <row r="35">
           <cell r="F35">
-            <v>573.71428571428567</v>
+            <v>583.26666666666665</v>
           </cell>
           <cell r="G35">
-            <v>-8.796366389099175E-2</v>
+            <v>-7.2778198334594979E-2</v>
           </cell>
           <cell r="H35" t="str">
             <v>BAJO</v>
@@ -753,10 +755,10 @@
         </row>
         <row r="36">
           <cell r="F36">
-            <v>768.78571428571433</v>
+            <v>773</v>
           </cell>
           <cell r="G36">
-            <v>-9.7871032632990462E-2</v>
+            <v>-9.2925793473401797E-2</v>
           </cell>
           <cell r="H36" t="str">
             <v>BAJO</v>
@@ -764,10 +766,10 @@
         </row>
         <row r="37">
           <cell r="F37">
-            <v>496</v>
+            <v>506.46666666666664</v>
           </cell>
           <cell r="G37">
-            <v>-0.14335060449050085</v>
+            <v>-0.12527345998848594</v>
           </cell>
           <cell r="H37" t="str">
             <v>BAJO</v>
@@ -775,10 +777,10 @@
         </row>
         <row r="38">
           <cell r="F38">
-            <v>3.8571428571428572</v>
+            <v>3.6666666666666665</v>
           </cell>
           <cell r="G38">
-            <v>0.55769230769230771</v>
+            <v>0.48076923076923062</v>
           </cell>
           <cell r="H38" t="str">
             <v>SUBIÓ</v>
@@ -786,10 +788,10 @@
         </row>
         <row r="39">
           <cell r="F39">
-            <v>0.5</v>
+            <v>0.46666666666666667</v>
           </cell>
           <cell r="G39">
-            <v>0.16666666666666674</v>
+            <v>8.8888888888889017E-2</v>
           </cell>
           <cell r="H39" t="str">
             <v>SUBIÓ</v>
@@ -797,10 +799,10 @@
         </row>
         <row r="40">
           <cell r="F40">
-            <v>138.85714285714286</v>
+            <v>142.06666666666666</v>
           </cell>
           <cell r="G40">
-            <v>1.2499999999999956E-2</v>
+            <v>3.5902777777777839E-2</v>
           </cell>
           <cell r="H40" t="str">
             <v>SUBIÓ</v>
@@ -808,10 +810,10 @@
         </row>
         <row r="41">
           <cell r="F41">
-            <v>527.14285714285711</v>
+            <v>539.86666666666667</v>
           </cell>
           <cell r="G41">
-            <v>-4.9214120072146428E-2</v>
+            <v>-2.6264708408485826E-2</v>
           </cell>
           <cell r="H41" t="str">
             <v>BAJO</v>
@@ -819,10 +821,10 @@
         </row>
         <row r="42">
           <cell r="F42">
-            <v>411.57142857142856</v>
+            <v>410.46666666666664</v>
           </cell>
           <cell r="G42">
-            <v>2.0989602007888135</v>
+            <v>2.0906418070993187</v>
           </cell>
           <cell r="H42" t="str">
             <v>SUBIÓ</v>
@@ -830,10 +832,10 @@
         </row>
         <row r="43">
           <cell r="F43">
-            <v>203.85714285714286</v>
+            <v>208.33333333333334</v>
           </cell>
           <cell r="G43">
-            <v>-0.31162566328991803</v>
+            <v>-0.29651069303746591</v>
           </cell>
           <cell r="H43" t="str">
             <v>BAJO</v>
@@ -841,10 +843,10 @@
         </row>
         <row r="44">
           <cell r="F44">
-            <v>455.64285714285717</v>
+            <v>472.2</v>
           </cell>
           <cell r="G44">
-            <v>-0.13820589029991881</v>
+            <v>-0.10689002972169681</v>
           </cell>
           <cell r="H44" t="str">
             <v>BAJO</v>
@@ -852,10 +854,10 @@
         </row>
         <row r="45">
           <cell r="F45">
-            <v>281.57142857142856</v>
+            <v>280.93333333333334</v>
           </cell>
           <cell r="G45">
-            <v>-7.8541374474053294E-2</v>
+            <v>-8.0629577684276033E-2</v>
           </cell>
           <cell r="H45" t="str">
             <v>BAJO</v>
@@ -863,10 +865,10 @@
         </row>
         <row r="46">
           <cell r="F46">
-            <v>277</v>
+            <v>283.86666666666667</v>
           </cell>
           <cell r="G46">
-            <v>-4.4513797634691321E-2</v>
+            <v>-2.0827858081471806E-2</v>
           </cell>
           <cell r="H46" t="str">
             <v>BAJO</v>
@@ -874,21 +876,21 @@
         </row>
         <row r="47">
           <cell r="F47">
-            <v>55.357142857142854</v>
+            <v>57.8</v>
           </cell>
           <cell r="G47">
-            <v>-4.0841584158415878E-2</v>
+            <v>1.4851485148514865E-3</v>
           </cell>
           <cell r="H47" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="48">
           <cell r="F48">
-            <v>129.21428571428572</v>
+            <v>130.26666666666668</v>
           </cell>
           <cell r="G48">
-            <v>0.23396998635743538</v>
+            <v>0.24402000909504351</v>
           </cell>
           <cell r="H48" t="str">
             <v>SUBIÓ</v>
@@ -896,10 +898,10 @@
         </row>
         <row r="49">
           <cell r="F49">
-            <v>40.071428571428569</v>
+            <v>43.866666666666667</v>
           </cell>
           <cell r="G49">
-            <v>-0.18774131274131278</v>
+            <v>-0.11081081081081079</v>
           </cell>
           <cell r="H49" t="str">
             <v>BAJO</v>
@@ -907,10 +909,10 @@
         </row>
         <row r="50">
           <cell r="F50">
-            <v>53</v>
+            <v>52.733333333333334</v>
           </cell>
           <cell r="G50">
-            <v>-4.2168674698795261E-2</v>
+            <v>-4.6987951807228923E-2</v>
           </cell>
           <cell r="H50" t="str">
             <v>BAJO</v>
@@ -1173,11 +1175,11 @@
       </c>
       <c r="E2" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F4</f>
-        <v>1195.7857142857142</v>
+        <v>1204.6666666666667</v>
       </c>
       <c r="F2" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G4</f>
-        <v>6.4729458917835991E-3</v>
+        <v>1.3947895791583287E-2</v>
       </c>
       <c r="G2" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H4</f>
@@ -1202,11 +1204,11 @@
       </c>
       <c r="E3" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F5</f>
-        <v>62.785714285714285</v>
+        <v>59.06666666666667</v>
       </c>
       <c r="F3" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G5</f>
-        <v>-0.17799251870324184</v>
+        <v>-0.22668329177057356</v>
       </c>
       <c r="G3" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H5</f>
@@ -1231,11 +1233,11 @@
       </c>
       <c r="E4" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F6</f>
-        <v>483.64285714285717</v>
+        <v>495.13333333333333</v>
       </c>
       <c r="F4" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G6</f>
-        <v>-5.0705673427423048E-2</v>
+        <v>-2.8152163753621839E-2</v>
       </c>
       <c r="G4" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H6</f>
@@ -1260,11 +1262,11 @@
       </c>
       <c r="E5" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F7</f>
-        <v>110.5</v>
+        <v>105.4</v>
       </c>
       <c r="F5" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G7</f>
-        <v>0.12755102040816335</v>
+        <v>7.551020408163267E-2</v>
       </c>
       <c r="G5" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H7</f>
@@ -1289,11 +1291,11 @@
       </c>
       <c r="E6" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F8</f>
-        <v>13.785714285714286</v>
+        <v>13.2</v>
       </c>
       <c r="F6" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G8</f>
-        <v>0.15338645418326702</v>
+        <v>0.10438247011952173</v>
       </c>
       <c r="G6" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H8</f>
@@ -1318,11 +1320,11 @@
       </c>
       <c r="E7" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F9</f>
-        <v>1408.6428571428571</v>
+        <v>1422.2666666666667</v>
       </c>
       <c r="F7" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G9</f>
-        <v>-3.5396354387452256E-2</v>
+        <v>-2.6067107966217695E-2</v>
       </c>
       <c r="G7" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H9</f>
@@ -1347,11 +1349,11 @@
       </c>
       <c r="E8" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F10</f>
-        <v>143.28571428571428</v>
+        <v>143.33333333333334</v>
       </c>
       <c r="F8" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G10</f>
-        <v>-4.7181760607979739E-2</v>
+        <v>-4.6865104496516707E-2</v>
       </c>
       <c r="G8" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H10</f>
@@ -1376,11 +1378,11 @@
       </c>
       <c r="E9" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F11</f>
-        <v>289.78571428571428</v>
+        <v>295.66666666666669</v>
       </c>
       <c r="F9" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G11</f>
-        <v>-0.15654885654885653</v>
+        <v>-0.13943173943173937</v>
       </c>
       <c r="G9" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H11</f>
@@ -1405,11 +1407,11 @@
       </c>
       <c r="E10" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F12</f>
-        <v>724.78571428571433</v>
+        <v>739.6</v>
       </c>
       <c r="F10" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G12</f>
-        <v>-5.4039776258545613E-2</v>
+        <v>-3.4704785581106234E-2</v>
       </c>
       <c r="G10" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H12</f>
@@ -1434,11 +1436,11 @@
       </c>
       <c r="E11" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F13</f>
-        <v>341.92857142857144</v>
+        <v>351.26666666666665</v>
       </c>
       <c r="F11" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G13</f>
-        <v>-5.7553484709279346E-2</v>
+        <v>-3.1815198844992731E-2</v>
       </c>
       <c r="G11" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H13</f>
@@ -1463,11 +1465,11 @@
       </c>
       <c r="E12" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F14</f>
-        <v>3334.6428571428573</v>
+        <v>3358.6</v>
       </c>
       <c r="F12" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G14</f>
-        <v>-5.3068206404153995E-2</v>
+        <v>-4.6265144958892335E-2</v>
       </c>
       <c r="G12" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H14</f>
@@ -1492,11 +1494,11 @@
       </c>
       <c r="E13" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F15</f>
-        <v>2062.9285714285716</v>
+        <v>2080.5333333333333</v>
       </c>
       <c r="F13" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G15</f>
-        <v>-0.10502014254725744</v>
+        <v>-9.7382501807664501E-2</v>
       </c>
       <c r="G13" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H15</f>
@@ -1521,11 +1523,11 @@
       </c>
       <c r="E14" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F16</f>
-        <v>2112.3571428571427</v>
+        <v>2120.8000000000002</v>
       </c>
       <c r="F14" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G16</f>
-        <v>-6.7999411715270242E-2</v>
+        <v>-6.4274308765442378E-2</v>
       </c>
       <c r="G14" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H16</f>
@@ -1550,11 +1552,11 @@
       </c>
       <c r="E15" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F17</f>
-        <v>2573.3571428571427</v>
+        <v>2601.8666666666668</v>
       </c>
       <c r="F15" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G17</f>
-        <v>-3.7637568116251852E-2</v>
+        <v>-2.6975816504612227E-2</v>
       </c>
       <c r="G15" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H17</f>
@@ -1579,11 +1581,11 @@
       </c>
       <c r="E16" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F18</f>
-        <v>678.5</v>
+        <v>682.13333333333333</v>
       </c>
       <c r="F16" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G18</f>
-        <v>0.74336229046861613</v>
+        <v>0.75269790774501399</v>
       </c>
       <c r="G16" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H18</f>
@@ -1608,11 +1610,11 @@
       </c>
       <c r="E17" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F19</f>
-        <v>769.35714285714289</v>
+        <v>781.8</v>
       </c>
       <c r="F17" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G19</f>
-        <v>0.79596487327701193</v>
+        <v>0.82501111605157829</v>
       </c>
       <c r="G17" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H19</f>
@@ -1637,11 +1639,11 @@
       </c>
       <c r="E18" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F20</f>
-        <v>818.71428571428567</v>
+        <v>831.73333333333335</v>
       </c>
       <c r="F18" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G20</f>
-        <v>1.0951742627345844</v>
+        <v>1.1284913477942968</v>
       </c>
       <c r="G18" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H20</f>
@@ -1666,11 +1668,11 @@
       </c>
       <c r="E19" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F21</f>
-        <v>243.42857142857142</v>
+        <v>257.8</v>
       </c>
       <c r="F19" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G21</f>
-        <v>5.9031877213695516E-3</v>
+        <v>6.5289256198347134E-2</v>
       </c>
       <c r="G19" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H21</f>
@@ -1695,11 +1697,11 @@
       </c>
       <c r="E20" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F22</f>
-        <v>116.14285714285714</v>
+        <v>120.86666666666666</v>
       </c>
       <c r="F20" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G22</f>
-        <v>-0.18318821165438726</v>
+        <v>-0.14996651038178177</v>
       </c>
       <c r="G20" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H22</f>
@@ -1724,11 +1726,11 @@
       </c>
       <c r="E21" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F23</f>
-        <v>483.64285714285717</v>
+        <v>497.13333333333333</v>
       </c>
       <c r="F21" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G23</f>
-        <v>-5.7401392111368854E-2</v>
+        <v>-3.1109048723897859E-2</v>
       </c>
       <c r="G21" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H23</f>
@@ -1753,11 +1755,11 @@
       </c>
       <c r="E22" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F24</f>
-        <v>813.71428571428567</v>
+        <v>828.4666666666667</v>
       </c>
       <c r="F22" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G24</f>
-        <v>2.8757556194611844E-3</v>
+        <v>2.1057573801279483E-2</v>
       </c>
       <c r="G22" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H24</f>
@@ -1782,11 +1784,11 @@
       </c>
       <c r="E23" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F25</f>
-        <v>70.857142857142861</v>
+        <v>68.8</v>
       </c>
       <c r="F23" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G25</f>
-        <v>-5.4637865311308653E-2</v>
+        <v>-8.2083862770012672E-2</v>
       </c>
       <c r="G23" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H25</f>
@@ -1811,11 +1813,11 @@
       </c>
       <c r="E24" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F26</f>
-        <v>686</v>
+        <v>696.66666666666663</v>
       </c>
       <c r="F24" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G26</f>
-        <v>-0.12938901311415962</v>
+        <v>-0.11585181603916128</v>
       </c>
       <c r="G24" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H26</f>
@@ -1840,11 +1842,11 @@
       </c>
       <c r="E25" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F27</f>
-        <v>1077.5</v>
+        <v>1084.8</v>
       </c>
       <c r="F25" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G27</f>
-        <v>-0.15404890085240019</v>
+        <v>-0.1483176312247646</v>
       </c>
       <c r="G25" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H27</f>
@@ -1869,11 +1871,11 @@
       </c>
       <c r="E26" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F28</f>
-        <v>539.28571428571433</v>
+        <v>540.79999999999995</v>
       </c>
       <c r="F26" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G28</f>
-        <v>1.9076756951318385E-2</v>
+        <v>2.1938270494016088E-2</v>
       </c>
       <c r="G26" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H28</f>
@@ -1898,11 +1900,11 @@
       </c>
       <c r="E27" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F29</f>
-        <v>420.28571428571428</v>
+        <v>409.93333333333334</v>
       </c>
       <c r="F27" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G29</f>
-        <v>4.5858514041948073E-2</v>
+        <v>2.009716791088989E-2</v>
       </c>
       <c r="G27" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H29</f>
@@ -1927,11 +1929,11 @@
       </c>
       <c r="E28" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F30</f>
-        <v>228.71428571428572</v>
+        <v>243.33333333333334</v>
       </c>
       <c r="F28" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G30</f>
-        <v>2.0056320400500622</v>
+        <v>2.1977471839799749</v>
       </c>
       <c r="G28" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H30</f>
@@ -1956,11 +1958,11 @@
       </c>
       <c r="E29" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F31</f>
-        <v>274.78571428571428</v>
+        <v>299.73333333333335</v>
       </c>
       <c r="F29" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G31</f>
-        <v>2.8114266842800522</v>
+        <v>3.1574636723910166</v>
       </c>
       <c r="G29" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H31</f>
@@ -1985,11 +1987,11 @@
       </c>
       <c r="E30" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F32</f>
-        <v>121.14285714285714</v>
+        <v>124.06666666666666</v>
       </c>
       <c r="F30" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G32</f>
-        <v>-5.2513966480447039E-2</v>
+        <v>-2.9646182495344564E-2</v>
       </c>
       <c r="G30" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H32</f>
@@ -2014,11 +2016,11 @@
       </c>
       <c r="E31" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F33</f>
-        <v>133.14285714285714</v>
+        <v>134.33333333333334</v>
       </c>
       <c r="F31" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G33</f>
-        <v>-7.1096345514950254E-2</v>
+        <v>-6.2790697674418583E-2</v>
       </c>
       <c r="G31" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H33</f>
@@ -2043,11 +2045,11 @@
       </c>
       <c r="E32" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F34</f>
-        <v>735.21428571428567</v>
+        <v>738.33333333333337</v>
       </c>
       <c r="F32" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G34</f>
-        <v>0.12729994158878499</v>
+        <v>0.13208235981308425</v>
       </c>
       <c r="G32" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H34</f>
@@ -2072,11 +2074,11 @@
       </c>
       <c r="E33" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F35</f>
-        <v>573.71428571428567</v>
+        <v>583.26666666666665</v>
       </c>
       <c r="F33" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G35</f>
-        <v>-8.796366389099175E-2</v>
+        <v>-7.2778198334594979E-2</v>
       </c>
       <c r="G33" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H35</f>
@@ -2101,11 +2103,11 @@
       </c>
       <c r="E34" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F36</f>
-        <v>768.78571428571433</v>
+        <v>773</v>
       </c>
       <c r="F34" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G36</f>
-        <v>-9.7871032632990462E-2</v>
+        <v>-9.2925793473401797E-2</v>
       </c>
       <c r="G34" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H36</f>
@@ -2130,11 +2132,11 @@
       </c>
       <c r="E35" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F37</f>
-        <v>496</v>
+        <v>506.46666666666664</v>
       </c>
       <c r="F35" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G37</f>
-        <v>-0.14335060449050085</v>
+        <v>-0.12527345998848594</v>
       </c>
       <c r="G35" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H37</f>
@@ -2159,11 +2161,11 @@
       </c>
       <c r="E36" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F38</f>
-        <v>3.8571428571428572</v>
+        <v>3.6666666666666665</v>
       </c>
       <c r="F36" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G38</f>
-        <v>0.55769230769230771</v>
+        <v>0.48076923076923062</v>
       </c>
       <c r="G36" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H38</f>
@@ -2188,11 +2190,11 @@
       </c>
       <c r="E37" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F39</f>
-        <v>0.5</v>
+        <v>0.46666666666666667</v>
       </c>
       <c r="F37" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G39</f>
-        <v>0.16666666666666674</v>
+        <v>8.8888888888889017E-2</v>
       </c>
       <c r="G37" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H39</f>
@@ -2217,11 +2219,11 @@
       </c>
       <c r="E38" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F40</f>
-        <v>138.85714285714286</v>
+        <v>142.06666666666666</v>
       </c>
       <c r="F38" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G40</f>
-        <v>1.2499999999999956E-2</v>
+        <v>3.5902777777777839E-2</v>
       </c>
       <c r="G38" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H40</f>
@@ -2246,11 +2248,11 @@
       </c>
       <c r="E39" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F41</f>
-        <v>527.14285714285711</v>
+        <v>539.86666666666667</v>
       </c>
       <c r="F39" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G41</f>
-        <v>-4.9214120072146428E-2</v>
+        <v>-2.6264708408485826E-2</v>
       </c>
       <c r="G39" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H41</f>
@@ -2275,11 +2277,11 @@
       </c>
       <c r="E40" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F42</f>
-        <v>411.57142857142856</v>
+        <v>410.46666666666664</v>
       </c>
       <c r="F40" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G42</f>
-        <v>2.0989602007888135</v>
+        <v>2.0906418070993187</v>
       </c>
       <c r="G40" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H42</f>
@@ -2304,11 +2306,11 @@
       </c>
       <c r="E41" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F43</f>
-        <v>203.85714285714286</v>
+        <v>208.33333333333334</v>
       </c>
       <c r="F41" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G43</f>
-        <v>-0.31162566328991803</v>
+        <v>-0.29651069303746591</v>
       </c>
       <c r="G41" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H43</f>
@@ -2333,11 +2335,11 @@
       </c>
       <c r="E42" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F44</f>
-        <v>455.64285714285717</v>
+        <v>472.2</v>
       </c>
       <c r="F42" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G44</f>
-        <v>-0.13820589029991881</v>
+        <v>-0.10689002972169681</v>
       </c>
       <c r="G42" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H44</f>
@@ -2362,11 +2364,11 @@
       </c>
       <c r="E43" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F45</f>
-        <v>281.57142857142856</v>
+        <v>280.93333333333334</v>
       </c>
       <c r="F43" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G45</f>
-        <v>-7.8541374474053294E-2</v>
+        <v>-8.0629577684276033E-2</v>
       </c>
       <c r="G43" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H45</f>
@@ -2391,11 +2393,11 @@
       </c>
       <c r="E44" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F46</f>
-        <v>277</v>
+        <v>283.86666666666667</v>
       </c>
       <c r="F44" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G46</f>
-        <v>-4.4513797634691321E-2</v>
+        <v>-2.0827858081471806E-2</v>
       </c>
       <c r="G44" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H46</f>
@@ -2420,15 +2422,15 @@
       </c>
       <c r="E45" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F47</f>
-        <v>55.357142857142854</v>
+        <v>57.8</v>
       </c>
       <c r="F45" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G47</f>
-        <v>-4.0841584158415878E-2</v>
+        <v>1.4851485148514865E-3</v>
       </c>
       <c r="G45" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H47</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H45">
         <v>2.62</v>
@@ -2449,11 +2451,11 @@
       </c>
       <c r="E46" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F48</f>
-        <v>129.21428571428572</v>
+        <v>130.26666666666668</v>
       </c>
       <c r="F46" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G48</f>
-        <v>0.23396998635743538</v>
+        <v>0.24402000909504351</v>
       </c>
       <c r="G46" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H48</f>
@@ -2478,11 +2480,11 @@
       </c>
       <c r="E47" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F49</f>
-        <v>40.071428571428569</v>
+        <v>43.866666666666667</v>
       </c>
       <c r="F47" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G49</f>
-        <v>-0.18774131274131278</v>
+        <v>-0.11081081081081079</v>
       </c>
       <c r="G47" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H49</f>
@@ -2507,11 +2509,11 @@
       </c>
       <c r="E48" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F50</f>
-        <v>53</v>
+        <v>52.733333333333334</v>
       </c>
       <c r="F48" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G50</f>
-        <v>-4.2168674698795261E-2</v>
+        <v>-4.6987951807228923E-2</v>
       </c>
       <c r="G48" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H50</f>

--- a/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
+++ b/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B234038D-3495-4A68-9664-1B33A7C05584}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D08A7434-AA8E-4C89-AD0C-3406D8B0C654}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -375,6 +375,7 @@
       <sheetName val="INVENTARIO NACIONAL 18-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 21-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 22-09-26"/>
+      <sheetName val="INVENTARIO NACIONAL 23-09-26"/>
       <sheetName val="CCC"/>
       <sheetName val="VINCULO VTS BY SKU AGOSTO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
@@ -400,13 +401,14 @@
       <sheetData sheetId="16"/>
       <sheetData sheetId="17"/>
       <sheetData sheetId="18"/>
-      <sheetData sheetId="19">
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20">
         <row r="4">
           <cell r="F4">
-            <v>1204.6666666666667</v>
+            <v>1206.1875</v>
           </cell>
           <cell r="G4">
-            <v>1.3947895791583287E-2</v>
+            <v>1.5227955911823576E-2</v>
           </cell>
           <cell r="H4" t="str">
             <v>SUBIÓ</v>
@@ -414,10 +416,10 @@
         </row>
         <row r="5">
           <cell r="F5">
-            <v>59.06666666666667</v>
+            <v>55.375</v>
           </cell>
           <cell r="G5">
-            <v>-0.22668329177057356</v>
+            <v>-0.27501558603491272</v>
           </cell>
           <cell r="H5" t="str">
             <v>BAJO</v>
@@ -425,10 +427,10 @@
         </row>
         <row r="6">
           <cell r="F6">
-            <v>495.13333333333333</v>
+            <v>493.125</v>
           </cell>
           <cell r="G6">
-            <v>-2.8152163753621839E-2</v>
+            <v>-3.209412094588282E-2</v>
           </cell>
           <cell r="H6" t="str">
             <v>BAJO</v>
@@ -436,10 +438,10 @@
         </row>
         <row r="7">
           <cell r="F7">
-            <v>105.4</v>
+            <v>107.5</v>
           </cell>
           <cell r="G7">
-            <v>7.551020408163267E-2</v>
+            <v>9.6938775510204023E-2</v>
           </cell>
           <cell r="H7" t="str">
             <v>SUBIÓ</v>
@@ -447,10 +449,10 @@
         </row>
         <row r="8">
           <cell r="F8">
-            <v>13.2</v>
+            <v>13.1875</v>
           </cell>
           <cell r="G8">
-            <v>0.10438247011952173</v>
+            <v>0.10333665338645415</v>
           </cell>
           <cell r="H8" t="str">
             <v>SUBIÓ</v>
@@ -458,10 +460,10 @@
         </row>
         <row r="9">
           <cell r="F9">
-            <v>1422.2666666666667</v>
+            <v>1420.8125</v>
           </cell>
           <cell r="G9">
-            <v>-2.6067107966217695E-2</v>
+            <v>-2.7062885186030505E-2</v>
           </cell>
           <cell r="H9" t="str">
             <v>BAJO</v>
@@ -469,10 +471,10 @@
         </row>
         <row r="10">
           <cell r="F10">
-            <v>143.33333333333334</v>
+            <v>147.5</v>
           </cell>
           <cell r="G10">
-            <v>-4.6865104496516707E-2</v>
+            <v>-1.9157694743508591E-2</v>
           </cell>
           <cell r="H10" t="str">
             <v>BAJO</v>
@@ -480,10 +482,10 @@
         </row>
         <row r="11">
           <cell r="F11">
-            <v>295.66666666666669</v>
+            <v>306.75</v>
           </cell>
           <cell r="G11">
-            <v>-0.13943173943173937</v>
+            <v>-0.10717255717255714</v>
           </cell>
           <cell r="H11" t="str">
             <v>BAJO</v>
@@ -491,32 +493,32 @@
         </row>
         <row r="12">
           <cell r="F12">
-            <v>739.6</v>
+            <v>767.0625</v>
           </cell>
           <cell r="G12">
-            <v>-3.4704785581106234E-2</v>
+            <v>1.1381292728402936E-3</v>
           </cell>
           <cell r="H12" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="13">
           <cell r="F13">
-            <v>351.26666666666665</v>
+            <v>368.5</v>
           </cell>
           <cell r="G13">
-            <v>-3.1815198844992731E-2</v>
+            <v>1.5684473027956392E-2</v>
           </cell>
           <cell r="H13" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="14">
           <cell r="F14">
-            <v>3358.6</v>
+            <v>3359.8125</v>
           </cell>
           <cell r="G14">
-            <v>-4.6265144958892335E-2</v>
+            <v>-4.5920833784076187E-2</v>
           </cell>
           <cell r="H14" t="str">
             <v>BAJO</v>
@@ -524,10 +526,10 @@
         </row>
         <row r="15">
           <cell r="F15">
-            <v>2080.5333333333333</v>
+            <v>2102</v>
           </cell>
           <cell r="G15">
-            <v>-9.7382501807664501E-2</v>
+            <v>-8.8069414316702788E-2</v>
           </cell>
           <cell r="H15" t="str">
             <v>BAJO</v>
@@ -535,10 +537,10 @@
         </row>
         <row r="16">
           <cell r="F16">
-            <v>2120.8000000000002</v>
+            <v>2141.9375</v>
           </cell>
           <cell r="G16">
-            <v>-6.4274308765442378E-2</v>
+            <v>-5.4948157408185483E-2</v>
           </cell>
           <cell r="H16" t="str">
             <v>BAJO</v>
@@ -546,10 +548,10 @@
         </row>
         <row r="17">
           <cell r="F17">
-            <v>2601.8666666666668</v>
+            <v>2611.25</v>
           </cell>
           <cell r="G17">
-            <v>-2.6975816504612227E-2</v>
+            <v>-2.3466716529543796E-2</v>
           </cell>
           <cell r="H17" t="str">
             <v>BAJO</v>
@@ -557,10 +559,10 @@
         </row>
         <row r="18">
           <cell r="F18">
-            <v>682.13333333333333</v>
+            <v>709.4375</v>
           </cell>
           <cell r="G18">
-            <v>0.75269790774501399</v>
+            <v>0.82285421509849499</v>
           </cell>
           <cell r="H18" t="str">
             <v>SUBIÓ</v>
@@ -568,10 +570,10 @@
         </row>
         <row r="19">
           <cell r="F19">
-            <v>781.8</v>
+            <v>813.4375</v>
           </cell>
           <cell r="G19">
-            <v>0.82501111605157829</v>
+            <v>0.89886477323254765</v>
           </cell>
           <cell r="H19" t="str">
             <v>SUBIÓ</v>
@@ -579,10 +581,10 @@
         </row>
         <row r="20">
           <cell r="F20">
-            <v>831.73333333333335</v>
+            <v>857.125</v>
           </cell>
           <cell r="G20">
-            <v>1.1284913477942968</v>
+            <v>1.1934712405556911</v>
           </cell>
           <cell r="H20" t="str">
             <v>SUBIÓ</v>
@@ -590,10 +592,10 @@
         </row>
         <row r="21">
           <cell r="F21">
-            <v>257.8</v>
+            <v>271.75</v>
           </cell>
           <cell r="G21">
-            <v>6.5289256198347134E-2</v>
+            <v>0.12293388429752072</v>
           </cell>
           <cell r="H21" t="str">
             <v>SUBIÓ</v>
@@ -601,10 +603,10 @@
         </row>
         <row r="22">
           <cell r="F22">
-            <v>120.86666666666666</v>
+            <v>127.75</v>
           </cell>
           <cell r="G22">
-            <v>-0.14996651038178177</v>
+            <v>-0.10155726724715342</v>
           </cell>
           <cell r="H22" t="str">
             <v>BAJO</v>
@@ -612,10 +614,10 @@
         </row>
         <row r="23">
           <cell r="F23">
-            <v>497.13333333333333</v>
+            <v>505.1875</v>
           </cell>
           <cell r="G23">
-            <v>-3.1109048723897859E-2</v>
+            <v>-1.5411832946635728E-2</v>
           </cell>
           <cell r="H23" t="str">
             <v>BAJO</v>
@@ -623,10 +625,10 @@
         </row>
         <row r="24">
           <cell r="F24">
-            <v>828.4666666666667</v>
+            <v>849.5</v>
           </cell>
           <cell r="G24">
-            <v>2.1057573801279483E-2</v>
+            <v>4.6980456599565734E-2</v>
           </cell>
           <cell r="H24" t="str">
             <v>SUBIÓ</v>
@@ -634,10 +636,10 @@
         </row>
         <row r="25">
           <cell r="F25">
-            <v>68.8</v>
+            <v>64.5</v>
           </cell>
           <cell r="G25">
-            <v>-8.2083862770012672E-2</v>
+            <v>-0.13945362134688688</v>
           </cell>
           <cell r="H25" t="str">
             <v>BAJO</v>
@@ -645,10 +647,10 @@
         </row>
         <row r="26">
           <cell r="F26">
-            <v>696.66666666666663</v>
+            <v>701.8125</v>
           </cell>
           <cell r="G26">
-            <v>-0.11585181603916128</v>
+            <v>-0.10932117604399594</v>
           </cell>
           <cell r="H26" t="str">
             <v>BAJO</v>
@@ -656,10 +658,10 @@
         </row>
         <row r="27">
           <cell r="F27">
-            <v>1084.8</v>
+            <v>1094</v>
           </cell>
           <cell r="G27">
-            <v>-0.1483176312247646</v>
+            <v>-0.14109466128308668</v>
           </cell>
           <cell r="H27" t="str">
             <v>BAJO</v>
@@ -667,10 +669,10 @@
         </row>
         <row r="28">
           <cell r="F28">
-            <v>540.79999999999995</v>
+            <v>564.5</v>
           </cell>
           <cell r="G28">
-            <v>2.1938270494016088E-2</v>
+            <v>6.6723656978313839E-2</v>
           </cell>
           <cell r="H28" t="str">
             <v>SUBIÓ</v>
@@ -678,10 +680,10 @@
         </row>
         <row r="29">
           <cell r="F29">
-            <v>409.93333333333334</v>
+            <v>422.125</v>
           </cell>
           <cell r="G29">
-            <v>2.009716791088989E-2</v>
+            <v>5.0435478137220047E-2</v>
           </cell>
           <cell r="H29" t="str">
             <v>SUBIÓ</v>
@@ -689,10 +691,10 @@
         </row>
         <row r="30">
           <cell r="F30">
-            <v>243.33333333333334</v>
+            <v>240.75</v>
           </cell>
           <cell r="G30">
-            <v>2.1977471839799749</v>
+            <v>2.1637984981226532</v>
           </cell>
           <cell r="H30" t="str">
             <v>SUBIÓ</v>
@@ -700,10 +702,10 @@
         </row>
         <row r="31">
           <cell r="F31">
-            <v>299.73333333333335</v>
+            <v>290.8125</v>
           </cell>
           <cell r="G31">
-            <v>3.1574636723910166</v>
+            <v>3.0337268824306465</v>
           </cell>
           <cell r="H31" t="str">
             <v>SUBIÓ</v>
@@ -711,21 +713,21 @@
         </row>
         <row r="32">
           <cell r="F32">
-            <v>124.06666666666666</v>
+            <v>131.4375</v>
           </cell>
           <cell r="G32">
-            <v>-2.9646182495344564E-2</v>
+            <v>2.8002793296089346E-2</v>
           </cell>
           <cell r="H32" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="33">
           <cell r="F33">
-            <v>134.33333333333334</v>
+            <v>137.4375</v>
           </cell>
           <cell r="G33">
-            <v>-6.2790697674418583E-2</v>
+            <v>-4.1133720930232598E-2</v>
           </cell>
           <cell r="H33" t="str">
             <v>BAJO</v>
@@ -733,10 +735,10 @@
         </row>
         <row r="34">
           <cell r="F34">
-            <v>738.33333333333337</v>
+            <v>759.875</v>
           </cell>
           <cell r="G34">
-            <v>0.13208235981308425</v>
+            <v>0.16511207651869175</v>
           </cell>
           <cell r="H34" t="str">
             <v>SUBIÓ</v>
@@ -744,10 +746,10 @@
         </row>
         <row r="35">
           <cell r="F35">
-            <v>583.26666666666665</v>
+            <v>598.3125</v>
           </cell>
           <cell r="G35">
-            <v>-7.2778198334594979E-2</v>
+            <v>-4.8859765329295923E-2</v>
           </cell>
           <cell r="H35" t="str">
             <v>BAJO</v>
@@ -755,10 +757,10 @@
         </row>
         <row r="36">
           <cell r="F36">
-            <v>773</v>
+            <v>791.625</v>
           </cell>
           <cell r="G36">
-            <v>-9.2925793473401797E-2</v>
+            <v>-7.10703509164059E-2</v>
           </cell>
           <cell r="H36" t="str">
             <v>BAJO</v>
@@ -766,10 +768,10 @@
         </row>
         <row r="37">
           <cell r="F37">
-            <v>506.46666666666664</v>
+            <v>519.8125</v>
           </cell>
           <cell r="G37">
-            <v>-0.12527345998848594</v>
+            <v>-0.10222366148531947</v>
           </cell>
           <cell r="H37" t="str">
             <v>BAJO</v>
@@ -777,10 +779,10 @@
         </row>
         <row r="38">
           <cell r="F38">
-            <v>3.6666666666666665</v>
+            <v>3.625</v>
           </cell>
           <cell r="G38">
-            <v>0.48076923076923062</v>
+            <v>0.46394230769230771</v>
           </cell>
           <cell r="H38" t="str">
             <v>SUBIÓ</v>
@@ -788,10 +790,10 @@
         </row>
         <row r="39">
           <cell r="F39">
-            <v>0.46666666666666667</v>
+            <v>0.4375</v>
           </cell>
           <cell r="G39">
-            <v>8.8888888888889017E-2</v>
+            <v>2.0833333333333481E-2</v>
           </cell>
           <cell r="H39" t="str">
             <v>SUBIÓ</v>
@@ -799,10 +801,10 @@
         </row>
         <row r="40">
           <cell r="F40">
-            <v>142.06666666666666</v>
+            <v>146.5625</v>
           </cell>
           <cell r="G40">
-            <v>3.5902777777777839E-2</v>
+            <v>6.8684895833333259E-2</v>
           </cell>
           <cell r="H40" t="str">
             <v>SUBIÓ</v>
@@ -810,21 +812,21 @@
         </row>
         <row r="41">
           <cell r="F41">
-            <v>539.86666666666667</v>
+            <v>568</v>
           </cell>
           <cell r="G41">
-            <v>-2.6264708408485826E-2</v>
+            <v>2.4478227261015117E-2</v>
           </cell>
           <cell r="H41" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="42">
           <cell r="F42">
-            <v>410.46666666666664</v>
+            <v>408.625</v>
           </cell>
           <cell r="G42">
-            <v>2.0906418070993187</v>
+            <v>2.0767748296880604</v>
           </cell>
           <cell r="H42" t="str">
             <v>SUBIÓ</v>
@@ -832,10 +834,10 @@
         </row>
         <row r="43">
           <cell r="F43">
-            <v>208.33333333333334</v>
+            <v>213.0625</v>
           </cell>
           <cell r="G43">
-            <v>-0.29651069303746591</v>
+            <v>-0.2805414857694164</v>
           </cell>
           <cell r="H43" t="str">
             <v>BAJO</v>
@@ -843,10 +845,10 @@
         </row>
         <row r="44">
           <cell r="F44">
-            <v>472.2</v>
+            <v>478.1875</v>
           </cell>
           <cell r="G44">
-            <v>-0.10689002972169681</v>
+            <v>-9.5565387733045015E-2</v>
           </cell>
           <cell r="H44" t="str">
             <v>BAJO</v>
@@ -854,10 +856,10 @@
         </row>
         <row r="45">
           <cell r="F45">
-            <v>280.93333333333334</v>
+            <v>281.25</v>
           </cell>
           <cell r="G45">
-            <v>-8.0629577684276033E-2</v>
+            <v>-7.9593267882187901E-2</v>
           </cell>
           <cell r="H45" t="str">
             <v>BAJO</v>
@@ -865,10 +867,10 @@
         </row>
         <row r="46">
           <cell r="F46">
-            <v>283.86666666666667</v>
+            <v>286.125</v>
           </cell>
           <cell r="G46">
-            <v>-2.0827858081471806E-2</v>
+            <v>-1.3037943495400883E-2</v>
           </cell>
           <cell r="H46" t="str">
             <v>BAJO</v>
@@ -876,10 +878,10 @@
         </row>
         <row r="47">
           <cell r="F47">
-            <v>57.8</v>
+            <v>59</v>
           </cell>
           <cell r="G47">
-            <v>1.4851485148514865E-3</v>
+            <v>2.2277227722772297E-2</v>
           </cell>
           <cell r="H47" t="str">
             <v>SUBIÓ</v>
@@ -887,10 +889,10 @@
         </row>
         <row r="48">
           <cell r="F48">
-            <v>130.26666666666668</v>
+            <v>128.875</v>
           </cell>
           <cell r="G48">
-            <v>0.24402000909504351</v>
+            <v>0.23072987721691685</v>
           </cell>
           <cell r="H48" t="str">
             <v>SUBIÓ</v>
@@ -898,10 +900,10 @@
         </row>
         <row r="49">
           <cell r="F49">
-            <v>43.866666666666667</v>
+            <v>43.875</v>
           </cell>
           <cell r="G49">
-            <v>-0.11081081081081079</v>
+            <v>-0.11064189189189189</v>
           </cell>
           <cell r="H49" t="str">
             <v>BAJO</v>
@@ -909,10 +911,10 @@
         </row>
         <row r="50">
           <cell r="F50">
-            <v>52.733333333333334</v>
+            <v>55.25</v>
           </cell>
           <cell r="G50">
-            <v>-4.6987951807228923E-2</v>
+            <v>-1.5060240963855609E-3</v>
           </cell>
           <cell r="H50" t="str">
             <v>BAJO</v>
@@ -1175,11 +1177,11 @@
       </c>
       <c r="E2" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F4</f>
-        <v>1204.6666666666667</v>
+        <v>1206.1875</v>
       </c>
       <c r="F2" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G4</f>
-        <v>1.3947895791583287E-2</v>
+        <v>1.5227955911823576E-2</v>
       </c>
       <c r="G2" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H4</f>
@@ -1204,11 +1206,11 @@
       </c>
       <c r="E3" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F5</f>
-        <v>59.06666666666667</v>
+        <v>55.375</v>
       </c>
       <c r="F3" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G5</f>
-        <v>-0.22668329177057356</v>
+        <v>-0.27501558603491272</v>
       </c>
       <c r="G3" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H5</f>
@@ -1233,11 +1235,11 @@
       </c>
       <c r="E4" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F6</f>
-        <v>495.13333333333333</v>
+        <v>493.125</v>
       </c>
       <c r="F4" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G6</f>
-        <v>-2.8152163753621839E-2</v>
+        <v>-3.209412094588282E-2</v>
       </c>
       <c r="G4" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H6</f>
@@ -1262,11 +1264,11 @@
       </c>
       <c r="E5" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F7</f>
-        <v>105.4</v>
+        <v>107.5</v>
       </c>
       <c r="F5" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G7</f>
-        <v>7.551020408163267E-2</v>
+        <v>9.6938775510204023E-2</v>
       </c>
       <c r="G5" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H7</f>
@@ -1291,11 +1293,11 @@
       </c>
       <c r="E6" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F8</f>
-        <v>13.2</v>
+        <v>13.1875</v>
       </c>
       <c r="F6" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G8</f>
-        <v>0.10438247011952173</v>
+        <v>0.10333665338645415</v>
       </c>
       <c r="G6" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H8</f>
@@ -1320,11 +1322,11 @@
       </c>
       <c r="E7" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F9</f>
-        <v>1422.2666666666667</v>
+        <v>1420.8125</v>
       </c>
       <c r="F7" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G9</f>
-        <v>-2.6067107966217695E-2</v>
+        <v>-2.7062885186030505E-2</v>
       </c>
       <c r="G7" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H9</f>
@@ -1349,11 +1351,11 @@
       </c>
       <c r="E8" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F10</f>
-        <v>143.33333333333334</v>
+        <v>147.5</v>
       </c>
       <c r="F8" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G10</f>
-        <v>-4.6865104496516707E-2</v>
+        <v>-1.9157694743508591E-2</v>
       </c>
       <c r="G8" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H10</f>
@@ -1378,11 +1380,11 @@
       </c>
       <c r="E9" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F11</f>
-        <v>295.66666666666669</v>
+        <v>306.75</v>
       </c>
       <c r="F9" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G11</f>
-        <v>-0.13943173943173937</v>
+        <v>-0.10717255717255714</v>
       </c>
       <c r="G9" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H11</f>
@@ -1407,15 +1409,15 @@
       </c>
       <c r="E10" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F12</f>
-        <v>739.6</v>
+        <v>767.0625</v>
       </c>
       <c r="F10" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G12</f>
-        <v>-3.4704785581106234E-2</v>
+        <v>1.1381292728402936E-3</v>
       </c>
       <c r="G10" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H12</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H10">
         <v>1.0900000000000001</v>
@@ -1436,15 +1438,15 @@
       </c>
       <c r="E11" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F13</f>
-        <v>351.26666666666665</v>
+        <v>368.5</v>
       </c>
       <c r="F11" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G13</f>
-        <v>-3.1815198844992731E-2</v>
+        <v>1.5684473027956392E-2</v>
       </c>
       <c r="G11" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H13</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H11">
         <v>1.0900000000000001</v>
@@ -1465,11 +1467,11 @@
       </c>
       <c r="E12" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F14</f>
-        <v>3358.6</v>
+        <v>3359.8125</v>
       </c>
       <c r="F12" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G14</f>
-        <v>-4.6265144958892335E-2</v>
+        <v>-4.5920833784076187E-2</v>
       </c>
       <c r="G12" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H14</f>
@@ -1494,11 +1496,11 @@
       </c>
       <c r="E13" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F15</f>
-        <v>2080.5333333333333</v>
+        <v>2102</v>
       </c>
       <c r="F13" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G15</f>
-        <v>-9.7382501807664501E-2</v>
+        <v>-8.8069414316702788E-2</v>
       </c>
       <c r="G13" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H15</f>
@@ -1523,11 +1525,11 @@
       </c>
       <c r="E14" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F16</f>
-        <v>2120.8000000000002</v>
+        <v>2141.9375</v>
       </c>
       <c r="F14" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G16</f>
-        <v>-6.4274308765442378E-2</v>
+        <v>-5.4948157408185483E-2</v>
       </c>
       <c r="G14" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H16</f>
@@ -1552,11 +1554,11 @@
       </c>
       <c r="E15" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F17</f>
-        <v>2601.8666666666668</v>
+        <v>2611.25</v>
       </c>
       <c r="F15" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G17</f>
-        <v>-2.6975816504612227E-2</v>
+        <v>-2.3466716529543796E-2</v>
       </c>
       <c r="G15" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H17</f>
@@ -1581,11 +1583,11 @@
       </c>
       <c r="E16" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F18</f>
-        <v>682.13333333333333</v>
+        <v>709.4375</v>
       </c>
       <c r="F16" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G18</f>
-        <v>0.75269790774501399</v>
+        <v>0.82285421509849499</v>
       </c>
       <c r="G16" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H18</f>
@@ -1610,11 +1612,11 @@
       </c>
       <c r="E17" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F19</f>
-        <v>781.8</v>
+        <v>813.4375</v>
       </c>
       <c r="F17" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G19</f>
-        <v>0.82501111605157829</v>
+        <v>0.89886477323254765</v>
       </c>
       <c r="G17" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H19</f>
@@ -1639,11 +1641,11 @@
       </c>
       <c r="E18" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F20</f>
-        <v>831.73333333333335</v>
+        <v>857.125</v>
       </c>
       <c r="F18" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G20</f>
-        <v>1.1284913477942968</v>
+        <v>1.1934712405556911</v>
       </c>
       <c r="G18" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H20</f>
@@ -1668,11 +1670,11 @@
       </c>
       <c r="E19" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F21</f>
-        <v>257.8</v>
+        <v>271.75</v>
       </c>
       <c r="F19" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G21</f>
-        <v>6.5289256198347134E-2</v>
+        <v>0.12293388429752072</v>
       </c>
       <c r="G19" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H21</f>
@@ -1697,11 +1699,11 @@
       </c>
       <c r="E20" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F22</f>
-        <v>120.86666666666666</v>
+        <v>127.75</v>
       </c>
       <c r="F20" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G22</f>
-        <v>-0.14996651038178177</v>
+        <v>-0.10155726724715342</v>
       </c>
       <c r="G20" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H22</f>
@@ -1726,11 +1728,11 @@
       </c>
       <c r="E21" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F23</f>
-        <v>497.13333333333333</v>
+        <v>505.1875</v>
       </c>
       <c r="F21" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G23</f>
-        <v>-3.1109048723897859E-2</v>
+        <v>-1.5411832946635728E-2</v>
       </c>
       <c r="G21" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H23</f>
@@ -1755,11 +1757,11 @@
       </c>
       <c r="E22" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F24</f>
-        <v>828.4666666666667</v>
+        <v>849.5</v>
       </c>
       <c r="F22" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G24</f>
-        <v>2.1057573801279483E-2</v>
+        <v>4.6980456599565734E-2</v>
       </c>
       <c r="G22" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H24</f>
@@ -1784,11 +1786,11 @@
       </c>
       <c r="E23" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F25</f>
-        <v>68.8</v>
+        <v>64.5</v>
       </c>
       <c r="F23" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G25</f>
-        <v>-8.2083862770012672E-2</v>
+        <v>-0.13945362134688688</v>
       </c>
       <c r="G23" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H25</f>
@@ -1813,11 +1815,11 @@
       </c>
       <c r="E24" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F26</f>
-        <v>696.66666666666663</v>
+        <v>701.8125</v>
       </c>
       <c r="F24" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G26</f>
-        <v>-0.11585181603916128</v>
+        <v>-0.10932117604399594</v>
       </c>
       <c r="G24" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H26</f>
@@ -1842,11 +1844,11 @@
       </c>
       <c r="E25" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F27</f>
-        <v>1084.8</v>
+        <v>1094</v>
       </c>
       <c r="F25" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G27</f>
-        <v>-0.1483176312247646</v>
+        <v>-0.14109466128308668</v>
       </c>
       <c r="G25" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H27</f>
@@ -1871,11 +1873,11 @@
       </c>
       <c r="E26" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F28</f>
-        <v>540.79999999999995</v>
+        <v>564.5</v>
       </c>
       <c r="F26" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G28</f>
-        <v>2.1938270494016088E-2</v>
+        <v>6.6723656978313839E-2</v>
       </c>
       <c r="G26" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H28</f>
@@ -1900,11 +1902,11 @@
       </c>
       <c r="E27" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F29</f>
-        <v>409.93333333333334</v>
+        <v>422.125</v>
       </c>
       <c r="F27" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G29</f>
-        <v>2.009716791088989E-2</v>
+        <v>5.0435478137220047E-2</v>
       </c>
       <c r="G27" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H29</f>
@@ -1929,11 +1931,11 @@
       </c>
       <c r="E28" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F30</f>
-        <v>243.33333333333334</v>
+        <v>240.75</v>
       </c>
       <c r="F28" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G30</f>
-        <v>2.1977471839799749</v>
+        <v>2.1637984981226532</v>
       </c>
       <c r="G28" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H30</f>
@@ -1958,11 +1960,11 @@
       </c>
       <c r="E29" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F31</f>
-        <v>299.73333333333335</v>
+        <v>290.8125</v>
       </c>
       <c r="F29" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G31</f>
-        <v>3.1574636723910166</v>
+        <v>3.0337268824306465</v>
       </c>
       <c r="G29" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H31</f>
@@ -1987,15 +1989,15 @@
       </c>
       <c r="E30" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F32</f>
-        <v>124.06666666666666</v>
+        <v>131.4375</v>
       </c>
       <c r="F30" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G32</f>
-        <v>-2.9646182495344564E-2</v>
+        <v>2.8002793296089346E-2</v>
       </c>
       <c r="G30" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H32</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H30">
         <v>6.15</v>
@@ -2016,11 +2018,11 @@
       </c>
       <c r="E31" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F33</f>
-        <v>134.33333333333334</v>
+        <v>137.4375</v>
       </c>
       <c r="F31" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G33</f>
-        <v>-6.2790697674418583E-2</v>
+        <v>-4.1133720930232598E-2</v>
       </c>
       <c r="G31" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H33</f>
@@ -2045,11 +2047,11 @@
       </c>
       <c r="E32" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F34</f>
-        <v>738.33333333333337</v>
+        <v>759.875</v>
       </c>
       <c r="F32" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G34</f>
-        <v>0.13208235981308425</v>
+        <v>0.16511207651869175</v>
       </c>
       <c r="G32" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H34</f>
@@ -2074,11 +2076,11 @@
       </c>
       <c r="E33" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F35</f>
-        <v>583.26666666666665</v>
+        <v>598.3125</v>
       </c>
       <c r="F33" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G35</f>
-        <v>-7.2778198334594979E-2</v>
+        <v>-4.8859765329295923E-2</v>
       </c>
       <c r="G33" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H35</f>
@@ -2103,11 +2105,11 @@
       </c>
       <c r="E34" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F36</f>
-        <v>773</v>
+        <v>791.625</v>
       </c>
       <c r="F34" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G36</f>
-        <v>-9.2925793473401797E-2</v>
+        <v>-7.10703509164059E-2</v>
       </c>
       <c r="G34" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H36</f>
@@ -2132,11 +2134,11 @@
       </c>
       <c r="E35" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F37</f>
-        <v>506.46666666666664</v>
+        <v>519.8125</v>
       </c>
       <c r="F35" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G37</f>
-        <v>-0.12527345998848594</v>
+        <v>-0.10222366148531947</v>
       </c>
       <c r="G35" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H37</f>
@@ -2161,11 +2163,11 @@
       </c>
       <c r="E36" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F38</f>
-        <v>3.6666666666666665</v>
+        <v>3.625</v>
       </c>
       <c r="F36" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G38</f>
-        <v>0.48076923076923062</v>
+        <v>0.46394230769230771</v>
       </c>
       <c r="G36" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H38</f>
@@ -2190,11 +2192,11 @@
       </c>
       <c r="E37" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F39</f>
-        <v>0.46666666666666667</v>
+        <v>0.4375</v>
       </c>
       <c r="F37" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G39</f>
-        <v>8.8888888888889017E-2</v>
+        <v>2.0833333333333481E-2</v>
       </c>
       <c r="G37" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H39</f>
@@ -2219,11 +2221,11 @@
       </c>
       <c r="E38" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F40</f>
-        <v>142.06666666666666</v>
+        <v>146.5625</v>
       </c>
       <c r="F38" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G40</f>
-        <v>3.5902777777777839E-2</v>
+        <v>6.8684895833333259E-2</v>
       </c>
       <c r="G38" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H40</f>
@@ -2248,15 +2250,15 @@
       </c>
       <c r="E39" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F41</f>
-        <v>539.86666666666667</v>
+        <v>568</v>
       </c>
       <c r="F39" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G41</f>
-        <v>-2.6264708408485826E-2</v>
+        <v>2.4478227261015117E-2</v>
       </c>
       <c r="G39" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H41</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H39">
         <v>1.1599999999999999</v>
@@ -2277,11 +2279,11 @@
       </c>
       <c r="E40" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F42</f>
-        <v>410.46666666666664</v>
+        <v>408.625</v>
       </c>
       <c r="F40" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G42</f>
-        <v>2.0906418070993187</v>
+        <v>2.0767748296880604</v>
       </c>
       <c r="G40" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H42</f>
@@ -2306,11 +2308,11 @@
       </c>
       <c r="E41" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F43</f>
-        <v>208.33333333333334</v>
+        <v>213.0625</v>
       </c>
       <c r="F41" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G43</f>
-        <v>-0.29651069303746591</v>
+        <v>-0.2805414857694164</v>
       </c>
       <c r="G41" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H43</f>
@@ -2335,11 +2337,11 @@
       </c>
       <c r="E42" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F44</f>
-        <v>472.2</v>
+        <v>478.1875</v>
       </c>
       <c r="F42" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G44</f>
-        <v>-0.10689002972169681</v>
+        <v>-9.5565387733045015E-2</v>
       </c>
       <c r="G42" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H44</f>
@@ -2364,11 +2366,11 @@
       </c>
       <c r="E43" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F45</f>
-        <v>280.93333333333334</v>
+        <v>281.25</v>
       </c>
       <c r="F43" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G45</f>
-        <v>-8.0629577684276033E-2</v>
+        <v>-7.9593267882187901E-2</v>
       </c>
       <c r="G43" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H45</f>
@@ -2393,11 +2395,11 @@
       </c>
       <c r="E44" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F46</f>
-        <v>283.86666666666667</v>
+        <v>286.125</v>
       </c>
       <c r="F44" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G46</f>
-        <v>-2.0827858081471806E-2</v>
+        <v>-1.3037943495400883E-2</v>
       </c>
       <c r="G44" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H46</f>
@@ -2422,11 +2424,11 @@
       </c>
       <c r="E45" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F47</f>
-        <v>57.8</v>
+        <v>59</v>
       </c>
       <c r="F45" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G47</f>
-        <v>1.4851485148514865E-3</v>
+        <v>2.2277227722772297E-2</v>
       </c>
       <c r="G45" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H47</f>
@@ -2451,11 +2453,11 @@
       </c>
       <c r="E46" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F48</f>
-        <v>130.26666666666668</v>
+        <v>128.875</v>
       </c>
       <c r="F46" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G48</f>
-        <v>0.24402000909504351</v>
+        <v>0.23072987721691685</v>
       </c>
       <c r="G46" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H48</f>
@@ -2480,11 +2482,11 @@
       </c>
       <c r="E47" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F49</f>
-        <v>43.866666666666667</v>
+        <v>43.875</v>
       </c>
       <c r="F47" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G49</f>
-        <v>-0.11081081081081079</v>
+        <v>-0.11064189189189189</v>
       </c>
       <c r="G47" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H49</f>
@@ -2509,11 +2511,11 @@
       </c>
       <c r="E48" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F50</f>
-        <v>52.733333333333334</v>
+        <v>55.25</v>
       </c>
       <c r="F48" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G50</f>
-        <v>-4.6987951807228923E-2</v>
+        <v>-1.5060240963855609E-3</v>
       </c>
       <c r="G48" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H50</f>

--- a/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
+++ b/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D08A7434-AA8E-4C89-AD0C-3406D8B0C654}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79E2F14B-787F-4E71-A46E-5191BA03884E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -376,6 +376,7 @@
       <sheetName val="INVENTARIO NACIONAL 21-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 22-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 23-09-26"/>
+      <sheetName val="INVENTARIO NACIONAL 24-09-26"/>
       <sheetName val="CCC"/>
       <sheetName val="VINCULO VTS BY SKU AGOSTO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
@@ -402,13 +403,14 @@
       <sheetData sheetId="17"/>
       <sheetData sheetId="18"/>
       <sheetData sheetId="19"/>
-      <sheetData sheetId="20">
+      <sheetData sheetId="20"/>
+      <sheetData sheetId="21">
         <row r="4">
           <cell r="F4">
-            <v>1206.1875</v>
+            <v>1205.2941176470588</v>
           </cell>
           <cell r="G4">
-            <v>1.5227955911823576E-2</v>
+            <v>1.4476010845219767E-2</v>
           </cell>
           <cell r="H4" t="str">
             <v>SUBIÓ</v>
@@ -416,10 +418,10 @@
         </row>
         <row r="5">
           <cell r="F5">
-            <v>55.375</v>
+            <v>53.823529411764703</v>
           </cell>
           <cell r="G5">
-            <v>-0.27501558603491272</v>
+            <v>-0.29532785682851692</v>
           </cell>
           <cell r="H5" t="str">
             <v>BAJO</v>
@@ -427,10 +429,10 @@
         </row>
         <row r="6">
           <cell r="F6">
-            <v>493.125</v>
+            <v>492.1764705882353</v>
           </cell>
           <cell r="G6">
-            <v>-3.209412094588282E-2</v>
+            <v>-3.3955894723530999E-2</v>
           </cell>
           <cell r="H6" t="str">
             <v>BAJO</v>
@@ -438,10 +440,10 @@
         </row>
         <row r="7">
           <cell r="F7">
-            <v>107.5</v>
+            <v>108.70588235294117</v>
           </cell>
           <cell r="G7">
-            <v>9.6938775510204023E-2</v>
+            <v>0.10924369747899165</v>
           </cell>
           <cell r="H7" t="str">
             <v>SUBIÓ</v>
@@ -449,10 +451,10 @@
         </row>
         <row r="8">
           <cell r="F8">
-            <v>13.1875</v>
+            <v>14.176470588235293</v>
           </cell>
           <cell r="G8">
-            <v>0.10333665338645415</v>
+            <v>0.18607921256151849</v>
           </cell>
           <cell r="H8" t="str">
             <v>SUBIÓ</v>
@@ -460,10 +462,10 @@
         </row>
         <row r="9">
           <cell r="F9">
-            <v>1420.8125</v>
+            <v>1412.8823529411766</v>
           </cell>
           <cell r="G9">
-            <v>-2.7062885186030505E-2</v>
+            <v>-3.2493252950575258E-2</v>
           </cell>
           <cell r="H9" t="str">
             <v>BAJO</v>
@@ -471,10 +473,10 @@
         </row>
         <row r="10">
           <cell r="F10">
-            <v>147.5</v>
+            <v>147.52941176470588</v>
           </cell>
           <cell r="G10">
-            <v>-1.9157694743508591E-2</v>
+            <v>-1.8962113027604977E-2</v>
           </cell>
           <cell r="H10" t="str">
             <v>BAJO</v>
@@ -482,10 +484,10 @@
         </row>
         <row r="11">
           <cell r="F11">
-            <v>306.75</v>
+            <v>318.41176470588238</v>
           </cell>
           <cell r="G11">
-            <v>-0.10717255717255714</v>
+            <v>-7.3229790876849554E-2</v>
           </cell>
           <cell r="H11" t="str">
             <v>BAJO</v>
@@ -493,10 +495,10 @@
         </row>
         <row r="12">
           <cell r="F12">
-            <v>767.0625</v>
+            <v>788.47058823529414</v>
           </cell>
           <cell r="G12">
-            <v>1.1381292728402936E-3</v>
+            <v>2.907907724929637E-2</v>
           </cell>
           <cell r="H12" t="str">
             <v>SUBIÓ</v>
@@ -504,10 +506,10 @@
         </row>
         <row r="13">
           <cell r="F13">
-            <v>368.5</v>
+            <v>383.8235294117647</v>
           </cell>
           <cell r="G13">
-            <v>1.5684473027956392E-2</v>
+            <v>5.7920214942519976E-2</v>
           </cell>
           <cell r="H13" t="str">
             <v>SUBIÓ</v>
@@ -515,10 +517,10 @@
         </row>
         <row r="14">
           <cell r="F14">
-            <v>3359.8125</v>
+            <v>3419.5294117647059</v>
           </cell>
           <cell r="G14">
-            <v>-4.5920833784076187E-2</v>
+            <v>-2.8963143024410165E-2</v>
           </cell>
           <cell r="H14" t="str">
             <v>BAJO</v>
@@ -526,10 +528,10 @@
         </row>
         <row r="15">
           <cell r="F15">
-            <v>2102</v>
+            <v>2119.4705882352941</v>
           </cell>
           <cell r="G15">
-            <v>-8.8069414316702788E-2</v>
+            <v>-8.048998341201985E-2</v>
           </cell>
           <cell r="H15" t="str">
             <v>BAJO</v>
@@ -537,10 +539,10 @@
         </row>
         <row r="16">
           <cell r="F16">
-            <v>2141.9375</v>
+            <v>2147.1176470588234</v>
           </cell>
           <cell r="G16">
-            <v>-5.4948157408185483E-2</v>
+            <v>-5.2662606348531482E-2</v>
           </cell>
           <cell r="H16" t="str">
             <v>BAJO</v>
@@ -548,10 +550,10 @@
         </row>
         <row r="17">
           <cell r="F17">
-            <v>2611.25</v>
+            <v>2656.1764705882351</v>
           </cell>
           <cell r="G17">
-            <v>-2.3466716529543796E-2</v>
+            <v>-6.6654934225000018E-3</v>
           </cell>
           <cell r="H17" t="str">
             <v>BAJO</v>
@@ -559,10 +561,10 @@
         </row>
         <row r="18">
           <cell r="F18">
-            <v>709.4375</v>
+            <v>719.94117647058829</v>
           </cell>
           <cell r="G18">
-            <v>0.82285421509849499</v>
+            <v>0.84984273900432572</v>
           </cell>
           <cell r="H18" t="str">
             <v>SUBIÓ</v>
@@ -570,10 +572,10 @@
         </row>
         <row r="19">
           <cell r="F19">
-            <v>813.4375</v>
+            <v>842.47058823529414</v>
           </cell>
           <cell r="G19">
-            <v>0.89886477323254765</v>
+            <v>0.96663876755682265</v>
           </cell>
           <cell r="H19" t="str">
             <v>SUBIÓ</v>
@@ -581,10 +583,10 @@
         </row>
         <row r="20">
           <cell r="F20">
-            <v>857.125</v>
+            <v>864.58823529411768</v>
           </cell>
           <cell r="G20">
-            <v>1.1934712405556911</v>
+            <v>1.212570429097791</v>
           </cell>
           <cell r="H20" t="str">
             <v>SUBIÓ</v>
@@ -592,10 +594,10 @@
         </row>
         <row r="21">
           <cell r="F21">
-            <v>271.75</v>
+            <v>281</v>
           </cell>
           <cell r="G21">
-            <v>0.12293388429752072</v>
+            <v>0.16115702479338845</v>
           </cell>
           <cell r="H21" t="str">
             <v>SUBIÓ</v>
@@ -603,10 +605,10 @@
         </row>
         <row r="22">
           <cell r="F22">
-            <v>127.75</v>
+            <v>132.64705882352942</v>
           </cell>
           <cell r="G22">
-            <v>-0.10155726724715342</v>
+            <v>-6.7117134864662531E-2</v>
           </cell>
           <cell r="H22" t="str">
             <v>BAJO</v>
@@ -614,21 +616,21 @@
         </row>
         <row r="23">
           <cell r="F23">
-            <v>505.1875</v>
+            <v>519.11764705882354</v>
           </cell>
           <cell r="G23">
-            <v>-1.5411832946635728E-2</v>
+            <v>1.173740958100189E-2</v>
           </cell>
           <cell r="H23" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="24">
           <cell r="F24">
-            <v>849.5</v>
+            <v>874.41176470588232</v>
           </cell>
           <cell r="G24">
-            <v>4.6980456599565734E-2</v>
+            <v>7.7683376889695843E-2</v>
           </cell>
           <cell r="H24" t="str">
             <v>SUBIÓ</v>
@@ -636,10 +638,10 @@
         </row>
         <row r="25">
           <cell r="F25">
-            <v>64.5</v>
+            <v>60.705882352941174</v>
           </cell>
           <cell r="G25">
-            <v>-0.13945362134688688</v>
+            <v>-0.19007399656177593</v>
           </cell>
           <cell r="H25" t="str">
             <v>BAJO</v>
@@ -647,10 +649,10 @@
         </row>
         <row r="26">
           <cell r="F26">
-            <v>701.8125</v>
+            <v>697.70588235294122</v>
           </cell>
           <cell r="G26">
-            <v>-0.10932117604399594</v>
+            <v>-0.11453293470648662</v>
           </cell>
           <cell r="H26" t="str">
             <v>BAJO</v>
@@ -658,10 +660,10 @@
         </row>
         <row r="27">
           <cell r="F27">
-            <v>1094</v>
+            <v>1074.3529411764705</v>
           </cell>
           <cell r="G27">
-            <v>-0.14109466128308668</v>
+            <v>-0.1565196738183835</v>
           </cell>
           <cell r="H27" t="str">
             <v>BAJO</v>
@@ -669,10 +671,10 @@
         </row>
         <row r="28">
           <cell r="F28">
-            <v>564.5</v>
+            <v>571.47058823529414</v>
           </cell>
           <cell r="G28">
-            <v>6.6723656978313839E-2</v>
+            <v>7.9895829473695557E-2</v>
           </cell>
           <cell r="H28" t="str">
             <v>SUBIÓ</v>
@@ -680,10 +682,10 @@
         </row>
         <row r="29">
           <cell r="F29">
-            <v>422.125</v>
+            <v>429.11764705882354</v>
           </cell>
           <cell r="G29">
-            <v>5.0435478137220047E-2</v>
+            <v>6.7836306225298681E-2</v>
           </cell>
           <cell r="H29" t="str">
             <v>SUBIÓ</v>
@@ -691,10 +693,10 @@
         </row>
         <row r="30">
           <cell r="F30">
-            <v>240.75</v>
+            <v>235.11764705882354</v>
           </cell>
           <cell r="G30">
-            <v>2.1637984981226532</v>
+            <v>2.0897813443274678</v>
           </cell>
           <cell r="H30" t="str">
             <v>SUBIÓ</v>
@@ -702,10 +704,10 @@
         </row>
         <row r="31">
           <cell r="F31">
-            <v>290.8125</v>
+            <v>287.58823529411762</v>
           </cell>
           <cell r="G31">
-            <v>3.0337268824306465</v>
+            <v>2.9890045846608122</v>
           </cell>
           <cell r="H31" t="str">
             <v>SUBIÓ</v>
@@ -713,10 +715,10 @@
         </row>
         <row r="32">
           <cell r="F32">
-            <v>131.4375</v>
+            <v>132.47058823529412</v>
           </cell>
           <cell r="G32">
-            <v>2.8002793296089346E-2</v>
+            <v>3.6082813013473602E-2</v>
           </cell>
           <cell r="H32" t="str">
             <v>SUBIÓ</v>
@@ -724,10 +726,10 @@
         </row>
         <row r="33">
           <cell r="F33">
-            <v>137.4375</v>
+            <v>138.58823529411765</v>
           </cell>
           <cell r="G33">
-            <v>-4.1133720930232598E-2</v>
+            <v>-3.3105335157318727E-2</v>
           </cell>
           <cell r="H33" t="str">
             <v>BAJO</v>
@@ -735,10 +737,10 @@
         </row>
         <row r="34">
           <cell r="F34">
-            <v>759.875</v>
+            <v>776.94117647058829</v>
           </cell>
           <cell r="G34">
-            <v>0.16511207651869175</v>
+            <v>0.19127954920285895</v>
           </cell>
           <cell r="H34" t="str">
             <v>SUBIÓ</v>
@@ -746,10 +748,10 @@
         </row>
         <row r="35">
           <cell r="F35">
-            <v>598.3125</v>
+            <v>605.52941176470586</v>
           </cell>
           <cell r="G35">
-            <v>-4.8859765329295923E-2</v>
+            <v>-3.7387006278665869E-2</v>
           </cell>
           <cell r="H35" t="str">
             <v>BAJO</v>
@@ -757,10 +759,10 @@
         </row>
         <row r="36">
           <cell r="F36">
-            <v>791.625</v>
+            <v>799.88235294117646</v>
           </cell>
           <cell r="G36">
-            <v>-7.10703509164059E-2</v>
+            <v>-6.1380788345736126E-2</v>
           </cell>
           <cell r="H36" t="str">
             <v>BAJO</v>
@@ -768,10 +770,10 @@
         </row>
         <row r="37">
           <cell r="F37">
-            <v>519.8125</v>
+            <v>530.94117647058829</v>
           </cell>
           <cell r="G37">
-            <v>-0.10222366148531947</v>
+            <v>-8.3003149446306934E-2</v>
           </cell>
           <cell r="H37" t="str">
             <v>BAJO</v>
@@ -779,10 +781,10 @@
         </row>
         <row r="38">
           <cell r="F38">
-            <v>3.625</v>
+            <v>4.0588235294117645</v>
           </cell>
           <cell r="G38">
-            <v>0.46394230769230771</v>
+            <v>0.63914027149321262</v>
           </cell>
           <cell r="H38" t="str">
             <v>SUBIÓ</v>
@@ -790,10 +792,10 @@
         </row>
         <row r="39">
           <cell r="F39">
-            <v>0.4375</v>
+            <v>0.6470588235294118</v>
           </cell>
           <cell r="G39">
-            <v>2.0833333333333481E-2</v>
+            <v>0.50980392156862764</v>
           </cell>
           <cell r="H39" t="str">
             <v>SUBIÓ</v>
@@ -801,10 +803,10 @@
         </row>
         <row r="40">
           <cell r="F40">
-            <v>146.5625</v>
+            <v>149.23529411764707</v>
           </cell>
           <cell r="G40">
-            <v>6.8684895833333259E-2</v>
+            <v>8.8174019607843324E-2</v>
           </cell>
           <cell r="H40" t="str">
             <v>SUBIÓ</v>
@@ -812,10 +814,10 @@
         </row>
         <row r="41">
           <cell r="F41">
-            <v>568</v>
+            <v>573.23529411764707</v>
           </cell>
           <cell r="G41">
-            <v>2.4478227261015117E-2</v>
+            <v>3.3920911832911571E-2</v>
           </cell>
           <cell r="H41" t="str">
             <v>SUBIÓ</v>
@@ -823,10 +825,10 @@
         </row>
         <row r="42">
           <cell r="F42">
-            <v>408.625</v>
+            <v>416.11764705882354</v>
           </cell>
           <cell r="G42">
-            <v>2.0767748296880604</v>
+            <v>2.1331913188366065</v>
           </cell>
           <cell r="H42" t="str">
             <v>SUBIÓ</v>
@@ -834,10 +836,10 @@
         </row>
         <row r="43">
           <cell r="F43">
-            <v>213.0625</v>
+            <v>235.05882352941177</v>
           </cell>
           <cell r="G43">
-            <v>-0.2805414857694164</v>
+            <v>-0.2062654294713544</v>
           </cell>
           <cell r="H43" t="str">
             <v>BAJO</v>
@@ -845,10 +847,10 @@
         </row>
         <row r="44">
           <cell r="F44">
-            <v>478.1875</v>
+            <v>499.23529411764707</v>
           </cell>
           <cell r="G44">
-            <v>-9.5565387733045015E-2</v>
+            <v>-5.575599599472314E-2</v>
           </cell>
           <cell r="H44" t="str">
             <v>BAJO</v>
@@ -856,10 +858,10 @@
         </row>
         <row r="45">
           <cell r="F45">
-            <v>281.25</v>
+            <v>298.76470588235293</v>
           </cell>
           <cell r="G45">
-            <v>-7.9593267882187901E-2</v>
+            <v>-2.2275389819321867E-2</v>
           </cell>
           <cell r="H45" t="str">
             <v>BAJO</v>
@@ -867,32 +869,32 @@
         </row>
         <row r="46">
           <cell r="F46">
-            <v>286.125</v>
+            <v>300.11764705882354</v>
           </cell>
           <cell r="G46">
-            <v>-1.3037943495400883E-2</v>
+            <v>3.5228414624719706E-2</v>
           </cell>
           <cell r="H46" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="47">
           <cell r="F47">
-            <v>59</v>
+            <v>57.647058823529413</v>
           </cell>
           <cell r="G47">
-            <v>2.2277227722772297E-2</v>
+            <v>-1.1648223645893685E-3</v>
           </cell>
           <cell r="H47" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="48">
           <cell r="F48">
-            <v>128.875</v>
+            <v>125.64705882352941</v>
           </cell>
           <cell r="G48">
-            <v>0.23072987721691685</v>
+            <v>0.19990369954257292</v>
           </cell>
           <cell r="H48" t="str">
             <v>SUBIÓ</v>
@@ -900,10 +902,10 @@
         </row>
         <row r="49">
           <cell r="F49">
-            <v>43.875</v>
+            <v>43.705882352941174</v>
           </cell>
           <cell r="G49">
-            <v>-0.11064189189189189</v>
+            <v>-0.11406995230524652</v>
           </cell>
           <cell r="H49" t="str">
             <v>BAJO</v>
@@ -911,10 +913,10 @@
         </row>
         <row r="50">
           <cell r="F50">
-            <v>55.25</v>
+            <v>53.470588235294116</v>
           </cell>
           <cell r="G50">
-            <v>-1.5060240963855609E-3</v>
+            <v>-3.3664068036853401E-2</v>
           </cell>
           <cell r="H50" t="str">
             <v>BAJO</v>
@@ -1177,11 +1179,11 @@
       </c>
       <c r="E2" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F4</f>
-        <v>1206.1875</v>
+        <v>1205.2941176470588</v>
       </c>
       <c r="F2" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G4</f>
-        <v>1.5227955911823576E-2</v>
+        <v>1.4476010845219767E-2</v>
       </c>
       <c r="G2" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H4</f>
@@ -1206,11 +1208,11 @@
       </c>
       <c r="E3" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F5</f>
-        <v>55.375</v>
+        <v>53.823529411764703</v>
       </c>
       <c r="F3" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G5</f>
-        <v>-0.27501558603491272</v>
+        <v>-0.29532785682851692</v>
       </c>
       <c r="G3" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H5</f>
@@ -1235,11 +1237,11 @@
       </c>
       <c r="E4" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F6</f>
-        <v>493.125</v>
+        <v>492.1764705882353</v>
       </c>
       <c r="F4" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G6</f>
-        <v>-3.209412094588282E-2</v>
+        <v>-3.3955894723530999E-2</v>
       </c>
       <c r="G4" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H6</f>
@@ -1264,11 +1266,11 @@
       </c>
       <c r="E5" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F7</f>
-        <v>107.5</v>
+        <v>108.70588235294117</v>
       </c>
       <c r="F5" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G7</f>
-        <v>9.6938775510204023E-2</v>
+        <v>0.10924369747899165</v>
       </c>
       <c r="G5" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H7</f>
@@ -1293,11 +1295,11 @@
       </c>
       <c r="E6" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F8</f>
-        <v>13.1875</v>
+        <v>14.176470588235293</v>
       </c>
       <c r="F6" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G8</f>
-        <v>0.10333665338645415</v>
+        <v>0.18607921256151849</v>
       </c>
       <c r="G6" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H8</f>
@@ -1322,11 +1324,11 @@
       </c>
       <c r="E7" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F9</f>
-        <v>1420.8125</v>
+        <v>1412.8823529411766</v>
       </c>
       <c r="F7" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G9</f>
-        <v>-2.7062885186030505E-2</v>
+        <v>-3.2493252950575258E-2</v>
       </c>
       <c r="G7" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H9</f>
@@ -1351,11 +1353,11 @@
       </c>
       <c r="E8" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F10</f>
-        <v>147.5</v>
+        <v>147.52941176470588</v>
       </c>
       <c r="F8" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G10</f>
-        <v>-1.9157694743508591E-2</v>
+        <v>-1.8962113027604977E-2</v>
       </c>
       <c r="G8" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H10</f>
@@ -1380,11 +1382,11 @@
       </c>
       <c r="E9" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F11</f>
-        <v>306.75</v>
+        <v>318.41176470588238</v>
       </c>
       <c r="F9" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G11</f>
-        <v>-0.10717255717255714</v>
+        <v>-7.3229790876849554E-2</v>
       </c>
       <c r="G9" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H11</f>
@@ -1409,11 +1411,11 @@
       </c>
       <c r="E10" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F12</f>
-        <v>767.0625</v>
+        <v>788.47058823529414</v>
       </c>
       <c r="F10" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G12</f>
-        <v>1.1381292728402936E-3</v>
+        <v>2.907907724929637E-2</v>
       </c>
       <c r="G10" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H12</f>
@@ -1438,11 +1440,11 @@
       </c>
       <c r="E11" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F13</f>
-        <v>368.5</v>
+        <v>383.8235294117647</v>
       </c>
       <c r="F11" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G13</f>
-        <v>1.5684473027956392E-2</v>
+        <v>5.7920214942519976E-2</v>
       </c>
       <c r="G11" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H13</f>
@@ -1467,11 +1469,11 @@
       </c>
       <c r="E12" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F14</f>
-        <v>3359.8125</v>
+        <v>3419.5294117647059</v>
       </c>
       <c r="F12" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G14</f>
-        <v>-4.5920833784076187E-2</v>
+        <v>-2.8963143024410165E-2</v>
       </c>
       <c r="G12" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H14</f>
@@ -1496,11 +1498,11 @@
       </c>
       <c r="E13" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F15</f>
-        <v>2102</v>
+        <v>2119.4705882352941</v>
       </c>
       <c r="F13" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G15</f>
-        <v>-8.8069414316702788E-2</v>
+        <v>-8.048998341201985E-2</v>
       </c>
       <c r="G13" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H15</f>
@@ -1525,11 +1527,11 @@
       </c>
       <c r="E14" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F16</f>
-        <v>2141.9375</v>
+        <v>2147.1176470588234</v>
       </c>
       <c r="F14" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G16</f>
-        <v>-5.4948157408185483E-2</v>
+        <v>-5.2662606348531482E-2</v>
       </c>
       <c r="G14" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H16</f>
@@ -1554,11 +1556,11 @@
       </c>
       <c r="E15" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F17</f>
-        <v>2611.25</v>
+        <v>2656.1764705882351</v>
       </c>
       <c r="F15" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G17</f>
-        <v>-2.3466716529543796E-2</v>
+        <v>-6.6654934225000018E-3</v>
       </c>
       <c r="G15" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H17</f>
@@ -1583,11 +1585,11 @@
       </c>
       <c r="E16" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F18</f>
-        <v>709.4375</v>
+        <v>719.94117647058829</v>
       </c>
       <c r="F16" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G18</f>
-        <v>0.82285421509849499</v>
+        <v>0.84984273900432572</v>
       </c>
       <c r="G16" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H18</f>
@@ -1612,11 +1614,11 @@
       </c>
       <c r="E17" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F19</f>
-        <v>813.4375</v>
+        <v>842.47058823529414</v>
       </c>
       <c r="F17" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G19</f>
-        <v>0.89886477323254765</v>
+        <v>0.96663876755682265</v>
       </c>
       <c r="G17" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H19</f>
@@ -1641,11 +1643,11 @@
       </c>
       <c r="E18" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F20</f>
-        <v>857.125</v>
+        <v>864.58823529411768</v>
       </c>
       <c r="F18" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G20</f>
-        <v>1.1934712405556911</v>
+        <v>1.212570429097791</v>
       </c>
       <c r="G18" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H20</f>
@@ -1670,11 +1672,11 @@
       </c>
       <c r="E19" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F21</f>
-        <v>271.75</v>
+        <v>281</v>
       </c>
       <c r="F19" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G21</f>
-        <v>0.12293388429752072</v>
+        <v>0.16115702479338845</v>
       </c>
       <c r="G19" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H21</f>
@@ -1699,11 +1701,11 @@
       </c>
       <c r="E20" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F22</f>
-        <v>127.75</v>
+        <v>132.64705882352942</v>
       </c>
       <c r="F20" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G22</f>
-        <v>-0.10155726724715342</v>
+        <v>-6.7117134864662531E-2</v>
       </c>
       <c r="G20" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H22</f>
@@ -1728,15 +1730,15 @@
       </c>
       <c r="E21" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F23</f>
-        <v>505.1875</v>
+        <v>519.11764705882354</v>
       </c>
       <c r="F21" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G23</f>
-        <v>-1.5411832946635728E-2</v>
+        <v>1.173740958100189E-2</v>
       </c>
       <c r="G21" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H23</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H21">
         <v>4.1500000000000004</v>
@@ -1757,11 +1759,11 @@
       </c>
       <c r="E22" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F24</f>
-        <v>849.5</v>
+        <v>874.41176470588232</v>
       </c>
       <c r="F22" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G24</f>
-        <v>4.6980456599565734E-2</v>
+        <v>7.7683376889695843E-2</v>
       </c>
       <c r="G22" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H24</f>
@@ -1786,11 +1788,11 @@
       </c>
       <c r="E23" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F25</f>
-        <v>64.5</v>
+        <v>60.705882352941174</v>
       </c>
       <c r="F23" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G25</f>
-        <v>-0.13945362134688688</v>
+        <v>-0.19007399656177593</v>
       </c>
       <c r="G23" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H25</f>
@@ -1815,11 +1817,11 @@
       </c>
       <c r="E24" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F26</f>
-        <v>701.8125</v>
+        <v>697.70588235294122</v>
       </c>
       <c r="F24" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G26</f>
-        <v>-0.10932117604399594</v>
+        <v>-0.11453293470648662</v>
       </c>
       <c r="G24" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H26</f>
@@ -1844,11 +1846,11 @@
       </c>
       <c r="E25" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F27</f>
-        <v>1094</v>
+        <v>1074.3529411764705</v>
       </c>
       <c r="F25" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G27</f>
-        <v>-0.14109466128308668</v>
+        <v>-0.1565196738183835</v>
       </c>
       <c r="G25" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H27</f>
@@ -1873,11 +1875,11 @@
       </c>
       <c r="E26" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F28</f>
-        <v>564.5</v>
+        <v>571.47058823529414</v>
       </c>
       <c r="F26" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G28</f>
-        <v>6.6723656978313839E-2</v>
+        <v>7.9895829473695557E-2</v>
       </c>
       <c r="G26" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H28</f>
@@ -1902,11 +1904,11 @@
       </c>
       <c r="E27" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F29</f>
-        <v>422.125</v>
+        <v>429.11764705882354</v>
       </c>
       <c r="F27" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G29</f>
-        <v>5.0435478137220047E-2</v>
+        <v>6.7836306225298681E-2</v>
       </c>
       <c r="G27" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H29</f>
@@ -1931,11 +1933,11 @@
       </c>
       <c r="E28" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F30</f>
-        <v>240.75</v>
+        <v>235.11764705882354</v>
       </c>
       <c r="F28" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G30</f>
-        <v>2.1637984981226532</v>
+        <v>2.0897813443274678</v>
       </c>
       <c r="G28" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H30</f>
@@ -1960,11 +1962,11 @@
       </c>
       <c r="E29" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F31</f>
-        <v>290.8125</v>
+        <v>287.58823529411762</v>
       </c>
       <c r="F29" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G31</f>
-        <v>3.0337268824306465</v>
+        <v>2.9890045846608122</v>
       </c>
       <c r="G29" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H31</f>
@@ -1989,11 +1991,11 @@
       </c>
       <c r="E30" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F32</f>
-        <v>131.4375</v>
+        <v>132.47058823529412</v>
       </c>
       <c r="F30" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G32</f>
-        <v>2.8002793296089346E-2</v>
+        <v>3.6082813013473602E-2</v>
       </c>
       <c r="G30" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H32</f>
@@ -2018,11 +2020,11 @@
       </c>
       <c r="E31" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F33</f>
-        <v>137.4375</v>
+        <v>138.58823529411765</v>
       </c>
       <c r="F31" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G33</f>
-        <v>-4.1133720930232598E-2</v>
+        <v>-3.3105335157318727E-2</v>
       </c>
       <c r="G31" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H33</f>
@@ -2047,11 +2049,11 @@
       </c>
       <c r="E32" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F34</f>
-        <v>759.875</v>
+        <v>776.94117647058829</v>
       </c>
       <c r="F32" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G34</f>
-        <v>0.16511207651869175</v>
+        <v>0.19127954920285895</v>
       </c>
       <c r="G32" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H34</f>
@@ -2076,11 +2078,11 @@
       </c>
       <c r="E33" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F35</f>
-        <v>598.3125</v>
+        <v>605.52941176470586</v>
       </c>
       <c r="F33" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G35</f>
-        <v>-4.8859765329295923E-2</v>
+        <v>-3.7387006278665869E-2</v>
       </c>
       <c r="G33" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H35</f>
@@ -2105,11 +2107,11 @@
       </c>
       <c r="E34" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F36</f>
-        <v>791.625</v>
+        <v>799.88235294117646</v>
       </c>
       <c r="F34" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G36</f>
-        <v>-7.10703509164059E-2</v>
+        <v>-6.1380788345736126E-2</v>
       </c>
       <c r="G34" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H36</f>
@@ -2134,11 +2136,11 @@
       </c>
       <c r="E35" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F37</f>
-        <v>519.8125</v>
+        <v>530.94117647058829</v>
       </c>
       <c r="F35" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G37</f>
-        <v>-0.10222366148531947</v>
+        <v>-8.3003149446306934E-2</v>
       </c>
       <c r="G35" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H37</f>
@@ -2163,11 +2165,11 @@
       </c>
       <c r="E36" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F38</f>
-        <v>3.625</v>
+        <v>4.0588235294117645</v>
       </c>
       <c r="F36" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G38</f>
-        <v>0.46394230769230771</v>
+        <v>0.63914027149321262</v>
       </c>
       <c r="G36" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H38</f>
@@ -2192,11 +2194,11 @@
       </c>
       <c r="E37" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F39</f>
-        <v>0.4375</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="F37" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G39</f>
-        <v>2.0833333333333481E-2</v>
+        <v>0.50980392156862764</v>
       </c>
       <c r="G37" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H39</f>
@@ -2221,11 +2223,11 @@
       </c>
       <c r="E38" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F40</f>
-        <v>146.5625</v>
+        <v>149.23529411764707</v>
       </c>
       <c r="F38" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G40</f>
-        <v>6.8684895833333259E-2</v>
+        <v>8.8174019607843324E-2</v>
       </c>
       <c r="G38" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H40</f>
@@ -2250,11 +2252,11 @@
       </c>
       <c r="E39" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F41</f>
-        <v>568</v>
+        <v>573.23529411764707</v>
       </c>
       <c r="F39" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G41</f>
-        <v>2.4478227261015117E-2</v>
+        <v>3.3920911832911571E-2</v>
       </c>
       <c r="G39" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H41</f>
@@ -2279,11 +2281,11 @@
       </c>
       <c r="E40" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F42</f>
-        <v>408.625</v>
+        <v>416.11764705882354</v>
       </c>
       <c r="F40" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G42</f>
-        <v>2.0767748296880604</v>
+        <v>2.1331913188366065</v>
       </c>
       <c r="G40" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H42</f>
@@ -2308,11 +2310,11 @@
       </c>
       <c r="E41" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F43</f>
-        <v>213.0625</v>
+        <v>235.05882352941177</v>
       </c>
       <c r="F41" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G43</f>
-        <v>-0.2805414857694164</v>
+        <v>-0.2062654294713544</v>
       </c>
       <c r="G41" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H43</f>
@@ -2337,11 +2339,11 @@
       </c>
       <c r="E42" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F44</f>
-        <v>478.1875</v>
+        <v>499.23529411764707</v>
       </c>
       <c r="F42" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G44</f>
-        <v>-9.5565387733045015E-2</v>
+        <v>-5.575599599472314E-2</v>
       </c>
       <c r="G42" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H44</f>
@@ -2366,11 +2368,11 @@
       </c>
       <c r="E43" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F45</f>
-        <v>281.25</v>
+        <v>298.76470588235293</v>
       </c>
       <c r="F43" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G45</f>
-        <v>-7.9593267882187901E-2</v>
+        <v>-2.2275389819321867E-2</v>
       </c>
       <c r="G43" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H45</f>
@@ -2395,15 +2397,15 @@
       </c>
       <c r="E44" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F46</f>
-        <v>286.125</v>
+        <v>300.11764705882354</v>
       </c>
       <c r="F44" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G46</f>
-        <v>-1.3037943495400883E-2</v>
+        <v>3.5228414624719706E-2</v>
       </c>
       <c r="G44" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H46</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H44">
         <v>0.81</v>
@@ -2424,15 +2426,15 @@
       </c>
       <c r="E45" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F47</f>
-        <v>59</v>
+        <v>57.647058823529413</v>
       </c>
       <c r="F45" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G47</f>
-        <v>2.2277227722772297E-2</v>
+        <v>-1.1648223645893685E-3</v>
       </c>
       <c r="G45" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H47</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H45">
         <v>2.62</v>
@@ -2453,11 +2455,11 @@
       </c>
       <c r="E46" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F48</f>
-        <v>128.875</v>
+        <v>125.64705882352941</v>
       </c>
       <c r="F46" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G48</f>
-        <v>0.23072987721691685</v>
+        <v>0.19990369954257292</v>
       </c>
       <c r="G46" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H48</f>
@@ -2482,11 +2484,11 @@
       </c>
       <c r="E47" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F49</f>
-        <v>43.875</v>
+        <v>43.705882352941174</v>
       </c>
       <c r="F47" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G49</f>
-        <v>-0.11064189189189189</v>
+        <v>-0.11406995230524652</v>
       </c>
       <c r="G47" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H49</f>
@@ -2511,11 +2513,11 @@
       </c>
       <c r="E48" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F50</f>
-        <v>55.25</v>
+        <v>53.470588235294116</v>
       </c>
       <c r="F48" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G50</f>
-        <v>-1.5060240963855609E-3</v>
+        <v>-3.3664068036853401E-2</v>
       </c>
       <c r="G48" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H50</f>

--- a/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
+++ b/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79E2F14B-787F-4E71-A46E-5191BA03884E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAF8602D-4CDD-4D2E-896A-4E73B2D82A02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -377,6 +377,7 @@
       <sheetName val="INVENTARIO NACIONAL 22-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 23-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 24-09-26"/>
+      <sheetName val="INVENTARIO NACIONAL 25-09-26"/>
       <sheetName val="CCC"/>
       <sheetName val="VINCULO VTS BY SKU AGOSTO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
@@ -404,13 +405,14 @@
       <sheetData sheetId="18"/>
       <sheetData sheetId="19"/>
       <sheetData sheetId="20"/>
-      <sheetData sheetId="21">
+      <sheetData sheetId="21"/>
+      <sheetData sheetId="22">
         <row r="4">
           <cell r="F4">
-            <v>1205.2941176470588</v>
+            <v>1200.3888888888889</v>
           </cell>
           <cell r="G4">
-            <v>1.4476010845219767E-2</v>
+            <v>1.0347361389445586E-2</v>
           </cell>
           <cell r="H4" t="str">
             <v>SUBIÓ</v>
@@ -418,10 +420,10 @@
         </row>
         <row r="5">
           <cell r="F5">
-            <v>53.823529411764703</v>
+            <v>51.333333333333336</v>
           </cell>
           <cell r="G5">
-            <v>-0.29532785682851692</v>
+            <v>-0.32793017456359097</v>
           </cell>
           <cell r="H5" t="str">
             <v>BAJO</v>
@@ -429,10 +431,10 @@
         </row>
         <row r="6">
           <cell r="F6">
-            <v>492.1764705882353</v>
+            <v>494.11111111111109</v>
           </cell>
           <cell r="G6">
-            <v>-3.3955894723530999E-2</v>
+            <v>-3.0158581798922057E-2</v>
           </cell>
           <cell r="H6" t="str">
             <v>BAJO</v>
@@ -440,10 +442,10 @@
         </row>
         <row r="7">
           <cell r="F7">
-            <v>108.70588235294117</v>
+            <v>109.22222222222223</v>
           </cell>
           <cell r="G7">
-            <v>0.10924369747899165</v>
+            <v>0.11451247165532896</v>
           </cell>
           <cell r="H7" t="str">
             <v>SUBIÓ</v>
@@ -451,10 +453,10 @@
         </row>
         <row r="8">
           <cell r="F8">
-            <v>14.176470588235293</v>
+            <v>13.944444444444445</v>
           </cell>
           <cell r="G8">
-            <v>0.18607921256151849</v>
+            <v>0.16666666666666674</v>
           </cell>
           <cell r="H8" t="str">
             <v>SUBIÓ</v>
@@ -462,10 +464,10 @@
         </row>
         <row r="9">
           <cell r="F9">
-            <v>1412.8823529411766</v>
+            <v>1431.6666666666667</v>
           </cell>
           <cell r="G9">
-            <v>-3.2493252950575258E-2</v>
+            <v>-1.963022141063675E-2</v>
           </cell>
           <cell r="H9" t="str">
             <v>BAJO</v>
@@ -473,21 +475,21 @@
         </row>
         <row r="10">
           <cell r="F10">
-            <v>147.52941176470588</v>
+            <v>153.88888888888889</v>
           </cell>
           <cell r="G10">
-            <v>-1.8962113027604977E-2</v>
+            <v>2.3327000211104121E-2</v>
           </cell>
           <cell r="H10" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="11">
           <cell r="F11">
-            <v>318.41176470588238</v>
+            <v>322.83333333333331</v>
           </cell>
           <cell r="G11">
-            <v>-7.3229790876849554E-2</v>
+            <v>-6.036036036036041E-2</v>
           </cell>
           <cell r="H11" t="str">
             <v>BAJO</v>
@@ -495,10 +497,10 @@
         </row>
         <row r="12">
           <cell r="F12">
-            <v>788.47058823529414</v>
+            <v>794.33333333333337</v>
           </cell>
           <cell r="G12">
-            <v>2.907907724929637E-2</v>
+            <v>3.6730888750776902E-2</v>
           </cell>
           <cell r="H12" t="str">
             <v>SUBIÓ</v>
@@ -506,10 +508,10 @@
         </row>
         <row r="13">
           <cell r="F13">
-            <v>383.8235294117647</v>
+            <v>388</v>
           </cell>
           <cell r="G13">
-            <v>5.7920214942519976E-2</v>
+            <v>6.9431683948024681E-2</v>
           </cell>
           <cell r="H13" t="str">
             <v>SUBIÓ</v>
@@ -517,10 +519,10 @@
         </row>
         <row r="14">
           <cell r="F14">
-            <v>3419.5294117647059</v>
+            <v>3425.9444444444443</v>
           </cell>
           <cell r="G14">
-            <v>-2.8963143024410165E-2</v>
+            <v>-2.714147915765186E-2</v>
           </cell>
           <cell r="H14" t="str">
             <v>BAJO</v>
@@ -528,10 +530,10 @@
         </row>
         <row r="15">
           <cell r="F15">
-            <v>2119.4705882352941</v>
+            <v>2144.2222222222222</v>
           </cell>
           <cell r="G15">
-            <v>-8.048998341201985E-2</v>
+            <v>-6.9751747409014242E-2</v>
           </cell>
           <cell r="H15" t="str">
             <v>BAJO</v>
@@ -539,10 +541,10 @@
         </row>
         <row r="16">
           <cell r="F16">
-            <v>2147.1176470588234</v>
+            <v>2161.6666666666665</v>
           </cell>
           <cell r="G16">
-            <v>-5.2662606348531482E-2</v>
+            <v>-4.6243381796789662E-2</v>
           </cell>
           <cell r="H16" t="str">
             <v>BAJO</v>
@@ -550,10 +552,10 @@
         </row>
         <row r="17">
           <cell r="F17">
-            <v>2656.1764705882351</v>
+            <v>2671.0555555555557</v>
           </cell>
           <cell r="G17">
-            <v>-6.6654934225000018E-3</v>
+            <v>-1.1011385356934911E-3</v>
           </cell>
           <cell r="H17" t="str">
             <v>BAJO</v>
@@ -561,10 +563,10 @@
         </row>
         <row r="18">
           <cell r="F18">
-            <v>719.94117647058829</v>
+            <v>728.72222222222217</v>
           </cell>
           <cell r="G18">
-            <v>0.84984273900432572</v>
+            <v>0.87240507361637887</v>
           </cell>
           <cell r="H18" t="str">
             <v>SUBIÓ</v>
@@ -572,10 +574,10 @@
         </row>
         <row r="19">
           <cell r="F19">
-            <v>842.47058823529414</v>
+            <v>858.83333333333337</v>
           </cell>
           <cell r="G19">
-            <v>0.96663876755682265</v>
+            <v>1.0048354824366386</v>
           </cell>
           <cell r="H19" t="str">
             <v>SUBIÓ</v>
@@ -583,10 +585,10 @@
         </row>
         <row r="20">
           <cell r="F20">
-            <v>864.58823529411768</v>
+            <v>872.16666666666663</v>
           </cell>
           <cell r="G20">
-            <v>1.212570429097791</v>
+            <v>1.2319644162807699</v>
           </cell>
           <cell r="H20" t="str">
             <v>SUBIÓ</v>
@@ -594,10 +596,10 @@
         </row>
         <row r="21">
           <cell r="F21">
-            <v>281</v>
+            <v>277.83333333333331</v>
           </cell>
           <cell r="G21">
-            <v>0.16115702479338845</v>
+            <v>0.14807162534435259</v>
           </cell>
           <cell r="H21" t="str">
             <v>SUBIÓ</v>
@@ -605,10 +607,10 @@
         </row>
         <row r="22">
           <cell r="F22">
-            <v>132.64705882352942</v>
+            <v>133.88888888888889</v>
           </cell>
           <cell r="G22">
-            <v>-6.7117134864662531E-2</v>
+            <v>-5.8383567760661004E-2</v>
           </cell>
           <cell r="H22" t="str">
             <v>BAJO</v>
@@ -616,21 +618,21 @@
         </row>
         <row r="23">
           <cell r="F23">
-            <v>519.11764705882354</v>
+            <v>512.44444444444446</v>
           </cell>
           <cell r="G23">
-            <v>1.173740958100189E-2</v>
+            <v>-1.2683681361175259E-3</v>
           </cell>
           <cell r="H23" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="24">
           <cell r="F24">
-            <v>874.41176470588232</v>
+            <v>877.83333333333337</v>
           </cell>
           <cell r="G24">
-            <v>7.7683376889695843E-2</v>
+            <v>8.1900346264452084E-2</v>
           </cell>
           <cell r="H24" t="str">
             <v>SUBIÓ</v>
@@ -638,10 +640,10 @@
         </row>
         <row r="25">
           <cell r="F25">
-            <v>60.705882352941174</v>
+            <v>64</v>
           </cell>
           <cell r="G25">
-            <v>-0.19007399656177593</v>
+            <v>-0.14612452350698857</v>
           </cell>
           <cell r="H25" t="str">
             <v>BAJO</v>
@@ -649,10 +651,10 @@
         </row>
         <row r="26">
           <cell r="F26">
-            <v>697.70588235294122</v>
+            <v>705.22222222222217</v>
           </cell>
           <cell r="G26">
-            <v>-0.11453293470648662</v>
+            <v>-0.10499385588525623</v>
           </cell>
           <cell r="H26" t="str">
             <v>BAJO</v>
@@ -660,10 +662,10 @@
         </row>
         <row r="27">
           <cell r="F27">
-            <v>1074.3529411764705</v>
+            <v>1084.4444444444443</v>
           </cell>
           <cell r="G27">
-            <v>-0.1565196738183835</v>
+            <v>-0.1485967798215444</v>
           </cell>
           <cell r="H27" t="str">
             <v>BAJO</v>
@@ -671,10 +673,10 @@
         </row>
         <row r="28">
           <cell r="F28">
-            <v>571.47058823529414</v>
+            <v>566.72222222222217</v>
           </cell>
           <cell r="G28">
-            <v>7.9895829473695557E-2</v>
+            <v>7.0922943099672953E-2</v>
           </cell>
           <cell r="H28" t="str">
             <v>SUBIÓ</v>
@@ -682,10 +684,10 @@
         </row>
         <row r="29">
           <cell r="F29">
-            <v>429.11764705882354</v>
+            <v>438.11111111111109</v>
           </cell>
           <cell r="G29">
-            <v>6.7836306225298681E-2</v>
+            <v>9.0216060354702421E-2</v>
           </cell>
           <cell r="H29" t="str">
             <v>SUBIÓ</v>
@@ -693,10 +695,10 @@
         </row>
         <row r="30">
           <cell r="F30">
-            <v>235.11764705882354</v>
+            <v>242.88888888888889</v>
           </cell>
           <cell r="G30">
-            <v>2.0897813443274678</v>
+            <v>2.191906549853984</v>
           </cell>
           <cell r="H30" t="str">
             <v>SUBIÓ</v>
@@ -704,10 +706,10 @@
         </row>
         <row r="31">
           <cell r="F31">
-            <v>287.58823529411762</v>
+            <v>295.38888888888891</v>
           </cell>
           <cell r="G31">
-            <v>2.9890045846608122</v>
+            <v>3.0972038749449577</v>
           </cell>
           <cell r="H31" t="str">
             <v>SUBIÓ</v>
@@ -715,10 +717,10 @@
         </row>
         <row r="32">
           <cell r="F32">
-            <v>132.47058823529412</v>
+            <v>132</v>
           </cell>
           <cell r="G32">
-            <v>3.6082813013473602E-2</v>
+            <v>3.240223463687153E-2</v>
           </cell>
           <cell r="H32" t="str">
             <v>SUBIÓ</v>
@@ -726,10 +728,10 @@
         </row>
         <row r="33">
           <cell r="F33">
-            <v>138.58823529411765</v>
+            <v>139.83333333333334</v>
           </cell>
           <cell r="G33">
-            <v>-3.3105335157318727E-2</v>
+            <v>-2.4418604651162745E-2</v>
           </cell>
           <cell r="H33" t="str">
             <v>BAJO</v>
@@ -737,10 +739,10 @@
         </row>
         <row r="34">
           <cell r="F34">
-            <v>776.94117647058829</v>
+            <v>786.16666666666663</v>
           </cell>
           <cell r="G34">
-            <v>0.19127954920285895</v>
+            <v>0.20542494158878499</v>
           </cell>
           <cell r="H34" t="str">
             <v>SUBIÓ</v>
@@ -748,10 +750,10 @@
         </row>
         <row r="35">
           <cell r="F35">
-            <v>605.52941176470586</v>
+            <v>614.83333333333337</v>
           </cell>
           <cell r="G35">
-            <v>-3.7387006278665869E-2</v>
+            <v>-2.2596517789553294E-2</v>
           </cell>
           <cell r="H35" t="str">
             <v>BAJO</v>
@@ -759,10 +761,10 @@
         </row>
         <row r="36">
           <cell r="F36">
-            <v>799.88235294117646</v>
+            <v>804.72222222222217</v>
           </cell>
           <cell r="G36">
-            <v>-6.1380788345736126E-2</v>
+            <v>-5.5701460289077631E-2</v>
           </cell>
           <cell r="H36" t="str">
             <v>BAJO</v>
@@ -770,10 +772,10 @@
         </row>
         <row r="37">
           <cell r="F37">
-            <v>530.94117647058829</v>
+            <v>535.55555555555554</v>
           </cell>
           <cell r="G37">
-            <v>-8.3003149446306934E-2</v>
+            <v>-7.5033582805603571E-2</v>
           </cell>
           <cell r="H37" t="str">
             <v>BAJO</v>
@@ -781,10 +783,10 @@
         </row>
         <row r="38">
           <cell r="F38">
-            <v>4.0588235294117645</v>
+            <v>4.2777777777777777</v>
           </cell>
           <cell r="G38">
-            <v>0.63914027149321262</v>
+            <v>0.72756410256410242</v>
           </cell>
           <cell r="H38" t="str">
             <v>SUBIÓ</v>
@@ -792,10 +794,10 @@
         </row>
         <row r="39">
           <cell r="F39">
-            <v>0.6470588235294118</v>
+            <v>0.61111111111111116</v>
           </cell>
           <cell r="G39">
-            <v>0.50980392156862764</v>
+            <v>0.42592592592592604</v>
           </cell>
           <cell r="H39" t="str">
             <v>SUBIÓ</v>
@@ -803,10 +805,10 @@
         </row>
         <row r="40">
           <cell r="F40">
-            <v>149.23529411764707</v>
+            <v>145.16666666666666</v>
           </cell>
           <cell r="G40">
-            <v>8.8174019607843324E-2</v>
+            <v>5.8506944444444375E-2</v>
           </cell>
           <cell r="H40" t="str">
             <v>SUBIÓ</v>
@@ -814,10 +816,10 @@
         </row>
         <row r="41">
           <cell r="F41">
-            <v>573.23529411764707</v>
+            <v>570.72222222222217</v>
           </cell>
           <cell r="G41">
-            <v>3.3920911832911571E-2</v>
+            <v>2.9388187466002247E-2</v>
           </cell>
           <cell r="H41" t="str">
             <v>SUBIÓ</v>
@@ -825,10 +827,10 @@
         </row>
         <row r="42">
           <cell r="F42">
-            <v>416.11764705882354</v>
+            <v>420.88888888888891</v>
           </cell>
           <cell r="G42">
-            <v>2.1331913188366065</v>
+            <v>2.1691167682562451</v>
           </cell>
           <cell r="H42" t="str">
             <v>SUBIÓ</v>
@@ -836,10 +838,10 @@
         </row>
         <row r="43">
           <cell r="F43">
-            <v>235.05882352941177</v>
+            <v>237.72222222222223</v>
           </cell>
           <cell r="G43">
-            <v>-0.2062654294713544</v>
+            <v>-0.19727180146861767</v>
           </cell>
           <cell r="H43" t="str">
             <v>BAJO</v>
@@ -847,10 +849,10 @@
         </row>
         <row r="44">
           <cell r="F44">
-            <v>499.23529411764707</v>
+            <v>495.55555555555554</v>
           </cell>
           <cell r="G44">
-            <v>-5.575599599472314E-2</v>
+            <v>-6.2715782521240437E-2</v>
           </cell>
           <cell r="H44" t="str">
             <v>BAJO</v>
@@ -858,10 +860,10 @@
         </row>
         <row r="45">
           <cell r="F45">
-            <v>298.76470588235293</v>
+            <v>300.27777777777777</v>
           </cell>
           <cell r="G45">
-            <v>-2.2275389819321867E-2</v>
+            <v>-1.732377538829144E-2</v>
           </cell>
           <cell r="H45" t="str">
             <v>BAJO</v>
@@ -869,10 +871,10 @@
         </row>
         <row r="46">
           <cell r="F46">
-            <v>300.11764705882354</v>
+            <v>299.33333333333331</v>
           </cell>
           <cell r="G46">
-            <v>3.5228414624719706E-2</v>
+            <v>3.2522996057818609E-2</v>
           </cell>
           <cell r="H46" t="str">
             <v>SUBIÓ</v>
@@ -880,10 +882,10 @@
         </row>
         <row r="47">
           <cell r="F47">
-            <v>57.647058823529413</v>
+            <v>55.111111111111114</v>
           </cell>
           <cell r="G47">
-            <v>-1.1648223645893685E-3</v>
+            <v>-4.5104510451045021E-2</v>
           </cell>
           <cell r="H47" t="str">
             <v>BAJO</v>
@@ -891,10 +893,10 @@
         </row>
         <row r="48">
           <cell r="F48">
-            <v>125.64705882352941</v>
+            <v>126.83333333333333</v>
           </cell>
           <cell r="G48">
-            <v>0.19990369954257292</v>
+            <v>0.21123237835379727</v>
           </cell>
           <cell r="H48" t="str">
             <v>SUBIÓ</v>
@@ -902,10 +904,10 @@
         </row>
         <row r="49">
           <cell r="F49">
-            <v>43.705882352941174</v>
+            <v>43.555555555555557</v>
           </cell>
           <cell r="G49">
-            <v>-0.11406995230524652</v>
+            <v>-0.11711711711711714</v>
           </cell>
           <cell r="H49" t="str">
             <v>BAJO</v>
@@ -913,10 +915,10 @@
         </row>
         <row r="50">
           <cell r="F50">
-            <v>53.470588235294116</v>
+            <v>54.444444444444443</v>
           </cell>
           <cell r="G50">
-            <v>-3.3664068036853401E-2</v>
+            <v>-1.6064257028112539E-2</v>
           </cell>
           <cell r="H50" t="str">
             <v>BAJO</v>
@@ -1179,11 +1181,11 @@
       </c>
       <c r="E2" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F4</f>
-        <v>1205.2941176470588</v>
+        <v>1200.3888888888889</v>
       </c>
       <c r="F2" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G4</f>
-        <v>1.4476010845219767E-2</v>
+        <v>1.0347361389445586E-2</v>
       </c>
       <c r="G2" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H4</f>
@@ -1208,11 +1210,11 @@
       </c>
       <c r="E3" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F5</f>
-        <v>53.823529411764703</v>
+        <v>51.333333333333336</v>
       </c>
       <c r="F3" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G5</f>
-        <v>-0.29532785682851692</v>
+        <v>-0.32793017456359097</v>
       </c>
       <c r="G3" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H5</f>
@@ -1237,11 +1239,11 @@
       </c>
       <c r="E4" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F6</f>
-        <v>492.1764705882353</v>
+        <v>494.11111111111109</v>
       </c>
       <c r="F4" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G6</f>
-        <v>-3.3955894723530999E-2</v>
+        <v>-3.0158581798922057E-2</v>
       </c>
       <c r="G4" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H6</f>
@@ -1266,11 +1268,11 @@
       </c>
       <c r="E5" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F7</f>
-        <v>108.70588235294117</v>
+        <v>109.22222222222223</v>
       </c>
       <c r="F5" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G7</f>
-        <v>0.10924369747899165</v>
+        <v>0.11451247165532896</v>
       </c>
       <c r="G5" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H7</f>
@@ -1295,11 +1297,11 @@
       </c>
       <c r="E6" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F8</f>
-        <v>14.176470588235293</v>
+        <v>13.944444444444445</v>
       </c>
       <c r="F6" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G8</f>
-        <v>0.18607921256151849</v>
+        <v>0.16666666666666674</v>
       </c>
       <c r="G6" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H8</f>
@@ -1324,11 +1326,11 @@
       </c>
       <c r="E7" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F9</f>
-        <v>1412.8823529411766</v>
+        <v>1431.6666666666667</v>
       </c>
       <c r="F7" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G9</f>
-        <v>-3.2493252950575258E-2</v>
+        <v>-1.963022141063675E-2</v>
       </c>
       <c r="G7" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H9</f>
@@ -1353,15 +1355,15 @@
       </c>
       <c r="E8" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F10</f>
-        <v>147.52941176470588</v>
+        <v>153.88888888888889</v>
       </c>
       <c r="F8" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G10</f>
-        <v>-1.8962113027604977E-2</v>
+        <v>2.3327000211104121E-2</v>
       </c>
       <c r="G8" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H10</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H8">
         <v>0.63</v>
@@ -1382,11 +1384,11 @@
       </c>
       <c r="E9" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F11</f>
-        <v>318.41176470588238</v>
+        <v>322.83333333333331</v>
       </c>
       <c r="F9" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G11</f>
-        <v>-7.3229790876849554E-2</v>
+        <v>-6.036036036036041E-2</v>
       </c>
       <c r="G9" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H11</f>
@@ -1411,11 +1413,11 @@
       </c>
       <c r="E10" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F12</f>
-        <v>788.47058823529414</v>
+        <v>794.33333333333337</v>
       </c>
       <c r="F10" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G12</f>
-        <v>2.907907724929637E-2</v>
+        <v>3.6730888750776902E-2</v>
       </c>
       <c r="G10" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H12</f>
@@ -1440,11 +1442,11 @@
       </c>
       <c r="E11" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F13</f>
-        <v>383.8235294117647</v>
+        <v>388</v>
       </c>
       <c r="F11" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G13</f>
-        <v>5.7920214942519976E-2</v>
+        <v>6.9431683948024681E-2</v>
       </c>
       <c r="G11" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H13</f>
@@ -1469,11 +1471,11 @@
       </c>
       <c r="E12" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F14</f>
-        <v>3419.5294117647059</v>
+        <v>3425.9444444444443</v>
       </c>
       <c r="F12" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G14</f>
-        <v>-2.8963143024410165E-2</v>
+        <v>-2.714147915765186E-2</v>
       </c>
       <c r="G12" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H14</f>
@@ -1498,11 +1500,11 @@
       </c>
       <c r="E13" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F15</f>
-        <v>2119.4705882352941</v>
+        <v>2144.2222222222222</v>
       </c>
       <c r="F13" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G15</f>
-        <v>-8.048998341201985E-2</v>
+        <v>-6.9751747409014242E-2</v>
       </c>
       <c r="G13" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H15</f>
@@ -1527,11 +1529,11 @@
       </c>
       <c r="E14" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F16</f>
-        <v>2147.1176470588234</v>
+        <v>2161.6666666666665</v>
       </c>
       <c r="F14" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G16</f>
-        <v>-5.2662606348531482E-2</v>
+        <v>-4.6243381796789662E-2</v>
       </c>
       <c r="G14" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H16</f>
@@ -1556,11 +1558,11 @@
       </c>
       <c r="E15" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F17</f>
-        <v>2656.1764705882351</v>
+        <v>2671.0555555555557</v>
       </c>
       <c r="F15" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G17</f>
-        <v>-6.6654934225000018E-3</v>
+        <v>-1.1011385356934911E-3</v>
       </c>
       <c r="G15" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H17</f>
@@ -1585,11 +1587,11 @@
       </c>
       <c r="E16" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F18</f>
-        <v>719.94117647058829</v>
+        <v>728.72222222222217</v>
       </c>
       <c r="F16" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G18</f>
-        <v>0.84984273900432572</v>
+        <v>0.87240507361637887</v>
       </c>
       <c r="G16" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H18</f>
@@ -1614,11 +1616,11 @@
       </c>
       <c r="E17" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F19</f>
-        <v>842.47058823529414</v>
+        <v>858.83333333333337</v>
       </c>
       <c r="F17" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G19</f>
-        <v>0.96663876755682265</v>
+        <v>1.0048354824366386</v>
       </c>
       <c r="G17" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H19</f>
@@ -1643,11 +1645,11 @@
       </c>
       <c r="E18" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F20</f>
-        <v>864.58823529411768</v>
+        <v>872.16666666666663</v>
       </c>
       <c r="F18" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G20</f>
-        <v>1.212570429097791</v>
+        <v>1.2319644162807699</v>
       </c>
       <c r="G18" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H20</f>
@@ -1672,11 +1674,11 @@
       </c>
       <c r="E19" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F21</f>
-        <v>281</v>
+        <v>277.83333333333331</v>
       </c>
       <c r="F19" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G21</f>
-        <v>0.16115702479338845</v>
+        <v>0.14807162534435259</v>
       </c>
       <c r="G19" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H21</f>
@@ -1701,11 +1703,11 @@
       </c>
       <c r="E20" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F22</f>
-        <v>132.64705882352942</v>
+        <v>133.88888888888889</v>
       </c>
       <c r="F20" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G22</f>
-        <v>-6.7117134864662531E-2</v>
+        <v>-5.8383567760661004E-2</v>
       </c>
       <c r="G20" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H22</f>
@@ -1730,15 +1732,15 @@
       </c>
       <c r="E21" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F23</f>
-        <v>519.11764705882354</v>
+        <v>512.44444444444446</v>
       </c>
       <c r="F21" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G23</f>
-        <v>1.173740958100189E-2</v>
+        <v>-1.2683681361175259E-3</v>
       </c>
       <c r="G21" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H23</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H21">
         <v>4.1500000000000004</v>
@@ -1759,11 +1761,11 @@
       </c>
       <c r="E22" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F24</f>
-        <v>874.41176470588232</v>
+        <v>877.83333333333337</v>
       </c>
       <c r="F22" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G24</f>
-        <v>7.7683376889695843E-2</v>
+        <v>8.1900346264452084E-2</v>
       </c>
       <c r="G22" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H24</f>
@@ -1788,11 +1790,11 @@
       </c>
       <c r="E23" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F25</f>
-        <v>60.705882352941174</v>
+        <v>64</v>
       </c>
       <c r="F23" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G25</f>
-        <v>-0.19007399656177593</v>
+        <v>-0.14612452350698857</v>
       </c>
       <c r="G23" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H25</f>
@@ -1817,11 +1819,11 @@
       </c>
       <c r="E24" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F26</f>
-        <v>697.70588235294122</v>
+        <v>705.22222222222217</v>
       </c>
       <c r="F24" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G26</f>
-        <v>-0.11453293470648662</v>
+        <v>-0.10499385588525623</v>
       </c>
       <c r="G24" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H26</f>
@@ -1846,11 +1848,11 @@
       </c>
       <c r="E25" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F27</f>
-        <v>1074.3529411764705</v>
+        <v>1084.4444444444443</v>
       </c>
       <c r="F25" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G27</f>
-        <v>-0.1565196738183835</v>
+        <v>-0.1485967798215444</v>
       </c>
       <c r="G25" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H27</f>
@@ -1875,11 +1877,11 @@
       </c>
       <c r="E26" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F28</f>
-        <v>571.47058823529414</v>
+        <v>566.72222222222217</v>
       </c>
       <c r="F26" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G28</f>
-        <v>7.9895829473695557E-2</v>
+        <v>7.0922943099672953E-2</v>
       </c>
       <c r="G26" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H28</f>
@@ -1904,11 +1906,11 @@
       </c>
       <c r="E27" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F29</f>
-        <v>429.11764705882354</v>
+        <v>438.11111111111109</v>
       </c>
       <c r="F27" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G29</f>
-        <v>6.7836306225298681E-2</v>
+        <v>9.0216060354702421E-2</v>
       </c>
       <c r="G27" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H29</f>
@@ -1933,11 +1935,11 @@
       </c>
       <c r="E28" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F30</f>
-        <v>235.11764705882354</v>
+        <v>242.88888888888889</v>
       </c>
       <c r="F28" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G30</f>
-        <v>2.0897813443274678</v>
+        <v>2.191906549853984</v>
       </c>
       <c r="G28" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H30</f>
@@ -1962,11 +1964,11 @@
       </c>
       <c r="E29" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F31</f>
-        <v>287.58823529411762</v>
+        <v>295.38888888888891</v>
       </c>
       <c r="F29" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G31</f>
-        <v>2.9890045846608122</v>
+        <v>3.0972038749449577</v>
       </c>
       <c r="G29" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H31</f>
@@ -1991,11 +1993,11 @@
       </c>
       <c r="E30" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F32</f>
-        <v>132.47058823529412</v>
+        <v>132</v>
       </c>
       <c r="F30" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G32</f>
-        <v>3.6082813013473602E-2</v>
+        <v>3.240223463687153E-2</v>
       </c>
       <c r="G30" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H32</f>
@@ -2020,11 +2022,11 @@
       </c>
       <c r="E31" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F33</f>
-        <v>138.58823529411765</v>
+        <v>139.83333333333334</v>
       </c>
       <c r="F31" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G33</f>
-        <v>-3.3105335157318727E-2</v>
+        <v>-2.4418604651162745E-2</v>
       </c>
       <c r="G31" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H33</f>
@@ -2049,11 +2051,11 @@
       </c>
       <c r="E32" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F34</f>
-        <v>776.94117647058829</v>
+        <v>786.16666666666663</v>
       </c>
       <c r="F32" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G34</f>
-        <v>0.19127954920285895</v>
+        <v>0.20542494158878499</v>
       </c>
       <c r="G32" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H34</f>
@@ -2078,11 +2080,11 @@
       </c>
       <c r="E33" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F35</f>
-        <v>605.52941176470586</v>
+        <v>614.83333333333337</v>
       </c>
       <c r="F33" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G35</f>
-        <v>-3.7387006278665869E-2</v>
+        <v>-2.2596517789553294E-2</v>
       </c>
       <c r="G33" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H35</f>
@@ -2107,11 +2109,11 @@
       </c>
       <c r="E34" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F36</f>
-        <v>799.88235294117646</v>
+        <v>804.72222222222217</v>
       </c>
       <c r="F34" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G36</f>
-        <v>-6.1380788345736126E-2</v>
+        <v>-5.5701460289077631E-2</v>
       </c>
       <c r="G34" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H36</f>
@@ -2136,11 +2138,11 @@
       </c>
       <c r="E35" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F37</f>
-        <v>530.94117647058829</v>
+        <v>535.55555555555554</v>
       </c>
       <c r="F35" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G37</f>
-        <v>-8.3003149446306934E-2</v>
+        <v>-7.5033582805603571E-2</v>
       </c>
       <c r="G35" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H37</f>
@@ -2165,11 +2167,11 @@
       </c>
       <c r="E36" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F38</f>
-        <v>4.0588235294117645</v>
+        <v>4.2777777777777777</v>
       </c>
       <c r="F36" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G38</f>
-        <v>0.63914027149321262</v>
+        <v>0.72756410256410242</v>
       </c>
       <c r="G36" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H38</f>
@@ -2194,11 +2196,11 @@
       </c>
       <c r="E37" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F39</f>
-        <v>0.6470588235294118</v>
+        <v>0.61111111111111116</v>
       </c>
       <c r="F37" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G39</f>
-        <v>0.50980392156862764</v>
+        <v>0.42592592592592604</v>
       </c>
       <c r="G37" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H39</f>
@@ -2223,11 +2225,11 @@
       </c>
       <c r="E38" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F40</f>
-        <v>149.23529411764707</v>
+        <v>145.16666666666666</v>
       </c>
       <c r="F38" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G40</f>
-        <v>8.8174019607843324E-2</v>
+        <v>5.8506944444444375E-2</v>
       </c>
       <c r="G38" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H40</f>
@@ -2252,11 +2254,11 @@
       </c>
       <c r="E39" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F41</f>
-        <v>573.23529411764707</v>
+        <v>570.72222222222217</v>
       </c>
       <c r="F39" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G41</f>
-        <v>3.3920911832911571E-2</v>
+        <v>2.9388187466002247E-2</v>
       </c>
       <c r="G39" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H41</f>
@@ -2281,11 +2283,11 @@
       </c>
       <c r="E40" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F42</f>
-        <v>416.11764705882354</v>
+        <v>420.88888888888891</v>
       </c>
       <c r="F40" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G42</f>
-        <v>2.1331913188366065</v>
+        <v>2.1691167682562451</v>
       </c>
       <c r="G40" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H42</f>
@@ -2310,11 +2312,11 @@
       </c>
       <c r="E41" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F43</f>
-        <v>235.05882352941177</v>
+        <v>237.72222222222223</v>
       </c>
       <c r="F41" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G43</f>
-        <v>-0.2062654294713544</v>
+        <v>-0.19727180146861767</v>
       </c>
       <c r="G41" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H43</f>
@@ -2339,11 +2341,11 @@
       </c>
       <c r="E42" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F44</f>
-        <v>499.23529411764707</v>
+        <v>495.55555555555554</v>
       </c>
       <c r="F42" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G44</f>
-        <v>-5.575599599472314E-2</v>
+        <v>-6.2715782521240437E-2</v>
       </c>
       <c r="G42" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H44</f>
@@ -2368,11 +2370,11 @@
       </c>
       <c r="E43" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F45</f>
-        <v>298.76470588235293</v>
+        <v>300.27777777777777</v>
       </c>
       <c r="F43" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G45</f>
-        <v>-2.2275389819321867E-2</v>
+        <v>-1.732377538829144E-2</v>
       </c>
       <c r="G43" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H45</f>
@@ -2397,11 +2399,11 @@
       </c>
       <c r="E44" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F46</f>
-        <v>300.11764705882354</v>
+        <v>299.33333333333331</v>
       </c>
       <c r="F44" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G46</f>
-        <v>3.5228414624719706E-2</v>
+        <v>3.2522996057818609E-2</v>
       </c>
       <c r="G44" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H46</f>
@@ -2426,11 +2428,11 @@
       </c>
       <c r="E45" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F47</f>
-        <v>57.647058823529413</v>
+        <v>55.111111111111114</v>
       </c>
       <c r="F45" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G47</f>
-        <v>-1.1648223645893685E-3</v>
+        <v>-4.5104510451045021E-2</v>
       </c>
       <c r="G45" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H47</f>
@@ -2455,11 +2457,11 @@
       </c>
       <c r="E46" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F48</f>
-        <v>125.64705882352941</v>
+        <v>126.83333333333333</v>
       </c>
       <c r="F46" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G48</f>
-        <v>0.19990369954257292</v>
+        <v>0.21123237835379727</v>
       </c>
       <c r="G46" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H48</f>
@@ -2484,11 +2486,11 @@
       </c>
       <c r="E47" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F49</f>
-        <v>43.705882352941174</v>
+        <v>43.555555555555557</v>
       </c>
       <c r="F47" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G49</f>
-        <v>-0.11406995230524652</v>
+        <v>-0.11711711711711714</v>
       </c>
       <c r="G47" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H49</f>
@@ -2513,11 +2515,11 @@
       </c>
       <c r="E48" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F50</f>
-        <v>53.470588235294116</v>
+        <v>54.444444444444443</v>
       </c>
       <c r="F48" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G50</f>
-        <v>-3.3664068036853401E-2</v>
+        <v>-1.6064257028112539E-2</v>
       </c>
       <c r="G48" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H50</f>

--- a/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
+++ b/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAF8602D-4CDD-4D2E-896A-4E73B2D82A02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C0F8DAE-A2B3-4E14-B83F-306FB119F464}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -378,6 +378,7 @@
       <sheetName val="INVENTARIO NACIONAL 23-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 24-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 25-09-26"/>
+      <sheetName val="INVENTARIO NACIONAL 28-09-26"/>
       <sheetName val="CCC"/>
       <sheetName val="VINCULO VTS BY SKU AGOSTO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
@@ -406,24 +407,25 @@
       <sheetData sheetId="19"/>
       <sheetData sheetId="20"/>
       <sheetData sheetId="21"/>
-      <sheetData sheetId="22">
+      <sheetData sheetId="22"/>
+      <sheetData sheetId="23">
         <row r="4">
           <cell r="F4">
-            <v>1200.3888888888889</v>
+            <v>1173.5263157894738</v>
           </cell>
           <cell r="G4">
-            <v>1.0347361389445586E-2</v>
+            <v>-1.2262419575994055E-2</v>
           </cell>
           <cell r="H4" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="5">
           <cell r="F5">
-            <v>51.333333333333336</v>
+            <v>48.631578947368418</v>
           </cell>
           <cell r="G5">
-            <v>-0.32793017456359097</v>
+            <v>-0.36330227063919152</v>
           </cell>
           <cell r="H5" t="str">
             <v>BAJO</v>
@@ -431,10 +433,10 @@
         </row>
         <row r="6">
           <cell r="F6">
-            <v>494.11111111111109</v>
+            <v>491.73684210526318</v>
           </cell>
           <cell r="G6">
-            <v>-3.0158581798922057E-2</v>
+            <v>-3.4818797624962428E-2</v>
           </cell>
           <cell r="H6" t="str">
             <v>BAJO</v>
@@ -442,10 +444,10 @@
         </row>
         <row r="7">
           <cell r="F7">
-            <v>109.22222222222223</v>
+            <v>104.57894736842105</v>
           </cell>
           <cell r="G7">
-            <v>0.11451247165532896</v>
+            <v>6.7132116004296583E-2</v>
           </cell>
           <cell r="H7" t="str">
             <v>SUBIÓ</v>
@@ -453,10 +455,10 @@
         </row>
         <row r="8">
           <cell r="F8">
-            <v>13.944444444444445</v>
+            <v>13.263157894736842</v>
           </cell>
           <cell r="G8">
-            <v>0.16666666666666674</v>
+            <v>0.10966659677081148</v>
           </cell>
           <cell r="H8" t="str">
             <v>SUBIÓ</v>
@@ -464,10 +466,10 @@
         </row>
         <row r="9">
           <cell r="F9">
-            <v>1431.6666666666667</v>
+            <v>1401.6315789473683</v>
           </cell>
           <cell r="G9">
-            <v>-1.963022141063675E-2</v>
+            <v>-4.0197503574045834E-2</v>
           </cell>
           <cell r="H9" t="str">
             <v>BAJO</v>
@@ -475,21 +477,21 @@
         </row>
         <row r="10">
           <cell r="F10">
-            <v>153.88888888888889</v>
+            <v>147.57894736842104</v>
           </cell>
           <cell r="G10">
-            <v>2.3327000211104121E-2</v>
+            <v>-1.8632712242925287E-2</v>
           </cell>
           <cell r="H10" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="11">
           <cell r="F11">
-            <v>322.83333333333331</v>
+            <v>310.78947368421052</v>
           </cell>
           <cell r="G11">
-            <v>-6.036036036036041E-2</v>
+            <v>-9.5415253309990122E-2</v>
           </cell>
           <cell r="H11" t="str">
             <v>BAJO</v>
@@ -497,10 +499,10 @@
         </row>
         <row r="12">
           <cell r="F12">
-            <v>794.33333333333337</v>
+            <v>776.73684210526312</v>
           </cell>
           <cell r="G12">
-            <v>3.6730888750776902E-2</v>
+            <v>1.3764678944097275E-2</v>
           </cell>
           <cell r="H12" t="str">
             <v>SUBIÓ</v>
@@ -508,10 +510,10 @@
         </row>
         <row r="13">
           <cell r="F13">
-            <v>388</v>
+            <v>377.36842105263156</v>
           </cell>
           <cell r="G13">
-            <v>6.9431683948024681E-2</v>
+            <v>4.0128211327636665E-2</v>
           </cell>
           <cell r="H13" t="str">
             <v>SUBIÓ</v>
@@ -519,10 +521,10 @@
         </row>
         <row r="14">
           <cell r="F14">
-            <v>3425.9444444444443</v>
+            <v>3354.7894736842104</v>
           </cell>
           <cell r="G14">
-            <v>-2.714147915765186E-2</v>
+            <v>-4.7347212416588902E-2</v>
           </cell>
           <cell r="H14" t="str">
             <v>BAJO</v>
@@ -530,10 +532,10 @@
         </row>
         <row r="15">
           <cell r="F15">
-            <v>2144.2222222222222</v>
+            <v>2123.1052631578946</v>
           </cell>
           <cell r="G15">
-            <v>-6.9751747409014242E-2</v>
+            <v>-7.8913117935837551E-2</v>
           </cell>
           <cell r="H15" t="str">
             <v>BAJO</v>
@@ -541,10 +543,10 @@
         </row>
         <row r="16">
           <cell r="F16">
-            <v>2161.6666666666665</v>
+            <v>2121.6842105263158</v>
           </cell>
           <cell r="G16">
-            <v>-4.6243381796789662E-2</v>
+            <v>-6.3884183102516312E-2</v>
           </cell>
           <cell r="H16" t="str">
             <v>BAJO</v>
@@ -552,10 +554,10 @@
         </row>
         <row r="17">
           <cell r="F17">
-            <v>2671.0555555555557</v>
+            <v>2621.1578947368421</v>
           </cell>
           <cell r="G17">
-            <v>-1.1011385356934911E-3</v>
+            <v>-1.9761445498563179E-2</v>
           </cell>
           <cell r="H17" t="str">
             <v>BAJO</v>
@@ -563,10 +565,10 @@
         </row>
         <row r="18">
           <cell r="F18">
-            <v>728.72222222222217</v>
+            <v>707.63157894736844</v>
           </cell>
           <cell r="G18">
-            <v>0.87240507361637887</v>
+            <v>0.81821401662727711</v>
           </cell>
           <cell r="H18" t="str">
             <v>SUBIÓ</v>
@@ -574,10 +576,10 @@
         </row>
         <row r="19">
           <cell r="F19">
-            <v>858.83333333333337</v>
+            <v>836.57894736842104</v>
           </cell>
           <cell r="G19">
-            <v>1.0048354824366386</v>
+            <v>0.9528854929676347</v>
           </cell>
           <cell r="H19" t="str">
             <v>SUBIÓ</v>
@@ -585,10 +587,10 @@
         </row>
         <row r="20">
           <cell r="F20">
-            <v>872.16666666666663</v>
+            <v>846.47368421052636</v>
           </cell>
           <cell r="G20">
-            <v>1.2319644162807699</v>
+            <v>1.1662134253498726</v>
           </cell>
           <cell r="H20" t="str">
             <v>SUBIÓ</v>
@@ -596,10 +598,10 @@
         </row>
         <row r="21">
           <cell r="F21">
-            <v>277.83333333333331</v>
+            <v>271.78947368421052</v>
           </cell>
           <cell r="G21">
-            <v>0.14807162534435259</v>
+            <v>0.12309699869508473</v>
           </cell>
           <cell r="H21" t="str">
             <v>SUBIÓ</v>
@@ -607,10 +609,10 @@
         </row>
         <row r="22">
           <cell r="F22">
-            <v>133.88888888888889</v>
+            <v>132.42105263157896</v>
           </cell>
           <cell r="G22">
-            <v>-5.8383567760661004E-2</v>
+            <v>-6.8706595692177519E-2</v>
           </cell>
           <cell r="H22" t="str">
             <v>BAJO</v>
@@ -618,10 +620,10 @@
         </row>
         <row r="23">
           <cell r="F23">
-            <v>512.44444444444446</v>
+            <v>504.5263157894737</v>
           </cell>
           <cell r="G23">
-            <v>-1.2683681361175259E-3</v>
+            <v>-1.6700451825619633E-2</v>
           </cell>
           <cell r="H23" t="str">
             <v>BAJO</v>
@@ -629,10 +631,10 @@
         </row>
         <row r="24">
           <cell r="F24">
-            <v>877.83333333333337</v>
+            <v>862</v>
           </cell>
           <cell r="G24">
-            <v>8.1900346264452084E-2</v>
+            <v>6.2386290275250778E-2</v>
           </cell>
           <cell r="H24" t="str">
             <v>SUBIÓ</v>
@@ -640,10 +642,10 @@
         </row>
         <row r="25">
           <cell r="F25">
-            <v>64</v>
+            <v>60.631578947368418</v>
           </cell>
           <cell r="G25">
-            <v>-0.14612452350698857</v>
+            <v>-0.1910653380592523</v>
           </cell>
           <cell r="H25" t="str">
             <v>BAJO</v>
@@ -651,10 +653,10 @@
         </row>
         <row r="26">
           <cell r="F26">
-            <v>705.22222222222217</v>
+            <v>700.57894736842104</v>
           </cell>
           <cell r="G26">
-            <v>-0.10499385588525623</v>
+            <v>-0.11088669276987717</v>
           </cell>
           <cell r="H26" t="str">
             <v>BAJO</v>
@@ -662,10 +664,10 @@
         </row>
         <row r="27">
           <cell r="F27">
-            <v>1084.4444444444443</v>
+            <v>1085</v>
           </cell>
           <cell r="G27">
-            <v>-0.1485967798215444</v>
+            <v>-0.14816061013907589</v>
           </cell>
           <cell r="H27" t="str">
             <v>BAJO</v>
@@ -673,10 +675,10 @@
         </row>
         <row r="28">
           <cell r="F28">
-            <v>566.72222222222217</v>
+            <v>561.26315789473688</v>
           </cell>
           <cell r="G28">
-            <v>7.0922943099672953E-2</v>
+            <v>6.0607065219965284E-2</v>
           </cell>
           <cell r="H28" t="str">
             <v>SUBIÓ</v>
@@ -684,10 +686,10 @@
         </row>
         <row r="29">
           <cell r="F29">
-            <v>438.11111111111109</v>
+            <v>428.42105263157896</v>
           </cell>
           <cell r="G29">
-            <v>9.0216060354702421E-2</v>
+            <v>6.6102868262016612E-2</v>
           </cell>
           <cell r="H29" t="str">
             <v>SUBIÓ</v>
@@ -695,10 +697,10 @@
         </row>
         <row r="30">
           <cell r="F30">
-            <v>242.88888888888889</v>
+            <v>249.78947368421052</v>
           </cell>
           <cell r="G30">
-            <v>2.191906549853984</v>
+            <v>2.2825900797048937</v>
           </cell>
           <cell r="H30" t="str">
             <v>SUBIÓ</v>
@@ -706,10 +708,10 @@
         </row>
         <row r="31">
           <cell r="F31">
-            <v>295.38888888888891</v>
+            <v>301.89473684210526</v>
           </cell>
           <cell r="G31">
-            <v>3.0972038749449577</v>
+            <v>3.1874435096989497</v>
           </cell>
           <cell r="H31" t="str">
             <v>SUBIÓ</v>
@@ -717,10 +719,10 @@
         </row>
         <row r="32">
           <cell r="F32">
-            <v>132</v>
+            <v>129.31578947368422</v>
           </cell>
           <cell r="G32">
-            <v>3.240223463687153E-2</v>
+            <v>1.1408409291384869E-2</v>
           </cell>
           <cell r="H32" t="str">
             <v>SUBIÓ</v>
@@ -728,10 +730,10 @@
         </row>
         <row r="33">
           <cell r="F33">
-            <v>139.83333333333334</v>
+            <v>141.78947368421052</v>
           </cell>
           <cell r="G33">
-            <v>-2.4418604651162745E-2</v>
+            <v>-1.0771113831089418E-2</v>
           </cell>
           <cell r="H33" t="str">
             <v>BAJO</v>
@@ -739,10 +741,10 @@
         </row>
         <row r="34">
           <cell r="F34">
-            <v>786.16666666666663</v>
+            <v>785</v>
           </cell>
           <cell r="G34">
-            <v>0.20542494158878499</v>
+            <v>0.20363609813084116</v>
           </cell>
           <cell r="H34" t="str">
             <v>SUBIÓ</v>
@@ -750,10 +752,10 @@
         </row>
         <row r="35">
           <cell r="F35">
-            <v>614.83333333333337</v>
+            <v>607.73684210526312</v>
           </cell>
           <cell r="G35">
-            <v>-2.2596517789553294E-2</v>
+            <v>-3.3877843738794433E-2</v>
           </cell>
           <cell r="H35" t="str">
             <v>BAJO</v>
@@ -761,10 +763,10 @@
         </row>
         <row r="36">
           <cell r="F36">
-            <v>804.72222222222217</v>
+            <v>804.36842105263156</v>
           </cell>
           <cell r="G36">
-            <v>-5.5701460289077631E-2</v>
+            <v>-5.6116627061619129E-2</v>
           </cell>
           <cell r="H36" t="str">
             <v>BAJO</v>
@@ -772,10 +774,10 @@
         </row>
         <row r="37">
           <cell r="F37">
-            <v>535.55555555555554</v>
+            <v>532.52631578947364</v>
           </cell>
           <cell r="G37">
-            <v>-7.5033582805603571E-2</v>
+            <v>-8.0265430415416894E-2</v>
           </cell>
           <cell r="H37" t="str">
             <v>BAJO</v>
@@ -783,10 +785,10 @@
         </row>
         <row r="38">
           <cell r="F38">
-            <v>4.2777777777777777</v>
+            <v>4.1052631578947372</v>
           </cell>
           <cell r="G38">
-            <v>0.72756410256410242</v>
+            <v>0.65789473684210531</v>
           </cell>
           <cell r="H38" t="str">
             <v>SUBIÓ</v>
@@ -794,10 +796,10 @@
         </row>
         <row r="39">
           <cell r="F39">
-            <v>0.61111111111111116</v>
+            <v>0.57894736842105265</v>
           </cell>
           <cell r="G39">
-            <v>0.42592592592592604</v>
+            <v>0.35087719298245634</v>
           </cell>
           <cell r="H39" t="str">
             <v>SUBIÓ</v>
@@ -805,10 +807,10 @@
         </row>
         <row r="40">
           <cell r="F40">
-            <v>145.16666666666666</v>
+            <v>139.05263157894737</v>
           </cell>
           <cell r="G40">
-            <v>5.8506944444444375E-2</v>
+            <v>1.3925438596491313E-2</v>
           </cell>
           <cell r="H40" t="str">
             <v>SUBIÓ</v>
@@ -816,10 +818,10 @@
         </row>
         <row r="41">
           <cell r="F41">
-            <v>570.72222222222217</v>
+            <v>563.57894736842104</v>
           </cell>
           <cell r="G41">
-            <v>2.9388187466002247E-2</v>
+            <v>1.6504156552163751E-2</v>
           </cell>
           <cell r="H41" t="str">
             <v>SUBIÓ</v>
@@ -827,10 +829,10 @@
         </row>
         <row r="42">
           <cell r="F42">
-            <v>420.88888888888891</v>
+            <v>405.73684210526318</v>
           </cell>
           <cell r="G42">
-            <v>2.1691167682562451</v>
+            <v>2.0550282123379446</v>
           </cell>
           <cell r="H42" t="str">
             <v>SUBIÓ</v>
@@ -838,10 +840,10 @@
         </row>
         <row r="43">
           <cell r="F43">
-            <v>237.72222222222223</v>
+            <v>238.26315789473685</v>
           </cell>
           <cell r="G43">
-            <v>-0.19727180146861767</v>
+            <v>-0.19544519765404833</v>
           </cell>
           <cell r="H43" t="str">
             <v>BAJO</v>
@@ -849,10 +851,10 @@
         </row>
         <row r="44">
           <cell r="F44">
-            <v>495.55555555555554</v>
+            <v>495.5263157894737</v>
           </cell>
           <cell r="G44">
-            <v>-6.2715782521240437E-2</v>
+            <v>-6.2771086050711689E-2</v>
           </cell>
           <cell r="H44" t="str">
             <v>BAJO</v>
@@ -860,10 +862,10 @@
         </row>
         <row r="45">
           <cell r="F45">
-            <v>300.27777777777777</v>
+            <v>303.4736842105263</v>
           </cell>
           <cell r="G45">
-            <v>-1.732377538829144E-2</v>
+            <v>-6.8649885583523806E-3</v>
           </cell>
           <cell r="H45" t="str">
             <v>BAJO</v>
@@ -871,10 +873,10 @@
         </row>
         <row r="46">
           <cell r="F46">
-            <v>299.33333333333331</v>
+            <v>297.94736842105266</v>
           </cell>
           <cell r="G46">
-            <v>3.2522996057818609E-2</v>
+            <v>2.7742236669202613E-2</v>
           </cell>
           <cell r="H46" t="str">
             <v>SUBIÓ</v>
@@ -882,10 +884,10 @@
         </row>
         <row r="47">
           <cell r="F47">
-            <v>55.111111111111114</v>
+            <v>53.736842105263158</v>
           </cell>
           <cell r="G47">
-            <v>-4.5104510451045021E-2</v>
+            <v>-6.8916102136529434E-2</v>
           </cell>
           <cell r="H47" t="str">
             <v>BAJO</v>
@@ -893,10 +895,10 @@
         </row>
         <row r="48">
           <cell r="F48">
-            <v>126.83333333333333</v>
+            <v>120.42105263157895</v>
           </cell>
           <cell r="G48">
-            <v>0.21123237835379727</v>
+            <v>0.14999640985136797</v>
           </cell>
           <cell r="H48" t="str">
             <v>SUBIÓ</v>
@@ -904,10 +906,10 @@
         </row>
         <row r="49">
           <cell r="F49">
-            <v>43.555555555555557</v>
+            <v>41.578947368421055</v>
           </cell>
           <cell r="G49">
-            <v>-0.11711711711711714</v>
+            <v>-0.15718349928876241</v>
           </cell>
           <cell r="H49" t="str">
             <v>BAJO</v>
@@ -915,10 +917,10 @@
         </row>
         <row r="50">
           <cell r="F50">
-            <v>54.444444444444443</v>
+            <v>52.421052631578945</v>
           </cell>
           <cell r="G50">
-            <v>-1.6064257028112539E-2</v>
+            <v>-5.2631578947368474E-2</v>
           </cell>
           <cell r="H50" t="str">
             <v>BAJO</v>
@@ -1181,15 +1183,15 @@
       </c>
       <c r="E2" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F4</f>
-        <v>1200.3888888888889</v>
+        <v>1173.5263157894738</v>
       </c>
       <c r="F2" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G4</f>
-        <v>1.0347361389445586E-2</v>
+        <v>-1.2262419575994055E-2</v>
       </c>
       <c r="G2" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H4</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H2">
         <v>1.36</v>
@@ -1210,11 +1212,11 @@
       </c>
       <c r="E3" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F5</f>
-        <v>51.333333333333336</v>
+        <v>48.631578947368418</v>
       </c>
       <c r="F3" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G5</f>
-        <v>-0.32793017456359097</v>
+        <v>-0.36330227063919152</v>
       </c>
       <c r="G3" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H5</f>
@@ -1239,11 +1241,11 @@
       </c>
       <c r="E4" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F6</f>
-        <v>494.11111111111109</v>
+        <v>491.73684210526318</v>
       </c>
       <c r="F4" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G6</f>
-        <v>-3.0158581798922057E-2</v>
+        <v>-3.4818797624962428E-2</v>
       </c>
       <c r="G4" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H6</f>
@@ -1268,11 +1270,11 @@
       </c>
       <c r="E5" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F7</f>
-        <v>109.22222222222223</v>
+        <v>104.57894736842105</v>
       </c>
       <c r="F5" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G7</f>
-        <v>0.11451247165532896</v>
+        <v>6.7132116004296583E-2</v>
       </c>
       <c r="G5" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H7</f>
@@ -1297,11 +1299,11 @@
       </c>
       <c r="E6" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F8</f>
-        <v>13.944444444444445</v>
+        <v>13.263157894736842</v>
       </c>
       <c r="F6" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G8</f>
-        <v>0.16666666666666674</v>
+        <v>0.10966659677081148</v>
       </c>
       <c r="G6" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H8</f>
@@ -1326,11 +1328,11 @@
       </c>
       <c r="E7" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F9</f>
-        <v>1431.6666666666667</v>
+        <v>1401.6315789473683</v>
       </c>
       <c r="F7" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G9</f>
-        <v>-1.963022141063675E-2</v>
+        <v>-4.0197503574045834E-2</v>
       </c>
       <c r="G7" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H9</f>
@@ -1355,15 +1357,15 @@
       </c>
       <c r="E8" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F10</f>
-        <v>153.88888888888889</v>
+        <v>147.57894736842104</v>
       </c>
       <c r="F8" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G10</f>
-        <v>2.3327000211104121E-2</v>
+        <v>-1.8632712242925287E-2</v>
       </c>
       <c r="G8" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H10</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H8">
         <v>0.63</v>
@@ -1384,11 +1386,11 @@
       </c>
       <c r="E9" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F11</f>
-        <v>322.83333333333331</v>
+        <v>310.78947368421052</v>
       </c>
       <c r="F9" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G11</f>
-        <v>-6.036036036036041E-2</v>
+        <v>-9.5415253309990122E-2</v>
       </c>
       <c r="G9" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H11</f>
@@ -1413,11 +1415,11 @@
       </c>
       <c r="E10" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F12</f>
-        <v>794.33333333333337</v>
+        <v>776.73684210526312</v>
       </c>
       <c r="F10" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G12</f>
-        <v>3.6730888750776902E-2</v>
+        <v>1.3764678944097275E-2</v>
       </c>
       <c r="G10" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H12</f>
@@ -1442,11 +1444,11 @@
       </c>
       <c r="E11" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F13</f>
-        <v>388</v>
+        <v>377.36842105263156</v>
       </c>
       <c r="F11" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G13</f>
-        <v>6.9431683948024681E-2</v>
+        <v>4.0128211327636665E-2</v>
       </c>
       <c r="G11" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H13</f>
@@ -1471,11 +1473,11 @@
       </c>
       <c r="E12" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F14</f>
-        <v>3425.9444444444443</v>
+        <v>3354.7894736842104</v>
       </c>
       <c r="F12" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G14</f>
-        <v>-2.714147915765186E-2</v>
+        <v>-4.7347212416588902E-2</v>
       </c>
       <c r="G12" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H14</f>
@@ -1500,11 +1502,11 @@
       </c>
       <c r="E13" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F15</f>
-        <v>2144.2222222222222</v>
+        <v>2123.1052631578946</v>
       </c>
       <c r="F13" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G15</f>
-        <v>-6.9751747409014242E-2</v>
+        <v>-7.8913117935837551E-2</v>
       </c>
       <c r="G13" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H15</f>
@@ -1529,11 +1531,11 @@
       </c>
       <c r="E14" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F16</f>
-        <v>2161.6666666666665</v>
+        <v>2121.6842105263158</v>
       </c>
       <c r="F14" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G16</f>
-        <v>-4.6243381796789662E-2</v>
+        <v>-6.3884183102516312E-2</v>
       </c>
       <c r="G14" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H16</f>
@@ -1558,11 +1560,11 @@
       </c>
       <c r="E15" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F17</f>
-        <v>2671.0555555555557</v>
+        <v>2621.1578947368421</v>
       </c>
       <c r="F15" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G17</f>
-        <v>-1.1011385356934911E-3</v>
+        <v>-1.9761445498563179E-2</v>
       </c>
       <c r="G15" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H17</f>
@@ -1587,11 +1589,11 @@
       </c>
       <c r="E16" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F18</f>
-        <v>728.72222222222217</v>
+        <v>707.63157894736844</v>
       </c>
       <c r="F16" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G18</f>
-        <v>0.87240507361637887</v>
+        <v>0.81821401662727711</v>
       </c>
       <c r="G16" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H18</f>
@@ -1616,11 +1618,11 @@
       </c>
       <c r="E17" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F19</f>
-        <v>858.83333333333337</v>
+        <v>836.57894736842104</v>
       </c>
       <c r="F17" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G19</f>
-        <v>1.0048354824366386</v>
+        <v>0.9528854929676347</v>
       </c>
       <c r="G17" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H19</f>
@@ -1645,11 +1647,11 @@
       </c>
       <c r="E18" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F20</f>
-        <v>872.16666666666663</v>
+        <v>846.47368421052636</v>
       </c>
       <c r="F18" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G20</f>
-        <v>1.2319644162807699</v>
+        <v>1.1662134253498726</v>
       </c>
       <c r="G18" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H20</f>
@@ -1674,11 +1676,11 @@
       </c>
       <c r="E19" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F21</f>
-        <v>277.83333333333331</v>
+        <v>271.78947368421052</v>
       </c>
       <c r="F19" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G21</f>
-        <v>0.14807162534435259</v>
+        <v>0.12309699869508473</v>
       </c>
       <c r="G19" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H21</f>
@@ -1703,11 +1705,11 @@
       </c>
       <c r="E20" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F22</f>
-        <v>133.88888888888889</v>
+        <v>132.42105263157896</v>
       </c>
       <c r="F20" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G22</f>
-        <v>-5.8383567760661004E-2</v>
+        <v>-6.8706595692177519E-2</v>
       </c>
       <c r="G20" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H22</f>
@@ -1732,11 +1734,11 @@
       </c>
       <c r="E21" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F23</f>
-        <v>512.44444444444446</v>
+        <v>504.5263157894737</v>
       </c>
       <c r="F21" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G23</f>
-        <v>-1.2683681361175259E-3</v>
+        <v>-1.6700451825619633E-2</v>
       </c>
       <c r="G21" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H23</f>
@@ -1761,11 +1763,11 @@
       </c>
       <c r="E22" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F24</f>
-        <v>877.83333333333337</v>
+        <v>862</v>
       </c>
       <c r="F22" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G24</f>
-        <v>8.1900346264452084E-2</v>
+        <v>6.2386290275250778E-2</v>
       </c>
       <c r="G22" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H24</f>
@@ -1790,11 +1792,11 @@
       </c>
       <c r="E23" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F25</f>
-        <v>64</v>
+        <v>60.631578947368418</v>
       </c>
       <c r="F23" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G25</f>
-        <v>-0.14612452350698857</v>
+        <v>-0.1910653380592523</v>
       </c>
       <c r="G23" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H25</f>
@@ -1819,11 +1821,11 @@
       </c>
       <c r="E24" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F26</f>
-        <v>705.22222222222217</v>
+        <v>700.57894736842104</v>
       </c>
       <c r="F24" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G26</f>
-        <v>-0.10499385588525623</v>
+        <v>-0.11088669276987717</v>
       </c>
       <c r="G24" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H26</f>
@@ -1848,11 +1850,11 @@
       </c>
       <c r="E25" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F27</f>
-        <v>1084.4444444444443</v>
+        <v>1085</v>
       </c>
       <c r="F25" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G27</f>
-        <v>-0.1485967798215444</v>
+        <v>-0.14816061013907589</v>
       </c>
       <c r="G25" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H27</f>
@@ -1877,11 +1879,11 @@
       </c>
       <c r="E26" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F28</f>
-        <v>566.72222222222217</v>
+        <v>561.26315789473688</v>
       </c>
       <c r="F26" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G28</f>
-        <v>7.0922943099672953E-2</v>
+        <v>6.0607065219965284E-2</v>
       </c>
       <c r="G26" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H28</f>
@@ -1906,11 +1908,11 @@
       </c>
       <c r="E27" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F29</f>
-        <v>438.11111111111109</v>
+        <v>428.42105263157896</v>
       </c>
       <c r="F27" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G29</f>
-        <v>9.0216060354702421E-2</v>
+        <v>6.6102868262016612E-2</v>
       </c>
       <c r="G27" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H29</f>
@@ -1935,11 +1937,11 @@
       </c>
       <c r="E28" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F30</f>
-        <v>242.88888888888889</v>
+        <v>249.78947368421052</v>
       </c>
       <c r="F28" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G30</f>
-        <v>2.191906549853984</v>
+        <v>2.2825900797048937</v>
       </c>
       <c r="G28" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H30</f>
@@ -1964,11 +1966,11 @@
       </c>
       <c r="E29" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F31</f>
-        <v>295.38888888888891</v>
+        <v>301.89473684210526</v>
       </c>
       <c r="F29" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G31</f>
-        <v>3.0972038749449577</v>
+        <v>3.1874435096989497</v>
       </c>
       <c r="G29" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H31</f>
@@ -1993,11 +1995,11 @@
       </c>
       <c r="E30" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F32</f>
-        <v>132</v>
+        <v>129.31578947368422</v>
       </c>
       <c r="F30" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G32</f>
-        <v>3.240223463687153E-2</v>
+        <v>1.1408409291384869E-2</v>
       </c>
       <c r="G30" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H32</f>
@@ -2022,11 +2024,11 @@
       </c>
       <c r="E31" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F33</f>
-        <v>139.83333333333334</v>
+        <v>141.78947368421052</v>
       </c>
       <c r="F31" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G33</f>
-        <v>-2.4418604651162745E-2</v>
+        <v>-1.0771113831089418E-2</v>
       </c>
       <c r="G31" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H33</f>
@@ -2051,11 +2053,11 @@
       </c>
       <c r="E32" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F34</f>
-        <v>786.16666666666663</v>
+        <v>785</v>
       </c>
       <c r="F32" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G34</f>
-        <v>0.20542494158878499</v>
+        <v>0.20363609813084116</v>
       </c>
       <c r="G32" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H34</f>
@@ -2080,11 +2082,11 @@
       </c>
       <c r="E33" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F35</f>
-        <v>614.83333333333337</v>
+        <v>607.73684210526312</v>
       </c>
       <c r="F33" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G35</f>
-        <v>-2.2596517789553294E-2</v>
+        <v>-3.3877843738794433E-2</v>
       </c>
       <c r="G33" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H35</f>
@@ -2109,11 +2111,11 @@
       </c>
       <c r="E34" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F36</f>
-        <v>804.72222222222217</v>
+        <v>804.36842105263156</v>
       </c>
       <c r="F34" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G36</f>
-        <v>-5.5701460289077631E-2</v>
+        <v>-5.6116627061619129E-2</v>
       </c>
       <c r="G34" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H36</f>
@@ -2138,11 +2140,11 @@
       </c>
       <c r="E35" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F37</f>
-        <v>535.55555555555554</v>
+        <v>532.52631578947364</v>
       </c>
       <c r="F35" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G37</f>
-        <v>-7.5033582805603571E-2</v>
+        <v>-8.0265430415416894E-2</v>
       </c>
       <c r="G35" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H37</f>
@@ -2167,11 +2169,11 @@
       </c>
       <c r="E36" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F38</f>
-        <v>4.2777777777777777</v>
+        <v>4.1052631578947372</v>
       </c>
       <c r="F36" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G38</f>
-        <v>0.72756410256410242</v>
+        <v>0.65789473684210531</v>
       </c>
       <c r="G36" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H38</f>
@@ -2196,11 +2198,11 @@
       </c>
       <c r="E37" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F39</f>
-        <v>0.61111111111111116</v>
+        <v>0.57894736842105265</v>
       </c>
       <c r="F37" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G39</f>
-        <v>0.42592592592592604</v>
+        <v>0.35087719298245634</v>
       </c>
       <c r="G37" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H39</f>
@@ -2225,11 +2227,11 @@
       </c>
       <c r="E38" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F40</f>
-        <v>145.16666666666666</v>
+        <v>139.05263157894737</v>
       </c>
       <c r="F38" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G40</f>
-        <v>5.8506944444444375E-2</v>
+        <v>1.3925438596491313E-2</v>
       </c>
       <c r="G38" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H40</f>
@@ -2254,11 +2256,11 @@
       </c>
       <c r="E39" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F41</f>
-        <v>570.72222222222217</v>
+        <v>563.57894736842104</v>
       </c>
       <c r="F39" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G41</f>
-        <v>2.9388187466002247E-2</v>
+        <v>1.6504156552163751E-2</v>
       </c>
       <c r="G39" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H41</f>
@@ -2283,11 +2285,11 @@
       </c>
       <c r="E40" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F42</f>
-        <v>420.88888888888891</v>
+        <v>405.73684210526318</v>
       </c>
       <c r="F40" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G42</f>
-        <v>2.1691167682562451</v>
+        <v>2.0550282123379446</v>
       </c>
       <c r="G40" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H42</f>
@@ -2312,11 +2314,11 @@
       </c>
       <c r="E41" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F43</f>
-        <v>237.72222222222223</v>
+        <v>238.26315789473685</v>
       </c>
       <c r="F41" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G43</f>
-        <v>-0.19727180146861767</v>
+        <v>-0.19544519765404833</v>
       </c>
       <c r="G41" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H43</f>
@@ -2341,11 +2343,11 @@
       </c>
       <c r="E42" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F44</f>
-        <v>495.55555555555554</v>
+        <v>495.5263157894737</v>
       </c>
       <c r="F42" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G44</f>
-        <v>-6.2715782521240437E-2</v>
+        <v>-6.2771086050711689E-2</v>
       </c>
       <c r="G42" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H44</f>
@@ -2370,11 +2372,11 @@
       </c>
       <c r="E43" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F45</f>
-        <v>300.27777777777777</v>
+        <v>303.4736842105263</v>
       </c>
       <c r="F43" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G45</f>
-        <v>-1.732377538829144E-2</v>
+        <v>-6.8649885583523806E-3</v>
       </c>
       <c r="G43" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H45</f>
@@ -2399,11 +2401,11 @@
       </c>
       <c r="E44" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F46</f>
-        <v>299.33333333333331</v>
+        <v>297.94736842105266</v>
       </c>
       <c r="F44" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G46</f>
-        <v>3.2522996057818609E-2</v>
+        <v>2.7742236669202613E-2</v>
       </c>
       <c r="G44" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H46</f>
@@ -2428,11 +2430,11 @@
       </c>
       <c r="E45" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F47</f>
-        <v>55.111111111111114</v>
+        <v>53.736842105263158</v>
       </c>
       <c r="F45" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G47</f>
-        <v>-4.5104510451045021E-2</v>
+        <v>-6.8916102136529434E-2</v>
       </c>
       <c r="G45" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H47</f>
@@ -2457,11 +2459,11 @@
       </c>
       <c r="E46" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F48</f>
-        <v>126.83333333333333</v>
+        <v>120.42105263157895</v>
       </c>
       <c r="F46" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G48</f>
-        <v>0.21123237835379727</v>
+        <v>0.14999640985136797</v>
       </c>
       <c r="G46" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H48</f>
@@ -2486,11 +2488,11 @@
       </c>
       <c r="E47" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F49</f>
-        <v>43.555555555555557</v>
+        <v>41.578947368421055</v>
       </c>
       <c r="F47" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G49</f>
-        <v>-0.11711711711711714</v>
+        <v>-0.15718349928876241</v>
       </c>
       <c r="G47" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H49</f>
@@ -2515,11 +2517,11 @@
       </c>
       <c r="E48" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F50</f>
-        <v>54.444444444444443</v>
+        <v>52.421052631578945</v>
       </c>
       <c r="F48" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G50</f>
-        <v>-1.6064257028112539E-2</v>
+        <v>-5.2631578947368474E-2</v>
       </c>
       <c r="G48" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H50</f>

--- a/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
+++ b/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C0F8DAE-A2B3-4E14-B83F-306FB119F464}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{883FE57B-5D8B-4197-86F7-73B6DE047519}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -379,6 +379,7 @@
       <sheetName val="INVENTARIO NACIONAL 24-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 25-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 28-09-26"/>
+      <sheetName val="INVENTARIO NACIONAL 29-09-26"/>
       <sheetName val="CCC"/>
       <sheetName val="VINCULO VTS BY SKU AGOSTO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
@@ -408,13 +409,14 @@
       <sheetData sheetId="20"/>
       <sheetData sheetId="21"/>
       <sheetData sheetId="22"/>
-      <sheetData sheetId="23">
+      <sheetData sheetId="23"/>
+      <sheetData sheetId="24">
         <row r="4">
           <cell r="F4">
-            <v>1173.5263157894738</v>
+            <v>1167.9000000000001</v>
           </cell>
           <cell r="G4">
-            <v>-1.2262419575994055E-2</v>
+            <v>-1.6997995991983927E-2</v>
           </cell>
           <cell r="H4" t="str">
             <v>BAJO</v>
@@ -422,10 +424,10 @@
         </row>
         <row r="5">
           <cell r="F5">
-            <v>48.631578947368418</v>
+            <v>46.45</v>
           </cell>
           <cell r="G5">
-            <v>-0.36330227063919152</v>
+            <v>-0.39186408977556109</v>
           </cell>
           <cell r="H5" t="str">
             <v>BAJO</v>
@@ -433,10 +435,10 @@
         </row>
         <row r="6">
           <cell r="F6">
-            <v>491.73684210526318</v>
+            <v>491.05</v>
           </cell>
           <cell r="G6">
-            <v>-3.4818797624962428E-2</v>
+            <v>-3.6166931488924137E-2</v>
           </cell>
           <cell r="H6" t="str">
             <v>BAJO</v>
@@ -444,10 +446,10 @@
         </row>
         <row r="7">
           <cell r="F7">
-            <v>104.57894736842105</v>
+            <v>104.45</v>
           </cell>
           <cell r="G7">
-            <v>6.7132116004296583E-2</v>
+            <v>6.5816326530612201E-2</v>
           </cell>
           <cell r="H7" t="str">
             <v>SUBIÓ</v>
@@ -455,10 +457,10 @@
         </row>
         <row r="8">
           <cell r="F8">
-            <v>13.263157894736842</v>
+            <v>14</v>
           </cell>
           <cell r="G8">
-            <v>0.10966659677081148</v>
+            <v>0.17131474103585664</v>
           </cell>
           <cell r="H8" t="str">
             <v>SUBIÓ</v>
@@ -466,10 +468,10 @@
         </row>
         <row r="9">
           <cell r="F9">
-            <v>1401.6315789473683</v>
+            <v>1405.35</v>
           </cell>
           <cell r="G9">
-            <v>-4.0197503574045834E-2</v>
+            <v>-3.7651221182378514E-2</v>
           </cell>
           <cell r="H9" t="str">
             <v>BAJO</v>
@@ -477,10 +479,10 @@
         </row>
         <row r="10">
           <cell r="F10">
-            <v>147.57894736842104</v>
+            <v>147.05000000000001</v>
           </cell>
           <cell r="G10">
-            <v>-1.8632712242925287E-2</v>
+            <v>-2.2150094996833403E-2</v>
           </cell>
           <cell r="H10" t="str">
             <v>BAJO</v>
@@ -488,10 +490,10 @@
         </row>
         <row r="11">
           <cell r="F11">
-            <v>310.78947368421052</v>
+            <v>314.2</v>
           </cell>
           <cell r="G11">
-            <v>-9.5415253309990122E-2</v>
+            <v>-8.5488565488565427E-2</v>
           </cell>
           <cell r="H11" t="str">
             <v>BAJO</v>
@@ -499,10 +501,10 @@
         </row>
         <row r="12">
           <cell r="F12">
-            <v>776.73684210526312</v>
+            <v>767.6</v>
           </cell>
           <cell r="G12">
-            <v>1.3764678944097275E-2</v>
+            <v>1.8396519577377202E-3</v>
           </cell>
           <cell r="H12" t="str">
             <v>SUBIÓ</v>
@@ -510,10 +512,10 @@
         </row>
         <row r="13">
           <cell r="F13">
-            <v>377.36842105263156</v>
+            <v>374.95</v>
           </cell>
           <cell r="G13">
-            <v>4.0128211327636665E-2</v>
+            <v>3.3462396639978964E-2</v>
           </cell>
           <cell r="H13" t="str">
             <v>SUBIÓ</v>
@@ -521,10 +523,10 @@
         </row>
         <row r="14">
           <cell r="F14">
-            <v>3354.7894736842104</v>
+            <v>3347.35</v>
           </cell>
           <cell r="G14">
-            <v>-4.7347212416588902E-2</v>
+            <v>-4.9459784725227274E-2</v>
           </cell>
           <cell r="H14" t="str">
             <v>BAJO</v>
@@ -532,10 +534,10 @@
         </row>
         <row r="15">
           <cell r="F15">
-            <v>2123.1052631578946</v>
+            <v>2112.6</v>
           </cell>
           <cell r="G15">
-            <v>-7.8913117935837551E-2</v>
+            <v>-8.3470715835140985E-2</v>
           </cell>
           <cell r="H15" t="str">
             <v>BAJO</v>
@@ -543,10 +545,10 @@
         </row>
         <row r="16">
           <cell r="F16">
-            <v>2121.6842105263158</v>
+            <v>2121.65</v>
           </cell>
           <cell r="G16">
-            <v>-6.3884183102516312E-2</v>
+            <v>-6.3899277250188957E-2</v>
           </cell>
           <cell r="H16" t="str">
             <v>BAJO</v>
@@ -554,10 +556,10 @@
         </row>
         <row r="17">
           <cell r="F17">
-            <v>2621.1578947368421</v>
+            <v>2607.9499999999998</v>
           </cell>
           <cell r="G17">
-            <v>-1.9761445498563179E-2</v>
+            <v>-2.4700822737471984E-2</v>
           </cell>
           <cell r="H17" t="str">
             <v>BAJO</v>
@@ -565,10 +567,10 @@
         </row>
         <row r="18">
           <cell r="F18">
-            <v>707.63157894736844</v>
+            <v>702.9</v>
           </cell>
           <cell r="G18">
-            <v>0.81821401662727711</v>
+            <v>0.80605652759084778</v>
           </cell>
           <cell r="H18" t="str">
             <v>SUBIÓ</v>
@@ -576,10 +578,10 @@
         </row>
         <row r="19">
           <cell r="F19">
-            <v>836.57894736842104</v>
+            <v>836.1</v>
           </cell>
           <cell r="G19">
-            <v>0.9528854929676347</v>
+            <v>0.95176745220097825</v>
           </cell>
           <cell r="H19" t="str">
             <v>SUBIÓ</v>
@@ -587,10 +589,10 @@
         </row>
         <row r="20">
           <cell r="F20">
-            <v>846.47368421052636</v>
+            <v>843.2</v>
           </cell>
           <cell r="G20">
-            <v>1.1662134253498726</v>
+            <v>1.1578357299536925</v>
           </cell>
           <cell r="H20" t="str">
             <v>SUBIÓ</v>
@@ -598,10 +600,10 @@
         </row>
         <row r="21">
           <cell r="F21">
-            <v>271.78947368421052</v>
+            <v>268.85000000000002</v>
           </cell>
           <cell r="G21">
-            <v>0.12309699869508473</v>
+            <v>0.1109504132231407</v>
           </cell>
           <cell r="H21" t="str">
             <v>SUBIÓ</v>
@@ -609,10 +611,10 @@
         </row>
         <row r="22">
           <cell r="F22">
-            <v>132.42105263157896</v>
+            <v>131.5</v>
           </cell>
           <cell r="G22">
-            <v>-6.8706595692177519E-2</v>
+            <v>-7.5184192900201063E-2</v>
           </cell>
           <cell r="H22" t="str">
             <v>BAJO</v>
@@ -620,10 +622,10 @@
         </row>
         <row r="23">
           <cell r="F23">
-            <v>504.5263157894737</v>
+            <v>503.6</v>
           </cell>
           <cell r="G23">
-            <v>-1.6700451825619633E-2</v>
+            <v>-1.8505800464037048E-2</v>
           </cell>
           <cell r="H23" t="str">
             <v>BAJO</v>
@@ -631,10 +633,10 @@
         </row>
         <row r="24">
           <cell r="F24">
-            <v>862</v>
+            <v>850.6</v>
           </cell>
           <cell r="G24">
-            <v>6.2386290275250778E-2</v>
+            <v>4.8336169963026032E-2</v>
           </cell>
           <cell r="H24" t="str">
             <v>SUBIÓ</v>
@@ -642,10 +644,10 @@
         </row>
         <row r="25">
           <cell r="F25">
-            <v>60.631578947368418</v>
+            <v>60</v>
           </cell>
           <cell r="G25">
-            <v>-0.1910653380592523</v>
+            <v>-0.19949174078780174</v>
           </cell>
           <cell r="H25" t="str">
             <v>BAJO</v>
@@ -653,10 +655,10 @@
         </row>
         <row r="26">
           <cell r="F26">
-            <v>700.57894736842104</v>
+            <v>703.45</v>
           </cell>
           <cell r="G26">
-            <v>-0.11088669276987717</v>
+            <v>-0.10724300477427928</v>
           </cell>
           <cell r="H26" t="str">
             <v>BAJO</v>
@@ -664,10 +666,10 @@
         </row>
         <row r="27">
           <cell r="F27">
-            <v>1085</v>
+            <v>1089.8499999999999</v>
           </cell>
           <cell r="G27">
-            <v>-0.14816061013907589</v>
+            <v>-0.1443528488111262</v>
           </cell>
           <cell r="H27" t="str">
             <v>BAJO</v>
@@ -675,10 +677,10 @@
         </row>
         <row r="28">
           <cell r="F28">
-            <v>561.26315789473688</v>
+            <v>552.79999999999995</v>
           </cell>
           <cell r="G28">
-            <v>6.0607065219965284E-2</v>
+            <v>4.4614415549356634E-2</v>
           </cell>
           <cell r="H28" t="str">
             <v>SUBIÓ</v>
@@ -686,10 +688,10 @@
         </row>
         <row r="29">
           <cell r="F29">
-            <v>428.42105263157896</v>
+            <v>437.5</v>
           </cell>
           <cell r="G29">
-            <v>6.6102868262016612E-2</v>
+            <v>8.8695343050124498E-2</v>
           </cell>
           <cell r="H29" t="str">
             <v>SUBIÓ</v>
@@ -697,10 +699,10 @@
         </row>
         <row r="30">
           <cell r="F30">
-            <v>249.78947368421052</v>
+            <v>254.2</v>
           </cell>
           <cell r="G30">
-            <v>2.2825900797048937</v>
+            <v>2.3405506883604503</v>
           </cell>
           <cell r="H30" t="str">
             <v>SUBIÓ</v>
@@ -708,10 +710,10 @@
         </row>
         <row r="31">
           <cell r="F31">
-            <v>301.89473684210526</v>
+            <v>312.8</v>
           </cell>
           <cell r="G31">
-            <v>3.1874435096989497</v>
+            <v>3.3387054161162482</v>
           </cell>
           <cell r="H31" t="str">
             <v>SUBIÓ</v>
@@ -719,10 +721,10 @@
         </row>
         <row r="32">
           <cell r="F32">
-            <v>129.31578947368422</v>
+            <v>127.95</v>
           </cell>
           <cell r="G32">
-            <v>1.1408409291384869E-2</v>
+            <v>7.2625698324024768E-4</v>
           </cell>
           <cell r="H32" t="str">
             <v>SUBIÓ</v>
@@ -730,21 +732,21 @@
         </row>
         <row r="33">
           <cell r="F33">
-            <v>141.78947368421052</v>
+            <v>144.69999999999999</v>
           </cell>
           <cell r="G33">
-            <v>-1.0771113831089418E-2</v>
+            <v>9.5348837209301429E-3</v>
           </cell>
           <cell r="H33" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="34">
           <cell r="F34">
-            <v>785</v>
+            <v>784.35</v>
           </cell>
           <cell r="G34">
-            <v>0.20363609813084116</v>
+            <v>0.20263945677570105</v>
           </cell>
           <cell r="H34" t="str">
             <v>SUBIÓ</v>
@@ -752,10 +754,10 @@
         </row>
         <row r="35">
           <cell r="F35">
-            <v>607.73684210526312</v>
+            <v>600.54999999999995</v>
           </cell>
           <cell r="G35">
-            <v>-3.3877843738794433E-2</v>
+            <v>-4.5302800908402774E-2</v>
           </cell>
           <cell r="H35" t="str">
             <v>BAJO</v>
@@ -763,10 +765,10 @@
         </row>
         <row r="36">
           <cell r="F36">
-            <v>804.36842105263156</v>
+            <v>800.95</v>
           </cell>
           <cell r="G36">
-            <v>-5.6116627061619129E-2</v>
+            <v>-6.0127961555654807E-2</v>
           </cell>
           <cell r="H36" t="str">
             <v>BAJO</v>
@@ -774,10 +776,10 @@
         </row>
         <row r="37">
           <cell r="F37">
-            <v>532.52631578947364</v>
+            <v>526.45000000000005</v>
           </cell>
           <cell r="G37">
-            <v>-8.0265430415416894E-2</v>
+            <v>-9.0759930915371267E-2</v>
           </cell>
           <cell r="H37" t="str">
             <v>BAJO</v>
@@ -785,10 +787,10 @@
         </row>
         <row r="38">
           <cell r="F38">
-            <v>4.1052631578947372</v>
+            <v>4</v>
           </cell>
           <cell r="G38">
-            <v>0.65789473684210531</v>
+            <v>0.61538461538461542</v>
           </cell>
           <cell r="H38" t="str">
             <v>SUBIÓ</v>
@@ -796,10 +798,10 @@
         </row>
         <row r="39">
           <cell r="F39">
-            <v>0.57894736842105265</v>
+            <v>0.55000000000000004</v>
           </cell>
           <cell r="G39">
-            <v>0.35087719298245634</v>
+            <v>0.28333333333333344</v>
           </cell>
           <cell r="H39" t="str">
             <v>SUBIÓ</v>
@@ -807,21 +809,21 @@
         </row>
         <row r="40">
           <cell r="F40">
-            <v>139.05263157894737</v>
+            <v>134.19999999999999</v>
           </cell>
           <cell r="G40">
-            <v>1.3925438596491313E-2</v>
+            <v>-2.1458333333333357E-2</v>
           </cell>
           <cell r="H40" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="41">
           <cell r="F41">
-            <v>563.57894736842104</v>
+            <v>567.25</v>
           </cell>
           <cell r="G41">
-            <v>1.6504156552163751E-2</v>
+            <v>2.312548312290641E-2</v>
           </cell>
           <cell r="H41" t="str">
             <v>SUBIÓ</v>
@@ -829,10 +831,10 @@
         </row>
         <row r="42">
           <cell r="F42">
-            <v>405.73684210526318</v>
+            <v>405.25</v>
           </cell>
           <cell r="G42">
-            <v>2.0550282123379446</v>
+            <v>2.0513624955181071</v>
           </cell>
           <cell r="H42" t="str">
             <v>SUBIÓ</v>
@@ -840,10 +842,10 @@
         </row>
         <row r="43">
           <cell r="F43">
-            <v>238.26315789473685</v>
+            <v>246.65</v>
           </cell>
           <cell r="G43">
-            <v>-0.19544519765404833</v>
+            <v>-0.16712493970091657</v>
           </cell>
           <cell r="H43" t="str">
             <v>BAJO</v>
@@ -851,10 +853,10 @@
         </row>
         <row r="44">
           <cell r="F44">
-            <v>495.5263157894737</v>
+            <v>491.45</v>
           </cell>
           <cell r="G44">
-            <v>-6.2771086050711689E-2</v>
+            <v>-7.0480951094298749E-2</v>
           </cell>
           <cell r="H44" t="str">
             <v>BAJO</v>
@@ -862,10 +864,10 @@
         </row>
         <row r="45">
           <cell r="F45">
-            <v>303.4736842105263</v>
+            <v>298.55</v>
           </cell>
           <cell r="G45">
-            <v>-6.8649885583523806E-3</v>
+            <v>-2.2978027115474475E-2</v>
           </cell>
           <cell r="H45" t="str">
             <v>BAJO</v>
@@ -873,10 +875,10 @@
         </row>
         <row r="46">
           <cell r="F46">
-            <v>297.94736842105266</v>
+            <v>293.35000000000002</v>
           </cell>
           <cell r="G46">
-            <v>2.7742236669202613E-2</v>
+            <v>1.1884034165571711E-2</v>
           </cell>
           <cell r="H46" t="str">
             <v>SUBIÓ</v>
@@ -884,10 +886,10 @@
         </row>
         <row r="47">
           <cell r="F47">
-            <v>53.736842105263158</v>
+            <v>53</v>
           </cell>
           <cell r="G47">
-            <v>-6.8916102136529434E-2</v>
+            <v>-8.1683168316831645E-2</v>
           </cell>
           <cell r="H47" t="str">
             <v>BAJO</v>
@@ -895,10 +897,10 @@
         </row>
         <row r="48">
           <cell r="F48">
-            <v>120.42105263157895</v>
+            <v>122.1</v>
           </cell>
           <cell r="G48">
-            <v>0.14999640985136797</v>
+            <v>0.16603001364256476</v>
           </cell>
           <cell r="H48" t="str">
             <v>SUBIÓ</v>
@@ -906,10 +908,10 @@
         </row>
         <row r="49">
           <cell r="F49">
-            <v>41.578947368421055</v>
+            <v>40.299999999999997</v>
           </cell>
           <cell r="G49">
-            <v>-0.15718349928876241</v>
+            <v>-0.18310810810810818</v>
           </cell>
           <cell r="H49" t="str">
             <v>BAJO</v>
@@ -917,10 +919,10 @@
         </row>
         <row r="50">
           <cell r="F50">
-            <v>52.421052631578945</v>
+            <v>51.3</v>
           </cell>
           <cell r="G50">
-            <v>-5.2631578947368474E-2</v>
+            <v>-7.2891566265060326E-2</v>
           </cell>
           <cell r="H50" t="str">
             <v>BAJO</v>
@@ -1183,11 +1185,11 @@
       </c>
       <c r="E2" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F4</f>
-        <v>1173.5263157894738</v>
+        <v>1167.9000000000001</v>
       </c>
       <c r="F2" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G4</f>
-        <v>-1.2262419575994055E-2</v>
+        <v>-1.6997995991983927E-2</v>
       </c>
       <c r="G2" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H4</f>
@@ -1212,11 +1214,11 @@
       </c>
       <c r="E3" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F5</f>
-        <v>48.631578947368418</v>
+        <v>46.45</v>
       </c>
       <c r="F3" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G5</f>
-        <v>-0.36330227063919152</v>
+        <v>-0.39186408977556109</v>
       </c>
       <c r="G3" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H5</f>
@@ -1241,11 +1243,11 @@
       </c>
       <c r="E4" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F6</f>
-        <v>491.73684210526318</v>
+        <v>491.05</v>
       </c>
       <c r="F4" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G6</f>
-        <v>-3.4818797624962428E-2</v>
+        <v>-3.6166931488924137E-2</v>
       </c>
       <c r="G4" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H6</f>
@@ -1270,11 +1272,11 @@
       </c>
       <c r="E5" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F7</f>
-        <v>104.57894736842105</v>
+        <v>104.45</v>
       </c>
       <c r="F5" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G7</f>
-        <v>6.7132116004296583E-2</v>
+        <v>6.5816326530612201E-2</v>
       </c>
       <c r="G5" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H7</f>
@@ -1299,11 +1301,11 @@
       </c>
       <c r="E6" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F8</f>
-        <v>13.263157894736842</v>
+        <v>14</v>
       </c>
       <c r="F6" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G8</f>
-        <v>0.10966659677081148</v>
+        <v>0.17131474103585664</v>
       </c>
       <c r="G6" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H8</f>
@@ -1328,11 +1330,11 @@
       </c>
       <c r="E7" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F9</f>
-        <v>1401.6315789473683</v>
+        <v>1405.35</v>
       </c>
       <c r="F7" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G9</f>
-        <v>-4.0197503574045834E-2</v>
+        <v>-3.7651221182378514E-2</v>
       </c>
       <c r="G7" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H9</f>
@@ -1357,11 +1359,11 @@
       </c>
       <c r="E8" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F10</f>
-        <v>147.57894736842104</v>
+        <v>147.05000000000001</v>
       </c>
       <c r="F8" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G10</f>
-        <v>-1.8632712242925287E-2</v>
+        <v>-2.2150094996833403E-2</v>
       </c>
       <c r="G8" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H10</f>
@@ -1386,11 +1388,11 @@
       </c>
       <c r="E9" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F11</f>
-        <v>310.78947368421052</v>
+        <v>314.2</v>
       </c>
       <c r="F9" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G11</f>
-        <v>-9.5415253309990122E-2</v>
+        <v>-8.5488565488565427E-2</v>
       </c>
       <c r="G9" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H11</f>
@@ -1415,11 +1417,11 @@
       </c>
       <c r="E10" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F12</f>
-        <v>776.73684210526312</v>
+        <v>767.6</v>
       </c>
       <c r="F10" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G12</f>
-        <v>1.3764678944097275E-2</v>
+        <v>1.8396519577377202E-3</v>
       </c>
       <c r="G10" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H12</f>
@@ -1444,11 +1446,11 @@
       </c>
       <c r="E11" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F13</f>
-        <v>377.36842105263156</v>
+        <v>374.95</v>
       </c>
       <c r="F11" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G13</f>
-        <v>4.0128211327636665E-2</v>
+        <v>3.3462396639978964E-2</v>
       </c>
       <c r="G11" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H13</f>
@@ -1473,11 +1475,11 @@
       </c>
       <c r="E12" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F14</f>
-        <v>3354.7894736842104</v>
+        <v>3347.35</v>
       </c>
       <c r="F12" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G14</f>
-        <v>-4.7347212416588902E-2</v>
+        <v>-4.9459784725227274E-2</v>
       </c>
       <c r="G12" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H14</f>
@@ -1502,11 +1504,11 @@
       </c>
       <c r="E13" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F15</f>
-        <v>2123.1052631578946</v>
+        <v>2112.6</v>
       </c>
       <c r="F13" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G15</f>
-        <v>-7.8913117935837551E-2</v>
+        <v>-8.3470715835140985E-2</v>
       </c>
       <c r="G13" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H15</f>
@@ -1531,11 +1533,11 @@
       </c>
       <c r="E14" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F16</f>
-        <v>2121.6842105263158</v>
+        <v>2121.65</v>
       </c>
       <c r="F14" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G16</f>
-        <v>-6.3884183102516312E-2</v>
+        <v>-6.3899277250188957E-2</v>
       </c>
       <c r="G14" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H16</f>
@@ -1560,11 +1562,11 @@
       </c>
       <c r="E15" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F17</f>
-        <v>2621.1578947368421</v>
+        <v>2607.9499999999998</v>
       </c>
       <c r="F15" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G17</f>
-        <v>-1.9761445498563179E-2</v>
+        <v>-2.4700822737471984E-2</v>
       </c>
       <c r="G15" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H17</f>
@@ -1589,11 +1591,11 @@
       </c>
       <c r="E16" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F18</f>
-        <v>707.63157894736844</v>
+        <v>702.9</v>
       </c>
       <c r="F16" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G18</f>
-        <v>0.81821401662727711</v>
+        <v>0.80605652759084778</v>
       </c>
       <c r="G16" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H18</f>
@@ -1618,11 +1620,11 @@
       </c>
       <c r="E17" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F19</f>
-        <v>836.57894736842104</v>
+        <v>836.1</v>
       </c>
       <c r="F17" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G19</f>
-        <v>0.9528854929676347</v>
+        <v>0.95176745220097825</v>
       </c>
       <c r="G17" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H19</f>
@@ -1647,11 +1649,11 @@
       </c>
       <c r="E18" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F20</f>
-        <v>846.47368421052636</v>
+        <v>843.2</v>
       </c>
       <c r="F18" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G20</f>
-        <v>1.1662134253498726</v>
+        <v>1.1578357299536925</v>
       </c>
       <c r="G18" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H20</f>
@@ -1676,11 +1678,11 @@
       </c>
       <c r="E19" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F21</f>
-        <v>271.78947368421052</v>
+        <v>268.85000000000002</v>
       </c>
       <c r="F19" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G21</f>
-        <v>0.12309699869508473</v>
+        <v>0.1109504132231407</v>
       </c>
       <c r="G19" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H21</f>
@@ -1705,11 +1707,11 @@
       </c>
       <c r="E20" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F22</f>
-        <v>132.42105263157896</v>
+        <v>131.5</v>
       </c>
       <c r="F20" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G22</f>
-        <v>-6.8706595692177519E-2</v>
+        <v>-7.5184192900201063E-2</v>
       </c>
       <c r="G20" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H22</f>
@@ -1734,11 +1736,11 @@
       </c>
       <c r="E21" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F23</f>
-        <v>504.5263157894737</v>
+        <v>503.6</v>
       </c>
       <c r="F21" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G23</f>
-        <v>-1.6700451825619633E-2</v>
+        <v>-1.8505800464037048E-2</v>
       </c>
       <c r="G21" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H23</f>
@@ -1763,11 +1765,11 @@
       </c>
       <c r="E22" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F24</f>
-        <v>862</v>
+        <v>850.6</v>
       </c>
       <c r="F22" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G24</f>
-        <v>6.2386290275250778E-2</v>
+        <v>4.8336169963026032E-2</v>
       </c>
       <c r="G22" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H24</f>
@@ -1792,11 +1794,11 @@
       </c>
       <c r="E23" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F25</f>
-        <v>60.631578947368418</v>
+        <v>60</v>
       </c>
       <c r="F23" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G25</f>
-        <v>-0.1910653380592523</v>
+        <v>-0.19949174078780174</v>
       </c>
       <c r="G23" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H25</f>
@@ -1821,11 +1823,11 @@
       </c>
       <c r="E24" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F26</f>
-        <v>700.57894736842104</v>
+        <v>703.45</v>
       </c>
       <c r="F24" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G26</f>
-        <v>-0.11088669276987717</v>
+        <v>-0.10724300477427928</v>
       </c>
       <c r="G24" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H26</f>
@@ -1850,11 +1852,11 @@
       </c>
       <c r="E25" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F27</f>
-        <v>1085</v>
+        <v>1089.8499999999999</v>
       </c>
       <c r="F25" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G27</f>
-        <v>-0.14816061013907589</v>
+        <v>-0.1443528488111262</v>
       </c>
       <c r="G25" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H27</f>
@@ -1879,11 +1881,11 @@
       </c>
       <c r="E26" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F28</f>
-        <v>561.26315789473688</v>
+        <v>552.79999999999995</v>
       </c>
       <c r="F26" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G28</f>
-        <v>6.0607065219965284E-2</v>
+        <v>4.4614415549356634E-2</v>
       </c>
       <c r="G26" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H28</f>
@@ -1908,11 +1910,11 @@
       </c>
       <c r="E27" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F29</f>
-        <v>428.42105263157896</v>
+        <v>437.5</v>
       </c>
       <c r="F27" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G29</f>
-        <v>6.6102868262016612E-2</v>
+        <v>8.8695343050124498E-2</v>
       </c>
       <c r="G27" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H29</f>
@@ -1937,11 +1939,11 @@
       </c>
       <c r="E28" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F30</f>
-        <v>249.78947368421052</v>
+        <v>254.2</v>
       </c>
       <c r="F28" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G30</f>
-        <v>2.2825900797048937</v>
+        <v>2.3405506883604503</v>
       </c>
       <c r="G28" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H30</f>
@@ -1966,11 +1968,11 @@
       </c>
       <c r="E29" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F31</f>
-        <v>301.89473684210526</v>
+        <v>312.8</v>
       </c>
       <c r="F29" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G31</f>
-        <v>3.1874435096989497</v>
+        <v>3.3387054161162482</v>
       </c>
       <c r="G29" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H31</f>
@@ -1995,11 +1997,11 @@
       </c>
       <c r="E30" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F32</f>
-        <v>129.31578947368422</v>
+        <v>127.95</v>
       </c>
       <c r="F30" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G32</f>
-        <v>1.1408409291384869E-2</v>
+        <v>7.2625698324024768E-4</v>
       </c>
       <c r="G30" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H32</f>
@@ -2024,15 +2026,15 @@
       </c>
       <c r="E31" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F33</f>
-        <v>141.78947368421052</v>
+        <v>144.69999999999999</v>
       </c>
       <c r="F31" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G33</f>
-        <v>-1.0771113831089418E-2</v>
+        <v>9.5348837209301429E-3</v>
       </c>
       <c r="G31" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H33</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H31">
         <v>6.15</v>
@@ -2053,11 +2055,11 @@
       </c>
       <c r="E32" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F34</f>
-        <v>785</v>
+        <v>784.35</v>
       </c>
       <c r="F32" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G34</f>
-        <v>0.20363609813084116</v>
+        <v>0.20263945677570105</v>
       </c>
       <c r="G32" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H34</f>
@@ -2082,11 +2084,11 @@
       </c>
       <c r="E33" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F35</f>
-        <v>607.73684210526312</v>
+        <v>600.54999999999995</v>
       </c>
       <c r="F33" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G35</f>
-        <v>-3.3877843738794433E-2</v>
+        <v>-4.5302800908402774E-2</v>
       </c>
       <c r="G33" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H35</f>
@@ -2111,11 +2113,11 @@
       </c>
       <c r="E34" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F36</f>
-        <v>804.36842105263156</v>
+        <v>800.95</v>
       </c>
       <c r="F34" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G36</f>
-        <v>-5.6116627061619129E-2</v>
+        <v>-6.0127961555654807E-2</v>
       </c>
       <c r="G34" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H36</f>
@@ -2140,11 +2142,11 @@
       </c>
       <c r="E35" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F37</f>
-        <v>532.52631578947364</v>
+        <v>526.45000000000005</v>
       </c>
       <c r="F35" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G37</f>
-        <v>-8.0265430415416894E-2</v>
+        <v>-9.0759930915371267E-2</v>
       </c>
       <c r="G35" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H37</f>
@@ -2169,11 +2171,11 @@
       </c>
       <c r="E36" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F38</f>
-        <v>4.1052631578947372</v>
+        <v>4</v>
       </c>
       <c r="F36" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G38</f>
-        <v>0.65789473684210531</v>
+        <v>0.61538461538461542</v>
       </c>
       <c r="G36" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H38</f>
@@ -2198,11 +2200,11 @@
       </c>
       <c r="E37" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F39</f>
-        <v>0.57894736842105265</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="F37" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G39</f>
-        <v>0.35087719298245634</v>
+        <v>0.28333333333333344</v>
       </c>
       <c r="G37" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H39</f>
@@ -2227,15 +2229,15 @@
       </c>
       <c r="E38" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F40</f>
-        <v>139.05263157894737</v>
+        <v>134.19999999999999</v>
       </c>
       <c r="F38" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G40</f>
-        <v>1.3925438596491313E-2</v>
+        <v>-2.1458333333333357E-2</v>
       </c>
       <c r="G38" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H40</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H38">
         <v>1.1599999999999999</v>
@@ -2256,11 +2258,11 @@
       </c>
       <c r="E39" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F41</f>
-        <v>563.57894736842104</v>
+        <v>567.25</v>
       </c>
       <c r="F39" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G41</f>
-        <v>1.6504156552163751E-2</v>
+        <v>2.312548312290641E-2</v>
       </c>
       <c r="G39" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H41</f>
@@ -2285,11 +2287,11 @@
       </c>
       <c r="E40" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F42</f>
-        <v>405.73684210526318</v>
+        <v>405.25</v>
       </c>
       <c r="F40" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G42</f>
-        <v>2.0550282123379446</v>
+        <v>2.0513624955181071</v>
       </c>
       <c r="G40" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H42</f>
@@ -2314,11 +2316,11 @@
       </c>
       <c r="E41" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F43</f>
-        <v>238.26315789473685</v>
+        <v>246.65</v>
       </c>
       <c r="F41" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G43</f>
-        <v>-0.19544519765404833</v>
+        <v>-0.16712493970091657</v>
       </c>
       <c r="G41" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H43</f>
@@ -2343,11 +2345,11 @@
       </c>
       <c r="E42" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F44</f>
-        <v>495.5263157894737</v>
+        <v>491.45</v>
       </c>
       <c r="F42" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G44</f>
-        <v>-6.2771086050711689E-2</v>
+        <v>-7.0480951094298749E-2</v>
       </c>
       <c r="G42" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H44</f>
@@ -2372,11 +2374,11 @@
       </c>
       <c r="E43" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F45</f>
-        <v>303.4736842105263</v>
+        <v>298.55</v>
       </c>
       <c r="F43" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G45</f>
-        <v>-6.8649885583523806E-3</v>
+        <v>-2.2978027115474475E-2</v>
       </c>
       <c r="G43" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H45</f>
@@ -2401,11 +2403,11 @@
       </c>
       <c r="E44" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F46</f>
-        <v>297.94736842105266</v>
+        <v>293.35000000000002</v>
       </c>
       <c r="F44" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G46</f>
-        <v>2.7742236669202613E-2</v>
+        <v>1.1884034165571711E-2</v>
       </c>
       <c r="G44" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H46</f>
@@ -2430,11 +2432,11 @@
       </c>
       <c r="E45" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F47</f>
-        <v>53.736842105263158</v>
+        <v>53</v>
       </c>
       <c r="F45" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G47</f>
-        <v>-6.8916102136529434E-2</v>
+        <v>-8.1683168316831645E-2</v>
       </c>
       <c r="G45" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H47</f>
@@ -2459,11 +2461,11 @@
       </c>
       <c r="E46" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F48</f>
-        <v>120.42105263157895</v>
+        <v>122.1</v>
       </c>
       <c r="F46" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G48</f>
-        <v>0.14999640985136797</v>
+        <v>0.16603001364256476</v>
       </c>
       <c r="G46" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H48</f>
@@ -2488,11 +2490,11 @@
       </c>
       <c r="E47" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F49</f>
-        <v>41.578947368421055</v>
+        <v>40.299999999999997</v>
       </c>
       <c r="F47" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G49</f>
-        <v>-0.15718349928876241</v>
+        <v>-0.18310810810810818</v>
       </c>
       <c r="G47" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H49</f>
@@ -2517,11 +2519,11 @@
       </c>
       <c r="E48" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F50</f>
-        <v>52.421052631578945</v>
+        <v>51.3</v>
       </c>
       <c r="F48" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G50</f>
-        <v>-5.2631578947368474E-2</v>
+        <v>-7.2891566265060326E-2</v>
       </c>
       <c r="G48" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H50</f>

--- a/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
+++ b/data/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{883FE57B-5D8B-4197-86F7-73B6DE047519}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCF65B18-F685-4A73-A77D-260B174A322D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -380,6 +380,7 @@
       <sheetName val="INVENTARIO NACIONAL 25-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 28-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 29-09-26"/>
+      <sheetName val="INVENTARIO NACIONAL 30-09-26"/>
       <sheetName val="CCC"/>
       <sheetName val="VINCULO VTS BY SKU AGOSTO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
@@ -410,13 +411,14 @@
       <sheetData sheetId="21"/>
       <sheetData sheetId="22"/>
       <sheetData sheetId="23"/>
-      <sheetData sheetId="24">
+      <sheetData sheetId="24"/>
+      <sheetData sheetId="25">
         <row r="4">
           <cell r="F4">
-            <v>1167.9000000000001</v>
+            <v>1180.3333333333333</v>
           </cell>
           <cell r="G4">
-            <v>-1.6997995991983927E-2</v>
+            <v>-6.5330661322645645E-3</v>
           </cell>
           <cell r="H4" t="str">
             <v>BAJO</v>
@@ -424,10 +426,10 @@
         </row>
         <row r="5">
           <cell r="F5">
-            <v>46.45</v>
+            <v>44.61904761904762</v>
           </cell>
           <cell r="G5">
-            <v>-0.39186408977556109</v>
+            <v>-0.41583541147132164</v>
           </cell>
           <cell r="H5" t="str">
             <v>BAJO</v>
@@ -435,10 +437,10 @@
         </row>
         <row r="6">
           <cell r="F6">
-            <v>491.05</v>
+            <v>489.42857142857144</v>
           </cell>
           <cell r="G6">
-            <v>-3.6166931488924137E-2</v>
+            <v>-3.9349471913262879E-2</v>
           </cell>
           <cell r="H6" t="str">
             <v>BAJO</v>
@@ -446,10 +448,10 @@
         </row>
         <row r="7">
           <cell r="F7">
-            <v>104.45</v>
+            <v>107.47619047619048</v>
           </cell>
           <cell r="G7">
-            <v>6.5816326530612201E-2</v>
+            <v>9.6695821185617259E-2</v>
           </cell>
           <cell r="H7" t="str">
             <v>SUBIÓ</v>
@@ -457,10 +459,10 @@
         </row>
         <row r="8">
           <cell r="F8">
-            <v>14</v>
+            <v>14.571428571428571</v>
           </cell>
           <cell r="G8">
-            <v>0.17131474103585664</v>
+            <v>0.21912350597609564</v>
           </cell>
           <cell r="H8" t="str">
             <v>SUBIÓ</v>
@@ -468,10 +470,10 @@
         </row>
         <row r="9">
           <cell r="F9">
-            <v>1405.35</v>
+            <v>1391.7619047619048</v>
           </cell>
           <cell r="G9">
-            <v>-3.7651221182378514E-2</v>
+            <v>-4.6956011347702664E-2</v>
           </cell>
           <cell r="H9" t="str">
             <v>BAJO</v>
@@ -479,10 +481,10 @@
         </row>
         <row r="10">
           <cell r="F10">
-            <v>147.05000000000001</v>
+            <v>148.23809523809524</v>
           </cell>
           <cell r="G10">
-            <v>-2.2150094996833403E-2</v>
+            <v>-1.4249525015832765E-2</v>
           </cell>
           <cell r="H10" t="str">
             <v>BAJO</v>
@@ -490,10 +492,10 @@
         </row>
         <row r="11">
           <cell r="F11">
-            <v>314.2</v>
+            <v>321.28571428571428</v>
           </cell>
           <cell r="G11">
-            <v>-8.5488565488565427E-2</v>
+            <v>-6.4864864864864868E-2</v>
           </cell>
           <cell r="H11" t="str">
             <v>BAJO</v>
@@ -501,10 +503,10 @@
         </row>
         <row r="12">
           <cell r="F12">
-            <v>767.6</v>
+            <v>787.66666666666663</v>
           </cell>
           <cell r="G12">
-            <v>1.8396519577377202E-3</v>
+            <v>2.8029832193909199E-2</v>
           </cell>
           <cell r="H12" t="str">
             <v>SUBIÓ</v>
@@ -512,10 +514,10 @@
         </row>
         <row r="13">
           <cell r="F13">
-            <v>374.95</v>
+            <v>388.14285714285717</v>
           </cell>
           <cell r="G13">
-            <v>3.3462396639978964E-2</v>
+            <v>6.9825436408977648E-2</v>
           </cell>
           <cell r="H13" t="str">
             <v>SUBIÓ</v>
@@ -523,10 +525,10 @@
         </row>
         <row r="14">
           <cell r="F14">
-            <v>3347.35</v>
+            <v>3366.2857142857142</v>
           </cell>
           <cell r="G14">
-            <v>-4.9459784725227274E-2</v>
+            <v>-4.4082648204240682E-2</v>
           </cell>
           <cell r="H14" t="str">
             <v>BAJO</v>
@@ -534,10 +536,10 @@
         </row>
         <row r="15">
           <cell r="F15">
-            <v>2112.6</v>
+            <v>2119</v>
           </cell>
           <cell r="G15">
-            <v>-8.3470715835140985E-2</v>
+            <v>-8.0694143167028165E-2</v>
           </cell>
           <cell r="H15" t="str">
             <v>BAJO</v>
@@ -545,10 +547,10 @@
         </row>
         <row r="16">
           <cell r="F16">
-            <v>2121.65</v>
+            <v>2125.2380952380954</v>
           </cell>
           <cell r="G16">
-            <v>-6.3899277250188957E-2</v>
+            <v>-6.2316161021934491E-2</v>
           </cell>
           <cell r="H16" t="str">
             <v>BAJO</v>
@@ -556,10 +558,10 @@
         </row>
         <row r="17">
           <cell r="F17">
-            <v>2607.9499999999998</v>
+            <v>2625.0952380952381</v>
           </cell>
           <cell r="G17">
-            <v>-2.4700822737471984E-2</v>
+            <v>-1.8288990989065779E-2</v>
           </cell>
           <cell r="H17" t="str">
             <v>BAJO</v>
@@ -567,10 +569,10 @@
         </row>
         <row r="18">
           <cell r="F18">
-            <v>702.9</v>
+            <v>709.76190476190482</v>
           </cell>
           <cell r="G18">
-            <v>0.80605652759084778</v>
+            <v>0.82368775235531633</v>
           </cell>
           <cell r="H18" t="str">
             <v>SUBIÓ</v>
@@ -578,10 +580,10 @@
         </row>
         <row r="19">
           <cell r="F19">
-            <v>836.1</v>
+            <v>848.52380952380952</v>
           </cell>
           <cell r="G19">
-            <v>0.95176745220097825</v>
+            <v>0.98076923076923062</v>
           </cell>
           <cell r="H19" t="str">
             <v>SUBIÓ</v>
@@ -589,10 +591,10 @@
         </row>
         <row r="20">
           <cell r="F20">
-            <v>843.2</v>
+            <v>852.23809523809518</v>
           </cell>
           <cell r="G20">
-            <v>1.1578357299536925</v>
+            <v>1.1809651474530831</v>
           </cell>
           <cell r="H20" t="str">
             <v>SUBIÓ</v>
@@ -600,10 +602,10 @@
         </row>
         <row r="21">
           <cell r="F21">
-            <v>268.85000000000002</v>
+            <v>276.61904761904759</v>
           </cell>
           <cell r="G21">
-            <v>0.1109504132231407</v>
+            <v>0.14305391578118831</v>
           </cell>
           <cell r="H21" t="str">
             <v>SUBIÓ</v>
@@ -611,10 +613,10 @@
         </row>
         <row r="22">
           <cell r="F22">
-            <v>131.5</v>
+            <v>136.8095238095238</v>
           </cell>
           <cell r="G22">
-            <v>-7.5184192900201063E-2</v>
+            <v>-3.7843268586738255E-2</v>
           </cell>
           <cell r="H22" t="str">
             <v>BAJO</v>
@@ -622,21 +624,21 @@
         </row>
         <row r="23">
           <cell r="F23">
-            <v>503.6</v>
+            <v>515.71428571428567</v>
           </cell>
           <cell r="G23">
-            <v>-1.8505800464037048E-2</v>
+            <v>5.1044083526681217E-3</v>
           </cell>
           <cell r="H23" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="24">
           <cell r="F24">
-            <v>850.6</v>
+            <v>874.95238095238096</v>
           </cell>
           <cell r="G24">
-            <v>4.8336169963026032E-2</v>
+            <v>7.8349668407770467E-2</v>
           </cell>
           <cell r="H24" t="str">
             <v>SUBIÓ</v>
@@ -644,10 +646,10 @@
         </row>
         <row r="25">
           <cell r="F25">
-            <v>60</v>
+            <v>68.571428571428569</v>
           </cell>
           <cell r="G25">
-            <v>-0.19949174078780174</v>
+            <v>-8.5133418043202069E-2</v>
           </cell>
           <cell r="H25" t="str">
             <v>BAJO</v>
@@ -655,10 +657,10 @@
         </row>
         <row r="26">
           <cell r="F26">
-            <v>703.45</v>
+            <v>702.76190476190482</v>
           </cell>
           <cell r="G26">
-            <v>-0.10724300477427928</v>
+            <v>-0.10811627485344766</v>
           </cell>
           <cell r="H26" t="str">
             <v>BAJO</v>
@@ -666,10 +668,10 @@
         </row>
         <row r="27">
           <cell r="F27">
-            <v>1089.8499999999999</v>
+            <v>1085.4285714285713</v>
           </cell>
           <cell r="G27">
-            <v>-0.1443528488111262</v>
+            <v>-0.1478241363840288</v>
           </cell>
           <cell r="H27" t="str">
             <v>BAJO</v>
@@ -677,10 +679,10 @@
         </row>
         <row r="28">
           <cell r="F28">
-            <v>552.79999999999995</v>
+            <v>566.42857142857144</v>
           </cell>
           <cell r="G28">
-            <v>4.4614415549356634E-2</v>
+            <v>7.0368037433636399E-2</v>
           </cell>
           <cell r="H28" t="str">
             <v>SUBIÓ</v>
@@ -688,10 +690,10 @@
         </row>
         <row r="29">
           <cell r="F29">
-            <v>437.5</v>
+            <v>450.38095238095241</v>
           </cell>
           <cell r="G29">
-            <v>8.8695343050124498E-2</v>
+            <v>0.1207489038985663</v>
           </cell>
           <cell r="H29" t="str">
             <v>SUBIÓ</v>
@@ -699,10 +701,10 @@
         </row>
         <row r="30">
           <cell r="F30">
-            <v>254.2</v>
+            <v>249.9047619047619</v>
           </cell>
           <cell r="G30">
-            <v>2.3405506883604503</v>
+            <v>2.2841051314142673</v>
           </cell>
           <cell r="H30" t="str">
             <v>SUBIÓ</v>
@@ -710,10 +712,10 @@
         </row>
         <row r="31">
           <cell r="F31">
-            <v>312.8</v>
+            <v>305.52380952380952</v>
           </cell>
           <cell r="G31">
-            <v>3.3387054161162482</v>
+            <v>3.2377807133421399</v>
           </cell>
           <cell r="H31" t="str">
             <v>SUBIÓ</v>
@@ -721,10 +723,10 @@
         </row>
         <row r="32">
           <cell r="F32">
-            <v>127.95</v>
+            <v>132.85714285714286</v>
           </cell>
           <cell r="G32">
-            <v>7.2625698324024768E-4</v>
+            <v>3.9106145251396551E-2</v>
           </cell>
           <cell r="H32" t="str">
             <v>SUBIÓ</v>
@@ -732,10 +734,10 @@
         </row>
         <row r="33">
           <cell r="F33">
-            <v>144.69999999999999</v>
+            <v>147.57142857142858</v>
           </cell>
           <cell r="G33">
-            <v>9.5348837209301429E-3</v>
+            <v>2.9568106312292342E-2</v>
           </cell>
           <cell r="H33" t="str">
             <v>SUBIÓ</v>
@@ -743,10 +745,10 @@
         </row>
         <row r="34">
           <cell r="F34">
-            <v>784.35</v>
+            <v>795.57142857142856</v>
           </cell>
           <cell r="G34">
-            <v>0.20263945677570105</v>
+            <v>0.21984521028037385</v>
           </cell>
           <cell r="H34" t="str">
             <v>SUBIÓ</v>
@@ -754,10 +756,10 @@
         </row>
         <row r="35">
           <cell r="F35">
-            <v>600.54999999999995</v>
+            <v>611.23809523809518</v>
           </cell>
           <cell r="G35">
-            <v>-4.5302800908402774E-2</v>
+            <v>-2.8311884935654841E-2</v>
           </cell>
           <cell r="H35" t="str">
             <v>BAJO</v>
@@ -765,10 +767,10 @@
         </row>
         <row r="36">
           <cell r="F36">
-            <v>800.95</v>
+            <v>810.09523809523807</v>
           </cell>
           <cell r="G36">
-            <v>-6.0127961555654807E-2</v>
+            <v>-4.9396513187304425E-2</v>
           </cell>
           <cell r="H36" t="str">
             <v>BAJO</v>
@@ -776,10 +778,10 @@
         </row>
         <row r="37">
           <cell r="F37">
-            <v>526.45000000000005</v>
+            <v>539.23809523809518</v>
           </cell>
           <cell r="G37">
-            <v>-9.0759930915371267E-2</v>
+            <v>-6.8673410642322685E-2</v>
           </cell>
           <cell r="H37" t="str">
             <v>BAJO</v>
@@ -787,10 +789,10 @@
         </row>
         <row r="38">
           <cell r="F38">
-            <v>4</v>
+            <v>3.8095238095238093</v>
           </cell>
           <cell r="G38">
-            <v>0.61538461538461542</v>
+            <v>0.53846153846153832</v>
           </cell>
           <cell r="H38" t="str">
             <v>SUBIÓ</v>
@@ -798,10 +800,10 @@
         </row>
         <row r="39">
           <cell r="F39">
-            <v>0.55000000000000004</v>
+            <v>0.52380952380952384</v>
           </cell>
           <cell r="G39">
-            <v>0.28333333333333344</v>
+            <v>0.22222222222222232</v>
           </cell>
           <cell r="H39" t="str">
             <v>SUBIÓ</v>
@@ -809,10 +811,10 @@
         </row>
         <row r="40">
           <cell r="F40">
-            <v>134.19999999999999</v>
+            <v>128.8095238095238</v>
           </cell>
           <cell r="G40">
-            <v>-2.1458333333333357E-2</v>
+            <v>-6.0763888888888951E-2</v>
           </cell>
           <cell r="H40" t="str">
             <v>BAJO</v>
@@ -820,10 +822,10 @@
         </row>
         <row r="41">
           <cell r="F41">
-            <v>567.25</v>
+            <v>583.57142857142856</v>
           </cell>
           <cell r="G41">
-            <v>2.312548312290641E-2</v>
+            <v>5.2563772223653604E-2</v>
           </cell>
           <cell r="H41" t="str">
             <v>SUBIÓ</v>
@@ -831,10 +833,10 @@
         </row>
         <row r="42">
           <cell r="F42">
-            <v>405.25</v>
+            <v>416.09523809523807</v>
           </cell>
           <cell r="G42">
-            <v>2.0513624955181071</v>
+            <v>2.1330225887414844</v>
           </cell>
           <cell r="H42" t="str">
             <v>SUBIÓ</v>
@@ -842,10 +844,10 @@
         </row>
         <row r="43">
           <cell r="F43">
-            <v>246.65</v>
+            <v>253.57142857142858</v>
           </cell>
           <cell r="G43">
-            <v>-0.16712493970091657</v>
+            <v>-0.1437530149541727</v>
           </cell>
           <cell r="H43" t="str">
             <v>BAJO</v>
@@ -853,10 +855,10 @@
         </row>
         <row r="44">
           <cell r="F44">
-            <v>491.45</v>
+            <v>492.47619047619048</v>
           </cell>
           <cell r="G44">
-            <v>-7.0480951094298749E-2</v>
+            <v>-6.8540034224984114E-2</v>
           </cell>
           <cell r="H44" t="str">
             <v>BAJO</v>
@@ -864,10 +866,10 @@
         </row>
         <row r="45">
           <cell r="F45">
-            <v>298.55</v>
+            <v>292.76190476190476</v>
           </cell>
           <cell r="G45">
-            <v>-2.2978027115474475E-2</v>
+            <v>-4.1919900264921206E-2</v>
           </cell>
           <cell r="H45" t="str">
             <v>BAJO</v>
@@ -875,21 +877,21 @@
         </row>
         <row r="46">
           <cell r="F46">
-            <v>293.35000000000002</v>
+            <v>287.38095238095241</v>
           </cell>
           <cell r="G46">
-            <v>1.1884034165571711E-2</v>
+            <v>-8.7056504599211104E-3</v>
           </cell>
           <cell r="H46" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="47">
           <cell r="F47">
-            <v>53</v>
+            <v>53.523809523809526</v>
           </cell>
           <cell r="G47">
-            <v>-8.1683168316831645E-2</v>
+            <v>-7.2607260726072598E-2</v>
           </cell>
           <cell r="H47" t="str">
             <v>BAJO</v>
@@ -897,10 +899,10 @@
         </row>
         <row r="48">
           <cell r="F48">
-            <v>122.1</v>
+            <v>120.14285714285714</v>
           </cell>
           <cell r="G48">
-            <v>0.16603001364256476</v>
+            <v>0.14733969986357431</v>
           </cell>
           <cell r="H48" t="str">
             <v>SUBIÓ</v>
@@ -908,10 +910,10 @@
         </row>
         <row r="49">
           <cell r="F49">
-            <v>40.299999999999997</v>
+            <v>41.523809523809526</v>
           </cell>
           <cell r="G49">
-            <v>-0.18310810810810818</v>
+            <v>-0.15830115830115832</v>
           </cell>
           <cell r="H49" t="str">
             <v>BAJO</v>
@@ -919,10 +921,10 @@
         </row>
         <row r="50">
           <cell r="F50">
-            <v>51.3</v>
+            <v>50.761904761904759</v>
           </cell>
           <cell r="G50">
-            <v>-7.2891566265060326E-2</v>
+            <v>-8.2616179001721246E-2</v>
           </cell>
           <cell r="H50" t="str">
             <v>BAJO</v>
@@ -1185,11 +1187,11 @@
       </c>
       <c r="E2" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F4</f>
-        <v>1167.9000000000001</v>
+        <v>1180.3333333333333</v>
       </c>
       <c r="F2" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G4</f>
-        <v>-1.6997995991983927E-2</v>
+        <v>-6.5330661322645645E-3</v>
       </c>
       <c r="G2" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H4</f>
@@ -1214,11 +1216,11 @@
       </c>
       <c r="E3" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F5</f>
-        <v>46.45</v>
+        <v>44.61904761904762</v>
       </c>
       <c r="F3" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G5</f>
-        <v>-0.39186408977556109</v>
+        <v>-0.41583541147132164</v>
       </c>
       <c r="G3" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H5</f>
@@ -1243,11 +1245,11 @@
       </c>
       <c r="E4" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F6</f>
-        <v>491.05</v>
+        <v>489.42857142857144</v>
       </c>
       <c r="F4" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G6</f>
-        <v>-3.6166931488924137E-2</v>
+        <v>-3.9349471913262879E-2</v>
       </c>
       <c r="G4" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H6</f>
@@ -1272,11 +1274,11 @@
       </c>
       <c r="E5" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F7</f>
-        <v>104.45</v>
+        <v>107.47619047619048</v>
       </c>
       <c r="F5" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G7</f>
-        <v>6.5816326530612201E-2</v>
+        <v>9.6695821185617259E-2</v>
       </c>
       <c r="G5" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H7</f>
@@ -1301,11 +1303,11 @@
       </c>
       <c r="E6" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F8</f>
-        <v>14</v>
+        <v>14.571428571428571</v>
       </c>
       <c r="F6" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G8</f>
-        <v>0.17131474103585664</v>
+        <v>0.21912350597609564</v>
       </c>
       <c r="G6" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H8</f>
@@ -1330,11 +1332,11 @@
       </c>
       <c r="E7" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F9</f>
-        <v>1405.35</v>
+        <v>1391.7619047619048</v>
       </c>
       <c r="F7" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G9</f>
-        <v>-3.7651221182378514E-2</v>
+        <v>-4.6956011347702664E-2</v>
       </c>
       <c r="G7" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H9</f>
@@ -1359,11 +1361,11 @@
       </c>
       <c r="E8" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F10</f>
-        <v>147.05000000000001</v>
+        <v>148.23809523809524</v>
       </c>
       <c r="F8" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G10</f>
-        <v>-2.2150094996833403E-2</v>
+        <v>-1.4249525015832765E-2</v>
       </c>
       <c r="G8" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H10</f>
@@ -1388,11 +1390,11 @@
       </c>
       <c r="E9" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F11</f>
-        <v>314.2</v>
+        <v>321.28571428571428</v>
       </c>
       <c r="F9" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G11</f>
-        <v>-8.5488565488565427E-2</v>
+        <v>-6.4864864864864868E-2</v>
       </c>
       <c r="G9" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H11</f>
@@ -1417,11 +1419,11 @@
       </c>
       <c r="E10" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F12</f>
-        <v>767.6</v>
+        <v>787.66666666666663</v>
       </c>
       <c r="F10" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G12</f>
-        <v>1.8396519577377202E-3</v>
+        <v>2.8029832193909199E-2</v>
       </c>
       <c r="G10" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H12</f>
@@ -1446,11 +1448,11 @@
       </c>
       <c r="E11" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F13</f>
-        <v>374.95</v>
+        <v>388.14285714285717</v>
       </c>
       <c r="F11" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G13</f>
-        <v>3.3462396639978964E-2</v>
+        <v>6.9825436408977648E-2</v>
       </c>
       <c r="G11" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H13</f>
@@ -1475,11 +1477,11 @@
       </c>
       <c r="E12" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F14</f>
-        <v>3347.35</v>
+        <v>3366.2857142857142</v>
       </c>
       <c r="F12" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G14</f>
-        <v>-4.9459784725227274E-2</v>
+        <v>-4.4082648204240682E-2</v>
       </c>
       <c r="G12" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H14</f>
@@ -1504,11 +1506,11 @@
       </c>
       <c r="E13" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F15</f>
-        <v>2112.6</v>
+        <v>2119</v>
       </c>
       <c r="F13" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G15</f>
-        <v>-8.3470715835140985E-2</v>
+        <v>-8.0694143167028165E-2</v>
       </c>
       <c r="G13" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H15</f>
@@ -1533,11 +1535,11 @@
       </c>
       <c r="E14" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F16</f>
-        <v>2121.65</v>
+        <v>2125.2380952380954</v>
       </c>
       <c r="F14" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G16</f>
-        <v>-6.3899277250188957E-2</v>
+        <v>-6.2316161021934491E-2</v>
       </c>
       <c r="G14" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H16</f>
@@ -1562,11 +1564,11 @@
       </c>
       <c r="E15" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F17</f>
-        <v>2607.9499999999998</v>
+        <v>2625.0952380952381</v>
       </c>
       <c r="F15" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G17</f>
-        <v>-2.4700822737471984E-2</v>
+        <v>-1.8288990989065779E-2</v>
       </c>
       <c r="G15" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H17</f>
@@ -1591,11 +1593,11 @@
       </c>
       <c r="E16" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F18</f>
-        <v>702.9</v>
+        <v>709.76190476190482</v>
       </c>
       <c r="F16" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G18</f>
-        <v>0.80605652759084778</v>
+        <v>0.82368775235531633</v>
       </c>
       <c r="G16" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H18</f>
@@ -1620,11 +1622,11 @@
       </c>
       <c r="E17" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F19</f>
-        <v>836.1</v>
+        <v>848.52380952380952</v>
       </c>
       <c r="F17" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G19</f>
-        <v>0.95176745220097825</v>
+        <v>0.98076923076923062</v>
       </c>
       <c r="G17" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H19</f>
@@ -1649,11 +1651,11 @@
       </c>
       <c r="E18" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F20</f>
-        <v>843.2</v>
+        <v>852.23809523809518</v>
       </c>
       <c r="F18" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G20</f>
-        <v>1.1578357299536925</v>
+        <v>1.1809651474530831</v>
       </c>
       <c r="G18" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H20</f>
@@ -1678,11 +1680,11 @@
       </c>
       <c r="E19" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F21</f>
-        <v>268.85000000000002</v>
+        <v>276.61904761904759</v>
       </c>
       <c r="F19" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G21</f>
-        <v>0.1109504132231407</v>
+        <v>0.14305391578118831</v>
       </c>
       <c r="G19" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H21</f>
@@ -1707,11 +1709,11 @@
       </c>
       <c r="E20" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F22</f>
-        <v>131.5</v>
+        <v>136.8095238095238</v>
       </c>
       <c r="F20" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G22</f>
-        <v>-7.5184192900201063E-2</v>
+        <v>-3.7843268586738255E-2</v>
       </c>
       <c r="G20" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H22</f>
@@ -1736,15 +1738,15 @@
       </c>
       <c r="E21" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F23</f>
-        <v>503.6</v>
+        <v>515.71428571428567</v>
       </c>
       <c r="F21" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G23</f>
-        <v>-1.8505800464037048E-2</v>
+        <v>5.1044083526681217E-3</v>
       </c>
       <c r="G21" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H23</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H21">
         <v>4.1500000000000004</v>
@@ -1765,11 +1767,11 @@
       </c>
       <c r="E22" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F24</f>
-        <v>850.6</v>
+        <v>874.95238095238096</v>
       </c>
       <c r="F22" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G24</f>
-        <v>4.8336169963026032E-2</v>
+        <v>7.8349668407770467E-2</v>
       </c>
       <c r="G22" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H24</f>
@@ -1794,11 +1796,11 @@
       </c>
       <c r="E23" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F25</f>
-        <v>60</v>
+        <v>68.571428571428569</v>
       </c>
       <c r="F23" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G25</f>
-        <v>-0.19949174078780174</v>
+        <v>-8.5133418043202069E-2</v>
       </c>
       <c r="G23" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H25</f>
@@ -1823,11 +1825,11 @@
       </c>
       <c r="E24" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F26</f>
-        <v>703.45</v>
+        <v>702.76190476190482</v>
       </c>
       <c r="F24" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G26</f>
-        <v>-0.10724300477427928</v>
+        <v>-0.10811627485344766</v>
       </c>
       <c r="G24" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H26</f>
@@ -1852,11 +1854,11 @@
       </c>
       <c r="E25" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F27</f>
-        <v>1089.8499999999999</v>
+        <v>1085.4285714285713</v>
       </c>
       <c r="F25" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G27</f>
-        <v>-0.1443528488111262</v>
+        <v>-0.1478241363840288</v>
       </c>
       <c r="G25" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H27</f>
@@ -1881,11 +1883,11 @@
       </c>
       <c r="E26" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F28</f>
-        <v>552.79999999999995</v>
+        <v>566.42857142857144</v>
       </c>
       <c r="F26" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G28</f>
-        <v>4.4614415549356634E-2</v>
+        <v>7.0368037433636399E-2</v>
       </c>
       <c r="G26" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H28</f>
@@ -1910,11 +1912,11 @@
       </c>
       <c r="E27" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F29</f>
-        <v>437.5</v>
+        <v>450.38095238095241</v>
       </c>
       <c r="F27" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G29</f>
-        <v>8.8695343050124498E-2</v>
+        <v>0.1207489038985663</v>
       </c>
       <c r="G27" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H29</f>
@@ -1939,11 +1941,11 @@
       </c>
       <c r="E28" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F30</f>
-        <v>254.2</v>
+        <v>249.9047619047619</v>
       </c>
       <c r="F28" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G30</f>
-        <v>2.3405506883604503</v>
+        <v>2.2841051314142673</v>
       </c>
       <c r="G28" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H30</f>
@@ -1968,11 +1970,11 @@
       </c>
       <c r="E29" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F31</f>
-        <v>312.8</v>
+        <v>305.52380952380952</v>
       </c>
       <c r="F29" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G31</f>
-        <v>3.3387054161162482</v>
+        <v>3.2377807133421399</v>
       </c>
       <c r="G29" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H31</f>
@@ -1997,11 +1999,11 @@
       </c>
       <c r="E30" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F32</f>
-        <v>127.95</v>
+        <v>132.85714285714286</v>
       </c>
       <c r="F30" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G32</f>
-        <v>7.2625698324024768E-4</v>
+        <v>3.9106145251396551E-2</v>
       </c>
       <c r="G30" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H32</f>
@@ -2026,11 +2028,11 @@
       </c>
       <c r="E31" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F33</f>
-        <v>144.69999999999999</v>
+        <v>147.57142857142858</v>
       </c>
       <c r="F31" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G33</f>
-        <v>9.5348837209301429E-3</v>
+        <v>2.9568106312292342E-2</v>
       </c>
       <c r="G31" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H33</f>
@@ -2055,11 +2057,11 @@
       </c>
       <c r="E32" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F34</f>
-        <v>784.35</v>
+        <v>795.57142857142856</v>
       </c>
       <c r="F32" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G34</f>
-        <v>0.20263945677570105</v>
+        <v>0.21984521028037385</v>
       </c>
       <c r="G32" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H34</f>
@@ -2084,11 +2086,11 @@
       </c>
       <c r="E33" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F35</f>
-        <v>600.54999999999995</v>
+        <v>611.23809523809518</v>
       </c>
       <c r="F33" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G35</f>
-        <v>-4.5302800908402774E-2</v>
+        <v>-2.8311884935654841E-2</v>
       </c>
       <c r="G33" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H35</f>
@@ -2113,11 +2115,11 @@
       </c>
       <c r="E34" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F36</f>
-        <v>800.95</v>
+        <v>810.09523809523807</v>
       </c>
       <c r="F34" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G36</f>
-        <v>-6.0127961555654807E-2</v>
+        <v>-4.9396513187304425E-2</v>
       </c>
       <c r="G34" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H36</f>
@@ -2142,11 +2144,11 @@
       </c>
       <c r="E35" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F37</f>
-        <v>526.45000000000005</v>
+        <v>539.23809523809518</v>
       </c>
       <c r="F35" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G37</f>
-        <v>-9.0759930915371267E-2</v>
+        <v>-6.8673410642322685E-2</v>
       </c>
       <c r="G35" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H37</f>
@@ -2171,11 +2173,11 @@
       </c>
       <c r="E36" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F38</f>
-        <v>4</v>
+        <v>3.8095238095238093</v>
       </c>
       <c r="F36" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G38</f>
-        <v>0.61538461538461542</v>
+        <v>0.53846153846153832</v>
       </c>
       <c r="G36" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H38</f>
@@ -2200,11 +2202,11 @@
       </c>
       <c r="E37" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F39</f>
-        <v>0.55000000000000004</v>
+        <v>0.52380952380952384</v>
       </c>
       <c r="F37" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G39</f>
-        <v>0.28333333333333344</v>
+        <v>0.22222222222222232</v>
       </c>
       <c r="G37" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H39</f>
@@ -2229,11 +2231,11 @@
       </c>
       <c r="E38" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F40</f>
-        <v>134.19999999999999</v>
+        <v>128.8095238095238</v>
       </c>
       <c r="F38" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G40</f>
-        <v>-2.1458333333333357E-2</v>
+        <v>-6.0763888888888951E-2</v>
       </c>
       <c r="G38" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H40</f>
@@ -2258,11 +2260,11 @@
       </c>
       <c r="E39" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F41</f>
-        <v>567.25</v>
+        <v>583.57142857142856</v>
       </c>
       <c r="F39" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G41</f>
-        <v>2.312548312290641E-2</v>
+        <v>5.2563772223653604E-2</v>
       </c>
       <c r="G39" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H41</f>
@@ -2287,11 +2289,11 @@
       </c>
       <c r="E40" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F42</f>
-        <v>405.25</v>
+        <v>416.09523809523807</v>
       </c>
       <c r="F40" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G42</f>
-        <v>2.0513624955181071</v>
+        <v>2.1330225887414844</v>
       </c>
       <c r="G40" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H42</f>
@@ -2316,11 +2318,11 @@
       </c>
       <c r="E41" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F43</f>
-        <v>246.65</v>
+        <v>253.57142857142858</v>
       </c>
       <c r="F41" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G43</f>
-        <v>-0.16712493970091657</v>
+        <v>-0.1437530149541727</v>
       </c>
       <c r="G41" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H43</f>
@@ -2345,11 +2347,11 @@
       </c>
       <c r="E42" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F44</f>
-        <v>491.45</v>
+        <v>492.47619047619048</v>
       </c>
       <c r="F42" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G44</f>
-        <v>-7.0480951094298749E-2</v>
+        <v>-6.8540034224984114E-2</v>
       </c>
       <c r="G42" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H44</f>
@@ -2374,11 +2376,11 @@
       </c>
       <c r="E43" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F45</f>
-        <v>298.55</v>
+        <v>292.76190476190476</v>
       </c>
       <c r="F43" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G45</f>
-        <v>-2.2978027115474475E-2</v>
+        <v>-4.1919900264921206E-2</v>
       </c>
       <c r="G43" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H45</f>
@@ -2403,15 +2405,15 @@
       </c>
       <c r="E44" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F46</f>
-        <v>293.35000000000002</v>
+        <v>287.38095238095241</v>
       </c>
       <c r="F44" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G46</f>
-        <v>1.1884034165571711E-2</v>
+        <v>-8.7056504599211104E-3</v>
       </c>
       <c r="G44" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H46</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H44">
         <v>0.81</v>
@@ -2432,11 +2434,11 @@
       </c>
       <c r="E45" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F47</f>
-        <v>53</v>
+        <v>53.523809523809526</v>
       </c>
       <c r="F45" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G47</f>
-        <v>-8.1683168316831645E-2</v>
+        <v>-7.2607260726072598E-2</v>
       </c>
       <c r="G45" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H47</f>
@@ -2461,11 +2463,11 @@
       </c>
       <c r="E46" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F48</f>
-        <v>122.1</v>
+        <v>120.14285714285714</v>
       </c>
       <c r="F46" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G48</f>
-        <v>0.16603001364256476</v>
+        <v>0.14733969986357431</v>
       </c>
       <c r="G46" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H48</f>
@@ -2490,11 +2492,11 @@
       </c>
       <c r="E47" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F49</f>
-        <v>40.299999999999997</v>
+        <v>41.523809523809526</v>
       </c>
       <c r="F47" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G49</f>
-        <v>-0.18310810810810818</v>
+        <v>-0.15830115830115832</v>
       </c>
       <c r="G47" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H49</f>
@@ -2519,11 +2521,11 @@
       </c>
       <c r="E48" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F50</f>
-        <v>51.3</v>
+        <v>50.761904761904759</v>
       </c>
       <c r="F48" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G50</f>
-        <v>-7.2891566265060326E-2</v>
+        <v>-8.2616179001721246E-2</v>
       </c>
       <c r="G48" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H50</f>
